--- a/data/raw/USGS.xlsx
+++ b/data/raw/USGS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,29 +487,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nc75327512</t>
+          <t>nc75327567</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-122.738670349121</v>
+        <v>-120.093002319336</v>
       </c>
       <c r="C2" t="n">
-        <v>38.7863349914551</v>
+        <v>36.1063346862793</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00999999977648258</v>
+        <v>8.239999771118161</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2.08</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km ENE of The Geysers, CA</t>
+          <t>M 2.1 - 11 km S of Huron, CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2 km ENE of The Geysers, CA</t>
+          <t>11 km S of Huron, CA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,38 +518,38 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46095.98437893519</v>
+        <v>46096.16129594907</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46095.9855096875</v>
+        <v>46096.16244400463</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nc75327502</t>
+          <t>aka2026fehrkj</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-122.85383605957</v>
+        <v>-149.708</v>
       </c>
       <c r="C3" t="n">
-        <v>38.8251647949219</v>
+        <v>62.155</v>
       </c>
       <c r="D3" t="n">
-        <v>2.40000009536743</v>
+        <v>31.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M 1.4 - 10 km WNW of The Geysers, CA</t>
+          <t>M 1.5 - 7 km E of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10 km WNW of The Geysers, CA</t>
+          <t>7 km E of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,38 +558,38 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46095.97872789352</v>
+        <v>46096.16061565972</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46096.00512835648</v>
+        <v>46096.16211004629</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nc75327497</t>
+          <t>nn00912678</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-122.783668518066</v>
+        <v>-117.1285</v>
       </c>
       <c r="C4" t="n">
-        <v>38.8083343505859</v>
+        <v>37.2457</v>
       </c>
       <c r="D4" t="n">
-        <v>0.129999995231628</v>
+        <v>13.004</v>
       </c>
       <c r="E4" t="n">
-        <v>1.08</v>
+        <v>1.59</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M 1.1 - 4 km NW of The Geysers, CA</t>
+          <t>M 1.6 - 49 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4 km NW of The Geysers, CA</t>
+          <t>49 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -598,38 +598,38 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46095.97843564815</v>
+        <v>46096.16059528935</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46095.99816079861</v>
+        <v>46096.16208465278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nn00912667</t>
+          <t>ok2026fdrh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-117.1013</v>
+        <v>-98.18229675000001</v>
       </c>
       <c r="C5" t="n">
-        <v>37.1878</v>
+        <v>35.44195557</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4482</v>
+        <v>0.324695766</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>2.56</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M 1.6 - 43 km NW of Beatty, Nevada</t>
+          <t>M 2.6 - 16 km ESE of Hinton, Oklahoma</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>43 km NW of Beatty, Nevada</t>
+          <t>16 km ESE of Hinton, Oklahoma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,38 +638,38 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46095.97793467592</v>
+        <v>46096.15941979166</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46095.97987364583</v>
+        <v>46096.16168333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hv74917452</t>
+          <t>aka2026fegqal</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-155.482498168945</v>
+        <v>-152.568</v>
       </c>
       <c r="C6" t="n">
-        <v>19.3939990997314</v>
+        <v>60.006</v>
       </c>
       <c r="D6" t="n">
-        <v>6.3899998664856</v>
+        <v>104.2</v>
       </c>
       <c r="E6" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M 1.7 - 21 km N of Pāhala, Hawaii</t>
+          <t>M 1.3 - 47 km W of Happy Valley, Alaska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21 km N of Pāhala, Hawaii</t>
+          <t>47 km W of Happy Valley, Alaska</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -678,38 +678,38 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46095.97703333334</v>
+        <v>46096.13842898148</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46095.97968425926</v>
+        <v>46096.139836875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aka2026fdyhrh</t>
+          <t>tx2026fegnxw</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-147.392</v>
+        <v>-104.455</v>
       </c>
       <c r="C7" t="n">
-        <v>64.99299999999999</v>
+        <v>31.63</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>2.4207</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M 1.0 - 11 km ENE of Fox, Alaska</t>
+          <t>M 1.7 - 60 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11 km ENE of Fox, Alaska</t>
+          <t>60 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -718,38 +718,38 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46095.96407459491</v>
+        <v>46096.13677427083</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46095.96494929398</v>
+        <v>46096.13850288194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hv74917442</t>
+          <t>tx2026fegkvq</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-155.372329711914</v>
+        <v>-104.448</v>
       </c>
       <c r="C8" t="n">
-        <v>19.2784996032715</v>
+        <v>31.631</v>
       </c>
       <c r="D8" t="n">
-        <v>30.7099990844727</v>
+        <v>3.4418</v>
       </c>
       <c r="E8" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M 2.1 - 13 km NE of Pāhala, Hawaii</t>
+          <t>M 2.4 - 60 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13 km NE of Pāhala, Hawaii</t>
+          <t>60 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -758,38 +758,38 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46095.95855648148</v>
+        <v>46096.13426179398</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46095.96108136574</v>
+        <v>46096.16708719907</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>aka2026fdxbnk</t>
+          <t>nn00912675</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-144.31</v>
+        <v>-116.8506</v>
       </c>
       <c r="C9" t="n">
-        <v>69.447</v>
+        <v>37.1599</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>6.4687</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4</v>
+        <v>1.06</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M 3.4 - 80 km SSW of Kaktovik, Alaska</t>
+          <t>M 1.1 - 29 km NNW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>80 km SSW of Kaktovik, Alaska</t>
+          <t>29 km NNW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -798,38 +798,38 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46095.93817033565</v>
+        <v>46096.13401565972</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46095.97282453704</v>
+        <v>46096.13532696759</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nc75327467</t>
+          <t>aka2026feghag</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-122.796333312988</v>
+        <v>-152.61</v>
       </c>
       <c r="C10" t="n">
-        <v>38.8341674804688</v>
+        <v>60.069</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km WNW of Cobb, CA</t>
+          <t>M 2.3 - 50 km WNW of Happy Valley, Alaska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6 km WNW of Cobb, CA</t>
+          <t>50 km WNW of Happy Valley, Alaska</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -838,38 +838,38 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46095.91037789352</v>
+        <v>46096.13122143519</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46095.93216912037</v>
+        <v>46096.13240575232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aka2026fdvlcf</t>
+          <t>nc75327557</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-151.258</v>
+        <v>-122.757667541504</v>
       </c>
       <c r="C11" t="n">
-        <v>63.207</v>
+        <v>38.7836685180664</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7</v>
+        <v>2.04999995231628</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M 1.7 - 43 km SSE of Denali National Park, Alaska</t>
+          <t>M 1.2 - 1 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>43 km SSE of Denali National Park, Alaska</t>
+          <t>1 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -878,38 +878,38 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46095.90397135416</v>
+        <v>46096.12735844908</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46095.90514605324</v>
+        <v>46096.14749365741</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ci41204303</t>
+          <t>nc75327552</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-116.167833333333</v>
+        <v>-120.159332275391</v>
       </c>
       <c r="C12" t="n">
-        <v>33.8496666666667</v>
+        <v>36.105167388916</v>
       </c>
       <c r="D12" t="n">
-        <v>3.25</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="E12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M 1.3 - 15 km NNE of Indio, CA</t>
+          <t>M 1.4 - 12 km NNW of Avenal, CA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>15 km NNE of Indio, CA</t>
+          <t>12 km NNW of Avenal, CA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -918,38 +918,38 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46095.89176631944</v>
+        <v>46096.12601481481</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46095.89934652777</v>
+        <v>46096.15440421296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nn00912666</t>
+          <t>hv74917472</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-116.4902</v>
+        <v>-155.253005981445</v>
       </c>
       <c r="C13" t="n">
-        <v>38.4843</v>
+        <v>19.2596664428711</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2159</v>
+        <v>24.2299995422363</v>
       </c>
       <c r="E13" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M 2.1 - 79 km NE of Tonopah, Nevada</t>
+          <t>M 2.4 - 20 km S of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>79 km NE of Tonopah, Nevada</t>
+          <t>20 km S of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -958,38 +958,38 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46095.88495538195</v>
+        <v>46096.11974375</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46095.88782293982</v>
+        <v>46096.1222449074</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tx2026fdulai</t>
+          <t>hv74917477</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-104.423</v>
+        <v>-155.235000610352</v>
       </c>
       <c r="C14" t="n">
-        <v>31.637</v>
+        <v>19.2304992675781</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1495</v>
+        <v>27.8999996185303</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M 2.5 - 59 km S of Whites City, New Mexico</t>
+          <t>M 2.6 - 23 km S of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>59 km S of Whites City, New Mexico</t>
+          <t>23 km S of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -998,38 +998,38 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46095.88303170139</v>
+        <v>46096.11969131944</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46095.96269722222</v>
+        <v>46096.12205555556</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ci41204295</t>
+          <t>us6000sgdx</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-116.754669189453</v>
+        <v>152.8602</v>
       </c>
       <c r="C15" t="n">
-        <v>33.6506652832031</v>
+        <v>47.1076</v>
       </c>
       <c r="D15" t="n">
-        <v>13.289999961853</v>
+        <v>85.952</v>
       </c>
       <c r="E15" t="n">
-        <v>0.952443359159076</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M 1.0 - 10 km SSW of Idyllwild, CA</t>
+          <t>M 4.3 - Kuril Islands</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10 km SSW of Idyllwild, CA</t>
+          <t>Kuril Islands</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1038,38 +1038,38 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46095.87724398148</v>
+        <v>46096.11952268519</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46095.87864965278</v>
+        <v>46096.14409768519</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aka2026fdudwi</t>
+          <t>nc75327547</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-157.149</v>
+        <v>-122.466499328613</v>
       </c>
       <c r="C16" t="n">
-        <v>66.373</v>
+        <v>37.5961685180664</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>9.72999954223633</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M 3.0 - 57 km S of Shungnak, Alaska</t>
+          <t>M 1.5 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>57 km S of Shungnak, Alaska</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1078,38 +1078,38 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46095.87685564814</v>
+        <v>46096.10495636574</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46095.94651666666</v>
+        <v>46096.13706527778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nn00912662</t>
+          <t>nn00912672</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-116.526</v>
+        <v>-116.7812</v>
       </c>
       <c r="C17" t="n">
-        <v>38.4379</v>
+        <v>38.3201</v>
       </c>
       <c r="D17" t="n">
-        <v>12.8814</v>
+        <v>3.2364</v>
       </c>
       <c r="E17" t="n">
-        <v>3.37</v>
+        <v>1.94</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M 3.4 - 74 km ENE of Tonopah, Nevada</t>
+          <t>M 1.9 - 48 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>74 km ENE of Tonopah, Nevada</t>
+          <t>48 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1118,38 +1118,38 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46095.87443729167</v>
+        <v>46096.09975644676</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46095.94132894676</v>
+        <v>46096.1015644213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nn00912660</t>
+          <t>us6000sgdm</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-116.6966</v>
+        <v>-111.8909</v>
       </c>
       <c r="C18" t="n">
-        <v>38.3742</v>
+        <v>32.5527</v>
       </c>
       <c r="D18" t="n">
-        <v>4.278</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>M 2.1 - 57 km NE of Tonopah, Nevada</t>
+          <t>M 2.5 - 5 km S of Tat Momoli, Arizona</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>57 km NE of Tonopah, Nevada</t>
+          <t>5 km S of Tat Momoli, Arizona</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1158,38 +1158,38 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46095.86389622685</v>
+        <v>46096.09697278935</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46095.86570340278</v>
+        <v>46096.11536375</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>aka2026fdtdkp</t>
+          <t>ci41204383</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-150.918</v>
+        <v>-117.512</v>
       </c>
       <c r="C19" t="n">
-        <v>64.81</v>
+        <v>35.7071666666667</v>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>6.97</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>M 1.3 - 25 km SSW of Manley Hot Springs, Alaska</t>
+          <t>M 1.1 - 12 km SW of Searles Valley, CA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25 km SSW of Manley Hot Springs, Alaska</t>
+          <t>12 km SW of Searles Valley, CA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1198,38 +1198,38 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46095.85587677083</v>
+        <v>46096.09368009259</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46095.85710167824</v>
+        <v>46096.09604913194</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nn00912655</t>
+          <t>nc75327527</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-116.532</v>
+        <v>-122.815002441406</v>
       </c>
       <c r="C20" t="n">
-        <v>38.4506</v>
+        <v>38.8293342590332</v>
       </c>
       <c r="D20" t="n">
-        <v>6.2192</v>
+        <v>1.63999998569489</v>
       </c>
       <c r="E20" t="n">
-        <v>3.17</v>
+        <v>1.23</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>M 3.2 - 74 km NE of Tonopah, Nevada</t>
+          <t>M 1.2 - 8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>74 km NE of Tonopah, Nevada</t>
+          <t>8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,38 +1238,38 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46095.85289917824</v>
+        <v>46096.07455567129</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46096.00872172454</v>
+        <v>46096.09885387732</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hv74917417</t>
+          <t>aka2026fedenj</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-155.371002197266</v>
+        <v>-151.271</v>
       </c>
       <c r="C21" t="n">
-        <v>19.2818336486816</v>
+        <v>63.271</v>
       </c>
       <c r="D21" t="n">
-        <v>30.0100002288818</v>
+        <v>1.3</v>
       </c>
       <c r="E21" t="n">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M 2.0 - 14 km NE of Pāhala, Hawaii</t>
+          <t>M 1.3 - 37 km SE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14 km NE of Pāhala, Hawaii</t>
+          <t>37 km SE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46095.84536168981</v>
+        <v>46096.06629653935</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46095.84858645833</v>
+        <v>46096.06743400463</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nc75327447</t>
+          <t>ci41204359</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-122.818496704102</v>
+        <v>-118.145668029785</v>
       </c>
       <c r="C22" t="n">
-        <v>38.8343315124512</v>
+        <v>33.7991676330566</v>
       </c>
       <c r="D22" t="n">
-        <v>1.87999999523163</v>
+        <v>18.5900001525879</v>
       </c>
       <c r="E22" t="n">
-        <v>1.16</v>
+        <v>1.19227960814025</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M 1.2 - 8 km NW of The Geysers, CA</t>
+          <t>M 1.2 - 1 km ESE of Long Beach, CA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8 km NW of The Geysers, CA</t>
+          <t>1 km ESE of Long Beach, CA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1318,38 +1318,38 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46095.81590775463</v>
+        <v>46096.06262638889</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46095.85925590277</v>
+        <v>46096.06503234954</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>us6000sgc5</t>
+          <t>ci41204343</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-116.4136</v>
+        <v>-116.714833333333</v>
       </c>
       <c r="C23" t="n">
-        <v>38.5775</v>
+        <v>34.0266666666667</v>
       </c>
       <c r="D23" t="n">
-        <v>12.516</v>
+        <v>14.15</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M 2.5 - 90 km SE of Kingston, Nevada</t>
+          <t>M 1.0 - 13 km W of Morongo Valley, CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>90 km SE of Kingston, Nevada</t>
+          <t>13 km W of Morongo Valley, CA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1358,38 +1358,38 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46095.77945232639</v>
+        <v>46096.05851504629</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46095.92890092592</v>
+        <v>46096.0609565625</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>us6000sgc2</t>
+          <t>us6000sgdf</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>153.3556</v>
+        <v>-91.7302</v>
       </c>
       <c r="C24" t="n">
-        <v>46.5573</v>
+        <v>15.4081</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>184.119</v>
       </c>
       <c r="E24" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M 5.1 - Kuril Islands</t>
+          <t>M 4.8 - 1 km W of Colotenango, Guatemala</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kuril Islands</t>
+          <t>1 km W of Colotenango, Guatemala</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1398,38 +1398,38 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46095.77235402778</v>
+        <v>46096.01585359954</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46095.78642407407</v>
+        <v>46096.03232685186</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>us6000sgc4</t>
+          <t>nn00912669</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>176.5308</v>
+        <v>-117.7692</v>
       </c>
       <c r="C25" t="n">
-        <v>52.2911</v>
+        <v>37.2938</v>
       </c>
       <c r="D25" t="n">
-        <v>8.986000000000001</v>
+        <v>6.5097</v>
       </c>
       <c r="E25" t="n">
-        <v>4.2</v>
+        <v>1.61</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M 4.2 - 235 km ESE of Attu Station, Alaska</t>
+          <t>M 1.6 - 48 km ENE of Big Pine, California</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>235 km ESE of Attu Station, Alaska</t>
+          <t>48 km ENE of Big Pine, California</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1438,38 +1438,38 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46095.76988208333</v>
+        <v>46096.01070017361</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46095.90945648148</v>
+        <v>46096.01346155092</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>aka2026fdoonh</t>
+          <t>aka2026feamjb</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-152.919</v>
+        <v>-151.579</v>
       </c>
       <c r="C26" t="n">
-        <v>59.948</v>
+        <v>61.273</v>
       </c>
       <c r="D26" t="n">
-        <v>110.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M 2.9 - 63 km WNW of Anchor Point, Alaska</t>
+          <t>M 1.7 - 30 km WNW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>63 km WNW of Anchor Point, Alaska</t>
+          <t>30 km WNW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1478,38 +1478,38 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46095.76006307871</v>
+        <v>46096.00978141204</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46095.89397037037</v>
+        <v>46096.0110008912</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nc75327417</t>
+          <t>nc75327512</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-121.6181640625</v>
+        <v>-122.738670349121</v>
       </c>
       <c r="C27" t="n">
-        <v>36.0970001220703</v>
+        <v>38.7863349914551</v>
       </c>
       <c r="D27" t="n">
-        <v>13.6000003814697</v>
+        <v>-0.00999999977648258</v>
       </c>
       <c r="E27" t="n">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M 1.3 - 10 km NNW of Lopez Point, CA</t>
+          <t>M 1.0 - 2 km ENE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10 km NNW of Lopez Point, CA</t>
+          <t>2 km ENE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1518,38 +1518,38 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46095.75923622686</v>
+        <v>46095.98437893519</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46095.82109177083</v>
+        <v>46095.9855096875</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>aka2026fdoioz</t>
+          <t>nc75327502</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-150.653</v>
+        <v>-122.85383605957</v>
       </c>
       <c r="C28" t="n">
-        <v>62.91</v>
+        <v>38.8251647949219</v>
       </c>
       <c r="D28" t="n">
-        <v>95.90000000000001</v>
+        <v>2.40000009536743</v>
       </c>
       <c r="E28" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M 2.4 - 46 km N of Petersville, Alaska</t>
+          <t>M 1.4 - 10 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>46 km N of Petersville, Alaska</t>
+          <t>10 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1558,38 +1558,38 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46095.7552774537</v>
+        <v>46095.97872789352</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46095.75831664352</v>
+        <v>46096.03290916666</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nc75327407</t>
+          <t>nc75327497</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-122.807830810547</v>
+        <v>-122.783668518066</v>
       </c>
       <c r="C29" t="n">
-        <v>38.8185005187988</v>
+        <v>38.8083343505859</v>
       </c>
       <c r="D29" t="n">
-        <v>3.05999994277954</v>
+        <v>0.129999995231628</v>
       </c>
       <c r="E29" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M 1.3 - 6 km NW of The Geysers, CA</t>
+          <t>M 1.1 - 4 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>4 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1598,38 +1598,38 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46095.74812962963</v>
+        <v>46095.97843564815</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46095.80374011574</v>
+        <v>46096.01551138889</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>aka2026fdnzor</t>
+          <t>nn00912667</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-157.911</v>
+        <v>-117.1013</v>
       </c>
       <c r="C30" t="n">
-        <v>56.193</v>
+        <v>37.1878</v>
       </c>
       <c r="D30" t="n">
-        <v>63.7</v>
+        <v>2.4482</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M 1.7 - 32 km ESE of Chignik, Alaska</t>
+          <t>M 1.6 - 43 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>32 km ESE of Chignik, Alaska</t>
+          <t>43 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46095.74800765047</v>
+        <v>46095.97793467592</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46095.7494846875</v>
+        <v>46095.97987364583</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>us6000sgbx</t>
+          <t>hv74917452</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-46.6402</v>
+        <v>-155.482498168945</v>
       </c>
       <c r="C31" t="n">
-        <v>16.556</v>
+        <v>19.3939990997314</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>6.3899998664856</v>
       </c>
       <c r="E31" t="n">
-        <v>5.1</v>
+        <v>1.73</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M 5.1 - northern Mid-Atlantic Ridge</t>
+          <t>M 1.7 - 21 km N of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>northern Mid-Atlantic Ridge</t>
+          <t>21 km N of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1678,38 +1678,38 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46095.73839887731</v>
+        <v>46095.97703333334</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46095.75246574074</v>
+        <v>46095.97968425926</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nc75327402</t>
+          <t>aka2026fdyhrh</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-122.281829833984</v>
+        <v>-147.392</v>
       </c>
       <c r="C32" t="n">
-        <v>37.3633346557617</v>
+        <v>64.99299999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>3.32999992370605</v>
+        <v>1.2</v>
       </c>
       <c r="E32" t="n">
-        <v>2.56</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M 2.6 - 5 km WSW of Portola Valley, CA</t>
+          <t>M 1.0 - 11 km ENE of Fox, Alaska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5 km WSW of Portola Valley, CA</t>
+          <t>11 km ENE of Fox, Alaska</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1718,38 +1718,38 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46095.73607071759</v>
+        <v>46095.96407459491</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46095.91402037037</v>
+        <v>46095.96494929398</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>aka2026fdnjta</t>
+          <t>hv74917442</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-148.1</v>
+        <v>-155.372329711914</v>
       </c>
       <c r="C33" t="n">
-        <v>62.28</v>
+        <v>19.2784996032715</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1</v>
+        <v>30.7099990844727</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M 1.7 - 57 km NNE of Chickaloon, Alaska</t>
+          <t>M 2.1 - 13 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>57 km NNE of Chickaloon, Alaska</t>
+          <t>13 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1758,38 +1758,38 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46095.73525334491</v>
+        <v>46095.95855648148</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46095.73619780093</v>
+        <v>46095.96108136574</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>us6000sgbr</t>
+          <t>aka2026fdxbnk</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-72.0967</v>
+        <v>-144.31</v>
       </c>
       <c r="C34" t="n">
-        <v>-42.429</v>
+        <v>69.447</v>
       </c>
       <c r="D34" t="n">
-        <v>5.985</v>
+        <v>1.2</v>
       </c>
       <c r="E34" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>M 4.7 - 57 km SW of Lago Puelo, Argentina</t>
+          <t>M 3.4 - 80 km SSW of Kaktovik, Alaska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>57 km SW of Lago Puelo, Argentina</t>
+          <t>80 km SSW of Kaktovik, Alaska</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1798,38 +1798,38 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46095.73344064815</v>
+        <v>46095.93817033565</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46095.8081949074</v>
+        <v>46095.97282453704</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nc75327397</t>
+          <t>nc75327467</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-122.782165527344</v>
+        <v>-122.796333312988</v>
       </c>
       <c r="C35" t="n">
-        <v>38.8131675720215</v>
+        <v>38.8341674804688</v>
       </c>
       <c r="D35" t="n">
-        <v>0.280000001192093</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>1.08</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
+          <t>M 1.1 - 6 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>6 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1838,38 +1838,38 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46095.73288171296</v>
+        <v>46095.91037789352</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46095.74467230324</v>
+        <v>46095.93216912037</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>us6000sgbq</t>
+          <t>aka2026fdvlcf</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-177.6605</v>
+        <v>-151.258</v>
       </c>
       <c r="C36" t="n">
-        <v>-20.6389</v>
+        <v>63.207</v>
       </c>
       <c r="D36" t="n">
-        <v>519.203</v>
+        <v>0.7</v>
       </c>
       <c r="E36" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M 4.4 - 252 km WNW of Houma, Tonga</t>
+          <t>M 1.7 - 43 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>252 km WNW of Houma, Tonga</t>
+          <t>43 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1878,38 +1878,38 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46095.72445238426</v>
+        <v>46095.90397135416</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46095.7970375</v>
+        <v>46095.90514605324</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ci41204215</t>
+          <t>ci41204303</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-116.8055</v>
+        <v>-116.167833333333</v>
       </c>
       <c r="C37" t="n">
-        <v>33.2446666666667</v>
+        <v>33.8496666666667</v>
       </c>
       <c r="D37" t="n">
-        <v>10.12</v>
+        <v>3.25</v>
       </c>
       <c r="E37" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M 1.5 - 4 km W of Lake Henshaw, CA</t>
+          <t>M 1.3 - 15 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4 km W of Lake Henshaw, CA</t>
+          <t>15 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1918,38 +1918,38 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46095.71835150463</v>
+        <v>46095.89176631944</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46095.72597673611</v>
+        <v>46095.89934652777</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nc75327377</t>
+          <t>nn00912666</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-120.121002197266</v>
+        <v>-116.4902</v>
       </c>
       <c r="C38" t="n">
-        <v>36.1983337402344</v>
+        <v>38.4843</v>
       </c>
       <c r="D38" t="n">
-        <v>10.8299999237061</v>
+        <v>1.2159</v>
       </c>
       <c r="E38" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M 1.6 - 2 km WSW of Huron, CA</t>
+          <t>M 2.1 - 79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2 km WSW of Huron, CA</t>
+          <t>79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1958,38 +1958,38 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46095.71190879629</v>
+        <v>46095.88495538195</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46095.76552966435</v>
+        <v>46095.88782293982</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tx2026fdmbdg</t>
+          <t>tx2026fdulai</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-100.546</v>
+        <v>-104.423</v>
       </c>
       <c r="C39" t="n">
-        <v>32.793</v>
+        <v>31.637</v>
       </c>
       <c r="D39" t="n">
-        <v>2.4872</v>
+        <v>4.1495</v>
       </c>
       <c r="E39" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M 1.5 - 9 km SW of Rotan, Texas</t>
+          <t>M 2.5 - 59 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>9 km SW of Rotan, Texas</t>
+          <t>59 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1998,38 +1998,38 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46095.70736677083</v>
+        <v>46095.88303170139</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46095.97094901621</v>
+        <v>46095.96269722222</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tx2026fdlfas</t>
+          <t>ci41204295</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-101.944</v>
+        <v>-116.754669189453</v>
       </c>
       <c r="C40" t="n">
-        <v>32.255</v>
+        <v>33.6506652832031</v>
       </c>
       <c r="D40" t="n">
-        <v>3.962</v>
+        <v>13.289999961853</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2</v>
+        <v>0.952443359159076</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M 1.2 - 20 km NW of Stanton, Texas</t>
+          <t>M 1.0 - 10 km SSW of Idyllwild, CA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20 km NW of Stanton, Texas</t>
+          <t>10 km SSW of Idyllwild, CA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2038,38 +2038,38 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46095.69110606481</v>
+        <v>46095.87724398148</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46095.97089986111</v>
+        <v>46095.87864965278</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nc75327372</t>
+          <t>aka2026fdudwi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-120.084503173828</v>
+        <v>-157.149</v>
       </c>
       <c r="C41" t="n">
-        <v>36.2008323669434</v>
+        <v>66.373</v>
       </c>
       <c r="D41" t="n">
-        <v>10.7700004577637</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M 2.9 - 2 km E of Huron, CA</t>
+          <t>M 3.0 - 57 km S of Shungnak, Alaska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2 km E of Huron, CA</t>
+          <t>57 km S of Shungnak, Alaska</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2078,38 +2078,38 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46095.68949560185</v>
+        <v>46095.87685564814</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46095.77751203704</v>
+        <v>46095.94651666666</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr71509878</t>
+          <t>nn00912662</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-67.01300000000001</v>
+        <v>-116.526</v>
       </c>
       <c r="C42" t="n">
-        <v>18.17</v>
+        <v>38.4379</v>
       </c>
       <c r="D42" t="n">
-        <v>27.16</v>
+        <v>12.8814</v>
       </c>
       <c r="E42" t="n">
-        <v>2.09</v>
+        <v>3.37</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M 2.1 - 3 km WSW of Maricao, Puerto Rico</t>
+          <t>M 3.4 - 74 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3 km WSW of Maricao, Puerto Rico</t>
+          <t>74 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2118,38 +2118,38 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46095.68730462963</v>
+        <v>46095.87443729167</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46095.69560127315</v>
+        <v>46096.08695996528</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>us6000sgbi</t>
+          <t>nn00912660</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23.2998</v>
+        <v>-116.6966</v>
       </c>
       <c r="C43" t="n">
-        <v>34.9004</v>
+        <v>38.3742</v>
       </c>
       <c r="D43" t="n">
-        <v>35.11</v>
+        <v>4.278</v>
       </c>
       <c r="E43" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M 4.8 - 50 km SW of Palaióchora, Greece</t>
+          <t>M 2.1 - 57 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>50 km SW of Palaióchora, Greece</t>
+          <t>57 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2158,38 +2158,38 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46095.68167795139</v>
+        <v>46095.86389622685</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46095.76548657408</v>
+        <v>46095.86570340278</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aka2026fdkqsi</t>
+          <t>aka2026fdtdkp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-151.229</v>
+        <v>-150.918</v>
       </c>
       <c r="C44" t="n">
-        <v>61.179</v>
+        <v>64.81</v>
       </c>
       <c r="D44" t="n">
-        <v>72.2</v>
+        <v>12.2</v>
       </c>
       <c r="E44" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>M 1.5 - 8 km WNW of Beluga, Alaska</t>
+          <t>M 1.3 - 25 km SSW of Manley Hot Springs, Alaska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8 km WNW of Beluga, Alaska</t>
+          <t>25 km SSW of Manley Hot Springs, Alaska</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2198,38 +2198,38 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46095.67801940972</v>
+        <v>46095.85587677083</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46095.67935157407</v>
+        <v>46095.85710167824</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aka2026fdkojc</t>
+          <t>nn00912655</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-152.251</v>
+        <v>-116.532</v>
       </c>
       <c r="C45" t="n">
-        <v>60.688</v>
+        <v>38.4506</v>
       </c>
       <c r="D45" t="n">
-        <v>103</v>
+        <v>6.2192</v>
       </c>
       <c r="E45" t="n">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>M 2.1 - 51 km W of Salamatof, Alaska</t>
+          <t>M 3.2 - 74 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>51 km W of Salamatof, Alaska</t>
+          <t>74 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2238,38 +2238,38 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46095.67615958333</v>
+        <v>46095.85289917824</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46095.67747614584</v>
+        <v>46096.08666041667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>us6000sgbf</t>
+          <t>hv74917417</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>74.6932</v>
+        <v>-155.371002197266</v>
       </c>
       <c r="C46" t="n">
-        <v>38.0328</v>
+        <v>19.2818336486816</v>
       </c>
       <c r="D46" t="n">
-        <v>97.70999999999999</v>
+        <v>30.0100002288818</v>
       </c>
       <c r="E46" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>M 4.4 - 65 km ESE of Murghob, Tajikistan</t>
+          <t>M 2.0 - 14 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>65 km ESE of Murghob, Tajikistan</t>
+          <t>14 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2278,38 +2278,38 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46095.67103631944</v>
+        <v>46095.84536168981</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46095.74024351852</v>
+        <v>46095.84858645833</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nn00912646</t>
+          <t>nc75327447</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-116.3557</v>
+        <v>-122.818496704102</v>
       </c>
       <c r="C47" t="n">
-        <v>37.5696</v>
+        <v>38.8343315124512</v>
       </c>
       <c r="D47" t="n">
-        <v>13.4041</v>
+        <v>1.87999999523163</v>
       </c>
       <c r="E47" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M 1.6 - 54 km W of Rachel, Nevada</t>
+          <t>M 1.2 - 8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>54 km W of Rachel, Nevada</t>
+          <t>8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2318,38 +2318,38 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46095.66677557871</v>
+        <v>46095.81590775463</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46095.66844216435</v>
+        <v>46095.85925590277</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ok2026fctl</t>
+          <t>us6000sgc5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-98.19499999999999</v>
+        <v>-116.4136</v>
       </c>
       <c r="C48" t="n">
-        <v>35.401</v>
+        <v>38.5775</v>
       </c>
       <c r="D48" t="n">
-        <v>6.38</v>
+        <v>12.516</v>
       </c>
       <c r="E48" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>M 2.2 - 16 km ENE of Lookeba, Oklahoma</t>
+          <t>M 2.5 - 90 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>16 km ENE of Lookeba, Oklahoma</t>
+          <t>90 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2358,38 +2358,38 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46095.65787973379</v>
+        <v>46095.77945232639</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46095.71147037037</v>
+        <v>46095.92890092592</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nn00912644</t>
+          <t>us6000sgc2</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-116.4773</v>
+        <v>153.3556</v>
       </c>
       <c r="C49" t="n">
-        <v>38.4845</v>
+        <v>46.5573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0212</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>1.69</v>
+        <v>5.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>M 1.7 - 80 km NE of Tonopah, Nevada</t>
+          <t>M 5.1 - Kuril Islands</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>80 km NE of Tonopah, Nevada</t>
+          <t>Kuril Islands</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2398,38 +2398,38 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46095.65554142361</v>
+        <v>46095.77235402778</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46095.65742730324</v>
+        <v>46095.78642407407</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nn00912642</t>
+          <t>us6000sgc4</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-116.3647</v>
+        <v>176.5308</v>
       </c>
       <c r="C50" t="n">
-        <v>37.3176</v>
+        <v>52.2911</v>
       </c>
       <c r="D50" t="n">
-        <v>13.2289</v>
+        <v>8.986000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>1.32</v>
+        <v>4.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M 1.3 - 57 km NE of Beatty, Nevada</t>
+          <t>M 4.2 - 235 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>57 km NE of Beatty, Nevada</t>
+          <t>235 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2438,38 +2438,38 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46095.65183778935</v>
+        <v>46095.76988208333</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46095.65348369213</v>
+        <v>46095.90945648148</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nn00912640</t>
+          <t>aka2026fdoonh</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-116.6675</v>
+        <v>-152.919</v>
       </c>
       <c r="C51" t="n">
-        <v>38.1891</v>
+        <v>59.948</v>
       </c>
       <c r="D51" t="n">
-        <v>5.8708</v>
+        <v>110.7</v>
       </c>
       <c r="E51" t="n">
-        <v>1.59</v>
+        <v>2.9</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>M 1.6 - 51 km ENE of Tonopah, Nevada</t>
+          <t>M 2.9 - 63 km WNW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>51 km ENE of Tonopah, Nevada</t>
+          <t>63 km WNW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2478,38 +2478,38 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46095.64834459491</v>
+        <v>46095.76006307871</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46095.65011091435</v>
+        <v>46095.89397037037</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nc75327352</t>
+          <t>nc75327417</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-122.776000976562</v>
+        <v>-121.6181640625</v>
       </c>
       <c r="C52" t="n">
-        <v>38.791332244873</v>
+        <v>36.0970001220703</v>
       </c>
       <c r="D52" t="n">
-        <v>1.4099999666214</v>
+        <v>13.6000003814697</v>
       </c>
       <c r="E52" t="n">
-        <v>2.13</v>
+        <v>1.34</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>M 2.1 - 2 km NW of The Geysers, CA</t>
+          <t>M 1.3 - 10 km NNW of Lopez Point, CA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2 km NW of The Geysers, CA</t>
+          <t>10 km NNW of Lopez Point, CA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2518,38 +2518,38 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46095.64618321759</v>
+        <v>46095.75923622686</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46095.72039762732</v>
+        <v>46095.82109177083</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>us6000sgb8</t>
+          <t>aka2026fdoioz</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-66.52290000000001</v>
+        <v>-150.653</v>
       </c>
       <c r="C53" t="n">
-        <v>-23.0932</v>
+        <v>62.91</v>
       </c>
       <c r="D53" t="n">
-        <v>229.541</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>M 4.5 - 87 km W of El Aguilar, Argentina</t>
+          <t>M 2.4 - 46 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>87 km W of El Aguilar, Argentina</t>
+          <t>46 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2558,38 +2558,38 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46095.63919398148</v>
+        <v>46095.7552774537</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46095.66461851852</v>
+        <v>46095.75831664352</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>nc75327347</t>
+          <t>nc75327407</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-122.761169433594</v>
+        <v>-122.807830810547</v>
       </c>
       <c r="C54" t="n">
-        <v>38.8240013122559</v>
+        <v>38.8185005187988</v>
       </c>
       <c r="D54" t="n">
-        <v>1.89999997615814</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="E54" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>M 1.1 - 3 km W of Cobb, CA</t>
+          <t>M 1.3 - 6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3 km W of Cobb, CA</t>
+          <t>6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2598,38 +2598,38 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46095.63465694444</v>
+        <v>46095.74812962963</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46095.71342921296</v>
+        <v>46095.80374011574</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nn00912635</t>
+          <t>aka2026fdnzor</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-116.5514</v>
+        <v>-157.911</v>
       </c>
       <c r="C55" t="n">
-        <v>38.4594</v>
+        <v>56.193</v>
       </c>
       <c r="D55" t="n">
-        <v>7.5756</v>
+        <v>63.7</v>
       </c>
       <c r="E55" t="n">
-        <v>3.52</v>
+        <v>1.7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>M 3.5 - 73 km NE of Tonopah, Nevada</t>
+          <t>M 1.7 - 32 km ESE of Chignik, Alaska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>73 km NE of Tonopah, Nevada</t>
+          <t>32 km ESE of Chignik, Alaska</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2638,38 +2638,38 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46095.62976957176</v>
+        <v>46095.74800765047</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46095.78223567129</v>
+        <v>46095.7494846875</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>nc75327332</t>
+          <t>us6000sgbx</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-122.814498901367</v>
+        <v>-46.6402</v>
       </c>
       <c r="C56" t="n">
-        <v>38.8346672058105</v>
+        <v>16.556</v>
       </c>
       <c r="D56" t="n">
-        <v>1.87000000476837</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>M 1.1 - 8 km W of Cobb, CA</t>
+          <t>M 5.1 - northern Mid-Atlantic Ridge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8 km W of Cobb, CA</t>
+          <t>northern Mid-Atlantic Ridge</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2678,38 +2678,38 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46095.6286193287</v>
+        <v>46095.73839887731</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46095.6752652662</v>
+        <v>46095.75246574074</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nc75327327</t>
+          <t>nc75327402</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-122.817497253418</v>
+        <v>-122.281829833984</v>
       </c>
       <c r="C57" t="n">
-        <v>38.8448333740234</v>
+        <v>37.3633346557617</v>
       </c>
       <c r="D57" t="n">
-        <v>0.790000021457672</v>
+        <v>3.32999992370605</v>
       </c>
       <c r="E57" t="n">
-        <v>1.06</v>
+        <v>2.56</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>M 1.1 - 9 km WNW of Cobb, CA</t>
+          <t>M 2.6 - 5 km WSW of Portola Valley, CA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>9 km WNW of Cobb, CA</t>
+          <t>5 km WSW of Portola Valley, CA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2718,38 +2718,38 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46095.62618368056</v>
+        <v>46095.73607071759</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46095.63710138889</v>
+        <v>46095.91402037037</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>nn00912634</t>
+          <t>aka2026fdnjta</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-116.5035</v>
+        <v>-148.1</v>
       </c>
       <c r="C58" t="n">
-        <v>38.4698</v>
+        <v>62.28</v>
       </c>
       <c r="D58" t="n">
-        <v>2.1064</v>
+        <v>0.1</v>
       </c>
       <c r="E58" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>M 2.1 - 77 km NE of Tonopah, Nevada</t>
+          <t>M 1.7 - 57 km NNE of Chickaloon, Alaska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>77 km NE of Tonopah, Nevada</t>
+          <t>57 km NNE of Chickaloon, Alaska</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2758,38 +2758,38 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46095.62491728009</v>
+        <v>46095.73525334491</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46095.6268653588</v>
+        <v>46095.73619780093</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>aka2026fdhwqq</t>
+          <t>us6000sgbr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-149.976</v>
+        <v>-72.0967</v>
       </c>
       <c r="C59" t="n">
-        <v>62.86</v>
+        <v>-42.429</v>
       </c>
       <c r="D59" t="n">
-        <v>76.5</v>
+        <v>5.985</v>
       </c>
       <c r="E59" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km N of Chase, Alaska</t>
+          <t>M 4.7 - 57 km SW of Lago Puelo, Argentina</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>46 km N of Chase, Alaska</t>
+          <t>57 km SW of Lago Puelo, Argentina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2798,38 +2798,38 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46095.61995665509</v>
+        <v>46095.73344064815</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46095.621306875</v>
+        <v>46095.8081949074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nn00912633</t>
+          <t>nc75327397</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-117.1019</v>
+        <v>-122.782165527344</v>
       </c>
       <c r="C60" t="n">
-        <v>37.2396</v>
+        <v>38.8131675720215</v>
       </c>
       <c r="D60" t="n">
-        <v>1.9242</v>
+        <v>0.280000001192093</v>
       </c>
       <c r="E60" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
+          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2838,38 +2838,38 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46095.61719795139</v>
+        <v>46095.73288171296</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46095.61863054398</v>
+        <v>46095.74467230324</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aka2026fdhpkc</t>
+          <t>us6000sgbq</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-152.14</v>
+        <v>-177.6605</v>
       </c>
       <c r="C61" t="n">
-        <v>60.245</v>
+        <v>-20.6389</v>
       </c>
       <c r="D61" t="n">
-        <v>81.5</v>
+        <v>519.203</v>
       </c>
       <c r="E61" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>M 1.3 - 34 km NW of Ninilchik, Alaska</t>
+          <t>M 4.4 - 252 km WNW of Houma, Tonga</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>34 km NW of Ninilchik, Alaska</t>
+          <t>252 km WNW of Houma, Tonga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2878,38 +2878,38 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46095.61409172454</v>
+        <v>46095.72445238426</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46095.61547047453</v>
+        <v>46095.7970375</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>nc75327322</t>
+          <t>ci41204215</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-123.477836608887</v>
+        <v>-116.8055</v>
       </c>
       <c r="C62" t="n">
-        <v>39.8306655883789</v>
+        <v>33.2446666666667</v>
       </c>
       <c r="D62" t="n">
-        <v>6.07999992370605</v>
+        <v>10.12</v>
       </c>
       <c r="E62" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>M 2.0 - 16 km N of Laytonville, CA</t>
+          <t>M 1.5 - 4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>16 km N of Laytonville, CA</t>
+          <t>4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2918,38 +2918,38 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46095.61145185185</v>
+        <v>46095.71835150463</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46095.65791388889</v>
+        <v>46095.72597673611</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nc75327312</t>
+          <t>nc75327377</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-123.477996826172</v>
+        <v>-120.121002197266</v>
       </c>
       <c r="C63" t="n">
-        <v>39.8306655883789</v>
+        <v>36.1983337402344</v>
       </c>
       <c r="D63" t="n">
-        <v>5.92999982833862</v>
+        <v>10.8299999237061</v>
       </c>
       <c r="E63" t="n">
-        <v>2.63</v>
+        <v>1.58</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>M 2.6 - 16 km N of Laytonville, CA</t>
+          <t>M 1.6 - 2 km WSW of Huron, CA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>16 km N of Laytonville, CA</t>
+          <t>2 km WSW of Huron, CA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2958,38 +2958,38 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46095.60974074074</v>
+        <v>46095.71190879629</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46095.63711296296</v>
+        <v>46095.76552966435</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>hv74917387</t>
+          <t>tx2026fdmbdg</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-155.589004516602</v>
+        <v>-100.546</v>
       </c>
       <c r="C64" t="n">
-        <v>19.4724998474121</v>
+        <v>32.793</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.600000023841858</v>
+        <v>2.4872</v>
       </c>
       <c r="E64" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>M 2.1 - 28 km E of Honaunau-Napoopoo, Hawaii</t>
+          <t>M 1.5 - 9 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>28 km E of Honaunau-Napoopoo, Hawaii</t>
+          <t>9 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2998,38 +2998,38 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46095.59852002315</v>
+        <v>46095.70736677083</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46095.60086608796</v>
+        <v>46095.97094901621</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>aka2026fdgrel</t>
+          <t>tx2026fdlfas</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>176.275</v>
+        <v>-101.944</v>
       </c>
       <c r="C65" t="n">
-        <v>51.991</v>
+        <v>32.255</v>
       </c>
       <c r="D65" t="n">
-        <v>15.7</v>
+        <v>3.962</v>
       </c>
       <c r="E65" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>M 3.9 - 230 km ESE of Attu Station, Alaska</t>
+          <t>M 1.2 - 20 km NW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>230 km ESE of Attu Station, Alaska</t>
+          <t>20 km NW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3038,38 +3038,38 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46095.59424848379</v>
+        <v>46095.69110606481</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46095.89015052083</v>
+        <v>46095.97089986111</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>nc75327302</t>
+          <t>nc75327372</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-121.5556640625</v>
+        <v>-120.084503173828</v>
       </c>
       <c r="C66" t="n">
-        <v>36.9501647949219</v>
+        <v>36.2008323669434</v>
       </c>
       <c r="D66" t="n">
-        <v>5.01000022888184</v>
+        <v>10.7700004577637</v>
       </c>
       <c r="E66" t="n">
-        <v>1.05</v>
+        <v>2.87</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km S of Gilroy, CA</t>
+          <t>M 2.9 - 2 km E of Huron, CA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6 km S of Gilroy, CA</t>
+          <t>2 km E of Huron, CA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3078,38 +3078,38 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46095.57577395834</v>
+        <v>46095.68949560185</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46095.57686728009</v>
+        <v>46095.77751203704</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>nc75327297</t>
+          <t>pr71509878</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-121.947334289551</v>
+        <v>-67.01300000000001</v>
       </c>
       <c r="C67" t="n">
-        <v>37.7569999694824</v>
+        <v>18.17</v>
       </c>
       <c r="D67" t="n">
-        <v>6.73999977111816</v>
+        <v>27.16</v>
       </c>
       <c r="E67" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>M 1.8 - 4 km SE of San Ramon, CA</t>
+          <t>M 2.1 - 3 km WSW of Maricao, Puerto Rico</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4 km SE of San Ramon, CA</t>
+          <t>3 km WSW of Maricao, Puerto Rico</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3118,38 +3118,38 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46095.57398888889</v>
+        <v>46095.68730462963</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46095.63013303241</v>
+        <v>46095.69560127315</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>nc75327287</t>
+          <t>us6000sgbi</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-122.825332641602</v>
+        <v>23.2998</v>
       </c>
       <c r="C68" t="n">
-        <v>38.8256683349609</v>
+        <v>34.9004</v>
       </c>
       <c r="D68" t="n">
-        <v>2.57999992370605</v>
+        <v>35.11</v>
       </c>
       <c r="E68" t="n">
-        <v>0.99</v>
+        <v>4.8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km NW of The Geysers, CA</t>
+          <t>M 4.8 - 50 km SW of Palaióchora, Greece</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8 km NW of The Geysers, CA</t>
+          <t>50 km SW of Palaióchora, Greece</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3158,38 +3158,38 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46095.55829305555</v>
+        <v>46095.68167795139</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46095.55934175926</v>
+        <v>46095.76548657408</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>nn00912632</t>
+          <t>aka2026fdkqsi</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-117.1262</v>
+        <v>-151.229</v>
       </c>
       <c r="C69" t="n">
-        <v>37.2113</v>
+        <v>61.179</v>
       </c>
       <c r="D69" t="n">
-        <v>0.008</v>
+        <v>72.2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>M 1.0 - 46 km NW of Beatty, Nevada</t>
+          <t>M 1.5 - 8 km WNW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>46 km NW of Beatty, Nevada</t>
+          <t>8 km WNW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3198,38 +3198,38 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46095.55455298611</v>
+        <v>46095.67801940972</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46095.55609993055</v>
+        <v>46095.67935157407</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>aka2026fdejza</t>
+          <t>aka2026fdkojc</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-150.859</v>
+        <v>-152.251</v>
       </c>
       <c r="C70" t="n">
-        <v>61.085</v>
+        <v>60.688</v>
       </c>
       <c r="D70" t="n">
-        <v>65.2</v>
+        <v>103</v>
       </c>
       <c r="E70" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>M 1.3 - 13 km ESE of Beluga, Alaska</t>
+          <t>M 2.1 - 51 km W of Salamatof, Alaska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>13 km ESE of Beluga, Alaska</t>
+          <t>51 km W of Salamatof, Alaska</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46095.5468615625</v>
+        <v>46095.67615958333</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46095.5479505787</v>
+        <v>46095.67747614584</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nc75327277</t>
+          <t>us6000sgbf</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-122.059669494629</v>
+        <v>74.6932</v>
       </c>
       <c r="C71" t="n">
-        <v>37.9770011901855</v>
+        <v>38.0328</v>
       </c>
       <c r="D71" t="n">
-        <v>14.2600002288818</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>1.51</v>
+        <v>4.4</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>M 1.5 - 2 km ESE of Pacheco, CA</t>
+          <t>M 4.4 - 65 km ESE of Murghob, Tajikistan</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2 km ESE of Pacheco, CA</t>
+          <t>65 km ESE of Murghob, Tajikistan</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3278,38 +3278,38 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46095.54660127315</v>
+        <v>46095.67103631944</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46095.5919228125</v>
+        <v>46095.74024351852</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tx2026fdehwc</t>
+          <t>nn00912646</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-101.914</v>
+        <v>-116.3557</v>
       </c>
       <c r="C72" t="n">
-        <v>32.382</v>
+        <v>37.5696</v>
       </c>
       <c r="D72" t="n">
-        <v>4.0769</v>
+        <v>13.4041</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>M 1.0 - 24 km SW of Ackerly, Texas</t>
+          <t>M 1.6 - 54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>24 km SW of Ackerly, Texas</t>
+          <t>54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3318,38 +3318,38 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46095.54530782408</v>
+        <v>46095.66677557871</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46095.96873667824</v>
+        <v>46095.66844216435</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nc75327267</t>
+          <t>ok2026fctl</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-122.798500061035</v>
+        <v>-98.19499999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>38.8173332214355</v>
+        <v>35.401</v>
       </c>
       <c r="D73" t="n">
-        <v>2.51999998092651</v>
+        <v>6.38</v>
       </c>
       <c r="E73" t="n">
-        <v>1.13</v>
+        <v>2.22</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
+          <t>M 2.2 - 16 km ENE of Lookeba, Oklahoma</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>16 km ENE of Lookeba, Oklahoma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3358,38 +3358,38 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46095.53511898148</v>
+        <v>46095.65787973379</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46095.55717452546</v>
+        <v>46095.71147037037</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nn00912629</t>
+          <t>nn00912644</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-117.1159</v>
+        <v>-116.4773</v>
       </c>
       <c r="C74" t="n">
-        <v>37.2086</v>
+        <v>38.4845</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0133</v>
+        <v>0.0212</v>
       </c>
       <c r="E74" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>M 1.3 - 45 km NW of Beatty, Nevada</t>
+          <t>M 1.7 - 80 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>45 km NW of Beatty, Nevada</t>
+          <t>80 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3398,38 +3398,38 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46095.53510384259</v>
+        <v>46095.65554142361</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46095.53669351852</v>
+        <v>46095.65742730324</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>pr71509873</t>
+          <t>nn00912642</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-66.8845</v>
+        <v>-116.3647</v>
       </c>
       <c r="C75" t="n">
-        <v>18.916</v>
+        <v>37.3176</v>
       </c>
       <c r="D75" t="n">
-        <v>23.61</v>
+        <v>13.2289</v>
       </c>
       <c r="E75" t="n">
-        <v>2.53</v>
+        <v>1.32</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>M 2.5 - 47 km N of Hatillo, Puerto Rico</t>
+          <t>M 1.3 - 57 km NE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>47 km N of Hatillo, Puerto Rico</t>
+          <t>57 km NE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3438,38 +3438,38 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46095.53112465278</v>
+        <v>46095.65183778935</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46095.55221423611</v>
+        <v>46095.65348369213</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>aka2026fddqdo</t>
+          <t>nn00912640</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-142.536</v>
+        <v>-116.6675</v>
       </c>
       <c r="C76" t="n">
-        <v>62.285</v>
+        <v>38.1891</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>5.8708</v>
       </c>
       <c r="E76" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>M 1.7 - 26 km ESE of Nabesna, Alaska</t>
+          <t>M 1.6 - 51 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>26 km ESE of Nabesna, Alaska</t>
+          <t>51 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3478,38 +3478,38 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46095.5308918287</v>
+        <v>46095.64834459491</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46095.53217123842</v>
+        <v>46095.65011091435</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>aka2026fdcpod</t>
+          <t>nc75327352</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-149.365</v>
+        <v>-122.776000976562</v>
       </c>
       <c r="C77" t="n">
-        <v>62.309</v>
+        <v>38.791332244873</v>
       </c>
       <c r="D77" t="n">
-        <v>54.2</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="E77" t="n">
-        <v>1.4</v>
+        <v>2.13</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>M 1.4 - 30 km ENE of Susitna North, Alaska</t>
+          <t>M 2.1 - 2 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>30 km ENE of Susitna North, Alaska</t>
+          <t>2 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3518,38 +3518,38 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46095.50947515047</v>
+        <v>46095.64618321759</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46095.51106810185</v>
+        <v>46095.72039762732</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>aka2026fdbymj</t>
+          <t>us6000sgb8</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-141.715</v>
+        <v>-66.52290000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>61.443</v>
+        <v>-23.0932</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>229.541</v>
       </c>
       <c r="E78" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M 1.4 - 64 km E of McCarthy, Alaska</t>
+          <t>M 4.5 - 87 km W of El Aguilar, Argentina</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>64 km E of McCarthy, Alaska</t>
+          <t>87 km W of El Aguilar, Argentina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3558,38 +3558,38 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46095.49578780092</v>
+        <v>46095.63919398148</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46095.88198071759</v>
+        <v>46095.66461851852</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>aka2026fdbvge</t>
+          <t>nc75327347</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-149.037</v>
+        <v>-122.761169433594</v>
       </c>
       <c r="C79" t="n">
-        <v>63.816</v>
+        <v>38.8240013122559</v>
       </c>
       <c r="D79" t="n">
-        <v>3.9</v>
+        <v>1.89999997615814</v>
       </c>
       <c r="E79" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>M 1.4 - 5 km SW of Healy, Alaska</t>
+          <t>M 1.1 - 3 km W of Cobb, CA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>5 km SW of Healy, Alaska</t>
+          <t>3 km W of Cobb, CA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3598,38 +3598,38 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46095.49308862269</v>
+        <v>46095.63465694444</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46095.49433715278</v>
+        <v>46095.71342921296</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nc75327262</t>
+          <t>nn00912635</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-118.524833679199</v>
+        <v>-116.5514</v>
       </c>
       <c r="C80" t="n">
-        <v>37.454833984375</v>
+        <v>38.4594</v>
       </c>
       <c r="D80" t="n">
-        <v>13.5500001907349</v>
+        <v>7.5756</v>
       </c>
       <c r="E80" t="n">
-        <v>1.63</v>
+        <v>3.52</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>M 1.6 - 8 km NE of Round Valley, CA</t>
+          <t>M 3.5 - 73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8 km NE of Round Valley, CA</t>
+          <t>73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3638,38 +3638,38 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46095.48521180556</v>
+        <v>46095.62976957176</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46095.50507347222</v>
+        <v>46096.08617975695</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>aka2026fdbgbs</t>
+          <t>nc75327332</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-151.084</v>
+        <v>-122.814498901367</v>
       </c>
       <c r="C81" t="n">
-        <v>60.677</v>
+        <v>38.8346672058105</v>
       </c>
       <c r="D81" t="n">
-        <v>71</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="E81" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>M 1.6 - 11 km E of Nikiski, Alaska</t>
+          <t>M 1.1 - 8 km W of Cobb, CA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>11 km E of Nikiski, Alaska</t>
+          <t>8 km W of Cobb, CA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3678,38 +3678,38 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46095.48086649305</v>
+        <v>46095.6286193287</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46095.48225108796</v>
+        <v>46095.6752652662</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tx2026fdawqc</t>
+          <t>nc75327327</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-104.396</v>
+        <v>-122.817497253418</v>
       </c>
       <c r="C82" t="n">
-        <v>31.672</v>
+        <v>38.8448333740234</v>
       </c>
       <c r="D82" t="n">
-        <v>7.9656</v>
+        <v>0.790000021457672</v>
       </c>
       <c r="E82" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>M 1.6 - 55 km S of Whites City, New Mexico</t>
+          <t>M 1.1 - 9 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>55 km S of Whites City, New Mexico</t>
+          <t>9 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3718,38 +3718,38 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46095.47324049768</v>
+        <v>46095.62618368056</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46095.47518646991</v>
+        <v>46095.63710138889</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>aka2026fdawfa</t>
+          <t>nn00912634</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-146.257</v>
+        <v>-116.5035</v>
       </c>
       <c r="C83" t="n">
-        <v>61.532</v>
+        <v>38.4698</v>
       </c>
       <c r="D83" t="n">
-        <v>15.8</v>
+        <v>2.1064</v>
       </c>
       <c r="E83" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>M 3.2 - 44 km N of Valdez, Alaska</t>
+          <t>M 2.1 - 77 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>44 km N of Valdez, Alaska</t>
+          <t>77 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3758,38 +3758,38 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46095.47291107639</v>
+        <v>46095.62491728009</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46095.50066519676</v>
+        <v>46095.6268653588</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tx2026fdatrz</t>
+          <t>aka2026fdhwqq</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-104.472</v>
+        <v>-149.976</v>
       </c>
       <c r="C84" t="n">
-        <v>31.607</v>
+        <v>62.86</v>
       </c>
       <c r="D84" t="n">
-        <v>3.8361</v>
+        <v>76.5</v>
       </c>
       <c r="E84" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>M 1.5 - 63 km S of Whites City, New Mexico</t>
+          <t>M 1.7 - 46 km N of Chase, Alaska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>63 km S of Whites City, New Mexico</t>
+          <t>46 km N of Chase, Alaska</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3798,38 +3798,38 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46095.47089748843</v>
+        <v>46095.61995665509</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46095.50040792824</v>
+        <v>46095.621306875</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nn00912622</t>
+          <t>nn00912633</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-116.5072</v>
+        <v>-117.1019</v>
       </c>
       <c r="C85" t="n">
-        <v>38.4542</v>
+        <v>37.2396</v>
       </c>
       <c r="D85" t="n">
-        <v>1.8632</v>
+        <v>1.9242</v>
       </c>
       <c r="E85" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>M 1.6 - 76 km NE of Tonopah, Nevada</t>
+          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>76 km NE of Tonopah, Nevada</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3838,38 +3838,38 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46095.4685462963</v>
+        <v>46095.61719795139</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46095.47066204861</v>
+        <v>46095.61863054398</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>nc75327252</t>
+          <t>aka2026fdhpkc</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-124.46900177002</v>
+        <v>-152.14</v>
       </c>
       <c r="C86" t="n">
-        <v>40.3064994812012</v>
+        <v>60.245</v>
       </c>
       <c r="D86" t="n">
-        <v>12.539999961853</v>
+        <v>81.5</v>
       </c>
       <c r="E86" t="n">
-        <v>3.15</v>
+        <v>1.3</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>M 3.2 - 16 km W of Petrolia, CA</t>
+          <t>M 1.3 - 34 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>16 km W of Petrolia, CA</t>
+          <t>34 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3878,38 +3878,38 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46095.4434332176</v>
+        <v>46095.61409172454</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46095.48426105324</v>
+        <v>46095.61547047453</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>aka2026fczlhg</t>
+          <t>nc75327322</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-153.184</v>
+        <v>-123.477836608887</v>
       </c>
       <c r="C87" t="n">
-        <v>59.849</v>
+        <v>39.8306655883789</v>
       </c>
       <c r="D87" t="n">
-        <v>131.2</v>
+        <v>6.07999992370605</v>
       </c>
       <c r="E87" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>M 2.3 - 52 km E of Pedro Bay, Alaska</t>
+          <t>M 2.0 - 16 km N of Laytonville, CA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>52 km E of Pedro Bay, Alaska</t>
+          <t>16 km N of Laytonville, CA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3918,38 +3918,38 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46095.44315893519</v>
+        <v>46095.61145185185</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46095.46118101852</v>
+        <v>46095.65791388889</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tx2026fczgra</t>
+          <t>nc75327312</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-104.119</v>
+        <v>-123.477996826172</v>
       </c>
       <c r="C88" t="n">
-        <v>31.667</v>
+        <v>39.8306655883789</v>
       </c>
       <c r="D88" t="n">
-        <v>4.0448</v>
+        <v>5.92999982833862</v>
       </c>
       <c r="E88" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>M 1.9 - 49 km W of Mentone, Texas</t>
+          <t>M 2.6 - 16 km N of Laytonville, CA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>16 km N of Laytonville, CA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3958,38 +3958,38 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46095.43945071759</v>
+        <v>46095.60974074074</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46095.44239887731</v>
+        <v>46095.63711296296</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nc75327242</t>
+          <t>hv74917387</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-121.980834960938</v>
+        <v>-155.589004516602</v>
       </c>
       <c r="C89" t="n">
-        <v>37.8216667175293</v>
+        <v>19.4724998474121</v>
       </c>
       <c r="D89" t="n">
-        <v>9.47999954223633</v>
+        <v>-0.600000023841858</v>
       </c>
       <c r="E89" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>M 2.0 - 2 km E of Danville, CA</t>
+          <t>M 2.1 - 28 km E of Honaunau-Napoopoo, Hawaii</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2 km E of Danville, CA</t>
+          <t>28 km E of Honaunau-Napoopoo, Hawaii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3998,38 +3998,38 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46095.43391921296</v>
+        <v>46095.59852002315</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46095.45647990741</v>
+        <v>46095.60086608796</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>us6000sgag</t>
+          <t>aka2026fdgrel</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>134.0262</v>
+        <v>176.275</v>
       </c>
       <c r="C90" t="n">
-        <v>38.2275</v>
+        <v>51.991</v>
       </c>
       <c r="D90" t="n">
-        <v>419.505</v>
+        <v>15.7</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>M 4.0 - 250 km NNE of Ama, Japan</t>
+          <t>M 3.9 - 230 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>250 km NNE of Ama, Japan</t>
+          <t>230 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4038,38 +4038,38 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46095.43000553241</v>
+        <v>46095.59424848379</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46095.45789398148</v>
+        <v>46095.89015052083</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>aka2026fcytaw</t>
+          <t>nc75327302</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-147.775</v>
+        <v>-121.5556640625</v>
       </c>
       <c r="C91" t="n">
-        <v>64.908</v>
+        <v>36.9501647949219</v>
       </c>
       <c r="D91" t="n">
-        <v>16.1</v>
+        <v>5.01000022888184</v>
       </c>
       <c r="E91" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>M 2.2 - 3 km W of Farmers Loop, Alaska</t>
+          <t>M 1.1 - 6 km S of Gilroy, CA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>3 km W of Farmers Loop, Alaska</t>
+          <t>6 km S of Gilroy, CA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4078,38 +4078,38 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46095.42845855324</v>
+        <v>46095.57577395834</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46095.42950167824</v>
+        <v>46095.57686728009</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>hv74917362</t>
+          <t>nc75327297</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-155.407836914062</v>
+        <v>-121.947334289551</v>
       </c>
       <c r="C92" t="n">
-        <v>19.2481670379639</v>
+        <v>37.7569999694824</v>
       </c>
       <c r="D92" t="n">
-        <v>32.8800010681152</v>
+        <v>6.73999977111816</v>
       </c>
       <c r="E92" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>M 2.2 - 8 km NE of Pāhala, Hawaii</t>
+          <t>M 1.8 - 4 km SE of San Ramon, CA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8 km NE of Pāhala, Hawaii</t>
+          <t>4 km SE of San Ramon, CA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4118,38 +4118,38 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46095.42089629629</v>
+        <v>46095.57398888889</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46095.42425393518</v>
+        <v>46095.63013303241</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>aka2026fcydsf</t>
+          <t>nc75327287</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-147.591</v>
+        <v>-122.825332641602</v>
       </c>
       <c r="C93" t="n">
-        <v>60.613</v>
+        <v>38.8256683349609</v>
       </c>
       <c r="D93" t="n">
-        <v>18.7</v>
+        <v>2.57999992370605</v>
       </c>
       <c r="E93" t="n">
-        <v>1.9</v>
+        <v>0.99</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>M 1.9 - 57 km WSW of Tatitlek, Alaska</t>
+          <t>M 1.0 - 8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>57 km WSW of Tatitlek, Alaska</t>
+          <t>8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4158,38 +4158,38 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46095.41621864583</v>
+        <v>46095.55829305555</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46095.41741854166</v>
+        <v>46095.55934175926</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tx2026fcxzqm</t>
+          <t>nn00912632</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-100.542</v>
+        <v>-117.1262</v>
       </c>
       <c r="C94" t="n">
-        <v>32.797</v>
+        <v>37.2113</v>
       </c>
       <c r="D94" t="n">
-        <v>0.8341</v>
+        <v>0.008</v>
       </c>
       <c r="E94" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>M 1.8 - 9 km SW of Rotan, Texas</t>
+          <t>M 1.0 - 46 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>9 km SW of Rotan, Texas</t>
+          <t>46 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4198,38 +4198,38 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46095.41282443287</v>
+        <v>46095.55455298611</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46095.41541297454</v>
+        <v>46095.55609993055</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tx2026fcxogc</t>
+          <t>aka2026fdejza</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-104.116</v>
+        <v>-150.859</v>
       </c>
       <c r="C95" t="n">
-        <v>31.667</v>
+        <v>61.085</v>
       </c>
       <c r="D95" t="n">
-        <v>6.0999</v>
+        <v>65.2</v>
       </c>
       <c r="E95" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>M 2.7 - 49 km W of Mentone, Texas</t>
+          <t>M 1.3 - 13 km ESE of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>13 km ESE of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4238,38 +4238,38 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46095.40363546296</v>
+        <v>46095.5468615625</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46095.89443695602</v>
+        <v>46095.5479505787</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tx2026fcxnmu</t>
+          <t>nc75327277</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-102.094</v>
+        <v>-122.059669494629</v>
       </c>
       <c r="C96" t="n">
-        <v>32.349</v>
+        <v>37.9770011901855</v>
       </c>
       <c r="D96" t="n">
-        <v>3.9111</v>
+        <v>14.2600002288818</v>
       </c>
       <c r="E96" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>M 1.1 - 37 km NW of Stanton, Texas</t>
+          <t>M 1.5 - 2 km ESE of Pacheco, CA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>37 km NW of Stanton, Texas</t>
+          <t>2 km ESE of Pacheco, CA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4278,38 +4278,38 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46095.4030390625</v>
+        <v>46095.54660127315</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46095.47299325231</v>
+        <v>46095.5919228125</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tx2026fcxkzg</t>
+          <t>tx2026fdehwc</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-104.117</v>
+        <v>-101.911</v>
       </c>
       <c r="C97" t="n">
-        <v>31.666</v>
+        <v>32.378</v>
       </c>
       <c r="D97" t="n">
-        <v>5.3308</v>
+        <v>8.667</v>
       </c>
       <c r="E97" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>M 2.3 - 49 km W of Mentone, Texas</t>
+          <t>M 1.2 - 24 km SW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>24 km SW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4318,38 +4318,38 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46095.40100652778</v>
+        <v>46095.54531115741</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46095.95376244213</v>
+        <v>46096.03998054398</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>tx2026fcxjaw</t>
+          <t>nc75327267</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-104.121</v>
+        <v>-122.798500061035</v>
       </c>
       <c r="C98" t="n">
-        <v>31.668</v>
+        <v>38.8173332214355</v>
       </c>
       <c r="D98" t="n">
-        <v>4.3438</v>
+        <v>2.51999998092651</v>
       </c>
       <c r="E98" t="n">
-        <v>2.6</v>
+        <v>1.13</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>M 2.6 - 49 km W of Mentone, Texas</t>
+          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4358,38 +4358,38 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46095.40024592593</v>
+        <v>46095.53511898148</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46095.41771622685</v>
+        <v>46095.55717452546</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>tx2026fcxjta</t>
+          <t>nn00912629</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-104.118</v>
+        <v>-117.1159</v>
       </c>
       <c r="C99" t="n">
-        <v>31.665</v>
+        <v>37.2086</v>
       </c>
       <c r="D99" t="n">
-        <v>6.0999</v>
+        <v>0.0133</v>
       </c>
       <c r="E99" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>M 2.6 - 49 km W of Mentone, Texas</t>
+          <t>M 1.3 - 45 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>45 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4398,38 +4398,38 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46095.40024378472</v>
+        <v>46095.53510384259</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46095.40782453704</v>
+        <v>46095.53669351852</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>tx2026fcxdxl</t>
+          <t>pr71509873</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-104.319</v>
+        <v>-66.8845</v>
       </c>
       <c r="C100" t="n">
-        <v>31.649</v>
+        <v>18.916</v>
       </c>
       <c r="D100" t="n">
-        <v>4.1032</v>
+        <v>23.61</v>
       </c>
       <c r="E100" t="n">
-        <v>1.9</v>
+        <v>2.53</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>M 1.9 - 58 km S of Whites City, New Mexico</t>
+          <t>M 2.5 - 47 km N of Hatillo, Puerto Rico</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>47 km N of Hatillo, Puerto Rico</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4438,38 +4438,38 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46095.39530927083</v>
+        <v>46095.53112465278</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46095.39790074074</v>
+        <v>46095.55221423611</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>tx2026fcxdjs</t>
+          <t>aka2026fddqdo</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-104.363</v>
+        <v>-142.536</v>
       </c>
       <c r="C101" t="n">
-        <v>31.593</v>
+        <v>62.285</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E101" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>M 1.6 - 62 km WNW of Toyah, Texas</t>
+          <t>M 1.7 - 26 km ESE of Nabesna, Alaska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>62 km WNW of Toyah, Texas</t>
+          <t>26 km ESE of Nabesna, Alaska</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4478,38 +4478,38 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46095.39488246528</v>
+        <v>46095.5308918287</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46095.41727866898</v>
+        <v>46095.53217123842</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>hv74917352</t>
+          <t>aka2026fdcpod</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-155.063003540039</v>
+        <v>-149.365</v>
       </c>
       <c r="C102" t="n">
-        <v>19.3636665344238</v>
+        <v>62.309</v>
       </c>
       <c r="D102" t="n">
-        <v>6.82999992370605</v>
+        <v>54.2</v>
       </c>
       <c r="E102" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>M 1.8 - 13 km SE of Fern Forest, Hawaii</t>
+          <t>M 1.4 - 30 km ENE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>13 km SE of Fern Forest, Hawaii</t>
+          <t>30 km ENE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4518,38 +4518,38 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46095.38912592593</v>
+        <v>46095.50947515047</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46095.39156377315</v>
+        <v>46095.51106810185</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>nn00912616</t>
+          <t>aka2026fdbymj</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-117.1065</v>
+        <v>-141.715</v>
       </c>
       <c r="C103" t="n">
-        <v>37.2155</v>
+        <v>61.443</v>
       </c>
       <c r="D103" t="n">
-        <v>0.03</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>M 1.3 - 45 km NW of Beatty, Nevada</t>
+          <t>M 1.4 - 64 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>45 km NW of Beatty, Nevada</t>
+          <t>64 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4558,38 +4558,38 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46095.38704399305</v>
+        <v>46095.49578780092</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46095.38848982639</v>
+        <v>46095.88198071759</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nc75327232</t>
+          <t>aka2026fdbvge</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-121.320503234863</v>
+        <v>-149.037</v>
       </c>
       <c r="C104" t="n">
-        <v>36.6573333740234</v>
+        <v>63.816</v>
       </c>
       <c r="D104" t="n">
-        <v>1.52999997138977</v>
+        <v>3.9</v>
       </c>
       <c r="E104" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>M 1.7 - 15 km S of Tres Pinos, CA</t>
+          <t>M 1.4 - 5 km SW of Healy, Alaska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>15 km S of Tres Pinos, CA</t>
+          <t>5 km SW of Healy, Alaska</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4598,38 +4598,38 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46095.38549236111</v>
+        <v>46095.49308862269</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46095.40788662037</v>
+        <v>46095.49433715278</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>aka2026fcwnpr</t>
+          <t>nc75327262</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-156.341</v>
+        <v>-118.524833679199</v>
       </c>
       <c r="C105" t="n">
-        <v>56.513</v>
+        <v>37.454833984375</v>
       </c>
       <c r="D105" t="n">
-        <v>62.7</v>
+        <v>13.5500001907349</v>
       </c>
       <c r="E105" t="n">
-        <v>3.3</v>
+        <v>1.63</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>M 3.3 - 128 km SSE of Ugashik, Alaska</t>
+          <t>M 1.6 - 8 km NE of Round Valley, CA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>128 km SSE of Ugashik, Alaska</t>
+          <t>8 km NE of Round Valley, CA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4638,38 +4638,38 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46095.38220442129</v>
+        <v>46095.48521180556</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46095.42112314815</v>
+        <v>46095.50507347222</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>aka2026fcwkyb</t>
+          <t>aka2026fdbgbs</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-152.224</v>
+        <v>-151.084</v>
       </c>
       <c r="C106" t="n">
-        <v>59.653</v>
+        <v>60.677</v>
       </c>
       <c r="D106" t="n">
-        <v>67.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="E106" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>M 2.9 - 26 km WSW of Anchor Point, Alaska</t>
+          <t>M 1.6 - 11 km E of Nikiski, Alaska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>26 km WSW of Anchor Point, Alaska</t>
+          <t>11 km E of Nikiski, Alaska</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4678,38 +4678,38 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46095.38009972222</v>
+        <v>46095.48086649305</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46095.41820648148</v>
+        <v>46095.48225108796</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ok2026fcfu</t>
+          <t>tx2026fdawqc</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-98.21438599</v>
+        <v>-104.396</v>
       </c>
       <c r="C107" t="n">
-        <v>35.43252182</v>
+        <v>31.672</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>7.9656</v>
       </c>
       <c r="E107" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>M 2.1 - 13 km ESE of Hinton, Oklahoma</t>
+          <t>M 1.6 - 55 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>13 km ESE of Hinton, Oklahoma</t>
+          <t>55 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4718,38 +4718,38 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46095.37014696759</v>
+        <v>46095.47324049768</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46095.37120069445</v>
+        <v>46095.47518646991</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>aka2026fcvpaw</t>
+          <t>aka2026fdawfa</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-150.883</v>
+        <v>-146.257</v>
       </c>
       <c r="C108" t="n">
-        <v>61.959</v>
+        <v>61.532</v>
       </c>
       <c r="D108" t="n">
-        <v>0.7</v>
+        <v>15.8</v>
       </c>
       <c r="E108" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>M 1.6 - 27 km E of Skwentna, Alaska</t>
+          <t>M 3.2 - 44 km N of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>27 km E of Skwentna, Alaska</t>
+          <t>44 km N of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4758,38 +4758,38 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46095.36237780093</v>
+        <v>46095.47291107639</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46095.36346644676</v>
+        <v>46095.50066519676</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>hv74917342</t>
+          <t>tx2026fdatrz</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-155.488494873047</v>
+        <v>-104.472</v>
       </c>
       <c r="C109" t="n">
-        <v>19.1765003204346</v>
+        <v>31.607</v>
       </c>
       <c r="D109" t="n">
-        <v>27.2299995422363</v>
+        <v>3.8361</v>
       </c>
       <c r="E109" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>M 2.4 - 3 km SSW of Pāhala, Hawaii</t>
+          <t>M 1.5 - 63 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>3 km SSW of Pāhala, Hawaii</t>
+          <t>63 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4798,38 +4798,38 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46095.3602056713</v>
+        <v>46095.47089748843</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46095.36287916666</v>
+        <v>46095.50040792824</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hv74917337</t>
+          <t>nn00912622</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-155.494003295898</v>
+        <v>-116.5072</v>
       </c>
       <c r="C110" t="n">
-        <v>19.1691665649414</v>
+        <v>38.4542</v>
       </c>
       <c r="D110" t="n">
-        <v>24.0799999237061</v>
+        <v>1.8632</v>
       </c>
       <c r="E110" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>M 1.9 - 4 km SSW of Pāhala, Hawaii</t>
+          <t>M 1.6 - 76 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4 km SSW of Pāhala, Hawaii</t>
+          <t>76 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4838,38 +4838,38 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46095.35828587963</v>
+        <v>46095.4685462963</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46095.360790625</v>
+        <v>46095.47066204861</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>aka2026fcvjoi</t>
+          <t>nc75327252</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-149.83</v>
+        <v>-124.46900177002</v>
       </c>
       <c r="C111" t="n">
-        <v>64.30800000000001</v>
+        <v>40.3064994812012</v>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>12.539999961853</v>
       </c>
       <c r="E111" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>M 1.3 - 31 km W of Anderson, Alaska</t>
+          <t>M 3.2 - 16 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>31 km W of Anderson, Alaska</t>
+          <t>16 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4878,38 +4878,38 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46095.35795271991</v>
+        <v>46095.4434332176</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46095.35929912037</v>
+        <v>46095.48426105324</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>us6000sg9g</t>
+          <t>aka2026fczlhg</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-25.6013</v>
+        <v>-153.184</v>
       </c>
       <c r="C112" t="n">
-        <v>-58.7858</v>
+        <v>59.849</v>
       </c>
       <c r="D112" t="n">
-        <v>73.994</v>
+        <v>131.2</v>
       </c>
       <c r="E112" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>M 5.2 - South Sandwich Islands region</t>
+          <t>M 2.3 - 52 km E of Pedro Bay, Alaska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>South Sandwich Islands region</t>
+          <t>52 km E of Pedro Bay, Alaska</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4918,38 +4918,38 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46095.35739234954</v>
+        <v>46095.44315893519</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46095.37358842593</v>
+        <v>46095.46118101852</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ci41204079</t>
+          <t>tx2026fczgra</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-118.0855</v>
+        <v>-104.119</v>
       </c>
       <c r="C113" t="n">
-        <v>35.3303333333333</v>
+        <v>31.667</v>
       </c>
       <c r="D113" t="n">
-        <v>7.19</v>
+        <v>4.0448</v>
       </c>
       <c r="E113" t="n">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>M 1.2 - 24 km NNW of California City, CA</t>
+          <t>M 1.9 - 49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>24 km NNW of California City, CA</t>
+          <t>49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4958,38 +4958,38 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46095.35599143519</v>
+        <v>46095.43945071759</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46095.35835270833</v>
+        <v>46095.44239887731</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nn00912612</t>
+          <t>nc75327242</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-117.1191</v>
+        <v>-121.980834960938</v>
       </c>
       <c r="C114" t="n">
-        <v>37.2198</v>
+        <v>37.8216667175293</v>
       </c>
       <c r="D114" t="n">
-        <v>0.0008</v>
+        <v>9.47999954223633</v>
       </c>
       <c r="E114" t="n">
-        <v>1.17</v>
+        <v>2.02</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
+          <t>M 2.0 - 2 km E of Danville, CA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>2 km E of Danville, CA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4998,38 +4998,38 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46095.35582130787</v>
+        <v>46095.43391921296</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46095.35709960648</v>
+        <v>46095.45647990741</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nn00912609</t>
+          <t>us6000sgag</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-116.4921</v>
+        <v>134.0262</v>
       </c>
       <c r="C115" t="n">
-        <v>38.467</v>
+        <v>38.2275</v>
       </c>
       <c r="D115" t="n">
-        <v>1.6026</v>
+        <v>419.505</v>
       </c>
       <c r="E115" t="n">
-        <v>1.74</v>
+        <v>4</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>M 1.7 - 78 km NE of Tonopah, Nevada</t>
+          <t>M 4.0 - 250 km NNE of Ama, Japan</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>78 km NE of Tonopah, Nevada</t>
+          <t>250 km NNE of Ama, Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5038,38 +5038,38 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46095.35160628472</v>
+        <v>46095.43000553241</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46095.35341947916</v>
+        <v>46095.45789398148</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ci41204071</t>
+          <t>aka2026fcytaw</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-117.079666666667</v>
+        <v>-147.775</v>
       </c>
       <c r="C116" t="n">
-        <v>34.021</v>
+        <v>64.908</v>
       </c>
       <c r="D116" t="n">
-        <v>18.33</v>
+        <v>16.1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.98</v>
+        <v>2.2</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km WSW of Yucaipa, CA</t>
+          <t>M 2.2 - 3 km W of Farmers Loop, Alaska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>4 km WSW of Yucaipa, CA</t>
+          <t>3 km W of Farmers Loop, Alaska</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5078,38 +5078,38 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46095.35113958333</v>
+        <v>46095.42845855324</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46095.35350167824</v>
+        <v>46095.42950167824</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>nn00912607</t>
+          <t>hv74917362</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-117.1176</v>
+        <v>-155.407836914062</v>
       </c>
       <c r="C117" t="n">
-        <v>37.2157</v>
+        <v>19.2481670379639</v>
       </c>
       <c r="D117" t="n">
-        <v>1.6995</v>
+        <v>32.8800010681152</v>
       </c>
       <c r="E117" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>M 1.2 - 46 km NW of Beatty, Nevada</t>
+          <t>M 2.2 - 8 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>46 km NW of Beatty, Nevada</t>
+          <t>8 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5118,38 +5118,38 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46095.35093659722</v>
+        <v>46095.42089629629</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46095.3522947338</v>
+        <v>46095.42425393518</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>tx2026fcuwli</t>
+          <t>aka2026fcydsf</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-102.216</v>
+        <v>-147.591</v>
       </c>
       <c r="C118" t="n">
-        <v>32.123</v>
+        <v>60.613</v>
       </c>
       <c r="D118" t="n">
-        <v>7.1155</v>
+        <v>18.7</v>
       </c>
       <c r="E118" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>M 1.1 - 19 km NW of Midland, Texas</t>
+          <t>M 1.9 - 57 km WSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>19 km NW of Midland, Texas</t>
+          <t>57 km WSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5158,38 +5158,38 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46095.34735415509</v>
+        <v>46095.41621864583</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46095.47295694445</v>
+        <v>46095.41741854166</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>aka2026fcutja</t>
+          <t>tx2026fcxzqm</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-151.07</v>
+        <v>-100.542</v>
       </c>
       <c r="C119" t="n">
-        <v>63.548</v>
+        <v>32.797</v>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>0.8341</v>
       </c>
       <c r="E119" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>M 1.4 - 32 km E of Denali National Park, Alaska</t>
+          <t>M 1.8 - 9 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>32 km E of Denali National Park, Alaska</t>
+          <t>9 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5198,38 +5198,38 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46095.34490104167</v>
+        <v>46095.41282443287</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46095.34610518518</v>
+        <v>46095.41541297454</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ci41204047</t>
+          <t>tx2026fcxogc</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-118.362</v>
+        <v>-104.116</v>
       </c>
       <c r="C120" t="n">
-        <v>34.1451666666667</v>
+        <v>31.667</v>
       </c>
       <c r="D120" t="n">
-        <v>15.54</v>
+        <v>6.0999</v>
       </c>
       <c r="E120" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>M 1.0 - 1 km NW of Universal City, CA</t>
+          <t>M 2.7 - 49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1 km NW of Universal City, CA</t>
+          <t>49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5238,38 +5238,38 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46095.34305972223</v>
+        <v>46095.40363546296</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46095.34540800926</v>
+        <v>46095.89443695602</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>pr71509853</t>
+          <t>tx2026fcxnmu</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-67.3061666666667</v>
+        <v>-102.094</v>
       </c>
       <c r="C121" t="n">
-        <v>18.3425</v>
+        <v>32.349</v>
       </c>
       <c r="D121" t="n">
-        <v>22.48</v>
+        <v>3.9111</v>
       </c>
       <c r="E121" t="n">
-        <v>2.43</v>
+        <v>1.1</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>M 2.4 - 5 km W of Rincón, Puerto Rico</t>
+          <t>M 1.1 - 37 km NW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>5 km W of Rincón, Puerto Rico</t>
+          <t>37 km NW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5278,38 +5278,38 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46095.34218113426</v>
+        <v>46095.4030390625</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46095.35034837963</v>
+        <v>46095.47299325231</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>aka2026fcukuz</t>
+          <t>tx2026fcxkzg</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-152.363</v>
+        <v>-104.117</v>
       </c>
       <c r="C122" t="n">
-        <v>59.584</v>
+        <v>31.666</v>
       </c>
       <c r="D122" t="n">
-        <v>79.90000000000001</v>
+        <v>5.3308</v>
       </c>
       <c r="E122" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>M 1.6 - 35 km NW of Nanwalek, Alaska</t>
+          <t>M 2.3 - 49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>35 km NW of Nanwalek, Alaska</t>
+          <t>49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5318,38 +5318,38 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46095.3380100463</v>
+        <v>46095.40100652778</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46095.33962047454</v>
+        <v>46095.95376244213</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>uw62234461</t>
+          <t>tx2026fcxjaw</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-121.969</v>
+        <v>-104.121</v>
       </c>
       <c r="C123" t="n">
-        <v>47.00283333333334</v>
+        <v>31.668</v>
       </c>
       <c r="D123" t="n">
-        <v>14.67</v>
+        <v>4.3438</v>
       </c>
       <c r="E123" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>M 1.8 - 10 km SE of Carbonado, Washington</t>
+          <t>M 2.6 - 49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>10 km SE of Carbonado, Washington</t>
+          <t>49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5358,38 +5358,38 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46095.32948564815</v>
+        <v>46095.40024592593</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46095.35692152777</v>
+        <v>46095.41771622685</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>aka2026fcttzo</t>
+          <t>tx2026fcxjta</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-150.606</v>
+        <v>-104.118</v>
       </c>
       <c r="C124" t="n">
-        <v>62.796</v>
+        <v>31.665</v>
       </c>
       <c r="D124" t="n">
-        <v>80.40000000000001</v>
+        <v>6.0999</v>
       </c>
       <c r="E124" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>M 1.6 - 34 km NNE of Petersville, Alaska</t>
+          <t>M 2.6 - 49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>34 km NNE of Petersville, Alaska</t>
+          <t>49 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5398,38 +5398,38 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46095.32446537037</v>
+        <v>46095.40024378472</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46095.32563423611</v>
+        <v>46095.40782453704</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>nc75327222</t>
+          <t>tx2026fcxdxl</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-122.813163757324</v>
+        <v>-104.319</v>
       </c>
       <c r="C125" t="n">
-        <v>38.8216667175293</v>
+        <v>31.649</v>
       </c>
       <c r="D125" t="n">
-        <v>2.85999989509583</v>
+        <v>4.1032</v>
       </c>
       <c r="E125" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>M 1.4 - 7 km NW of The Geysers, CA</t>
+          <t>M 1.9 - 58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>7 km NW of The Geysers, CA</t>
+          <t>58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5438,38 +5438,38 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46095.30817083333</v>
+        <v>46095.39530927083</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46095.35232532407</v>
+        <v>46095.39790074074</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>aka2026fcsvoz</t>
+          <t>tx2026fcxdjs</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-156.864</v>
+        <v>-104.363</v>
       </c>
       <c r="C126" t="n">
-        <v>57.941</v>
+        <v>31.593</v>
       </c>
       <c r="D126" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>M 1.3 - 42 km SE of Egegik, Alaska</t>
+          <t>M 1.6 - 62 km WNW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>42 km SE of Egegik, Alaska</t>
+          <t>62 km WNW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5478,38 +5478,38 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46095.30480278935</v>
+        <v>46095.39488246528</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46095.30609518519</v>
+        <v>46095.41727866898</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>hv74917327</t>
+          <t>hv74917352</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-155.509170532227</v>
+        <v>-155.063003540039</v>
       </c>
       <c r="C127" t="n">
-        <v>19.1896667480469</v>
+        <v>19.3636665344238</v>
       </c>
       <c r="D127" t="n">
-        <v>27.75</v>
+        <v>6.82999992370605</v>
       </c>
       <c r="E127" t="n">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>M 2.4 - 3 km WSW of Pāhala, Hawaii</t>
+          <t>M 1.8 - 13 km SE of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>3 km WSW of Pāhala, Hawaii</t>
+          <t>13 km SE of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5518,38 +5518,38 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46095.30339525463</v>
+        <v>46095.38912592593</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46095.30639085648</v>
+        <v>46095.39156377315</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>hv74917322</t>
+          <t>nn00912616</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-155.383666992188</v>
+        <v>-117.1065</v>
       </c>
       <c r="C128" t="n">
-        <v>19.2728328704834</v>
+        <v>37.2155</v>
       </c>
       <c r="D128" t="n">
-        <v>30.5599994659424</v>
+        <v>0.03</v>
       </c>
       <c r="E128" t="n">
-        <v>2.05</v>
+        <v>1.31</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>M 2.1 - 12 km NE of Pāhala, Hawaii</t>
+          <t>M 1.3 - 45 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>12 km NE of Pāhala, Hawaii</t>
+          <t>45 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5558,38 +5558,38 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46095.29624560185</v>
+        <v>46095.38704399305</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46095.29871585648</v>
+        <v>46095.38848982639</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>tx2026fcsawu</t>
+          <t>nc75327232</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-104.414</v>
+        <v>-121.320503234863</v>
       </c>
       <c r="C129" t="n">
-        <v>31.654</v>
+        <v>36.6573333740234</v>
       </c>
       <c r="D129" t="n">
-        <v>5.7571</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="E129" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>M 1.6 - 57 km S of Whites City, New Mexico</t>
+          <t>M 1.7 - 15 km S of Tres Pinos, CA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>57 km S of Whites City, New Mexico</t>
+          <t>15 km S of Tres Pinos, CA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5598,38 +5598,38 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46095.28811275463</v>
+        <v>46095.38549236111</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46095.29004396991</v>
+        <v>46095.40788662037</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>aka2026fcsapu</t>
+          <t>aka2026fcwnpr</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-147.001</v>
+        <v>-156.341</v>
       </c>
       <c r="C130" t="n">
-        <v>61.201</v>
+        <v>56.513</v>
       </c>
       <c r="D130" t="n">
-        <v>6.6</v>
+        <v>62.7</v>
       </c>
       <c r="E130" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>M 1.4 - 35 km WNW of Valdez, Alaska</t>
+          <t>M 3.3 - 128 km SSE of Ugashik, Alaska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>35 km WNW of Valdez, Alaska</t>
+          <t>128 km SSE of Ugashik, Alaska</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5638,38 +5638,38 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46095.28789450231</v>
+        <v>46095.38220442129</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46095.28883819444</v>
+        <v>46095.42112314815</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>nc75327212</t>
+          <t>aka2026fcwkyb</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-120.100997924805</v>
+        <v>-152.224</v>
       </c>
       <c r="C131" t="n">
-        <v>36.1946678161621</v>
+        <v>59.653</v>
       </c>
       <c r="D131" t="n">
-        <v>8.72999954223633</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>M 1.8 - 1 km S of Huron, CA</t>
+          <t>M 2.9 - 26 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1 km S of Huron, CA</t>
+          <t>26 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5678,38 +5678,38 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46095.28691342592</v>
+        <v>46095.38009972222</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46095.33843475694</v>
+        <v>46095.41820648148</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tx2026fcrrur</t>
+          <t>ok2026fcfu</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-101.926</v>
+        <v>-98.21438599</v>
       </c>
       <c r="C132" t="n">
-        <v>32.102</v>
+        <v>35.43252182</v>
       </c>
       <c r="D132" t="n">
-        <v>3.7297</v>
+        <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>M 1.4 - 13 km WSW of Stanton, Texas</t>
+          <t>M 2.1 - 13 km ESE of Hinton, Oklahoma</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>13 km ESE of Hinton, Oklahoma</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5718,38 +5718,38 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46095.28321513889</v>
+        <v>46095.37014696759</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46095.47412729167</v>
+        <v>46095.37120069445</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>aka2026fcrocu</t>
+          <t>aka2026fcvpaw</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-150.457</v>
+        <v>-150.883</v>
       </c>
       <c r="C133" t="n">
-        <v>63.275</v>
+        <v>61.959</v>
       </c>
       <c r="D133" t="n">
-        <v>129.2</v>
+        <v>0.7</v>
       </c>
       <c r="E133" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>M 2.2 - 69 km ESE of Denali National Park, Alaska</t>
+          <t>M 1.6 - 27 km E of Skwentna, Alaska</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>69 km ESE of Denali National Park, Alaska</t>
+          <t>27 km E of Skwentna, Alaska</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5758,38 +5758,38 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46095.27783107639</v>
+        <v>46095.36237780093</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46095.28106825231</v>
+        <v>46095.36346644676</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tx2026fcrdwa</t>
+          <t>hv74917342</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-104.39</v>
+        <v>-155.488494873047</v>
       </c>
       <c r="C134" t="n">
-        <v>31.669</v>
+        <v>19.1765003204346</v>
       </c>
       <c r="D134" t="n">
-        <v>6.8689</v>
+        <v>27.2299995422363</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>M 2.0 - 56 km S of Whites City, New Mexico</t>
+          <t>M 2.4 - 3 km SSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>56 km S of Whites City, New Mexico</t>
+          <t>3 km SSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5798,38 +5798,38 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46095.26955541666</v>
+        <v>46095.3602056713</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46095.98431269676</v>
+        <v>46095.36287916666</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>pr71509843</t>
+          <t>hv74917337</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-68.2081666666667</v>
+        <v>-155.494003295898</v>
       </c>
       <c r="C135" t="n">
-        <v>17.9796666666667</v>
+        <v>19.1691665649414</v>
       </c>
       <c r="D135" t="n">
-        <v>72.7</v>
+        <v>24.0799999237061</v>
       </c>
       <c r="E135" t="n">
-        <v>3.24</v>
+        <v>1.93</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>M 3.2 - 61 km SE of Boca de Yuma, Dominican Republic</t>
+          <t>M 1.9 - 4 km SSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>61 km SE of Boca de Yuma, Dominican Republic</t>
+          <t>4 km SSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5838,38 +5838,38 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46095.26694097222</v>
+        <v>46095.35828587963</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46095.28683090278</v>
+        <v>46095.360790625</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>tx2026fcrabk</t>
+          <t>aka2026fcvjoi</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-101.931</v>
+        <v>-149.83</v>
       </c>
       <c r="C136" t="n">
-        <v>32.103</v>
+        <v>64.30800000000001</v>
       </c>
       <c r="D136" t="n">
-        <v>3.7555</v>
+        <v>5</v>
       </c>
       <c r="E136" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>M 1.6 - 13 km WSW of Stanton, Texas</t>
+          <t>M 1.3 - 31 km W of Anderson, Alaska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>31 km W of Anderson, Alaska</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5878,38 +5878,38 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46095.26650071759</v>
+        <v>46095.35795271991</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46095.47247458333</v>
+        <v>46095.35929912037</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tx2026fcqynw</t>
+          <t>us6000sg9g</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-101.925</v>
+        <v>-25.6013</v>
       </c>
       <c r="C137" t="n">
-        <v>32.105</v>
+        <v>-58.7858</v>
       </c>
       <c r="D137" t="n">
-        <v>4.2234</v>
+        <v>73.994</v>
       </c>
       <c r="E137" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>M 2.4 - 13 km WSW of Stanton, Texas</t>
+          <t>M 5.2 - South Sandwich Islands region</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>South Sandwich Islands region</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5918,38 +5918,38 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46095.26526702546</v>
+        <v>46095.35739234954</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46095.47310884259</v>
+        <v>46095.37358842593</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>us6000sg8q</t>
+          <t>ci41204079</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-9.5571</v>
+        <v>-118.0855</v>
       </c>
       <c r="C138" t="n">
-        <v>-47.4228</v>
+        <v>35.3303333333333</v>
       </c>
       <c r="D138" t="n">
-        <v>10</v>
+        <v>7.19</v>
       </c>
       <c r="E138" t="n">
-        <v>5.1</v>
+        <v>1.16</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>M 5.1 - southern Mid-Atlantic Ridge</t>
+          <t>M 1.2 - 24 km NNW of California City, CA</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>southern Mid-Atlantic Ridge</t>
+          <t>24 km NNW of California City, CA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5958,38 +5958,38 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46095.26202418981</v>
+        <v>46095.35599143519</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46095.27231527778</v>
+        <v>46095.35835270833</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>tx2026fcqovv</t>
+          <t>nn00912612</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-100.549</v>
+        <v>-117.1191</v>
       </c>
       <c r="C139" t="n">
-        <v>32.794</v>
+        <v>37.2198</v>
       </c>
       <c r="D139" t="n">
-        <v>1.5277</v>
+        <v>0.0008</v>
       </c>
       <c r="E139" t="n">
-        <v>2.4</v>
+        <v>1.17</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>M 2.4 - 10 km SW of Rotan, Texas</t>
+          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>10 km SW of Rotan, Texas</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5998,38 +5998,38 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46095.25745070602</v>
+        <v>46095.35582130787</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46095.47303950231</v>
+        <v>46095.35709960648</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>tx2026fcqonn</t>
+          <t>nn00912609</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-100.55</v>
+        <v>-116.4921</v>
       </c>
       <c r="C140" t="n">
-        <v>32.793</v>
+        <v>38.467</v>
       </c>
       <c r="D140" t="n">
-        <v>2.2403</v>
+        <v>1.6026</v>
       </c>
       <c r="E140" t="n">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>M 2.4 - 10 km SW of Rotan, Texas</t>
+          <t>M 1.7 - 78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>10 km SW of Rotan, Texas</t>
+          <t>78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6038,38 +6038,38 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46095.25744922454</v>
+        <v>46095.35160628472</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46095.29300043981</v>
+        <v>46095.35341947916</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>nc75327197</t>
+          <t>ci41204071</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-122.781997680664</v>
+        <v>-117.079666666667</v>
       </c>
       <c r="C141" t="n">
-        <v>38.8363342285156</v>
+        <v>34.021</v>
       </c>
       <c r="D141" t="n">
-        <v>1.54999995231628</v>
+        <v>18.33</v>
       </c>
       <c r="E141" t="n">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>M 1.1 - 5 km WNW of Cobb, CA</t>
+          <t>M 1.0 - 4 km WSW of Yucaipa, CA</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>5 km WNW of Cobb, CA</t>
+          <t>4 km WSW of Yucaipa, CA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6078,38 +6078,38 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46095.25136446759</v>
+        <v>46095.35113958333</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46095.25248814815</v>
+        <v>46095.35350167824</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tx2026fcpyba</t>
+          <t>nn00912607</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-104.019</v>
+        <v>-117.1176</v>
       </c>
       <c r="C142" t="n">
-        <v>31.83</v>
+        <v>37.2157</v>
       </c>
       <c r="D142" t="n">
-        <v>16.8913</v>
+        <v>1.6995</v>
       </c>
       <c r="E142" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>M 1.6 - 42 km WNW of Mentone, Texas</t>
+          <t>M 1.2 - 46 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>42 km WNW of Mentone, Texas</t>
+          <t>46 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6118,38 +6118,38 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46095.24523908565</v>
+        <v>46095.35093659722</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46095.25056459491</v>
+        <v>46095.3522947338</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>se60505173</t>
+          <t>tx2026fcuwli</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-78.8535</v>
+        <v>-102.216</v>
       </c>
       <c r="C143" t="n">
-        <v>37.4065</v>
+        <v>32.123</v>
       </c>
       <c r="D143" t="n">
-        <v>3.1</v>
+        <v>7.1155</v>
       </c>
       <c r="E143" t="n">
-        <v>2.07</v>
+        <v>1.1</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>M 2.1 - 6 km NNW of Appomattox, Virginia</t>
+          <t>M 1.1 - 19 km NW of Midland, Texas</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>6 km NNW of Appomattox, Virginia</t>
+          <t>19 km NW of Midland, Texas</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6158,38 +6158,38 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46095.24491516204</v>
+        <v>46095.34735415509</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46095.56136655092</v>
+        <v>46095.47295694445</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tx2026fcpyki</t>
+          <t>aka2026fcutja</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-100.557</v>
+        <v>-151.07</v>
       </c>
       <c r="C144" t="n">
-        <v>32.791</v>
+        <v>63.548</v>
       </c>
       <c r="D144" t="n">
-        <v>4.5654</v>
+        <v>5</v>
       </c>
       <c r="E144" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>M 2.9 - 10 km SW of Rotan, Texas</t>
+          <t>M 1.4 - 32 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10 km SW of Rotan, Texas</t>
+          <t>32 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6198,38 +6198,38 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46095.24420026621</v>
+        <v>46095.34490104167</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46095.25962405092</v>
+        <v>46095.34610518518</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>nn00912597</t>
+          <t>ci41204047</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-117.1175</v>
+        <v>-118.362</v>
       </c>
       <c r="C145" t="n">
-        <v>37.2164</v>
+        <v>34.1451666666667</v>
       </c>
       <c r="D145" t="n">
-        <v>0.0444</v>
+        <v>15.54</v>
       </c>
       <c r="E145" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>M 1.2 - 46 km NW of Beatty, Nevada</t>
+          <t>M 1.0 - 1 km NW of Universal City, CA</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>46 km NW of Beatty, Nevada</t>
+          <t>1 km NW of Universal City, CA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6238,38 +6238,38 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46095.23686648148</v>
+        <v>46095.34305972223</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46095.23832854167</v>
+        <v>46095.34540800926</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>nn00912595</t>
+          <t>pr71509853</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-117.118</v>
+        <v>-67.3061666666667</v>
       </c>
       <c r="C146" t="n">
-        <v>37.2216</v>
+        <v>18.3425</v>
       </c>
       <c r="D146" t="n">
-        <v>0.0643</v>
+        <v>22.48</v>
       </c>
       <c r="E146" t="n">
-        <v>1.23</v>
+        <v>2.43</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
+          <t>M 2.4 - 5 km W of Rincón, Puerto Rico</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>5 km W of Rincón, Puerto Rico</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6278,38 +6278,38 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46095.23179822916</v>
+        <v>46095.34218113426</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46095.23326519676</v>
+        <v>46095.35034837963</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>us6000sg8i</t>
+          <t>aka2026fcukuz</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>176.4435</v>
+        <v>-152.363</v>
       </c>
       <c r="C147" t="n">
-        <v>52.0909</v>
+        <v>59.584</v>
       </c>
       <c r="D147" t="n">
-        <v>10</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E147" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>M 4.4 - 236 km ESE of Attu Station, Alaska</t>
+          <t>M 1.6 - 35 km NW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>236 km ESE of Attu Station, Alaska</t>
+          <t>35 km NW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6318,38 +6318,38 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>46095.22228541667</v>
+        <v>46095.3380100463</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46095.39254373842</v>
+        <v>46095.33962047454</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>nc75327172</t>
+          <t>uw62234461</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-121.30883026123</v>
+        <v>-121.969</v>
       </c>
       <c r="C148" t="n">
-        <v>36.6568336486816</v>
+        <v>47.00283333333334</v>
       </c>
       <c r="D148" t="n">
-        <v>4.17000007629395</v>
+        <v>14.67</v>
       </c>
       <c r="E148" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>M 1.8 - 15 km S of Tres Pinos, CA</t>
+          <t>M 1.8 - 10 km SE of Carbonado, Washington</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>15 km S of Tres Pinos, CA</t>
+          <t>10 km SE of Carbonado, Washington</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6358,38 +6358,38 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>46095.21819664352</v>
+        <v>46095.32948564815</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46095.26552178241</v>
+        <v>46095.35692152777</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tx2026fcontc</t>
+          <t>aka2026fcttzo</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-104.403</v>
+        <v>-150.606</v>
       </c>
       <c r="C149" t="n">
-        <v>31.657</v>
+        <v>62.796</v>
       </c>
       <c r="D149" t="n">
-        <v>5.177</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E149" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>M 2.1 - 57 km S of Whites City, New Mexico</t>
+          <t>M 1.6 - 34 km NNE of Petersville, Alaska</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>57 km S of Whites City, New Mexico</t>
+          <t>34 km NNE of Petersville, Alaska</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6398,38 +6398,38 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>46095.21465760416</v>
+        <v>46095.32446537037</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46095.92457752315</v>
+        <v>46095.32563423611</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>aka2026fcolgu</t>
+          <t>nc75327222</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-153.226</v>
+        <v>-122.813163757324</v>
       </c>
       <c r="C150" t="n">
-        <v>59.591</v>
+        <v>38.8216667175293</v>
       </c>
       <c r="D150" t="n">
-        <v>109.6</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="E150" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>M 1.3 - 54 km ESE of Pedro Bay, Alaska</t>
+          <t>M 1.4 - 7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>54 km ESE of Pedro Bay, Alaska</t>
+          <t>7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6438,38 +6438,38 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>46095.21267469908</v>
+        <v>46095.30817083333</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46095.21408049769</v>
+        <v>46095.35232532407</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>us6000sg8b</t>
+          <t>aka2026fcsvoz</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-90.6785</v>
+        <v>-156.864</v>
       </c>
       <c r="C151" t="n">
-        <v>13.7887</v>
+        <v>57.941</v>
       </c>
       <c r="D151" t="n">
-        <v>77.887</v>
+        <v>5.1</v>
       </c>
       <c r="E151" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>M 4.6 - 16 km S of Iztapa, Guatemala</t>
+          <t>M 1.3 - 42 km SE of Egegik, Alaska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>16 km S of Iztapa, Guatemala</t>
+          <t>42 km SE of Egegik, Alaska</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6478,38 +6478,38 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>46095.21222631945</v>
+        <v>46095.30480278935</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46095.26483412037</v>
+        <v>46095.30609518519</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ci41204015</t>
+          <t>hv74917327</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-117.714</v>
+        <v>-155.509170532227</v>
       </c>
       <c r="C152" t="n">
-        <v>35.8901666666667</v>
+        <v>19.1896667480469</v>
       </c>
       <c r="D152" t="n">
-        <v>6.02</v>
+        <v>27.75</v>
       </c>
       <c r="E152" t="n">
-        <v>1.19</v>
+        <v>2.43</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>M 1.2 - 18 km ESE of Little Lake, CA</t>
+          <t>M 2.4 - 3 km WSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>18 km ESE of Little Lake, CA</t>
+          <t>3 km WSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6518,38 +6518,38 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>46095.20766203704</v>
+        <v>46095.30339525463</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46095.21004755787</v>
+        <v>46095.30639085648</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ci41204007</t>
+          <t>hv74917322</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-116.802666666667</v>
+        <v>-155.383666992188</v>
       </c>
       <c r="C153" t="n">
-        <v>33.2805</v>
+        <v>19.2728328704834</v>
       </c>
       <c r="D153" t="n">
-        <v>12.26</v>
+        <v>30.5599994659424</v>
       </c>
       <c r="E153" t="n">
-        <v>1.06</v>
+        <v>2.05</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km NW of Lake Henshaw, CA</t>
+          <t>M 2.1 - 12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>6 km NW of Lake Henshaw, CA</t>
+          <t>12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6558,38 +6558,38 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>46095.20175289352</v>
+        <v>46095.29624560185</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46095.20411341435</v>
+        <v>46095.29871585648</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>nn00912593</t>
+          <t>tx2026fcsawu</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-117.1141</v>
+        <v>-104.414</v>
       </c>
       <c r="C154" t="n">
-        <v>37.2225</v>
+        <v>31.654</v>
       </c>
       <c r="D154" t="n">
-        <v>0.0456</v>
+        <v>5.7571</v>
       </c>
       <c r="E154" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
+          <t>M 1.6 - 57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6598,38 +6598,38 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>46095.20134099537</v>
+        <v>46095.28811275463</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46095.20256013889</v>
+        <v>46095.29004396991</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>nc75327167</t>
+          <t>aka2026fcsapu</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-122.810997009277</v>
+        <v>-147.001</v>
       </c>
       <c r="C155" t="n">
-        <v>38.8401679992676</v>
+        <v>61.201</v>
       </c>
       <c r="D155" t="n">
-        <v>1.67999994754791</v>
+        <v>6.6</v>
       </c>
       <c r="E155" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
+          <t>M 1.4 - 35 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8 km WNW of Cobb, CA</t>
+          <t>35 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6638,38 +6638,38 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>46095.19798460648</v>
+        <v>46095.28789450231</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46095.23077265047</v>
+        <v>46095.28883819444</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>aka2026fcnmeg</t>
+          <t>nc75327212</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-149.251</v>
+        <v>-120.100997924805</v>
       </c>
       <c r="C156" t="n">
-        <v>63.818</v>
+        <v>36.1946678161621</v>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>8.72999954223633</v>
       </c>
       <c r="E156" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>M 1.5 - 14 km WSW of Healy, Alaska</t>
+          <t>M 1.8 - 1 km S of Huron, CA</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>14 km WSW of Healy, Alaska</t>
+          <t>1 km S of Huron, CA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6678,38 +6678,38 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>46095.19244901621</v>
+        <v>46095.28691342592</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46095.19378540509</v>
+        <v>46095.33843475694</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>nc75327162</t>
+          <t>tx2026fcrrur</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-122.818496704102</v>
+        <v>-101.926</v>
       </c>
       <c r="C157" t="n">
-        <v>38.8294982910156</v>
+        <v>32.102</v>
       </c>
       <c r="D157" t="n">
-        <v>1.77999997138977</v>
+        <v>3.7297</v>
       </c>
       <c r="E157" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km NW of The Geysers, CA</t>
+          <t>M 1.4 - 13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8 km NW of The Geysers, CA</t>
+          <t>13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6718,38 +6718,38 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>46095.18678217592</v>
+        <v>46095.28321513889</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46095.20303782407</v>
+        <v>46095.47412729167</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>pr71509833</t>
+          <t>aka2026fcrocu</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-63.9228333333333</v>
+        <v>-150.457</v>
       </c>
       <c r="C158" t="n">
-        <v>18.5633333333333</v>
+        <v>63.275</v>
       </c>
       <c r="D158" t="n">
-        <v>7.9</v>
+        <v>129.2</v>
       </c>
       <c r="E158" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>M 3.4 - 95 km ENE of Cruz Bay, U.S. Virgin Islands</t>
+          <t>M 2.2 - 69 km ESE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>95 km ENE of Cruz Bay, U.S. Virgin Islands</t>
+          <t>69 km ESE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6758,38 +6758,38 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>46095.18653703704</v>
+        <v>46095.27783107639</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46095.90381990741</v>
+        <v>46095.28106825231</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>nc75327157</t>
+          <t>tx2026fcrdwa</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-122.810333251953</v>
+        <v>-104.39</v>
       </c>
       <c r="C159" t="n">
-        <v>38.8406677246094</v>
+        <v>31.669</v>
       </c>
       <c r="D159" t="n">
-        <v>1.82000005245209</v>
+        <v>6.8689</v>
       </c>
       <c r="E159" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>M 1.5 - 8 km WNW of Cobb, CA</t>
+          <t>M 2.0 - 56 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>8 km WNW of Cobb, CA</t>
+          <t>56 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6798,38 +6798,38 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>46095.18409155092</v>
+        <v>46095.26955541666</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46095.21343270833</v>
+        <v>46095.98431269676</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>aka2026fcnayu</t>
+          <t>pr71509843</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-155.647</v>
+        <v>-68.2081666666667</v>
       </c>
       <c r="C160" t="n">
-        <v>57.365</v>
+        <v>17.9796666666667</v>
       </c>
       <c r="D160" t="n">
-        <v>65.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E160" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>M 2.0 - 75 km WSW of Karluk, Alaska</t>
+          <t>M 3.2 - 61 km SE of Boca de Yuma, Dominican Republic</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>75 km WSW of Karluk, Alaska</t>
+          <t>61 km SE of Boca de Yuma, Dominican Republic</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6838,38 +6838,38 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>46095.18333099537</v>
+        <v>46095.26694097222</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46095.18473165509</v>
+        <v>46095.28683090278</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ci41203999</t>
+          <t>tx2026fcrabk</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-117.811166666667</v>
+        <v>-101.931</v>
       </c>
       <c r="C161" t="n">
-        <v>35.3465</v>
+        <v>32.103</v>
       </c>
       <c r="D161" t="n">
-        <v>8.34</v>
+        <v>3.7555</v>
       </c>
       <c r="E161" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>M 1.4 - 16 km W of Johannesburg, CA</t>
+          <t>M 1.6 - 13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>16 km W of Johannesburg, CA</t>
+          <t>13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6878,38 +6878,38 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>46095.18292777778</v>
+        <v>46095.26650071759</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46095.18525748843</v>
+        <v>46095.47247458333</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>pr2026073001</t>
+          <t>tx2026fcqynw</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-67.8205</v>
+        <v>-101.925</v>
       </c>
       <c r="C162" t="n">
-        <v>18.2136</v>
+        <v>32.105</v>
       </c>
       <c r="D162" t="n">
-        <v>127</v>
+        <v>4.2234</v>
       </c>
       <c r="E162" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>M 3.5 - 61 km WSW of Stella, Puerto Rico</t>
+          <t>M 2.4 - 13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>61 km WSW of Stella, Puerto Rico</t>
+          <t>13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6918,38 +6918,38 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>46095.18075243056</v>
+        <v>46095.26526702546</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46095.22414583333</v>
+        <v>46096.07358628472</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>pr2026073000</t>
+          <t>us6000sg8q</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-68.9123</v>
+        <v>-9.5571</v>
       </c>
       <c r="C163" t="n">
-        <v>18.4235</v>
+        <v>-47.4228</v>
       </c>
       <c r="D163" t="n">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="E163" t="n">
-        <v>3.81</v>
+        <v>5.1</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>M 3.8 - 6 km E of La Romana, Dominican Republic</t>
+          <t>M 5.1 - southern Mid-Atlantic Ridge</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>6 km E of La Romana, Dominican Republic</t>
+          <t>southern Mid-Atlantic Ridge</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6958,38 +6958,38 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>46095.17578113426</v>
+        <v>46095.26202418981</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46095.21100451389</v>
+        <v>46095.27231527778</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nn00912592</t>
+          <t>tx2026fcqovv</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-117.2731</v>
+        <v>-100.549</v>
       </c>
       <c r="C164" t="n">
-        <v>37.3542</v>
+        <v>32.794</v>
       </c>
       <c r="D164" t="n">
-        <v>3.3783</v>
+        <v>1.5277</v>
       </c>
       <c r="E164" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>M 1.1 - 39 km S of Goldfield, Nevada</t>
+          <t>M 2.4 - 10 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>39 km S of Goldfield, Nevada</t>
+          <t>10 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6998,38 +6998,38 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>46095.16339071759</v>
+        <v>46095.25745070602</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46095.16527454861</v>
+        <v>46095.47303950231</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tx2026fclpib</t>
+          <t>tx2026fcqonn</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-104.392</v>
+        <v>-100.55</v>
       </c>
       <c r="C165" t="n">
-        <v>31.652</v>
+        <v>32.793</v>
       </c>
       <c r="D165" t="n">
-        <v>3.3569</v>
+        <v>2.2403</v>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>M 2.0 - 58 km S of Whites City, New Mexico</t>
+          <t>M 2.4 - 10 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>10 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7038,38 +7038,38 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>46095.15319673611</v>
+        <v>46095.25744922454</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46095.99235391204</v>
+        <v>46095.29300043981</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>tx2026fcllfg</t>
+          <t>nc75327197</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-104.412</v>
+        <v>-122.781997680664</v>
       </c>
       <c r="C166" t="n">
-        <v>31.648</v>
+        <v>38.8363342285156</v>
       </c>
       <c r="D166" t="n">
-        <v>6.8176</v>
+        <v>1.54999995231628</v>
       </c>
       <c r="E166" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>M 1.8 - 58 km S of Whites City, New Mexico</t>
+          <t>M 1.1 - 5 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>5 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7078,38 +7078,38 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>46095.14974444445</v>
+        <v>46095.25136446759</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46095.97453802083</v>
+        <v>46095.25248814815</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ok2026fbvf</t>
+          <t>tx2026fcpyba</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-98.19416667</v>
+        <v>-104.019</v>
       </c>
       <c r="C167" t="n">
-        <v>35.39916667</v>
+        <v>31.83</v>
       </c>
       <c r="D167" t="n">
-        <v>6.1</v>
+        <v>16.8913</v>
       </c>
       <c r="E167" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>M 1.6 - 16 km ENE of Lookeba, Oklahoma</t>
+          <t>M 1.6 - 42 km WNW of Mentone, Texas</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>16 km ENE of Lookeba, Oklahoma</t>
+          <t>42 km WNW of Mentone, Texas</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7118,38 +7118,38 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>46095.14736377315</v>
+        <v>46095.24523908565</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46095.29280497685</v>
+        <v>46095.25056459491</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>tx2026fclhuu</t>
+          <t>se60505173</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-104.398</v>
+        <v>-78.8535</v>
       </c>
       <c r="C168" t="n">
-        <v>31.652</v>
+        <v>37.4065</v>
       </c>
       <c r="D168" t="n">
-        <v>5.0232</v>
+        <v>3.1</v>
       </c>
       <c r="E168" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>M 1.7 - 58 km S of Whites City, New Mexico</t>
+          <t>M 2.1 - 6 km NNW of Appomattox, Virginia</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>6 km NNW of Appomattox, Virginia</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7158,38 +7158,38 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>46095.14701486111</v>
+        <v>46095.24491516204</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46096.00719164352</v>
+        <v>46095.56136655092</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>nn00912589</t>
+          <t>tx2026fcpyki</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-117.1153</v>
+        <v>-100.557</v>
       </c>
       <c r="C169" t="n">
-        <v>37.2316</v>
+        <v>32.791</v>
       </c>
       <c r="D169" t="n">
-        <v>0.0045</v>
+        <v>4.5654</v>
       </c>
       <c r="E169" t="n">
-        <v>0.97</v>
+        <v>2.9</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>M 1.0 - 47 km NW of Beatty, Nevada</t>
+          <t>M 2.9 - 10 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>10 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7198,38 +7198,38 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>46095.14693564815</v>
+        <v>46095.24420026621</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46095.14830303241</v>
+        <v>46095.25962405092</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>nn00912587</t>
+          <t>nn00912597</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-116.5049</v>
+        <v>-117.1175</v>
       </c>
       <c r="C170" t="n">
-        <v>38.4311</v>
+        <v>37.2164</v>
       </c>
       <c r="D170" t="n">
-        <v>0.0319</v>
+        <v>0.0444</v>
       </c>
       <c r="E170" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>M 1.5 - 75 km ENE of Tonopah, Nevada</t>
+          <t>M 1.2 - 46 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>75 km ENE of Tonopah, Nevada</t>
+          <t>46 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7238,38 +7238,38 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>46095.14104785879</v>
+        <v>46095.23686648148</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46095.14377274305</v>
+        <v>46095.23832854167</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>hv74917307</t>
+          <t>nn00912595</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-155.503326416016</v>
+        <v>-117.118</v>
       </c>
       <c r="C171" t="n">
-        <v>19.1646671295166</v>
+        <v>37.2216</v>
       </c>
       <c r="D171" t="n">
-        <v>26.5599994659424</v>
+        <v>0.0643</v>
       </c>
       <c r="E171" t="n">
-        <v>2.04</v>
+        <v>1.23</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>M 2.0 - 4 km SSW of Pāhala, Hawaii</t>
+          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>4 km SSW of Pāhala, Hawaii</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7278,38 +7278,38 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>46095.13848483796</v>
+        <v>46095.23179822916</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46095.14087233796</v>
+        <v>46095.23326519676</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>nn00912585</t>
+          <t>us6000sg8i</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-117.2845</v>
+        <v>176.4435</v>
       </c>
       <c r="C172" t="n">
-        <v>37.2589</v>
+        <v>52.0909</v>
       </c>
       <c r="D172" t="n">
-        <v>0.063</v>
+        <v>10</v>
       </c>
       <c r="E172" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>M 1.1 - 50 km S of Goldfield, Nevada</t>
+          <t>M 4.4 - 236 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>50 km S of Goldfield, Nevada</t>
+          <t>236 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7318,38 +7318,38 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>46095.13453627315</v>
+        <v>46095.22228541667</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46095.13600027778</v>
+        <v>46095.39254373842</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>tx2026fcknod</t>
+          <t>nc75327172</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-103.939</v>
+        <v>-121.30883026123</v>
       </c>
       <c r="C173" t="n">
-        <v>31.434</v>
+        <v>36.6568336486816</v>
       </c>
       <c r="D173" t="n">
-        <v>5.9973</v>
+        <v>4.17000007629395</v>
       </c>
       <c r="E173" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>M 1.7 - 19 km NW of Toyah, Texas</t>
+          <t>M 1.8 - 15 km S of Tres Pinos, CA</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>19 km NW of Toyah, Texas</t>
+          <t>15 km S of Tres Pinos, CA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7358,38 +7358,38 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>46095.13070553241</v>
+        <v>46095.21819664352</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>46095.16008307871</v>
+        <v>46095.26552178241</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>us6000sg7q</t>
+          <t>tx2026fcontc</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>160.3337</v>
+        <v>-104.403</v>
       </c>
       <c r="C174" t="n">
-        <v>52.2825</v>
+        <v>31.657</v>
       </c>
       <c r="D174" t="n">
-        <v>35</v>
+        <v>5.177</v>
       </c>
       <c r="E174" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>M 4.5 - 144 km SE of Petropavlovsk-Kamchatsky, Russia</t>
+          <t>M 2.1 - 57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>144 km SE of Petropavlovsk-Kamchatsky, Russia</t>
+          <t>57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7398,38 +7398,38 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>46095.12654711805</v>
+        <v>46095.21465760416</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>46095.14320648148</v>
+        <v>46095.92457752315</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>nc75327137</t>
+          <t>aka2026fcolgu</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-120.770332336426</v>
+        <v>-153.226</v>
       </c>
       <c r="C175" t="n">
-        <v>36.1855010986328</v>
+        <v>59.591</v>
       </c>
       <c r="D175" t="n">
-        <v>6.71000003814697</v>
+        <v>109.6</v>
       </c>
       <c r="E175" t="n">
-        <v>1.98</v>
+        <v>1.3</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>M 2.0 - 22 km NNE of San Ardo, CA</t>
+          <t>M 1.3 - 54 km ESE of Pedro Bay, Alaska</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>22 km NNE of San Ardo, CA</t>
+          <t>54 km ESE of Pedro Bay, Alaska</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7438,38 +7438,38 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>46095.12405856481</v>
+        <v>46095.21267469908</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>46095.19611577546</v>
+        <v>46095.21408049769</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>nc75327132</t>
+          <t>us6000sg8b</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-122.815498352051</v>
+        <v>-90.6785</v>
       </c>
       <c r="C176" t="n">
-        <v>38.8291664123535</v>
+        <v>13.7887</v>
       </c>
       <c r="D176" t="n">
-        <v>2.04999995231628</v>
+        <v>77.887</v>
       </c>
       <c r="E176" t="n">
-        <v>1.07</v>
+        <v>4.6</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>M 1.1 - 8 km NW of The Geysers, CA</t>
+          <t>M 4.6 - 16 km S of Iztapa, Guatemala</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>8 km NW of The Geysers, CA</t>
+          <t>16 km S of Iztapa, Guatemala</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7478,38 +7478,38 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>46095.11967384259</v>
+        <v>46095.21222631945</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>46095.13359721065</v>
+        <v>46095.26483412037</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pr71509808</t>
+          <t>ci41204015</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-66.9188333333333</v>
+        <v>-117.714</v>
       </c>
       <c r="C177" t="n">
-        <v>17.9806666666667</v>
+        <v>35.8901666666667</v>
       </c>
       <c r="D177" t="n">
-        <v>8.18</v>
+        <v>6.02</v>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
+        <v>1.19</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>M 2.0 - 0 km SSW of Fuig, Puerto Rico</t>
+          <t>M 1.2 - 18 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>0 km SSW of Fuig, Puerto Rico</t>
+          <t>18 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -7518,38 +7518,38 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>46095.11640509259</v>
+        <v>46095.20766203704</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>46095.14769837963</v>
+        <v>46095.21004755787</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>nc75327127</t>
+          <t>ci41204007</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>-122.81916809082</v>
+        <v>-116.802666666667</v>
       </c>
       <c r="C178" t="n">
-        <v>38.8326683044434</v>
+        <v>33.2805</v>
       </c>
       <c r="D178" t="n">
-        <v>1.85000002384186</v>
+        <v>12.26</v>
       </c>
       <c r="E178" t="n">
-        <v>1.63</v>
+        <v>1.06</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>M 1.6 - 8 km NW of The Geysers, CA</t>
+          <t>M 1.1 - 6 km NW of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>8 km NW of The Geysers, CA</t>
+          <t>6 km NW of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -7558,38 +7558,38 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>46095.10306076389</v>
+        <v>46095.20175289352</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>46095.17871800926</v>
+        <v>46095.20411341435</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>aka2026fcixqj</t>
+          <t>nn00912593</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-151.45</v>
+        <v>-117.1141</v>
       </c>
       <c r="C179" t="n">
-        <v>63.117</v>
+        <v>37.2225</v>
       </c>
       <c r="D179" t="n">
-        <v>5</v>
+        <v>0.0456</v>
       </c>
       <c r="E179" t="n">
-        <v>1.9</v>
+        <v>1.12</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>M 1.9 - 49 km SSE of Denali National Park, Alaska</t>
+          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>49 km SSE of Denali National Park, Alaska</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -7598,38 +7598,38 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>46095.09682642361</v>
+        <v>46095.20134099537</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>46095.09789428241</v>
+        <v>46095.20256013889</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ok2026fbsa</t>
+          <t>nc75327167</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-98.20116667000001</v>
+        <v>-122.810997009277</v>
       </c>
       <c r="C180" t="n">
-        <v>35.40133333</v>
+        <v>38.8401679992676</v>
       </c>
       <c r="D180" t="n">
-        <v>6.36</v>
+        <v>1.67999994754791</v>
       </c>
       <c r="E180" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>M 1.8 - 15 km ENE of Lookeba, Oklahoma</t>
+          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>15 km ENE of Lookeba, Oklahoma</t>
+          <t>8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -7638,38 +7638,38 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>46095.08015068287</v>
+        <v>46095.19798460648</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>46095.12401331018</v>
+        <v>46095.23077265047</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ok2026fbrj</t>
+          <t>aka2026fcnmeg</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-98.03187561</v>
+        <v>-149.251</v>
       </c>
       <c r="C181" t="n">
-        <v>35.62902451</v>
+        <v>63.818</v>
       </c>
       <c r="D181" t="n">
-        <v>2.793530703</v>
+        <v>5</v>
       </c>
       <c r="E181" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>M 2.4 - 8 km ENE of Calumet, Oklahoma</t>
+          <t>M 1.5 - 14 km WSW of Healy, Alaska</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>8 km ENE of Calumet, Oklahoma</t>
+          <t>14 km WSW of Healy, Alaska</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -7678,38 +7678,38 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>46095.06607994213</v>
+        <v>46095.19244901621</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>46095.06767915509</v>
+        <v>46095.19378540509</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>aka2026fchgeg</t>
+          <t>nc75327162</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-153.283</v>
+        <v>-122.818496704102</v>
       </c>
       <c r="C182" t="n">
-        <v>62.163</v>
+        <v>38.8294982910156</v>
       </c>
       <c r="D182" t="n">
-        <v>3.3</v>
+        <v>1.77999997138977</v>
       </c>
       <c r="E182" t="n">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>M 1.6 - 100 km W of Skwentna, Alaska</t>
+          <t>M 1.0 - 8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>100 km W of Skwentna, Alaska</t>
+          <t>8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7718,38 +7718,38 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>46095.06188758102</v>
+        <v>46095.18678217592</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>46095.06435961805</v>
+        <v>46095.20303782407</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>hv74917302</t>
+          <t>pr71509833</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>-155.504333496094</v>
+        <v>-63.9228333333333</v>
       </c>
       <c r="C183" t="n">
-        <v>19.1511669158936</v>
+        <v>18.5633333333333</v>
       </c>
       <c r="D183" t="n">
-        <v>28.3500003814697</v>
+        <v>7.9</v>
       </c>
       <c r="E183" t="n">
-        <v>1.84</v>
+        <v>3.4</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>M 1.8 - 6 km SSW of Pāhala, Hawaii</t>
+          <t>M 3.4 - 95 km ENE of Cruz Bay, U.S. Virgin Islands</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>6 km SSW of Pāhala, Hawaii</t>
+          <t>95 km ENE of Cruz Bay, U.S. Virgin Islands</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -7758,38 +7758,38 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>46095.06014675926</v>
+        <v>46095.18653703704</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>46095.06263472222</v>
+        <v>46095.90381990741</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>us6000sg7h</t>
+          <t>nc75327157</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>176.3811</v>
+        <v>-122.810333251953</v>
       </c>
       <c r="C184" t="n">
-        <v>52.1118</v>
+        <v>38.8406677246094</v>
       </c>
       <c r="D184" t="n">
-        <v>10</v>
+        <v>1.82000005245209</v>
       </c>
       <c r="E184" t="n">
-        <v>4.4</v>
+        <v>1.48</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>M 4.4 - 231 km ESE of Attu Station, Alaska</t>
+          <t>M 1.5 - 8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>231 km ESE of Attu Station, Alaska</t>
+          <t>8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -7798,38 +7798,38 @@
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>46095.05798885417</v>
+        <v>46095.18409155092</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>46095.385294375</v>
+        <v>46095.21343270833</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>tx2026fcgqmi</t>
+          <t>aka2026fcnayu</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-103.948</v>
+        <v>-155.647</v>
       </c>
       <c r="C185" t="n">
-        <v>31.428</v>
+        <v>57.365</v>
       </c>
       <c r="D185" t="n">
-        <v>3.5925</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E185" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>M 1.6 - 19 km NW of Toyah, Texas</t>
+          <t>M 2.0 - 75 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>19 km NW of Toyah, Texas</t>
+          <t>75 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -7838,38 +7838,38 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>46095.04946612268</v>
+        <v>46095.18333099537</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>46095.21348333333</v>
+        <v>46095.18473165509</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>tx2026fcgqbn</t>
+          <t>ci41203999</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-103.939</v>
+        <v>-117.811166666667</v>
       </c>
       <c r="C186" t="n">
-        <v>31.434</v>
+        <v>35.3465</v>
       </c>
       <c r="D186" t="n">
-        <v>6.0486</v>
+        <v>8.34</v>
       </c>
       <c r="E186" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>M 1.6 - 19 km NW of Toyah, Texas</t>
+          <t>M 1.4 - 16 km W of Johannesburg, CA</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>19 km NW of Toyah, Texas</t>
+          <t>16 km W of Johannesburg, CA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -7878,38 +7878,38 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>46095.04946038195</v>
+        <v>46095.18292777778</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>46095.07846991898</v>
+        <v>46095.18525748843</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>hv74917297</t>
+          <t>pr2026073001</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-155.35466003418</v>
+        <v>-67.8205</v>
       </c>
       <c r="C187" t="n">
-        <v>19.1316661834717</v>
+        <v>18.2136</v>
       </c>
       <c r="D187" t="n">
-        <v>27.6700000762939</v>
+        <v>127</v>
       </c>
       <c r="E187" t="n">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>M 1.9 - 15 km ESE of Pāhala, Hawaii</t>
+          <t>M 3.5 - 61 km WSW of Stella, Puerto Rico</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>15 km ESE of Pāhala, Hawaii</t>
+          <t>61 km WSW of Stella, Puerto Rico</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -7918,38 +7918,38 @@
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>46095.04813726852</v>
+        <v>46095.18075243056</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>46095.05063773148</v>
+        <v>46095.22414583333</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>hv74917292</t>
+          <t>pr2026073000</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-155.48616027832</v>
+        <v>-68.9123</v>
       </c>
       <c r="C188" t="n">
-        <v>19.1668338775635</v>
+        <v>18.4235</v>
       </c>
       <c r="D188" t="n">
-        <v>27.1599998474121</v>
+        <v>107</v>
       </c>
       <c r="E188" t="n">
-        <v>1.81</v>
+        <v>3.81</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>M 1.8 - 4 km S of Pāhala, Hawaii</t>
+          <t>M 3.8 - 6 km E of La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>4 km S of Pāhala, Hawaii</t>
+          <t>6 km E of La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -7958,370 +7958,10 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>46095.04537453704</v>
+        <v>46095.17578113426</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>46095.04784224537</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>nc75327102</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>-121.111167907715</v>
-      </c>
-      <c r="C189" t="n">
-        <v>36.5576667785645</v>
-      </c>
-      <c r="D189" t="n">
-        <v>5.57999992370605</v>
-      </c>
-      <c r="E189" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>M 1.0 - 4 km NE of Pinnacles, CA</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>4 km NE of Pinnacles, CA</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I189" s="2" t="n">
-        <v>46095.03916770833</v>
-      </c>
-      <c r="J189" s="2" t="n">
-        <v>46095.04090886574</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>aka2026fcgdon</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>-152.769</v>
-      </c>
-      <c r="C190" t="n">
-        <v>58.841</v>
-      </c>
-      <c r="D190" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="E190" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>M 1.5 - 75 km SW of Nanwalek, Alaska</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>75 km SW of Nanwalek, Alaska</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="n">
-        <v>46095.03883496528</v>
-      </c>
-      <c r="J190" s="2" t="n">
-        <v>46095.04032881944</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>tx2026fcgcjq</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>-104.132</v>
-      </c>
-      <c r="C191" t="n">
-        <v>31.547</v>
-      </c>
-      <c r="D191" t="n">
-        <v>8.0481</v>
-      </c>
-      <c r="E191" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>M 1.7 - 41 km NW of Toyah, Texas</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>41 km NW of Toyah, Texas</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="n">
-        <v>46095.03804181713</v>
-      </c>
-      <c r="J191" s="2" t="n">
-        <v>46095.14741609953</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>us6000sg7e</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>48.3657</v>
-      </c>
-      <c r="C192" t="n">
-        <v>32.5524</v>
-      </c>
-      <c r="D192" t="n">
-        <v>10</v>
-      </c>
-      <c r="E192" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>M 4.3 - 24 km NNW of Shahrak-e Kūlūrī, Iran</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>24 km NNW of Shahrak-e Kūlūrī, Iran</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="n">
-        <v>46095.03794171297</v>
-      </c>
-      <c r="J192" s="2" t="n">
-        <v>46095.17872731481</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>ci41203935</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>-116.392666666667</v>
-      </c>
-      <c r="C193" t="n">
-        <v>33.3568333333333</v>
-      </c>
-      <c r="D193" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="E193" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>M 1.2 - 11 km N of Borrego Springs, CA</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>11 km N of Borrego Springs, CA</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="n">
-        <v>46095.03674907408</v>
-      </c>
-      <c r="J193" s="2" t="n">
-        <v>46095.04438761574</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>hv74917287</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>-155.584167480469</v>
-      </c>
-      <c r="C194" t="n">
-        <v>19.50950050354</v>
-      </c>
-      <c r="D194" t="n">
-        <v>14.210000038147</v>
-      </c>
-      <c r="E194" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>M 1.8 - 30 km ENE of Honaunau-Napoopoo, Hawaii</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>30 km ENE of Honaunau-Napoopoo, Hawaii</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="n">
-        <v>46095.02870601852</v>
-      </c>
-      <c r="J194" s="2" t="n">
-        <v>46095.03117395833</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>tx2026fcfelo</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>-104.308</v>
-      </c>
-      <c r="C195" t="n">
-        <v>31.469</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0.8657</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>M 1.7 - 51 km WNW of Toyah, Texas</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>51 km WNW of Toyah, Texas</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="n">
-        <v>46095.01859700232</v>
-      </c>
-      <c r="J195" s="2" t="n">
-        <v>46095.04201</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>nc75327087</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>-122.8193359375</v>
-      </c>
-      <c r="C196" t="n">
-        <v>38.8326683044434</v>
-      </c>
-      <c r="D196" t="n">
-        <v>2</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>M 1.6 - 8 km NW of The Geysers, CA</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>8 km NW of The Geysers, CA</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="n">
-        <v>46095.01149872685</v>
-      </c>
-      <c r="J196" s="2" t="n">
-        <v>46095.0363528588</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>ci41203927</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>-117.889166666667</v>
-      </c>
-      <c r="C197" t="n">
-        <v>36.1266666666667</v>
-      </c>
-      <c r="D197" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>M 1.2 - 11 km NNE of Coso Junction, CA</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>11 km NNE of Coso Junction, CA</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="n">
-        <v>46095.01137974537</v>
-      </c>
-      <c r="J197" s="2" t="n">
-        <v>46095.01376409722</v>
+        <v>46095.21100451389</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/USGS.xlsx
+++ b/data/raw/USGS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J188"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,29 +487,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nc75327567</t>
+          <t>tx2026ffzaya</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-120.093002319336</v>
+        <v>-104.188</v>
       </c>
       <c r="C2" t="n">
-        <v>36.1063346862793</v>
+        <v>31.703</v>
       </c>
       <c r="D2" t="n">
-        <v>8.239999771118161</v>
+        <v>4.4731</v>
       </c>
       <c r="E2" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M 2.1 - 11 km S of Huron, CA</t>
+          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11 km S of Huron, CA</t>
+          <t>55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,38 +518,38 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46096.16129594907</v>
+        <v>46097.06930607639</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46096.16244400463</v>
+        <v>46097.08380681713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aka2026fehrkj</t>
+          <t>hv74917612</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-149.708</v>
+        <v>-155.139495849609</v>
       </c>
       <c r="C3" t="n">
-        <v>62.155</v>
+        <v>19.3330001831055</v>
       </c>
       <c r="D3" t="n">
-        <v>31.4</v>
+        <v>3.76999998092651</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M 1.5 - 7 km E of Susitna North, Alaska</t>
+          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7 km E of Susitna North, Alaska</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,38 +558,38 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46096.16061565972</v>
+        <v>46097.06757199074</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46096.16211004629</v>
+        <v>46097.07008101852</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nn00912678</t>
+          <t>ci41204799</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-117.1285</v>
+        <v>-117.4825</v>
       </c>
       <c r="C4" t="n">
-        <v>37.2457</v>
+        <v>35.601</v>
       </c>
       <c r="D4" t="n">
-        <v>13.004</v>
+        <v>7.7</v>
       </c>
       <c r="E4" t="n">
-        <v>1.59</v>
+        <v>0.95</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M 1.6 - 49 km NW of Beatty, Nevada</t>
+          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>49 km NW of Beatty, Nevada</t>
+          <t>18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -598,38 +598,38 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46096.16059528935</v>
+        <v>46097.0600244213</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46096.16208465278</v>
+        <v>46097.06239535879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ok2026fdrh</t>
+          <t>tx2026ffyeyx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-98.18229675000001</v>
+        <v>-104.176</v>
       </c>
       <c r="C5" t="n">
-        <v>35.44195557</v>
+        <v>31.711</v>
       </c>
       <c r="D5" t="n">
-        <v>0.324695766</v>
+        <v>7.4969</v>
       </c>
       <c r="E5" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M 2.6 - 16 km ESE of Hinton, Oklahoma</t>
+          <t>M 1.9 - 54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>16 km ESE of Hinton, Oklahoma</t>
+          <t>54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,38 +638,38 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46096.15941979166</v>
+        <v>46097.05150728009</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46096.16168333333</v>
+        <v>46097.06865469908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aka2026fegqal</t>
+          <t>aka2026ffxzpn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-152.568</v>
+        <v>-150.668</v>
       </c>
       <c r="C6" t="n">
-        <v>60.006</v>
+        <v>63.582</v>
       </c>
       <c r="D6" t="n">
-        <v>104.2</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M 1.3 - 47 km W of Happy Valley, Alaska</t>
+          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>47 km W of Happy Valley, Alaska</t>
+          <t>52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -678,38 +678,38 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46096.13842898148</v>
+        <v>46097.0471140162</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46096.139836875</v>
+        <v>46097.04869516204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tx2026fegnxw</t>
+          <t>nn00912731</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-104.455</v>
+        <v>-114.5508</v>
       </c>
       <c r="C7" t="n">
-        <v>31.63</v>
+        <v>37.2919</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4207</v>
+        <v>15.9298</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M 1.7 - 60 km S of Whites City, New Mexico</t>
+          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>60 km S of Whites City, New Mexico</t>
+          <t>36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -718,38 +718,38 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46096.13677427083</v>
+        <v>46097.04372652778</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46096.13850288194</v>
+        <v>46097.04546596065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tx2026fegkvq</t>
+          <t>ci41204783</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-104.448</v>
+        <v>-116.366833333333</v>
       </c>
       <c r="C8" t="n">
-        <v>31.631</v>
+        <v>33.193</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4418</v>
+        <v>7.35</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M 2.4 - 60 km S of Whites City, New Mexico</t>
+          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>60 km S of Whites City, New Mexico</t>
+          <t>7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -758,38 +758,38 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46096.13426179398</v>
+        <v>46097.04078981481</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46096.16708719907</v>
+        <v>46097.04323087963</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nn00912675</t>
+          <t>nc75327962</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-116.8506</v>
+        <v>-120.523834228516</v>
       </c>
       <c r="C9" t="n">
-        <v>37.1599</v>
+        <v>35.9671669006348</v>
       </c>
       <c r="D9" t="n">
-        <v>6.4687</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="E9" t="n">
-        <v>1.06</v>
+        <v>1.72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M 1.1 - 29 km NNW of Beatty, Nevada</t>
+          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29 km NNW of Beatty, Nevada</t>
+          <t>11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -798,38 +798,38 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46096.13401565972</v>
+        <v>46097.03950659722</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46096.13532696759</v>
+        <v>46097.05378733797</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aka2026feghag</t>
+          <t>aka2026ffxmpi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-152.61</v>
+        <v>-149.174</v>
       </c>
       <c r="C10" t="n">
-        <v>60.069</v>
+        <v>63.002</v>
       </c>
       <c r="D10" t="n">
-        <v>99.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M 2.3 - 50 km WNW of Happy Valley, Alaska</t>
+          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>50 km WNW of Happy Valley, Alaska</t>
+          <t>44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -838,38 +838,38 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46096.13122143519</v>
+        <v>46097.03663675926</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46096.13240575232</v>
+        <v>46097.03896524305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nc75327557</t>
+          <t>nc75327947</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-122.757667541504</v>
+        <v>-124.239669799805</v>
       </c>
       <c r="C11" t="n">
-        <v>38.7836685180664</v>
+        <v>40.4664993286133</v>
       </c>
       <c r="D11" t="n">
-        <v>2.04999995231628</v>
+        <v>26.0400009155273</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M 1.2 - 1 km N of The Geysers, CA</t>
+          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1 km N of The Geysers, CA</t>
+          <t>12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -878,38 +878,38 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46096.12735844908</v>
+        <v>46097.03397256944</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46096.14749365741</v>
+        <v>46097.08151043981</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nc75327552</t>
+          <t>nn00912729</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-120.159332275391</v>
+        <v>-116.2867</v>
       </c>
       <c r="C12" t="n">
-        <v>36.105167388916</v>
+        <v>37.418</v>
       </c>
       <c r="D12" t="n">
-        <v>9.159999847412109</v>
+        <v>8.758599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M 1.4 - 12 km NNW of Avenal, CA</t>
+          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12 km NNW of Avenal, CA</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -918,38 +918,38 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46096.12601481481</v>
+        <v>46097.03219180556</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46096.15440421296</v>
+        <v>46097.03392417824</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hv74917472</t>
+          <t>hv74917602</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-155.253005981445</v>
+        <v>-155.143005371094</v>
       </c>
       <c r="C13" t="n">
-        <v>19.2596664428711</v>
+        <v>19.3344993591309</v>
       </c>
       <c r="D13" t="n">
-        <v>24.2299995422363</v>
+        <v>4.25</v>
       </c>
       <c r="E13" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M 2.4 - 20 km S of Volcano, Hawaii</t>
+          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20 km S of Volcano, Hawaii</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -958,38 +958,38 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46096.11974375</v>
+        <v>46097.02269363426</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46096.1222449074</v>
+        <v>46097.02506747685</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hv74917477</t>
+          <t>nn00912728</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-155.235000610352</v>
+        <v>-116.8948</v>
       </c>
       <c r="C14" t="n">
-        <v>19.2304992675781</v>
+        <v>38.2511</v>
       </c>
       <c r="D14" t="n">
-        <v>27.8999996185303</v>
+        <v>4.7942</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M 2.6 - 23 km S of Volcano, Hawaii</t>
+          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>23 km S of Volcano, Hawaii</t>
+          <t>35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -998,38 +998,38 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46096.11969131944</v>
+        <v>46097.02024291667</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46096.12205555556</v>
+        <v>46097.02206256944</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>us6000sgdx</t>
+          <t>nn00912725</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>152.8602</v>
+        <v>-116.3002</v>
       </c>
       <c r="C15" t="n">
-        <v>47.1076</v>
+        <v>36.4986</v>
       </c>
       <c r="D15" t="n">
-        <v>85.952</v>
+        <v>1.7633</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3</v>
+        <v>1.13</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M 4.3 - Kuril Islands</t>
+          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kuril Islands</t>
+          <t>42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1038,38 +1038,38 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46096.11952268519</v>
+        <v>46097.01676708333</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46096.14409768519</v>
+        <v>46097.01802194444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nc75327547</t>
+          <t>aka2026ffwkac</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-122.466499328613</v>
+        <v>-147.104</v>
       </c>
       <c r="C16" t="n">
-        <v>37.5961685180664</v>
+        <v>61.221</v>
       </c>
       <c r="D16" t="n">
-        <v>9.72999954223633</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M 1.5 - 3 km SE of Pacifica, CA</t>
+          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1078,38 +1078,38 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46096.10495636574</v>
+        <v>46097.01360875</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46096.13706527778</v>
+        <v>46097.01453715278</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nn00912672</t>
+          <t>nc75327937</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-116.7812</v>
+        <v>-120.16283416748</v>
       </c>
       <c r="C17" t="n">
-        <v>38.3201</v>
+        <v>36.1510009765625</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2364</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E17" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M 1.9 - 48 km NE of Tonopah, Nevada</t>
+          <t>M 1.8 - 8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>48 km NE of Tonopah, Nevada</t>
+          <t>8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1118,38 +1118,38 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46096.09975644676</v>
+        <v>46097.00379861111</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46096.1015644213</v>
+        <v>46097.07108120371</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>us6000sgdm</t>
+          <t>aka2026ffvrqe</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-111.8909</v>
+        <v>-150.318</v>
       </c>
       <c r="C18" t="n">
-        <v>32.5527</v>
+        <v>60.621</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>37.9</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>M 2.5 - 5 km S of Tat Momoli, Arizona</t>
+          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5 km S of Tat Momoli, Arizona</t>
+          <t>26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1158,38 +1158,38 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46096.09697278935</v>
+        <v>46096.99880960648</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46096.11536375</v>
+        <v>46097.06023194444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ci41204383</t>
+          <t>hv74917597</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-117.512</v>
+        <v>-154.981170654297</v>
       </c>
       <c r="C19" t="n">
-        <v>35.7071666666667</v>
+        <v>19.3976669311523</v>
       </c>
       <c r="D19" t="n">
-        <v>6.97</v>
+        <v>-0.560000002384186</v>
       </c>
       <c r="E19" t="n">
-        <v>1.13</v>
+        <v>1.79</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>M 1.1 - 12 km SW of Searles Valley, CA</t>
+          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12 km SW of Searles Valley, CA</t>
+          <t>10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1198,38 +1198,38 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46096.09368009259</v>
+        <v>46096.99111076389</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46096.09604913194</v>
+        <v>46096.993578125</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nc75327527</t>
+          <t>ci41204759</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-122.815002441406</v>
+        <v>-117.6875</v>
       </c>
       <c r="C20" t="n">
-        <v>38.8293342590332</v>
+        <v>35.0311666666667</v>
       </c>
       <c r="D20" t="n">
-        <v>1.63999998569489</v>
+        <v>-0.84</v>
       </c>
       <c r="E20" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>M 1.2 - 8 km NW of The Geysers, CA</t>
+          <t>M 1.3 - 5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8 km NW of The Geysers, CA</t>
+          <t>5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,38 +1238,38 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46096.07455567129</v>
+        <v>46096.98700925926</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46096.09885387732</v>
+        <v>46096.98945039352</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aka2026fedenj</t>
+          <t>aka2026ffvcuk</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-151.271</v>
+        <v>-147.706</v>
       </c>
       <c r="C21" t="n">
-        <v>63.271</v>
+        <v>63.18</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M 1.3 - 37 km SE of Denali National Park, Alaska</t>
+          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>37 km SE of Denali National Park, Alaska</t>
+          <t>66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46096.06629653935</v>
+        <v>46096.98682952546</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46096.06743400463</v>
+        <v>46097.05321805555</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ci41204359</t>
+          <t>aka2026ffuxwl</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-118.145668029785</v>
+        <v>-149.464</v>
       </c>
       <c r="C22" t="n">
-        <v>33.7991676330566</v>
+        <v>65.532</v>
       </c>
       <c r="D22" t="n">
-        <v>18.5900001525879</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.19227960814025</v>
+        <v>1.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M 1.2 - 1 km ESE of Long Beach, CA</t>
+          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1 km ESE of Long Beach, CA</t>
+          <t>32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1318,38 +1318,38 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46096.06262638889</v>
+        <v>46096.98287351852</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46096.06503234954</v>
+        <v>46096.98871584491</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ci41204343</t>
+          <t>nc75327927</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-116.714833333333</v>
+        <v>-122.759002685547</v>
       </c>
       <c r="C23" t="n">
-        <v>34.0266666666667</v>
+        <v>38.779167175293</v>
       </c>
       <c r="D23" t="n">
-        <v>14.15</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M 1.0 - 13 km W of Morongo Valley, CA</t>
+          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>13 km W of Morongo Valley, CA</t>
+          <t>0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1358,38 +1358,38 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46096.05851504629</v>
+        <v>46096.98031608796</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46096.0609565625</v>
+        <v>46096.9814612037</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>us6000sgdf</t>
+          <t>nc75327922</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-91.7302</v>
+        <v>-120.615669250488</v>
       </c>
       <c r="C24" t="n">
-        <v>15.4081</v>
+        <v>36.0485000610352</v>
       </c>
       <c r="D24" t="n">
-        <v>184.119</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="E24" t="n">
-        <v>4.8</v>
+        <v>1.65</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M 4.8 - 1 km W of Colotenango, Guatemala</t>
+          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1 km W of Colotenango, Guatemala</t>
+          <t>24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1398,38 +1398,38 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46096.01585359954</v>
+        <v>46096.97481886574</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46096.03232685186</v>
+        <v>46097.03291697917</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nn00912669</t>
+          <t>aka2026fftzga</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-117.7692</v>
+        <v>-147.469</v>
       </c>
       <c r="C25" t="n">
-        <v>37.2938</v>
+        <v>64.946</v>
       </c>
       <c r="D25" t="n">
-        <v>6.5097</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M 1.6 - 48 km ENE of Big Pine, California</t>
+          <t>M 1.2 - 7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>48 km ENE of Big Pine, California</t>
+          <t>7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1438,38 +1438,38 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46096.01070017361</v>
+        <v>46096.96303546296</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46096.01346155092</v>
+        <v>46096.96398349537</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>aka2026feamjb</t>
+          <t>nc75327902</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-151.579</v>
+        <v>-124.639663696289</v>
       </c>
       <c r="C26" t="n">
-        <v>61.273</v>
+        <v>40.34716796875</v>
       </c>
       <c r="D26" t="n">
-        <v>82.90000000000001</v>
+        <v>19.4500007629395</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7</v>
+        <v>2.76</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M 1.7 - 30 km WNW of Beluga, Alaska</t>
+          <t>M 2.8 - 30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>30 km WNW of Beluga, Alaska</t>
+          <t>30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1478,38 +1478,38 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46096.00978141204</v>
+        <v>46096.95174398148</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46096.0110008912</v>
+        <v>46097.04291712963</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nc75327512</t>
+          <t>us6000sgib</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-122.738670349121</v>
+        <v>176.3522</v>
       </c>
       <c r="C27" t="n">
-        <v>38.7863349914551</v>
+        <v>52.1304</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.00999999977648258</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km ENE of The Geysers, CA</t>
+          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2 km ENE of The Geysers, CA</t>
+          <t>229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1518,38 +1518,38 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46095.98437893519</v>
+        <v>46096.94854002315</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46095.9855096875</v>
+        <v>46097.03752361111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nc75327502</t>
+          <t>nn00912719</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-122.85383605957</v>
+        <v>-119.7167</v>
       </c>
       <c r="C28" t="n">
-        <v>38.8251647949219</v>
+        <v>40.512</v>
       </c>
       <c r="D28" t="n">
-        <v>2.40000009536743</v>
+        <v>0.7442</v>
       </c>
       <c r="E28" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M 1.4 - 10 km WNW of The Geysers, CA</t>
+          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10 km WNW of The Geysers, CA</t>
+          <t>32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1558,38 +1558,38 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46095.97872789352</v>
+        <v>46096.94697967593</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46096.03290916666</v>
+        <v>46096.94864458333</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nc75327497</t>
+          <t>aka2026fftern</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-122.783668518066</v>
+        <v>-145.732</v>
       </c>
       <c r="C29" t="n">
-        <v>38.8083343505859</v>
+        <v>62.165</v>
       </c>
       <c r="D29" t="n">
-        <v>0.129999995231628</v>
+        <v>4.6</v>
       </c>
       <c r="E29" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M 1.1 - 4 km NW of The Geysers, CA</t>
+          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4 km NW of The Geysers, CA</t>
+          <t>11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1598,38 +1598,38 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46095.97843564815</v>
+        <v>46096.94644289352</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46096.01551138889</v>
+        <v>46096.94759246528</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nn00912667</t>
+          <t>aka2026ffsxtw</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-117.1013</v>
+        <v>-150.289</v>
       </c>
       <c r="C30" t="n">
-        <v>37.1878</v>
+        <v>60.111</v>
       </c>
       <c r="D30" t="n">
-        <v>2.4482</v>
+        <v>46.9</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M 1.6 - 43 km NW of Beatty, Nevada</t>
+          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>43 km NW of Beatty, Nevada</t>
+          <t>46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46095.97793467592</v>
+        <v>46096.94087768519</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46095.97987364583</v>
+        <v>46096.94183203704</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hv74917452</t>
+          <t>aka2026ffsvcz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-155.482498168945</v>
+        <v>-141.243</v>
       </c>
       <c r="C31" t="n">
-        <v>19.3939990997314</v>
+        <v>61.573</v>
       </c>
       <c r="D31" t="n">
-        <v>6.3899998664856</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M 1.7 - 21 km N of Pāhala, Hawaii</t>
+          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>21 km N of Pāhala, Hawaii</t>
+          <t>90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1678,38 +1678,38 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46095.97703333334</v>
+        <v>46096.93874224537</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46095.97968425926</v>
+        <v>46096.93996863426</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aka2026fdyhrh</t>
+          <t>hv74917587</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-147.392</v>
+        <v>-155.404998779297</v>
       </c>
       <c r="C32" t="n">
-        <v>64.99299999999999</v>
+        <v>19.2546672821045</v>
       </c>
       <c r="D32" t="n">
-        <v>1.2</v>
+        <v>30.7900009155273</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>1.73</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M 1.0 - 11 km ENE of Fox, Alaska</t>
+          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11 km ENE of Fox, Alaska</t>
+          <t>9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1718,38 +1718,38 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46095.96407459491</v>
+        <v>46096.93382974537</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46095.96494929398</v>
+        <v>46096.93618622685</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hv74917442</t>
+          <t>nc75327892</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-155.372329711914</v>
+        <v>-120.513832092285</v>
       </c>
       <c r="C33" t="n">
-        <v>19.2784996032715</v>
+        <v>35.9599990844727</v>
       </c>
       <c r="D33" t="n">
-        <v>30.7099990844727</v>
+        <v>10.1700000762939</v>
       </c>
       <c r="E33" t="n">
-        <v>2.13</v>
+        <v>1.61</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M 2.1 - 13 km NE of Pāhala, Hawaii</t>
+          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13 km NE of Pāhala, Hawaii</t>
+          <t>10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1758,38 +1758,38 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46095.95855648148</v>
+        <v>46096.92984074074</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46095.96108136574</v>
+        <v>46096.98773833334</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>aka2026fdxbnk</t>
+          <t>tx2026ffruyn</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-144.31</v>
+        <v>-103.575</v>
       </c>
       <c r="C34" t="n">
-        <v>69.447</v>
+        <v>30.876</v>
       </c>
       <c r="D34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>M 3.4 - 80 km SSW of Kaktovik, Alaska</t>
+          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>80 km SSW of Kaktovik, Alaska</t>
+          <t>20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1798,38 +1798,38 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46095.93817033565</v>
+        <v>46096.91764664352</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46095.97282453704</v>
+        <v>46096.92133662037</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nc75327467</t>
+          <t>tx2026ffrhgd</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-122.796333312988</v>
+        <v>-101.817</v>
       </c>
       <c r="C35" t="n">
-        <v>38.8341674804688</v>
+        <v>32.349</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>11.8727</v>
       </c>
       <c r="E35" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km WNW of Cobb, CA</t>
+          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6 km WNW of Cobb, CA</t>
+          <t>21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1838,38 +1838,38 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46095.91037789352</v>
+        <v>46096.90660459491</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46095.93216912037</v>
+        <v>46096.91322768519</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aka2026fdvlcf</t>
+          <t>nc75327882</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-151.258</v>
+        <v>-122.730499267578</v>
       </c>
       <c r="C36" t="n">
-        <v>63.207</v>
+        <v>38.7738342285156</v>
       </c>
       <c r="D36" t="n">
-        <v>0.7</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="E36" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M 1.7 - 43 km SSE of Denali National Park, Alaska</t>
+          <t>M 1.0 - 2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>43 km SSE of Denali National Park, Alaska</t>
+          <t>2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1878,38 +1878,38 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46095.90397135416</v>
+        <v>46096.90556168981</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46095.90514605324</v>
+        <v>46096.92179327546</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ci41204303</t>
+          <t>aka2026ffqxwe</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-116.167833333333</v>
+        <v>-145.627</v>
       </c>
       <c r="C37" t="n">
-        <v>33.8496666666667</v>
+        <v>62.093</v>
       </c>
       <c r="D37" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M 1.3 - 15 km NNE of Indio, CA</t>
+          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15 km NNE of Indio, CA</t>
+          <t>4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1918,38 +1918,38 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46095.89176631944</v>
+        <v>46096.89903701389</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46095.89934652777</v>
+        <v>46096.90023371528</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nn00912666</t>
+          <t>nn00912718</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-116.4902</v>
+        <v>-117.1162</v>
       </c>
       <c r="C38" t="n">
-        <v>38.4843</v>
+        <v>37.2236</v>
       </c>
       <c r="D38" t="n">
-        <v>1.2159</v>
+        <v>0.039</v>
       </c>
       <c r="E38" t="n">
-        <v>2.14</v>
+        <v>1.08</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M 2.1 - 79 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>79 km NE of Tonopah, Nevada</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1958,38 +1958,38 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46095.88495538195</v>
+        <v>46096.8946965625</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46095.88782293982</v>
+        <v>46096.89624318287</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tx2026fdulai</t>
+          <t>nc75327877</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-104.423</v>
+        <v>-121.053001403809</v>
       </c>
       <c r="C39" t="n">
-        <v>31.637</v>
+        <v>36.4648323059082</v>
       </c>
       <c r="D39" t="n">
-        <v>4.1495</v>
+        <v>0.209999993443489</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M 2.5 - 59 km S of Whites City, New Mexico</t>
+          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>59 km S of Whites City, New Mexico</t>
+          <t>11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1998,38 +1998,38 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46095.88303170139</v>
+        <v>46096.89354375</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46095.96269722222</v>
+        <v>46096.95303508102</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ci41204295</t>
+          <t>us6000sghx</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-116.754669189453</v>
+        <v>-68.8159</v>
       </c>
       <c r="C40" t="n">
-        <v>33.6506652832031</v>
+        <v>-21.1625</v>
       </c>
       <c r="D40" t="n">
-        <v>13.289999961853</v>
+        <v>120.691</v>
       </c>
       <c r="E40" t="n">
-        <v>0.952443359159076</v>
+        <v>4.1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M 1.0 - 10 km SSW of Idyllwild, CA</t>
+          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10 km SSW of Idyllwild, CA</t>
+          <t>58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2038,38 +2038,38 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46095.87724398148</v>
+        <v>46096.89260434028</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46095.87864965278</v>
+        <v>46097.01954907407</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aka2026fdudwi</t>
+          <t>aka2026ffqnha</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-157.149</v>
+        <v>-146.565</v>
       </c>
       <c r="C41" t="n">
-        <v>66.373</v>
+        <v>61.519</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>38.2</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M 3.0 - 57 km S of Shungnak, Alaska</t>
+          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>57 km S of Shungnak, Alaska</t>
+          <t>44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2078,38 +2078,38 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46095.87685564814</v>
+        <v>46096.89050962963</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46095.94651666666</v>
+        <v>46096.89142732639</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>nn00912662</t>
+          <t>tx2026ffqmcg</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-116.526</v>
+        <v>-101.512</v>
       </c>
       <c r="C42" t="n">
-        <v>38.4379</v>
+        <v>31.874</v>
       </c>
       <c r="D42" t="n">
-        <v>12.8814</v>
+        <v>3.2716</v>
       </c>
       <c r="E42" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M 3.4 - 74 km ENE of Tonopah, Nevada</t>
+          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>74 km ENE of Tonopah, Nevada</t>
+          <t>3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2118,38 +2118,38 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46095.87443729167</v>
+        <v>46096.88956126157</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46096.08695996528</v>
+        <v>46096.9711172801</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nn00912660</t>
+          <t>nn00912716</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-116.6966</v>
+        <v>-116.5976</v>
       </c>
       <c r="C43" t="n">
-        <v>38.3742</v>
+        <v>38.2879</v>
       </c>
       <c r="D43" t="n">
-        <v>4.278</v>
+        <v>4.9318</v>
       </c>
       <c r="E43" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M 2.1 - 57 km NE of Tonopah, Nevada</t>
+          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>57 km NE of Tonopah, Nevada</t>
+          <t>60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2158,38 +2158,38 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46095.86389622685</v>
+        <v>46096.88044799768</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46095.86570340278</v>
+        <v>46096.88234515046</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aka2026fdtdkp</t>
+          <t>aka2026ffpwxx</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-150.918</v>
+        <v>-150.536</v>
       </c>
       <c r="C44" t="n">
-        <v>64.81</v>
+        <v>60.816</v>
       </c>
       <c r="D44" t="n">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="E44" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>M 1.3 - 25 km SSW of Manley Hot Springs, Alaska</t>
+          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>25 km SSW of Manley Hot Springs, Alaska</t>
+          <t>14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2198,38 +2198,38 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46095.85587677083</v>
+        <v>46096.87733195602</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46095.85710167824</v>
+        <v>46096.87884059027</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>nn00912655</t>
+          <t>tx2026ffpmmk</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-116.532</v>
+        <v>-102.596</v>
       </c>
       <c r="C45" t="n">
-        <v>38.4506</v>
+        <v>32.426</v>
       </c>
       <c r="D45" t="n">
-        <v>6.2192</v>
+        <v>7.1182</v>
       </c>
       <c r="E45" t="n">
-        <v>3.17</v>
+        <v>1.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>M 3.2 - 74 km NE of Tonopah, Nevada</t>
+          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>74 km NE of Tonopah, Nevada</t>
+          <t>12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2238,38 +2238,38 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46095.85289917824</v>
+        <v>46096.86891956018</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46096.08666041667</v>
+        <v>46096.87235497685</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hv74917417</t>
+          <t>aka2026ffpbrz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-155.371002197266</v>
+        <v>-151.569</v>
       </c>
       <c r="C46" t="n">
-        <v>19.2818336486816</v>
+        <v>61.397</v>
       </c>
       <c r="D46" t="n">
-        <v>30.0100002288818</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>M 2.0 - 14 km NE of Pāhala, Hawaii</t>
+          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 km NE of Pāhala, Hawaii</t>
+          <t>38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2278,38 +2278,38 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46095.84536168981</v>
+        <v>46096.86023665509</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46095.84858645833</v>
+        <v>46096.86153666666</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nc75327447</t>
+          <t>aka2026ffoxwo</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-122.818496704102</v>
+        <v>-153.073</v>
       </c>
       <c r="C47" t="n">
-        <v>38.8343315124512</v>
+        <v>60.494</v>
       </c>
       <c r="D47" t="n">
-        <v>1.87999999523163</v>
+        <v>146.3</v>
       </c>
       <c r="E47" t="n">
-        <v>1.16</v>
+        <v>2.1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M 1.2 - 8 km NW of The Geysers, CA</t>
+          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8 km NW of The Geysers, CA</t>
+          <t>75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2318,38 +2318,38 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46095.81590775463</v>
+        <v>46096.85716821759</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46095.85925590277</v>
+        <v>46096.85982177083</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>us6000sgc5</t>
+          <t>tx2026ffolko</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-116.4136</v>
+        <v>-104.401</v>
       </c>
       <c r="C48" t="n">
-        <v>38.5775</v>
+        <v>31.692</v>
       </c>
       <c r="D48" t="n">
-        <v>12.516</v>
+        <v>4.8181</v>
       </c>
       <c r="E48" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>M 2.5 - 90 km SE of Kingston, Nevada</t>
+          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>90 km SE of Kingston, Nevada</t>
+          <t>53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2358,38 +2358,38 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46095.77945232639</v>
+        <v>46096.84736503472</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46095.92890092592</v>
+        <v>46096.93883732639</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>us6000sgc2</t>
+          <t>nc75327852</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>153.3556</v>
+        <v>-122.464164733887</v>
       </c>
       <c r="C49" t="n">
-        <v>46.5573</v>
+        <v>37.5973320007324</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="E49" t="n">
-        <v>5.1</v>
+        <v>1.02</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>M 5.1 - Kuril Islands</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Kuril Islands</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2398,38 +2398,38 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46095.77235402778</v>
+        <v>46096.84368958334</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46095.78642407407</v>
+        <v>46096.84483373843</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>us6000sgc4</t>
+          <t>aka2026ffogkg</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>176.5308</v>
+        <v>-150.241</v>
       </c>
       <c r="C50" t="n">
-        <v>52.2911</v>
+        <v>61.578</v>
       </c>
       <c r="D50" t="n">
-        <v>8.986000000000001</v>
+        <v>30.7</v>
       </c>
       <c r="E50" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M 4.2 - 235 km ESE of Attu Station, Alaska</t>
+          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>235 km ESE of Attu Station, Alaska</t>
+          <t>14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2438,38 +2438,38 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46095.76988208333</v>
+        <v>46096.84307547453</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46095.90945648148</v>
+        <v>46096.84451351852</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aka2026fdoonh</t>
+          <t>nc75327847</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-152.919</v>
+        <v>-122.757667541504</v>
       </c>
       <c r="C51" t="n">
-        <v>59.948</v>
+        <v>38.7918319702148</v>
       </c>
       <c r="D51" t="n">
-        <v>110.7</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="E51" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>M 2.9 - 63 km WNW of Anchor Point, Alaska</t>
+          <t>M 1.0 - 2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>63 km WNW of Anchor Point, Alaska</t>
+          <t>2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2478,38 +2478,38 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46095.76006307871</v>
+        <v>46096.84258912037</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46095.89397037037</v>
+        <v>46096.84373324074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nc75327417</t>
+          <t>ci41204687</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-121.6181640625</v>
+        <v>-117.249</v>
       </c>
       <c r="C52" t="n">
-        <v>36.0970001220703</v>
+        <v>33.9988333333333</v>
       </c>
       <c r="D52" t="n">
-        <v>13.6000003814697</v>
+        <v>10.86</v>
       </c>
       <c r="E52" t="n">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>M 1.3 - 10 km NNW of Lopez Point, CA</t>
+          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10 km NNW of Lopez Point, CA</t>
+          <t>6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2518,38 +2518,38 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46095.75923622686</v>
+        <v>46096.83063032408</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46095.82109177083</v>
+        <v>46096.83300278935</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>aka2026fdoioz</t>
+          <t>nn00912714</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-150.653</v>
+        <v>-116.7227</v>
       </c>
       <c r="C53" t="n">
-        <v>62.91</v>
+        <v>38.3427</v>
       </c>
       <c r="D53" t="n">
-        <v>95.90000000000001</v>
+        <v>0.1382</v>
       </c>
       <c r="E53" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>M 2.4 - 46 km N of Petersville, Alaska</t>
+          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>46 km N of Petersville, Alaska</t>
+          <t>53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2558,38 +2558,38 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46095.7552774537</v>
+        <v>46096.82208777778</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46095.75831664352</v>
+        <v>46096.82386192129</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>nc75327407</t>
+          <t>aka2026ffmxvv</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-122.807830810547</v>
+        <v>-151.974</v>
       </c>
       <c r="C54" t="n">
-        <v>38.8185005187988</v>
+        <v>60.349</v>
       </c>
       <c r="D54" t="n">
-        <v>3.05999994277954</v>
+        <v>77.2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>M 1.3 - 6 km NW of The Geysers, CA</t>
+          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2598,38 +2598,38 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46095.74812962963</v>
+        <v>46096.81522726852</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46095.80374011574</v>
+        <v>46096.81638251158</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>aka2026fdnzor</t>
+          <t>nc75327827</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-157.911</v>
+        <v>-121.9375</v>
       </c>
       <c r="C55" t="n">
-        <v>56.193</v>
+        <v>37.7731666666667</v>
       </c>
       <c r="D55" t="n">
-        <v>63.7</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>M 1.7 - 32 km ESE of Chignik, Alaska</t>
+          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>32 km ESE of Chignik, Alaska</t>
+          <t>4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2638,38 +2638,38 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46095.74800765047</v>
+        <v>46096.81305393518</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46095.7494846875</v>
+        <v>46097.01551917824</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>us6000sgbx</t>
+          <t>nc75327822</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-46.6402</v>
+        <v>-122.787170410156</v>
       </c>
       <c r="C56" t="n">
-        <v>16.556</v>
+        <v>38.7934989929199</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="E56" t="n">
-        <v>5.1</v>
+        <v>1.38</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>M 5.1 - northern Mid-Atlantic Ridge</t>
+          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>northern Mid-Atlantic Ridge</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2678,38 +2678,38 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46095.73839887731</v>
+        <v>46096.81298229167</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46095.75246574074</v>
+        <v>46096.86627753473</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nc75327402</t>
+          <t>us6000sghq</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-122.281829833984</v>
+        <v>49.7256</v>
       </c>
       <c r="C57" t="n">
-        <v>37.3633346557617</v>
+        <v>32.4853</v>
       </c>
       <c r="D57" t="n">
-        <v>3.32999992370605</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>M 2.6 - 5 km WSW of Portola Valley, CA</t>
+          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>5 km WSW of Portola Valley, CA</t>
+          <t>62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2718,38 +2718,38 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46095.73607071759</v>
+        <v>46096.8103829051</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46095.91402037037</v>
+        <v>46096.86111157407</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>aka2026fdnjta</t>
+          <t>aka2026ffmjyx</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-148.1</v>
+        <v>-149.647</v>
       </c>
       <c r="C58" t="n">
-        <v>62.28</v>
+        <v>63.036</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>M 1.7 - 57 km NNE of Chickaloon, Alaska</t>
+          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>57 km NNE of Chickaloon, Alaska</t>
+          <t>52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2758,38 +2758,38 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46095.73525334491</v>
+        <v>46096.80405828704</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46095.73619780093</v>
+        <v>46096.80508491898</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>us6000sgbr</t>
+          <t>us6000sghd</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-72.0967</v>
+        <v>142.6105</v>
       </c>
       <c r="C59" t="n">
-        <v>-42.429</v>
+        <v>41.4045</v>
       </c>
       <c r="D59" t="n">
-        <v>5.985</v>
+        <v>42.986</v>
       </c>
       <c r="E59" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>M 4.7 - 57 km SW of Lago Puelo, Argentina</t>
+          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>57 km SW of Lago Puelo, Argentina</t>
+          <t>84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2798,38 +2798,38 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46095.73344064815</v>
+        <v>46096.78951814815</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46095.8081949074</v>
+        <v>46096.84466623842</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nc75327397</t>
+          <t>aka2026fflqih</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-122.782165527344</v>
+        <v>-150.765</v>
       </c>
       <c r="C60" t="n">
-        <v>38.8131675720215</v>
+        <v>63.04</v>
       </c>
       <c r="D60" t="n">
-        <v>0.280000001192093</v>
+        <v>117.3</v>
       </c>
       <c r="E60" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
+          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2838,38 +2838,38 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46095.73288171296</v>
+        <v>46096.78820800926</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46095.74467230324</v>
+        <v>46096.79154229166</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>us6000sgbq</t>
+          <t>us6000sghb</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-177.6605</v>
+        <v>131.6063</v>
       </c>
       <c r="C61" t="n">
-        <v>-20.6389</v>
+        <v>31.4194</v>
       </c>
       <c r="D61" t="n">
-        <v>519.203</v>
+        <v>32.903</v>
       </c>
       <c r="E61" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>M 4.4 - 252 km WNW of Houma, Tonga</t>
+          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>252 km WNW of Houma, Tonga</t>
+          <t>30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2878,38 +2878,38 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46095.72445238426</v>
+        <v>46096.77722483796</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46095.7970375</v>
+        <v>46096.91079450231</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ci41204215</t>
+          <t>us6000sgh9</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-116.8055</v>
+        <v>-77.5782</v>
       </c>
       <c r="C62" t="n">
-        <v>33.2446666666667</v>
+        <v>-1.3215</v>
       </c>
       <c r="D62" t="n">
-        <v>10.12</v>
+        <v>218.126</v>
       </c>
       <c r="E62" t="n">
-        <v>1.53</v>
+        <v>4.4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>M 1.5 - 4 km W of Lake Henshaw, CA</t>
+          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4 km W of Lake Henshaw, CA</t>
+          <t>44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2918,38 +2918,38 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46095.71835150463</v>
+        <v>46096.77198028936</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46095.72597673611</v>
+        <v>46096.78392407407</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nc75327377</t>
+          <t>nc75327792</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-120.121002197266</v>
+        <v>-122.471336364746</v>
       </c>
       <c r="C63" t="n">
-        <v>36.1983337402344</v>
+        <v>37.5974998474121</v>
       </c>
       <c r="D63" t="n">
-        <v>10.8299999237061</v>
+        <v>9.72999954223633</v>
       </c>
       <c r="E63" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>M 1.6 - 2 km WSW of Huron, CA</t>
+          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2 km WSW of Huron, CA</t>
+          <t>2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2958,38 +2958,38 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46095.71190879629</v>
+        <v>46096.77132291667</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46095.76552966435</v>
+        <v>46096.81413002315</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tx2026fdmbdg</t>
+          <t>aka2026ffklqv</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-100.546</v>
+        <v>-155.854</v>
       </c>
       <c r="C64" t="n">
-        <v>32.793</v>
+        <v>57.153</v>
       </c>
       <c r="D64" t="n">
-        <v>2.4872</v>
+        <v>63.2</v>
       </c>
       <c r="E64" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>M 1.5 - 9 km SW of Rotan, Texas</t>
+          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>9 km SW of Rotan, Texas</t>
+          <t>96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2998,38 +2998,38 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46095.70736677083</v>
+        <v>46096.76349226852</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46095.97094901621</v>
+        <v>46096.76507798611</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tx2026fdlfas</t>
+          <t>nc75327787</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-101.944</v>
+        <v>-123.346832275391</v>
       </c>
       <c r="C65" t="n">
-        <v>32.255</v>
+        <v>39.476001739502</v>
       </c>
       <c r="D65" t="n">
-        <v>3.962</v>
+        <v>4.19999980926514</v>
       </c>
       <c r="E65" t="n">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>M 1.2 - 20 km NW of Stanton, Texas</t>
+          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20 km NW of Stanton, Texas</t>
+          <t>5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3038,38 +3038,38 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46095.69110606481</v>
+        <v>46096.7527207176</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46095.97089986111</v>
+        <v>46096.79673230324</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>nc75327372</t>
+          <t>aka2026ffjrwj</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-120.084503173828</v>
+        <v>-149.163</v>
       </c>
       <c r="C66" t="n">
-        <v>36.2008323669434</v>
+        <v>62.869</v>
       </c>
       <c r="D66" t="n">
-        <v>10.7700004577637</v>
+        <v>0.3</v>
       </c>
       <c r="E66" t="n">
-        <v>2.87</v>
+        <v>1.6</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>M 2.9 - 2 km E of Huron, CA</t>
+          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2 km E of Huron, CA</t>
+          <t>59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3078,38 +3078,38 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46095.68949560185</v>
+        <v>46096.74754356482</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46095.77751203704</v>
+        <v>46096.7486603125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>pr71509878</t>
+          <t>aka2026ffjpxp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-67.01300000000001</v>
+        <v>-152.555</v>
       </c>
       <c r="C67" t="n">
-        <v>18.17</v>
+        <v>59.7</v>
       </c>
       <c r="D67" t="n">
-        <v>27.16</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>M 2.1 - 3 km WSW of Maricao, Puerto Rico</t>
+          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3 km WSW of Maricao, Puerto Rico</t>
+          <t>41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3118,38 +3118,38 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46095.68730462963</v>
+        <v>46096.74597070602</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46095.69560127315</v>
+        <v>46096.74724846065</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>us6000sgbi</t>
+          <t>us6000sgh3</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>23.2998</v>
+        <v>128.5163</v>
       </c>
       <c r="C68" t="n">
-        <v>34.9004</v>
+        <v>-7.3925</v>
       </c>
       <c r="D68" t="n">
-        <v>35.11</v>
+        <v>137.104</v>
       </c>
       <c r="E68" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>M 4.8 - 50 km SW of Palaióchora, Greece</t>
+          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>50 km SW of Palaióchora, Greece</t>
+          <t>208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3158,38 +3158,38 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46095.68167795139</v>
+        <v>46096.7350890625</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46095.76548657408</v>
+        <v>46096.81851898148</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>aka2026fdkqsi</t>
+          <t>ci41204623</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-151.229</v>
+        <v>-116.638166666667</v>
       </c>
       <c r="C69" t="n">
-        <v>61.179</v>
+        <v>32.8055</v>
       </c>
       <c r="D69" t="n">
-        <v>72.2</v>
+        <v>16.68</v>
       </c>
       <c r="E69" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>M 1.5 - 8 km WNW of Beluga, Alaska</t>
+          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8 km WNW of Beluga, Alaska</t>
+          <t>10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3198,38 +3198,38 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46095.67801940972</v>
+        <v>46096.72295416667</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46095.67935157407</v>
+        <v>46096.72542263889</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>aka2026fdkojc</t>
+          <t>aka2026ffhzps</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-152.251</v>
+        <v>-146.822</v>
       </c>
       <c r="C70" t="n">
-        <v>60.688</v>
+        <v>60.719</v>
       </c>
       <c r="D70" t="n">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="E70" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>M 2.1 - 51 km W of Salamatof, Alaska</t>
+          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>51 km W of Salamatof, Alaska</t>
+          <t>18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46095.67615958333</v>
+        <v>46096.71188380787</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46095.67747614584</v>
+        <v>46096.71385545139</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>us6000sgbf</t>
+          <t>tx2026ffhpux</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>74.6932</v>
+        <v>-103.799</v>
       </c>
       <c r="C71" t="n">
-        <v>38.0328</v>
+        <v>31.021</v>
       </c>
       <c r="D71" t="n">
-        <v>97.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>M 4.4 - 65 km ESE of Murghob, Tajikistan</t>
+          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>65 km ESE of Murghob, Tajikistan</t>
+          <t>6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3278,38 +3278,38 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46095.67103631944</v>
+        <v>46096.70398288195</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46095.74024351852</v>
+        <v>46096.71967913194</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>nn00912646</t>
+          <t>aka2026ffhkgu</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-116.3557</v>
+        <v>-154.974</v>
       </c>
       <c r="C72" t="n">
-        <v>37.5696</v>
+        <v>58.28</v>
       </c>
       <c r="D72" t="n">
-        <v>13.4041</v>
+        <v>0.3</v>
       </c>
       <c r="E72" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>M 1.6 - 54 km W of Rachel, Nevada</t>
+          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>54 km W of Rachel, Nevada</t>
+          <t>84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3318,38 +3318,38 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46095.66677557871</v>
+        <v>46096.6993729051</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46095.66844216435</v>
+        <v>46096.7007930787</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ok2026fctl</t>
+          <t>nc75327772</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-98.19499999999999</v>
+        <v>-122.78466796875</v>
       </c>
       <c r="C73" t="n">
-        <v>35.401</v>
+        <v>38.7933349609375</v>
       </c>
       <c r="D73" t="n">
-        <v>6.38</v>
+        <v>3.51999998092651</v>
       </c>
       <c r="E73" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>M 2.2 - 16 km ENE of Lookeba, Oklahoma</t>
+          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>16 km ENE of Lookeba, Oklahoma</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3358,38 +3358,38 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46095.65787973379</v>
+        <v>46096.69837233796</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46095.71147037037</v>
+        <v>46096.72732706019</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nn00912644</t>
+          <t>us6000sggw</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-116.4773</v>
+        <v>143.3074</v>
       </c>
       <c r="C74" t="n">
-        <v>38.4845</v>
+        <v>40.9048</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0212</v>
+        <v>37.859</v>
       </c>
       <c r="E74" t="n">
-        <v>1.69</v>
+        <v>4.8</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>M 1.7 - 80 km NE of Tonopah, Nevada</t>
+          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>80 km NE of Tonopah, Nevada</t>
+          <t>139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3398,38 +3398,38 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46095.65554142361</v>
+        <v>46096.68937086806</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46095.65742730324</v>
+        <v>46096.69961851852</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nn00912642</t>
+          <t>nc75327767</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-116.3647</v>
+        <v>-120.05883026123</v>
       </c>
       <c r="C75" t="n">
-        <v>37.3176</v>
+        <v>35.7056655883789</v>
       </c>
       <c r="D75" t="n">
-        <v>13.2289</v>
+        <v>7.76999998092651</v>
       </c>
       <c r="E75" t="n">
-        <v>1.32</v>
+        <v>2.22</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>M 1.3 - 57 km NE of Beatty, Nevada</t>
+          <t>M 2.2 - 22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>57 km NE of Beatty, Nevada</t>
+          <t>22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3438,38 +3438,38 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46095.65183778935</v>
+        <v>46096.68914074074</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46095.65348369213</v>
+        <v>46096.71344819444</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>nn00912640</t>
+          <t>aka2026ffgrhi</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-116.6675</v>
+        <v>-151.417</v>
       </c>
       <c r="C76" t="n">
-        <v>38.1891</v>
+        <v>63.08</v>
       </c>
       <c r="D76" t="n">
-        <v>5.8708</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>M 1.6 - 51 km ENE of Tonopah, Nevada</t>
+          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>51 km ENE of Tonopah, Nevada</t>
+          <t>53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3478,38 +3478,38 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46095.64834459491</v>
+        <v>46096.68422761574</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46095.65011091435</v>
+        <v>46096.68548758102</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nc75327352</t>
+          <t>nc75327742</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-122.776000976562</v>
+        <v>-121.291664123535</v>
       </c>
       <c r="C77" t="n">
-        <v>38.791332244873</v>
+        <v>36.9063339233398</v>
       </c>
       <c r="D77" t="n">
-        <v>1.4099999666214</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="E77" t="n">
-        <v>2.13</v>
+        <v>1.2</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>M 2.1 - 2 km NW of The Geysers, CA</t>
+          <t>M 1.2 - 12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2 km NW of The Geysers, CA</t>
+          <t>12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3518,38 +3518,38 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46095.64618321759</v>
+        <v>46096.65917303241</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46095.72039762732</v>
+        <v>46096.69960388889</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>us6000sgb8</t>
+          <t>nc75327737</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-66.52290000000001</v>
+        <v>-122.806663513184</v>
       </c>
       <c r="C78" t="n">
-        <v>-23.0932</v>
+        <v>38.8235015869141</v>
       </c>
       <c r="D78" t="n">
-        <v>229.541</v>
+        <v>2.41000008583069</v>
       </c>
       <c r="E78" t="n">
-        <v>4.5</v>
+        <v>1.06</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M 4.5 - 87 km W of El Aguilar, Argentina</t>
+          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>87 km W of El Aguilar, Argentina</t>
+          <t>7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3558,38 +3558,38 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46095.63919398148</v>
+        <v>46096.65873715278</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46095.66461851852</v>
+        <v>46096.67873339121</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>nc75327347</t>
+          <t>nn00912713</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-122.761169433594</v>
+        <v>-116.393</v>
       </c>
       <c r="C79" t="n">
-        <v>38.8240013122559</v>
+        <v>38.5366</v>
       </c>
       <c r="D79" t="n">
-        <v>1.89999997615814</v>
+        <v>0.0315</v>
       </c>
       <c r="E79" t="n">
-        <v>1.13</v>
+        <v>2.2</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>M 1.1 - 3 km W of Cobb, CA</t>
+          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3 km W of Cobb, CA</t>
+          <t>89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3598,38 +3598,38 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46095.63465694444</v>
+        <v>46096.64812005787</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46095.71342921296</v>
+        <v>46096.64995700232</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nn00912635</t>
+          <t>nc75327727</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-116.5514</v>
+        <v>-122.743835449219</v>
       </c>
       <c r="C80" t="n">
-        <v>38.4594</v>
+        <v>38.7863349914551</v>
       </c>
       <c r="D80" t="n">
-        <v>7.5756</v>
+        <v>0.850000023841858</v>
       </c>
       <c r="E80" t="n">
-        <v>3.52</v>
+        <v>1.28</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>M 3.5 - 73 km NE of Tonopah, Nevada</t>
+          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>73 km NE of Tonopah, Nevada</t>
+          <t>1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3638,38 +3638,38 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46095.62976957176</v>
+        <v>46096.64470740741</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46096.08617975695</v>
+        <v>46096.68219443287</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nc75327332</t>
+          <t>ci41204591</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-122.814498901367</v>
+        <v>-115.8325</v>
       </c>
       <c r="C81" t="n">
-        <v>38.8346672058105</v>
+        <v>31.8188333333333</v>
       </c>
       <c r="D81" t="n">
-        <v>1.87000000476837</v>
+        <v>13.69</v>
       </c>
       <c r="E81" t="n">
-        <v>1.1</v>
+        <v>2.04</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>M 1.1 - 8 km W of Cobb, CA</t>
+          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8 km W of Cobb, CA</t>
+          <t>70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3678,38 +3678,38 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46095.6286193287</v>
+        <v>46096.62630196759</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46095.6752652662</v>
+        <v>46096.62875739583</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nc75327327</t>
+          <t>nc75327717</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-122.817497253418</v>
+        <v>-121.055168151855</v>
       </c>
       <c r="C82" t="n">
-        <v>38.8448333740234</v>
+        <v>36.451000213623</v>
       </c>
       <c r="D82" t="n">
-        <v>0.790000021457672</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="E82" t="n">
-        <v>1.06</v>
+        <v>1.91</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>M 1.1 - 9 km WNW of Cobb, CA</t>
+          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>9 km WNW of Cobb, CA</t>
+          <t>12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3718,38 +3718,38 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46095.62618368056</v>
+        <v>46096.61927071759</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46095.63710138889</v>
+        <v>46096.64398418982</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nn00912634</t>
+          <t>tx2026ffdmwb</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-116.5035</v>
+        <v>-104.429</v>
       </c>
       <c r="C83" t="n">
-        <v>38.4698</v>
+        <v>31.64</v>
       </c>
       <c r="D83" t="n">
-        <v>2.1064</v>
+        <v>3.3848</v>
       </c>
       <c r="E83" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>M 2.1 - 77 km NE of Tonopah, Nevada</t>
+          <t>M 1.5 - 59 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>77 km NE of Tonopah, Nevada</t>
+          <t>59 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3758,38 +3758,38 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46095.62491728009</v>
+        <v>46096.6177771875</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46095.6268653588</v>
+        <v>46096.62529559027</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>aka2026fdhwqq</t>
+          <t>aka2026ffcpmw</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-149.976</v>
+        <v>-152.825</v>
       </c>
       <c r="C84" t="n">
-        <v>62.86</v>
+        <v>59.058</v>
       </c>
       <c r="D84" t="n">
-        <v>76.5</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km N of Chase, Alaska</t>
+          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>46 km N of Chase, Alaska</t>
+          <t>61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3798,38 +3798,38 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46095.61995665509</v>
+        <v>46096.59896729167</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46095.621306875</v>
+        <v>46096.91903732639</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nn00912633</t>
+          <t>us6000sggm</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-117.1019</v>
+        <v>130.0249</v>
       </c>
       <c r="C85" t="n">
-        <v>37.2396</v>
+        <v>-5.5263</v>
       </c>
       <c r="D85" t="n">
-        <v>1.9242</v>
+        <v>184.533</v>
       </c>
       <c r="E85" t="n">
-        <v>1.15</v>
+        <v>4.4</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
+          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3838,38 +3838,38 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46095.61719795139</v>
+        <v>46096.59319422454</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46095.61863054398</v>
+        <v>46096.69633148148</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>aka2026fdhpkc</t>
+          <t>hv74917522</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-152.14</v>
+        <v>-155.374328613281</v>
       </c>
       <c r="C86" t="n">
-        <v>60.245</v>
+        <v>19.1918334960938</v>
       </c>
       <c r="D86" t="n">
-        <v>81.5</v>
+        <v>31.7099990844727</v>
       </c>
       <c r="E86" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>M 1.3 - 34 km NW of Ninilchik, Alaska</t>
+          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>34 km NW of Ninilchik, Alaska</t>
+          <t>11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3878,38 +3878,38 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46095.61409172454</v>
+        <v>46096.59297361111</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46095.61547047453</v>
+        <v>46096.5954587963</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>nc75327322</t>
+          <t>ci41204575</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-123.477836608887</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C87" t="n">
-        <v>39.8306655883789</v>
+        <v>33.9901666666667</v>
       </c>
       <c r="D87" t="n">
-        <v>6.07999992370605</v>
+        <v>2.17</v>
       </c>
       <c r="E87" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>M 2.0 - 16 km N of Laytonville, CA</t>
+          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>16 km N of Laytonville, CA</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3918,38 +3918,38 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46095.61145185185</v>
+        <v>46096.58429085648</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46095.65791388889</v>
+        <v>46096.69570008102</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>nc75327312</t>
+          <t>ci41204567</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-123.477996826172</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C88" t="n">
-        <v>39.8306655883789</v>
+        <v>33.9915</v>
       </c>
       <c r="D88" t="n">
-        <v>5.92999982833862</v>
+        <v>2.18</v>
       </c>
       <c r="E88" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>M 2.6 - 16 km N of Laytonville, CA</t>
+          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>16 km N of Laytonville, CA</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3958,38 +3958,38 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46095.60974074074</v>
+        <v>46096.57788611111</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46095.63711296296</v>
+        <v>46096.58546979167</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>hv74917387</t>
+          <t>nn00912712</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-155.589004516602</v>
+        <v>-116.4988</v>
       </c>
       <c r="C89" t="n">
-        <v>19.4724998474121</v>
+        <v>38.4756</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.600000023841858</v>
+        <v>0.0689</v>
       </c>
       <c r="E89" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>M 2.1 - 28 km E of Honaunau-Napoopoo, Hawaii</t>
+          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>28 km E of Honaunau-Napoopoo, Hawaii</t>
+          <t>78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3998,38 +3998,38 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46095.59852002315</v>
+        <v>46096.57585082176</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46095.60086608796</v>
+        <v>46096.57864184028</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>aka2026fdgrel</t>
+          <t>ci41204559</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>176.275</v>
+        <v>-118.1145</v>
       </c>
       <c r="C90" t="n">
-        <v>51.991</v>
+        <v>34.0995</v>
       </c>
       <c r="D90" t="n">
-        <v>15.7</v>
+        <v>8.91</v>
       </c>
       <c r="E90" t="n">
-        <v>3.9</v>
+        <v>1.34</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>M 3.9 - 230 km ESE of Attu Station, Alaska</t>
+          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>230 km ESE of Attu Station, Alaska</t>
+          <t>1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4038,38 +4038,38 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46095.59424848379</v>
+        <v>46096.5639962963</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46095.89015052083</v>
+        <v>46096.56638376157</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nc75327302</t>
+          <t>aka2026ffaxsl</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-121.5556640625</v>
+        <v>-153.59</v>
       </c>
       <c r="C91" t="n">
-        <v>36.9501647949219</v>
+        <v>59.151</v>
       </c>
       <c r="D91" t="n">
-        <v>5.01000022888184</v>
+        <v>102.5</v>
       </c>
       <c r="E91" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km S of Gilroy, CA</t>
+          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>6 km S of Gilroy, CA</t>
+          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4078,38 +4078,38 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46095.57577395834</v>
+        <v>46096.56368013889</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46095.57686728009</v>
+        <v>46096.564885625</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>nc75327297</t>
+          <t>aka2026ffanxh</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-121.947334289551</v>
+        <v>-149.871</v>
       </c>
       <c r="C92" t="n">
-        <v>37.7569999694824</v>
+        <v>61.849</v>
       </c>
       <c r="D92" t="n">
-        <v>6.73999977111816</v>
+        <v>28.4</v>
       </c>
       <c r="E92" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>M 1.8 - 4 km SE of San Ramon, CA</t>
+          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4 km SE of San Ramon, CA</t>
+          <t>14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4118,38 +4118,38 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46095.57398888889</v>
+        <v>46096.55577541667</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46095.63013303241</v>
+        <v>46096.55684119213</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nc75327287</t>
+          <t>tx2026ffanng</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-122.825332641602</v>
+        <v>-101.924</v>
       </c>
       <c r="C93" t="n">
-        <v>38.8256683349609</v>
+        <v>32.101</v>
       </c>
       <c r="D93" t="n">
-        <v>2.57999992370605</v>
+        <v>3.9912</v>
       </c>
       <c r="E93" t="n">
-        <v>0.99</v>
+        <v>1.3</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km NW of The Geysers, CA</t>
+          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>8 km NW of The Geysers, CA</t>
+          <t>13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4158,38 +4158,38 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46095.55829305555</v>
+        <v>46096.55563410879</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46095.55934175926</v>
+        <v>46096.97107067129</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nn00912632</t>
+          <t>nn00912708</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-117.1262</v>
+        <v>-116.4027</v>
       </c>
       <c r="C94" t="n">
-        <v>37.2113</v>
+        <v>37.3392</v>
       </c>
       <c r="D94" t="n">
-        <v>0.008</v>
+        <v>13.9737</v>
       </c>
       <c r="E94" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>M 1.0 - 46 km NW of Beatty, Nevada</t>
+          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>46 km NW of Beatty, Nevada</t>
+          <t>57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4198,38 +4198,38 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46095.55455298611</v>
+        <v>46096.55248135416</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46095.55609993055</v>
+        <v>46096.55406869213</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>aka2026fdejza</t>
+          <t>nn00912710</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-150.859</v>
+        <v>-117.9202</v>
       </c>
       <c r="C95" t="n">
-        <v>61.085</v>
+        <v>38.5488</v>
       </c>
       <c r="D95" t="n">
-        <v>65.2</v>
+        <v>11.6085</v>
       </c>
       <c r="E95" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>M 1.3 - 13 km ESE of Beluga, Alaska</t>
+          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>13 km ESE of Beluga, Alaska</t>
+          <t>24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4238,38 +4238,38 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46095.5468615625</v>
+        <v>46096.55246195602</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46095.5479505787</v>
+        <v>46096.55466255787</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nc75327277</t>
+          <t>aka2026ffagux</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-122.059669494629</v>
+        <v>-149.012</v>
       </c>
       <c r="C96" t="n">
-        <v>37.9770011901855</v>
+        <v>62.698</v>
       </c>
       <c r="D96" t="n">
-        <v>14.2600002288818</v>
+        <v>62.2</v>
       </c>
       <c r="E96" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>M 1.5 - 2 km ESE of Pacheco, CA</t>
+          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2 km ESE of Pacheco, CA</t>
+          <t>62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4278,38 +4278,38 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46095.54660127315</v>
+        <v>46096.55006834491</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46095.5919228125</v>
+        <v>46096.5511231713</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tx2026fdehwc</t>
+          <t>aka2026ffacwz</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-101.911</v>
+        <v>-154.211</v>
       </c>
       <c r="C97" t="n">
-        <v>32.378</v>
+        <v>58.934</v>
       </c>
       <c r="D97" t="n">
-        <v>8.667</v>
+        <v>126.4</v>
       </c>
       <c r="E97" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>M 1.2 - 24 km SW of Ackerly, Texas</t>
+          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>24 km SW of Ackerly, Texas</t>
+          <t>64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4318,38 +4318,38 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46095.54531115741</v>
+        <v>46096.54689578704</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46096.03998054398</v>
+        <v>46096.54852043981</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>nc75327267</t>
+          <t>uw62235651</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-122.798500061035</v>
+        <v>-124.0351666666667</v>
       </c>
       <c r="C98" t="n">
-        <v>38.8173332214355</v>
+        <v>47.33166666666666</v>
       </c>
       <c r="D98" t="n">
-        <v>2.51999998092651</v>
+        <v>23.98</v>
       </c>
       <c r="E98" t="n">
-        <v>1.13</v>
+        <v>1.73</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
+          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4358,38 +4358,38 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46095.53511898148</v>
+        <v>46096.54669189815</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46095.55717452546</v>
+        <v>46096.58038923611</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nn00912629</t>
+          <t>nc75327692</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-117.1159</v>
+        <v>-122.779335021973</v>
       </c>
       <c r="C99" t="n">
-        <v>37.2086</v>
+        <v>38.8115005493164</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0133</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="E99" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>M 1.3 - 45 km NW of Beatty, Nevada</t>
+          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>45 km NW of Beatty, Nevada</t>
+          <t>4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4398,38 +4398,38 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46095.53510384259</v>
+        <v>46096.54474907408</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46095.53669351852</v>
+        <v>46096.5710708449</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>pr71509873</t>
+          <t>us6000sgg9</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-66.8845</v>
+        <v>-77.3565</v>
       </c>
       <c r="C100" t="n">
-        <v>18.916</v>
+        <v>-45.6923</v>
       </c>
       <c r="D100" t="n">
-        <v>23.61</v>
+        <v>10</v>
       </c>
       <c r="E100" t="n">
-        <v>2.53</v>
+        <v>4.6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>M 2.5 - 47 km N of Hatillo, Puerto Rico</t>
+          <t>M 4.6 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>47 km N of Hatillo, Puerto Rico</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4438,38 +4438,38 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46095.53112465278</v>
+        <v>46096.53758378472</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46095.55221423611</v>
+        <v>46096.58026666666</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>aka2026fddqdo</t>
+          <t>us6000sgg8</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-142.536</v>
+        <v>-77.3313</v>
       </c>
       <c r="C101" t="n">
-        <v>62.285</v>
+        <v>-45.741</v>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E101" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>M 1.7 - 26 km ESE of Nabesna, Alaska</t>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>26 km ESE of Nabesna, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4478,38 +4478,38 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46095.5308918287</v>
+        <v>46096.53580871528</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46095.53217123842</v>
+        <v>46096.59747731481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>aka2026fdcpod</t>
+          <t>aka2026fezlzd</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-149.365</v>
+        <v>-150.155</v>
       </c>
       <c r="C102" t="n">
-        <v>62.309</v>
+        <v>61.309</v>
       </c>
       <c r="D102" t="n">
-        <v>54.2</v>
+        <v>35.8</v>
       </c>
       <c r="E102" t="n">
         <v>1.4</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>M 1.4 - 30 km ENE of Susitna North, Alaska</t>
+          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>30 km ENE of Susitna North, Alaska</t>
+          <t>11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4518,38 +4518,38 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46095.50947515047</v>
+        <v>46096.53327611111</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46095.51106810185</v>
+        <v>46096.53437532407</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>aka2026fdbymj</t>
+          <t>aka2026feywwv</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-141.715</v>
+        <v>-148.811</v>
       </c>
       <c r="C103" t="n">
-        <v>61.443</v>
+        <v>63.988</v>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>113.5</v>
       </c>
       <c r="E103" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>M 1.4 - 64 km E of McCarthy, Alaska</t>
+          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>64 km E of McCarthy, Alaska</t>
+          <t>15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4558,38 +4558,38 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46095.49578780092</v>
+        <v>46096.52110533565</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46095.88198071759</v>
+        <v>46096.52266071759</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>aka2026fdbvge</t>
+          <t>us6000sgg7</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-149.037</v>
+        <v>-72.47499999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>63.816</v>
+        <v>41.5071</v>
       </c>
       <c r="D104" t="n">
-        <v>3.9</v>
+        <v>6.072</v>
       </c>
       <c r="E104" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>M 1.4 - 5 km SW of Healy, Alaska</t>
+          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5 km SW of Healy, Alaska</t>
+          <t>2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4598,38 +4598,38 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46095.49308862269</v>
+        <v>46096.51831680556</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46095.49433715278</v>
+        <v>46097.0635559375</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nc75327262</t>
+          <t>aka2026feypws</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-118.524833679199</v>
+        <v>-151.884</v>
       </c>
       <c r="C105" t="n">
-        <v>37.454833984375</v>
+        <v>61.213</v>
       </c>
       <c r="D105" t="n">
-        <v>13.5500001907349</v>
+        <v>92</v>
       </c>
       <c r="E105" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>M 1.6 - 8 km NE of Round Valley, CA</t>
+          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8 km NE of Round Valley, CA</t>
+          <t>43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4638,38 +4638,38 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46095.48521180556</v>
+        <v>46096.51546960648</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46095.50507347222</v>
+        <v>46096.51679775463</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>aka2026fdbgbs</t>
+          <t>hv74917517</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-151.084</v>
+        <v>-155.388671875</v>
       </c>
       <c r="C106" t="n">
-        <v>60.677</v>
+        <v>19.2761669158936</v>
       </c>
       <c r="D106" t="n">
-        <v>71</v>
+        <v>29.1200008392334</v>
       </c>
       <c r="E106" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>M 1.6 - 11 km E of Nikiski, Alaska</t>
+          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>11 km E of Nikiski, Alaska</t>
+          <t>12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4678,38 +4678,38 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46095.48086649305</v>
+        <v>46096.51510231481</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46095.48225108796</v>
+        <v>46096.51755763889</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tx2026fdawqc</t>
+          <t>us6000sgg3</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-104.396</v>
+        <v>-72.49160000000001</v>
       </c>
       <c r="C107" t="n">
-        <v>31.672</v>
+        <v>41.4904</v>
       </c>
       <c r="D107" t="n">
-        <v>7.9656</v>
+        <v>6.63</v>
       </c>
       <c r="E107" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>M 1.6 - 55 km S of Whites City, New Mexico</t>
+          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>55 km S of Whites City, New Mexico</t>
+          <t>3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4718,38 +4718,38 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46095.47324049768</v>
+        <v>46096.51474966435</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46095.47518646991</v>
+        <v>46097.05646988426</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>aka2026fdawfa</t>
+          <t>us6000sgg2</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-146.257</v>
+        <v>155.7691</v>
       </c>
       <c r="C108" t="n">
-        <v>61.532</v>
+        <v>50.1375</v>
       </c>
       <c r="D108" t="n">
-        <v>15.8</v>
+        <v>93.238</v>
       </c>
       <c r="E108" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>M 3.2 - 44 km N of Valdez, Alaska</t>
+          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>44 km N of Valdez, Alaska</t>
+          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4758,38 +4758,38 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46095.47291107639</v>
+        <v>46096.50655835648</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46095.50066519676</v>
+        <v>46096.52194490741</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tx2026fdatrz</t>
+          <t>aka2026feycns</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-104.472</v>
+        <v>-148.959</v>
       </c>
       <c r="C109" t="n">
-        <v>31.607</v>
+        <v>63.283</v>
       </c>
       <c r="D109" t="n">
-        <v>3.8361</v>
+        <v>0.6</v>
       </c>
       <c r="E109" t="n">
         <v>1.5</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>M 1.5 - 63 km S of Whites City, New Mexico</t>
+          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>63 km S of Whites City, New Mexico</t>
+          <t>12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4798,38 +4798,38 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46095.47089748843</v>
+        <v>46096.50470625</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46095.50040792824</v>
+        <v>46096.50576539352</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nn00912622</t>
+          <t>ci41204535</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-116.5072</v>
+        <v>-119.474833333333</v>
       </c>
       <c r="C110" t="n">
-        <v>38.4542</v>
+        <v>34.3685</v>
       </c>
       <c r="D110" t="n">
-        <v>1.8632</v>
+        <v>0.54</v>
       </c>
       <c r="E110" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>M 1.6 - 76 km NE of Tonopah, Nevada</t>
+          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>76 km NE of Tonopah, Nevada</t>
+          <t>5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4838,38 +4838,38 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46095.4685462963</v>
+        <v>46096.49835740741</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46095.47066204861</v>
+        <v>46096.50080350695</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nc75327252</t>
+          <t>aka2026fewzkc</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-124.46900177002</v>
+        <v>-148.795</v>
       </c>
       <c r="C111" t="n">
-        <v>40.3064994812012</v>
+        <v>62.2</v>
       </c>
       <c r="D111" t="n">
-        <v>12.539999961853</v>
+        <v>22.1</v>
       </c>
       <c r="E111" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>M 3.2 - 16 km W of Petrolia, CA</t>
+          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>16 km W of Petrolia, CA</t>
+          <t>47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4878,38 +4878,38 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46095.4434332176</v>
+        <v>46096.48122515046</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46095.48426105324</v>
+        <v>46096.48264917824</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>aka2026fczlhg</t>
+          <t>us6000sgfx</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-153.184</v>
+        <v>-80.1019</v>
       </c>
       <c r="C112" t="n">
-        <v>59.849</v>
+        <v>0.5871</v>
       </c>
       <c r="D112" t="n">
-        <v>131.2</v>
+        <v>36.381</v>
       </c>
       <c r="E112" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>M 2.3 - 52 km E of Pedro Bay, Alaska</t>
+          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>52 km E of Pedro Bay, Alaska</t>
+          <t>9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4918,38 +4918,38 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46095.44315893519</v>
+        <v>46096.47494160879</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46095.46118101852</v>
+        <v>46096.4911</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>tx2026fczgra</t>
+          <t>pr71509923</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-104.119</v>
+        <v>-66.1071666666667</v>
       </c>
       <c r="C113" t="n">
-        <v>31.667</v>
+        <v>18.1251666666667</v>
       </c>
       <c r="D113" t="n">
-        <v>4.0448</v>
+        <v>24.58</v>
       </c>
       <c r="E113" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>M 1.9 - 49 km W of Mentone, Texas</t>
+          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4958,38 +4958,38 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46095.43945071759</v>
+        <v>46096.47251458334</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46095.44239887731</v>
+        <v>46096.60321875</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nc75327242</t>
+          <t>ci41204519</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-121.980834960938</v>
+        <v>-118.627833333333</v>
       </c>
       <c r="C114" t="n">
-        <v>37.8216667175293</v>
+        <v>34.6043333333333</v>
       </c>
       <c r="D114" t="n">
-        <v>9.47999954223633</v>
+        <v>10.64</v>
       </c>
       <c r="E114" t="n">
-        <v>2.02</v>
+        <v>1.13</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>M 2.0 - 2 km E of Danville, CA</t>
+          <t>M 1.1 - 13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2 km E of Danville, CA</t>
+          <t>13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4998,38 +4998,38 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46095.43391921296</v>
+        <v>46096.46653668981</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46095.45647990741</v>
+        <v>46096.46890145833</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>us6000sgag</t>
+          <t>nn00912706</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>134.0262</v>
+        <v>-119.5178</v>
       </c>
       <c r="C115" t="n">
-        <v>38.2275</v>
+        <v>38.4812</v>
       </c>
       <c r="D115" t="n">
-        <v>419.505</v>
+        <v>3.3162</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>M 4.0 - 250 km NNE of Ama, Japan</t>
+          <t>M 1.3 - 5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>250 km NNE of Ama, Japan</t>
+          <t>5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5038,38 +5038,38 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46095.43000553241</v>
+        <v>46096.46134278935</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46095.45789398148</v>
+        <v>46096.46294350694</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>aka2026fcytaw</t>
+          <t>nc75327672</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-147.775</v>
+        <v>-122.810333251953</v>
       </c>
       <c r="C116" t="n">
-        <v>64.908</v>
+        <v>38.8395004272461</v>
       </c>
       <c r="D116" t="n">
-        <v>16.1</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="E116" t="n">
-        <v>2.2</v>
+        <v>0.97</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>M 2.2 - 3 km W of Farmers Loop, Alaska</t>
+          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>3 km W of Farmers Loop, Alaska</t>
+          <t>8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5078,38 +5078,38 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46095.42845855324</v>
+        <v>46096.46108472222</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46095.42950167824</v>
+        <v>46096.49469679398</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>hv74917362</t>
+          <t>pr71509913</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-155.407836914062</v>
+        <v>-67.0566666666667</v>
       </c>
       <c r="C117" t="n">
-        <v>19.2481670379639</v>
+        <v>18.1476666666667</v>
       </c>
       <c r="D117" t="n">
-        <v>32.8800010681152</v>
+        <v>17.11</v>
       </c>
       <c r="E117" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>M 2.2 - 8 km NE of Pāhala, Hawaii</t>
+          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8 km NE of Pāhala, Hawaii</t>
+          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5118,38 +5118,38 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46095.42089629629</v>
+        <v>46096.44030868055</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46095.42425393518</v>
+        <v>46096.59237719907</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>aka2026fcydsf</t>
+          <t>aka2026feukwz</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-147.591</v>
+        <v>-147.764</v>
       </c>
       <c r="C118" t="n">
-        <v>60.613</v>
+        <v>60.385</v>
       </c>
       <c r="D118" t="n">
-        <v>18.7</v>
+        <v>14.9</v>
       </c>
       <c r="E118" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>M 1.9 - 57 km WSW of Tatitlek, Alaska</t>
+          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>57 km WSW of Tatitlek, Alaska</t>
+          <t>38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5158,38 +5158,38 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46095.41621864583</v>
+        <v>46096.42763064815</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46095.41741854166</v>
+        <v>46096.4286147338</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>tx2026fcxzqm</t>
+          <t>aka2026fetqyo</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-100.542</v>
+        <v>-150.43</v>
       </c>
       <c r="C119" t="n">
-        <v>32.797</v>
+        <v>60.896</v>
       </c>
       <c r="D119" t="n">
-        <v>0.8341</v>
+        <v>45.5</v>
       </c>
       <c r="E119" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>M 1.8 - 9 km SW of Rotan, Texas</t>
+          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>9 km SW of Rotan, Texas</t>
+          <t>14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5198,38 +5198,38 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46095.41282443287</v>
+        <v>46096.41156589121</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46095.41541297454</v>
+        <v>46096.41261650463</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>tx2026fcxogc</t>
+          <t>ci41204503</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-104.116</v>
+        <v>-117.464333333333</v>
       </c>
       <c r="C120" t="n">
-        <v>31.667</v>
+        <v>34.157</v>
       </c>
       <c r="D120" t="n">
-        <v>6.0999</v>
+        <v>6.87</v>
       </c>
       <c r="E120" t="n">
-        <v>2.7</v>
+        <v>0.98</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>M 2.7 - 49 km W of Mentone, Texas</t>
+          <t>M 1.0 - 7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5238,38 +5238,38 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46095.40363546296</v>
+        <v>46096.39763148148</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46095.89443695602</v>
+        <v>46096.39998002315</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>tx2026fcxnmu</t>
+          <t>aka2026fessqh</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-102.094</v>
+        <v>-152.317</v>
       </c>
       <c r="C121" t="n">
-        <v>32.349</v>
+        <v>60.36</v>
       </c>
       <c r="D121" t="n">
-        <v>3.9111</v>
+        <v>90.3</v>
       </c>
       <c r="E121" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>M 1.1 - 37 km NW of Stanton, Texas</t>
+          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>37 km NW of Stanton, Texas</t>
+          <t>49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5278,38 +5278,38 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46095.4030390625</v>
+        <v>46096.39196349537</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46095.47299325231</v>
+        <v>46096.39365355324</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>tx2026fcxkzg</t>
+          <t>nc75327657</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-104.117</v>
+        <v>-122.805335998535</v>
       </c>
       <c r="C122" t="n">
-        <v>31.666</v>
+        <v>38.8190002441406</v>
       </c>
       <c r="D122" t="n">
-        <v>5.3308</v>
+        <v>2.17000007629395</v>
       </c>
       <c r="E122" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>M 2.3 - 49 km W of Mentone, Texas</t>
+          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5318,38 +5318,38 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46095.40100652778</v>
+        <v>46096.37721527777</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46095.95376244213</v>
+        <v>46096.42173711806</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>tx2026fcxjaw</t>
+          <t>aka2026fertpz</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-104.121</v>
+        <v>-157.698</v>
       </c>
       <c r="C123" t="n">
-        <v>31.668</v>
+        <v>55.194</v>
       </c>
       <c r="D123" t="n">
-        <v>4.3438</v>
+        <v>4.2</v>
       </c>
       <c r="E123" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>M 2.6 - 49 km W of Mentone, Texas</t>
+          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5358,38 +5358,38 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46095.40024592593</v>
+        <v>46096.37321436343</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46095.41771622685</v>
+        <v>46096.37804444444</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>tx2026fcxjta</t>
+          <t>uw62235646</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-104.118</v>
+        <v>-121.9746666666667</v>
       </c>
       <c r="C124" t="n">
-        <v>31.665</v>
+        <v>47.82666666666667</v>
       </c>
       <c r="D124" t="n">
-        <v>6.0999</v>
+        <v>26.62</v>
       </c>
       <c r="E124" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>M 2.6 - 49 km W of Mentone, Texas</t>
+          <t>M 2.0 - 3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>49 km W of Mentone, Texas</t>
+          <t>3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5398,38 +5398,38 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46095.40024378472</v>
+        <v>46096.36272453704</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46095.40782453704</v>
+        <v>46096.47082604167</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>tx2026fcxdxl</t>
+          <t>us6000sgfk</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-104.319</v>
+        <v>-77.27330000000001</v>
       </c>
       <c r="C125" t="n">
-        <v>31.649</v>
+        <v>-45.5694</v>
       </c>
       <c r="D125" t="n">
-        <v>4.1032</v>
+        <v>10</v>
       </c>
       <c r="E125" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>M 1.9 - 58 km S of Whites City, New Mexico</t>
+          <t>M 5.3 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5438,38 +5438,38 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46095.39530927083</v>
+        <v>46096.35320680556</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46095.39790074074</v>
+        <v>46096.38260266204</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>tx2026fcxdjs</t>
+          <t>us6000sgfh</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-104.363</v>
+        <v>122.0755</v>
       </c>
       <c r="C126" t="n">
-        <v>31.593</v>
+        <v>24.3607</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>27.716</v>
       </c>
       <c r="E126" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>M 1.6 - 62 km WNW of Toyah, Texas</t>
+          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>62 km WNW of Toyah, Texas</t>
+          <t>54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5478,38 +5478,38 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46095.39488246528</v>
+        <v>46096.34370333333</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46095.41727866898</v>
+        <v>46096.53583686343</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>hv74917352</t>
+          <t>nn00912705</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-155.063003540039</v>
+        <v>-116.5611</v>
       </c>
       <c r="C127" t="n">
-        <v>19.3636665344238</v>
+        <v>38.4412</v>
       </c>
       <c r="D127" t="n">
-        <v>6.82999992370605</v>
+        <v>3.8472</v>
       </c>
       <c r="E127" t="n">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>M 1.8 - 13 km SE of Fern Forest, Hawaii</t>
+          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>13 km SE of Fern Forest, Hawaii</t>
+          <t>71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5518,38 +5518,38 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46095.38912592593</v>
+        <v>46096.34194375</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46095.39156377315</v>
+        <v>46096.34380362269</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>nn00912616</t>
+          <t>ci41204487</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-117.1065</v>
+        <v>-116.419666666667</v>
       </c>
       <c r="C128" t="n">
-        <v>37.2155</v>
+        <v>32.9405</v>
       </c>
       <c r="D128" t="n">
-        <v>0.03</v>
+        <v>4.88</v>
       </c>
       <c r="E128" t="n">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>M 1.3 - 45 km NW of Beatty, Nevada</t>
+          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>45 km NW of Beatty, Nevada</t>
+          <t>17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5558,38 +5558,38 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46095.38704399305</v>
+        <v>46096.32685023148</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46095.38848982639</v>
+        <v>46096.32921789352</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>nc75327232</t>
+          <t>ci41204479</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-121.320503234863</v>
+        <v>-117.2475</v>
       </c>
       <c r="C129" t="n">
-        <v>36.6573333740234</v>
+        <v>34.0556666666667</v>
       </c>
       <c r="D129" t="n">
-        <v>1.52999997138977</v>
+        <v>15.21</v>
       </c>
       <c r="E129" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>M 1.7 - 15 km S of Tres Pinos, CA</t>
+          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>15 km S of Tres Pinos, CA</t>
+          <t>2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5598,38 +5598,38 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46095.38549236111</v>
+        <v>46096.32684571759</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46095.40788662037</v>
+        <v>46096.32920631945</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>aka2026fcwnpr</t>
+          <t>aka2026fephrq</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-156.341</v>
+        <v>-150.634</v>
       </c>
       <c r="C130" t="n">
-        <v>56.513</v>
+        <v>60.036</v>
       </c>
       <c r="D130" t="n">
-        <v>62.7</v>
+        <v>63.6</v>
       </c>
       <c r="E130" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>M 3.3 - 128 km SSE of Ugashik, Alaska</t>
+          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>128 km SSE of Ugashik, Alaska</t>
+          <t>26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5638,38 +5638,38 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46095.38220442129</v>
+        <v>46096.32028525463</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46095.42112314815</v>
+        <v>46096.32365</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>aka2026fcwkyb</t>
+          <t>nn00912702</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-152.224</v>
+        <v>-116.579</v>
       </c>
       <c r="C131" t="n">
-        <v>59.653</v>
+        <v>38.4398</v>
       </c>
       <c r="D131" t="n">
-        <v>67.09999999999999</v>
+        <v>3.5596</v>
       </c>
       <c r="E131" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>M 2.9 - 26 km WSW of Anchor Point, Alaska</t>
+          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>26 km WSW of Anchor Point, Alaska</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5678,38 +5678,38 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46095.38009972222</v>
+        <v>46096.30809262732</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46095.41820648148</v>
+        <v>46096.31003199074</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ok2026fcfu</t>
+          <t>nc75327637</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-98.21438599</v>
+        <v>-121.911003112793</v>
       </c>
       <c r="C132" t="n">
-        <v>35.43252182</v>
+        <v>38.0525016784668</v>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>17.0200004577637</v>
       </c>
       <c r="E132" t="n">
-        <v>2.08</v>
+        <v>1.51</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>M 2.1 - 13 km ESE of Hinton, Oklahoma</t>
+          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>13 km ESE of Hinton, Oklahoma</t>
+          <t>4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5718,38 +5718,38 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46095.37014696759</v>
+        <v>46096.29875555556</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46095.37120069445</v>
+        <v>46096.34190163195</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>aka2026fcvpaw</t>
+          <t>us6000sgf9</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-150.883</v>
+        <v>72.05249999999999</v>
       </c>
       <c r="C133" t="n">
-        <v>61.959</v>
+        <v>37.629</v>
       </c>
       <c r="D133" t="n">
-        <v>0.7</v>
+        <v>196.241</v>
       </c>
       <c r="E133" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>M 1.6 - 27 km E of Skwentna, Alaska</t>
+          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>27 km E of Skwentna, Alaska</t>
+          <t>46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5758,38 +5758,38 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46095.36237780093</v>
+        <v>46096.29624704861</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46095.36346644676</v>
+        <v>46096.31303287037</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hv74917342</t>
+          <t>aka2026fenxtb</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-155.488494873047</v>
+        <v>-154.253</v>
       </c>
       <c r="C134" t="n">
-        <v>19.1765003204346</v>
+        <v>58.558</v>
       </c>
       <c r="D134" t="n">
-        <v>27.2299995422363</v>
+        <v>5</v>
       </c>
       <c r="E134" t="n">
-        <v>2.37</v>
+        <v>1.3</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>M 2.4 - 3 km SSW of Pāhala, Hawaii</t>
+          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>3 km SSW of Pāhala, Hawaii</t>
+          <t>96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5798,38 +5798,38 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46095.3602056713</v>
+        <v>46096.29131623843</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46095.36287916666</v>
+        <v>46096.29275974537</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>hv74917337</t>
+          <t>nc75327632</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-155.494003295898</v>
+        <v>-121.910331726074</v>
       </c>
       <c r="C135" t="n">
-        <v>19.1691665649414</v>
+        <v>38.0643348693848</v>
       </c>
       <c r="D135" t="n">
-        <v>24.0799999237061</v>
+        <v>18.6900005340576</v>
       </c>
       <c r="E135" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>M 1.9 - 4 km SSW of Pāhala, Hawaii</t>
+          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>4 km SSW of Pāhala, Hawaii</t>
+          <t>5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5838,38 +5838,38 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46095.35828587963</v>
+        <v>46096.28527893518</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46095.360790625</v>
+        <v>46096.32459672454</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>aka2026fcvjoi</t>
+          <t>tx2026fenmna</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-149.83</v>
+        <v>-104.203</v>
       </c>
       <c r="C136" t="n">
-        <v>64.30800000000001</v>
+        <v>31.669</v>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>7.2278</v>
       </c>
       <c r="E136" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>M 1.3 - 31 km W of Anderson, Alaska</t>
+          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>31 km W of Anderson, Alaska</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5878,38 +5878,38 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46095.35795271991</v>
+        <v>46096.28226224537</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46095.35929912037</v>
+        <v>46096.83936486111</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>us6000sg9g</t>
+          <t>tx2026fenktd</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-25.6013</v>
+        <v>-104.202</v>
       </c>
       <c r="C137" t="n">
-        <v>-58.7858</v>
+        <v>31.669</v>
       </c>
       <c r="D137" t="n">
-        <v>73.994</v>
+        <v>7.5739</v>
       </c>
       <c r="E137" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>M 5.2 - South Sandwich Islands region</t>
+          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>South Sandwich Islands region</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5918,38 +5918,38 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46095.35739234954</v>
+        <v>46096.28124563657</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46095.37358842593</v>
+        <v>46096.70278489583</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ci41204079</t>
+          <t>ci41204455</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-118.0855</v>
+        <v>-116.806333333333</v>
       </c>
       <c r="C138" t="n">
-        <v>35.3303333333333</v>
+        <v>33.2463333333333</v>
       </c>
       <c r="D138" t="n">
-        <v>7.19</v>
+        <v>10.1</v>
       </c>
       <c r="E138" t="n">
-        <v>1.16</v>
+        <v>0.95</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>M 1.2 - 24 km NNW of California City, CA</t>
+          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>24 km NNW of California City, CA</t>
+          <t>4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5958,38 +5958,38 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46095.35599143519</v>
+        <v>46096.27805949074</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46095.35835270833</v>
+        <v>46096.28047209491</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>nn00912612</t>
+          <t>nn00912698</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-117.1191</v>
+        <v>-116.6054</v>
       </c>
       <c r="C139" t="n">
-        <v>37.2198</v>
+        <v>38.2724</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0008</v>
+        <v>5.7486</v>
       </c>
       <c r="E139" t="n">
-        <v>1.17</v>
+        <v>2.11</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
+          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5998,38 +5998,38 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46095.35582130787</v>
+        <v>46096.26913202546</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46095.35709960648</v>
+        <v>46096.27123583333</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>nn00912609</t>
+          <t>nn00912696</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-116.4921</v>
+        <v>-116.3473</v>
       </c>
       <c r="C140" t="n">
-        <v>38.467</v>
+        <v>37.5427</v>
       </c>
       <c r="D140" t="n">
-        <v>1.6026</v>
+        <v>15.7841</v>
       </c>
       <c r="E140" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>M 1.7 - 78 km NE of Tonopah, Nevada</t>
+          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>78 km NE of Tonopah, Nevada</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6038,38 +6038,38 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46095.35160628472</v>
+        <v>46096.26722096065</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46095.35341947916</v>
+        <v>46096.26890163194</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ci41204071</t>
+          <t>pr71509903</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-117.079666666667</v>
+        <v>-66.7433333333333</v>
       </c>
       <c r="C141" t="n">
-        <v>34.021</v>
+        <v>18.043</v>
       </c>
       <c r="D141" t="n">
-        <v>18.33</v>
+        <v>16.94</v>
       </c>
       <c r="E141" t="n">
-        <v>0.98</v>
+        <v>2.09</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km WSW of Yucaipa, CA</t>
+          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>4 km WSW of Yucaipa, CA</t>
+          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6078,38 +6078,38 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46095.35113958333</v>
+        <v>46096.26509143518</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46095.35350167824</v>
+        <v>46096.27459479167</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>nn00912607</t>
+          <t>nn00912694</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-117.1176</v>
+        <v>-116.5678</v>
       </c>
       <c r="C142" t="n">
-        <v>37.2157</v>
+        <v>38.4757</v>
       </c>
       <c r="D142" t="n">
-        <v>1.6995</v>
+        <v>5.2112</v>
       </c>
       <c r="E142" t="n">
-        <v>1.2</v>
+        <v>2.01</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>M 1.2 - 46 km NW of Beatty, Nevada</t>
+          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>46 km NW of Beatty, Nevada</t>
+          <t>73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6118,38 +6118,38 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46095.35093659722</v>
+        <v>46096.26149202546</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46095.3522947338</v>
+        <v>46096.26338644676</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tx2026fcuwli</t>
+          <t>aka2026femdbx</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-102.216</v>
+        <v>-154.971</v>
       </c>
       <c r="C143" t="n">
-        <v>32.123</v>
+        <v>57.961</v>
       </c>
       <c r="D143" t="n">
-        <v>7.1155</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E143" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>M 1.1 - 19 km NW of Midland, Texas</t>
+          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>19 km NW of Midland, Texas</t>
+          <t>53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6158,38 +6158,38 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46095.34735415509</v>
+        <v>46096.25371178241</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46095.47295694445</v>
+        <v>46096.2741787037</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>aka2026fcutja</t>
+          <t>nn00912691</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-151.07</v>
+        <v>-116.5734</v>
       </c>
       <c r="C144" t="n">
-        <v>63.548</v>
+        <v>38.4423</v>
       </c>
       <c r="D144" t="n">
-        <v>5</v>
+        <v>1.9073</v>
       </c>
       <c r="E144" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>M 1.4 - 32 km E of Denali National Park, Alaska</t>
+          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>32 km E of Denali National Park, Alaska</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6198,38 +6198,38 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46095.34490104167</v>
+        <v>46096.25128945602</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46095.34610518518</v>
+        <v>46096.25308243056</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ci41204047</t>
+          <t>ci41204447</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-118.362</v>
+        <v>-116.168333333333</v>
       </c>
       <c r="C145" t="n">
-        <v>34.1451666666667</v>
+        <v>33.8886666666667</v>
       </c>
       <c r="D145" t="n">
-        <v>15.54</v>
+        <v>5.52</v>
       </c>
       <c r="E145" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>M 1.0 - 1 km NW of Universal City, CA</t>
+          <t>M 1.3 - 19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>1 km NW of Universal City, CA</t>
+          <t>19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6238,38 +6238,38 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46095.34305972223</v>
+        <v>46096.24517546297</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46095.34540800926</v>
+        <v>46096.25266435185</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>pr71509853</t>
+          <t>nc75327597</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-67.3061666666667</v>
+        <v>-121.635665893555</v>
       </c>
       <c r="C146" t="n">
-        <v>18.3425</v>
+        <v>36.9845008850098</v>
       </c>
       <c r="D146" t="n">
-        <v>22.48</v>
+        <v>8.989999771118161</v>
       </c>
       <c r="E146" t="n">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>M 2.4 - 5 km W of Rincón, Puerto Rico</t>
+          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>5 km W of Rincón, Puerto Rico</t>
+          <t>6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6278,38 +6278,38 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46095.34218113426</v>
+        <v>46096.24306736111</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46095.35034837963</v>
+        <v>46096.29676952546</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>aka2026fcukuz</t>
+          <t>aka2026fekujg</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-152.363</v>
+        <v>-150.947</v>
       </c>
       <c r="C147" t="n">
-        <v>59.584</v>
+        <v>60.457</v>
       </c>
       <c r="D147" t="n">
-        <v>79.90000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="E147" t="n">
         <v>1.6</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>M 1.6 - 35 km NW of Nanwalek, Alaska</t>
+          <t>M 1.6 - 7 km ESE of Soldotna, Alaska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>35 km NW of Nanwalek, Alaska</t>
+          <t>7 km ESE of Soldotna, Alaska</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6318,38 +6318,38 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>46095.3380100463</v>
+        <v>46096.22573243055</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46095.33962047454</v>
+        <v>46096.22721925926</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>uw62234461</t>
+          <t>us6000sgel</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-121.969</v>
+        <v>-77.3734</v>
       </c>
       <c r="C148" t="n">
-        <v>47.00283333333334</v>
+        <v>-45.6673</v>
       </c>
       <c r="D148" t="n">
-        <v>14.67</v>
+        <v>10</v>
       </c>
       <c r="E148" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>M 1.8 - 10 km SE of Carbonado, Washington</t>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>10 km SE of Carbonado, Washington</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6358,38 +6358,38 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>46095.32948564815</v>
+        <v>46096.22567266204</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46095.35692152777</v>
+        <v>46096.32872731482</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>aka2026fcttzo</t>
+          <t>nn00912689</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-150.606</v>
+        <v>-116.8458</v>
       </c>
       <c r="C149" t="n">
-        <v>62.796</v>
+        <v>38.2828</v>
       </c>
       <c r="D149" t="n">
-        <v>80.40000000000001</v>
+        <v>5.3648</v>
       </c>
       <c r="E149" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>M 1.6 - 34 km NNE of Petersville, Alaska</t>
+          <t>M 1.9 - 41 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>34 km NNE of Petersville, Alaska</t>
+          <t>41 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6398,38 +6398,38 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>46095.32446537037</v>
+        <v>46096.2170634838</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46095.32563423611</v>
+        <v>46096.21891450231</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>nc75327222</t>
+          <t>us6000sgeb</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-122.813163757324</v>
+        <v>139.3214</v>
       </c>
       <c r="C150" t="n">
-        <v>38.8216667175293</v>
+        <v>36.3919</v>
       </c>
       <c r="D150" t="n">
-        <v>2.85999989509583</v>
+        <v>94.896</v>
       </c>
       <c r="E150" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>M 1.4 - 7 km NW of The Geysers, CA</t>
+          <t>M 4.8 - 1 km SW of Kiryū, Japan</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>7 km NW of The Geysers, CA</t>
+          <t>1 km SW of Kiryū, Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6438,38 +6438,38 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>46095.30817083333</v>
+        <v>46096.21257785879</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46095.35232532407</v>
+        <v>46096.66760255787</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>aka2026fcsvoz</t>
+          <t>us6000sgea</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-156.864</v>
+        <v>-88.2997</v>
       </c>
       <c r="C151" t="n">
-        <v>57.941</v>
+        <v>12.6324</v>
       </c>
       <c r="D151" t="n">
-        <v>5.1</v>
+        <v>55.856</v>
       </c>
       <c r="E151" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>M 1.3 - 42 km SE of Egegik, Alaska</t>
+          <t>M 5.3 - 67 km SSW of Chirilagua, El Salvador</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>42 km SE of Egegik, Alaska</t>
+          <t>67 km SSW of Chirilagua, El Salvador</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6478,38 +6478,38 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>46095.30480278935</v>
+        <v>46096.20880520833</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46095.30609518519</v>
+        <v>46096.62601605324</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>hv74917327</t>
+          <t>nn00912685</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-155.509170532227</v>
+        <v>-117.1071</v>
       </c>
       <c r="C152" t="n">
-        <v>19.1896667480469</v>
+        <v>37.2044</v>
       </c>
       <c r="D152" t="n">
-        <v>27.75</v>
+        <v>3.7302</v>
       </c>
       <c r="E152" t="n">
-        <v>2.43</v>
+        <v>1.42</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>M 2.4 - 3 km WSW of Pāhala, Hawaii</t>
+          <t>M 1.4 - 45 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>3 km WSW of Pāhala, Hawaii</t>
+          <t>45 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6518,38 +6518,38 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>46095.30339525463</v>
+        <v>46096.20641787037</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46095.30639085648</v>
+        <v>46096.20811390047</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>hv74917322</t>
+          <t>nc75327582</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-155.383666992188</v>
+        <v>-124.411834716797</v>
       </c>
       <c r="C153" t="n">
-        <v>19.2728328704834</v>
+        <v>40.2961654663086</v>
       </c>
       <c r="D153" t="n">
-        <v>30.5599994659424</v>
+        <v>9.22999954223633</v>
       </c>
       <c r="E153" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>M 2.1 - 12 km NE of Pāhala, Hawaii</t>
+          <t>M 1.9 - 11 km WSW of Petrolia, CA</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>12 km NE of Pāhala, Hawaii</t>
+          <t>11 km WSW of Petrolia, CA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6558,38 +6558,38 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>46095.29624560185</v>
+        <v>46096.20098622685</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46095.29871585648</v>
+        <v>46096.24126574074</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tx2026fcsawu</t>
+          <t>us6000sge9</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-104.414</v>
+        <v>142.5299</v>
       </c>
       <c r="C154" t="n">
-        <v>31.654</v>
+        <v>37.3728</v>
       </c>
       <c r="D154" t="n">
-        <v>5.7571</v>
+        <v>38.742</v>
       </c>
       <c r="E154" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>M 1.6 - 57 km S of Whites City, New Mexico</t>
+          <t>M 4.3 - 134 km E of Tomioka, Japan</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>57 km S of Whites City, New Mexico</t>
+          <t>134 km E of Tomioka, Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6598,38 +6598,38 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>46095.28811275463</v>
+        <v>46096.20051677083</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46095.29004396991</v>
+        <v>46096.2139587963</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>aka2026fcsapu</t>
+          <t>hv74917492</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-147.001</v>
+        <v>-155.501159667969</v>
       </c>
       <c r="C155" t="n">
-        <v>61.201</v>
+        <v>19.1526660919189</v>
       </c>
       <c r="D155" t="n">
-        <v>6.6</v>
+        <v>27.9200000762939</v>
       </c>
       <c r="E155" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>M 1.4 - 35 km WNW of Valdez, Alaska</t>
+          <t>M 2.2 - 6 km SSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>35 km WNW of Valdez, Alaska</t>
+          <t>6 km SSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6638,38 +6638,38 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>46095.28789450231</v>
+        <v>46096.19672719907</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46095.28883819444</v>
+        <v>46096.19926747686</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>nc75327212</t>
+          <t>ci41204415</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-120.100997924805</v>
+        <v>-115.949666666667</v>
       </c>
       <c r="C156" t="n">
-        <v>36.1946678161621</v>
+        <v>32.903</v>
       </c>
       <c r="D156" t="n">
-        <v>8.72999954223633</v>
+        <v>7.34</v>
       </c>
       <c r="E156" t="n">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>M 1.8 - 1 km S of Huron, CA</t>
+          <t>M 1.1 - 19 km NNE of Ocotillo, CA</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>1 km S of Huron, CA</t>
+          <t>19 km NNE of Ocotillo, CA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6678,38 +6678,38 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>46095.28691342592</v>
+        <v>46096.19181168982</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46095.33843475694</v>
+        <v>46096.19425657408</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tx2026fcrrur</t>
+          <t>us6000sge4</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-101.926</v>
+        <v>-98.1546</v>
       </c>
       <c r="C157" t="n">
-        <v>32.102</v>
+        <v>35.4408</v>
       </c>
       <c r="D157" t="n">
-        <v>3.7297</v>
+        <v>10</v>
       </c>
       <c r="E157" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>M 1.4 - 13 km WSW of Stanton, Texas</t>
+          <t>M 2.7 - 18 km S of Calumet, Oklahoma</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>18 km S of Calumet, Oklahoma</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6718,38 +6718,38 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>46095.28321513889</v>
+        <v>46096.17096916667</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46095.47412729167</v>
+        <v>46096.19517141204</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>aka2026fcrocu</t>
+          <t>nn00912683</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-150.457</v>
+        <v>-115.2794</v>
       </c>
       <c r="C158" t="n">
-        <v>63.275</v>
+        <v>37.043</v>
       </c>
       <c r="D158" t="n">
-        <v>129.2</v>
+        <v>3.4848</v>
       </c>
       <c r="E158" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>M 2.2 - 69 km ESE of Denali National Park, Alaska</t>
+          <t>M 1.7 - 37 km SSW of Alamo, Nevada</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>69 km ESE of Denali National Park, Alaska</t>
+          <t>37 km SSW of Alamo, Nevada</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6758,38 +6758,38 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>46095.27783107639</v>
+        <v>46096.16868928241</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46095.28106825231</v>
+        <v>46096.17050155093</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tx2026fcrdwa</t>
+          <t>nn00912681</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-104.39</v>
+        <v>-116.7898</v>
       </c>
       <c r="C159" t="n">
-        <v>31.669</v>
+        <v>38.3409</v>
       </c>
       <c r="D159" t="n">
-        <v>6.8689</v>
+        <v>6.6979</v>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>M 2.0 - 56 km S of Whites City, New Mexico</t>
+          <t>M 1.8 - 49 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>56 km S of Whites City, New Mexico</t>
+          <t>49 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6798,38 +6798,38 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>46095.26955541666</v>
+        <v>46096.16567495371</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46095.98431269676</v>
+        <v>46096.16754114583</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>pr71509843</t>
+          <t>nc75327567</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-68.2081666666667</v>
+        <v>-120.093002319336</v>
       </c>
       <c r="C160" t="n">
-        <v>17.9796666666667</v>
+        <v>36.1063346862793</v>
       </c>
       <c r="D160" t="n">
-        <v>72.7</v>
+        <v>8.239999771118161</v>
       </c>
       <c r="E160" t="n">
-        <v>3.24</v>
+        <v>2.08</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>M 3.2 - 61 km SE of Boca de Yuma, Dominican Republic</t>
+          <t>M 2.1 - 11 km S of Huron, CA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>61 km SE of Boca de Yuma, Dominican Republic</t>
+          <t>11 km S of Huron, CA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6838,38 +6838,38 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>46095.26694097222</v>
+        <v>46096.16129594907</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46095.28683090278</v>
+        <v>46096.18564616898</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tx2026fcrabk</t>
+          <t>aka2026fehrkj</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-101.931</v>
+        <v>-149.708</v>
       </c>
       <c r="C161" t="n">
-        <v>32.103</v>
+        <v>62.155</v>
       </c>
       <c r="D161" t="n">
-        <v>3.7555</v>
+        <v>31.4</v>
       </c>
       <c r="E161" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>M 1.6 - 13 km WSW of Stanton, Texas</t>
+          <t>M 1.5 - 7 km E of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>7 km E of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6878,38 +6878,38 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>46095.26650071759</v>
+        <v>46096.16061565972</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46095.47247458333</v>
+        <v>46096.16211004629</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tx2026fcqynw</t>
+          <t>nn00912678</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-101.925</v>
+        <v>-117.1285</v>
       </c>
       <c r="C162" t="n">
-        <v>32.105</v>
+        <v>37.2457</v>
       </c>
       <c r="D162" t="n">
-        <v>4.2234</v>
+        <v>13.004</v>
       </c>
       <c r="E162" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>M 2.4 - 13 km WSW of Stanton, Texas</t>
+          <t>M 1.6 - 49 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>49 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6918,38 +6918,38 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>46095.26526702546</v>
+        <v>46096.16059528935</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46096.07358628472</v>
+        <v>46096.16208465278</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>us6000sg8q</t>
+          <t>ok2026fdrh</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-9.5571</v>
+        <v>-98.18229675000001</v>
       </c>
       <c r="C163" t="n">
-        <v>-47.4228</v>
+        <v>35.44195557</v>
       </c>
       <c r="D163" t="n">
-        <v>10</v>
+        <v>0.324695766</v>
       </c>
       <c r="E163" t="n">
-        <v>5.1</v>
+        <v>2.56</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>M 5.1 - southern Mid-Atlantic Ridge</t>
+          <t>M 2.6 - 16 km ESE of Hinton, Oklahoma</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>southern Mid-Atlantic Ridge</t>
+          <t>16 km ESE of Hinton, Oklahoma</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6958,38 +6958,38 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>46095.26202418981</v>
+        <v>46096.15941979166</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46095.27231527778</v>
+        <v>46096.19862199074</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tx2026fcqovv</t>
+          <t>aka2026fegqal</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-100.549</v>
+        <v>-152.568</v>
       </c>
       <c r="C164" t="n">
-        <v>32.794</v>
+        <v>60.006</v>
       </c>
       <c r="D164" t="n">
-        <v>1.5277</v>
+        <v>104.2</v>
       </c>
       <c r="E164" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>M 2.4 - 10 km SW of Rotan, Texas</t>
+          <t>M 1.3 - 47 km W of Happy Valley, Alaska</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>10 km SW of Rotan, Texas</t>
+          <t>47 km W of Happy Valley, Alaska</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6998,38 +6998,38 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>46095.25745070602</v>
+        <v>46096.13842898148</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46095.47303950231</v>
+        <v>46096.139836875</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tx2026fcqonn</t>
+          <t>tx2026fegnxw</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-100.55</v>
+        <v>-104.428</v>
       </c>
       <c r="C165" t="n">
-        <v>32.793</v>
+        <v>31.649</v>
       </c>
       <c r="D165" t="n">
-        <v>2.2403</v>
+        <v>7.1765</v>
       </c>
       <c r="E165" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>M 2.4 - 10 km SW of Rotan, Texas</t>
+          <t>M 1.8 - 58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>10 km SW of Rotan, Texas</t>
+          <t>58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7038,38 +7038,38 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>46095.25744922454</v>
+        <v>46096.13676635417</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46095.29300043981</v>
+        <v>46096.82320827546</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>nc75327197</t>
+          <t>tx2026fegkvq</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-122.781997680664</v>
+        <v>-104.424</v>
       </c>
       <c r="C166" t="n">
-        <v>38.8363342285156</v>
+        <v>31.653</v>
       </c>
       <c r="D166" t="n">
-        <v>1.54999995231628</v>
+        <v>6.0999</v>
       </c>
       <c r="E166" t="n">
-        <v>1.07</v>
+        <v>2.4</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>M 1.1 - 5 km WNW of Cobb, CA</t>
+          <t>M 2.4 - 58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>5 km WNW of Cobb, CA</t>
+          <t>58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7078,38 +7078,38 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>46095.25136446759</v>
+        <v>46096.13426206019</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46095.25248814815</v>
+        <v>46097.05598633102</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tx2026fcpyba</t>
+          <t>nn00912675</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-104.019</v>
+        <v>-116.8506</v>
       </c>
       <c r="C167" t="n">
-        <v>31.83</v>
+        <v>37.1599</v>
       </c>
       <c r="D167" t="n">
-        <v>16.8913</v>
+        <v>6.4687</v>
       </c>
       <c r="E167" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>M 1.6 - 42 km WNW of Mentone, Texas</t>
+          <t>M 1.1 - 29 km NNW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>42 km WNW of Mentone, Texas</t>
+          <t>29 km NNW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7118,38 +7118,38 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>46095.24523908565</v>
+        <v>46096.13401565972</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46095.25056459491</v>
+        <v>46096.13532696759</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>se60505173</t>
+          <t>aka2026feghag</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-78.8535</v>
+        <v>-152.61</v>
       </c>
       <c r="C168" t="n">
-        <v>37.4065</v>
+        <v>60.069</v>
       </c>
       <c r="D168" t="n">
-        <v>3.1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E168" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>M 2.1 - 6 km NNW of Appomattox, Virginia</t>
+          <t>M 2.3 - 50 km WNW of Happy Valley, Alaska</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>6 km NNW of Appomattox, Virginia</t>
+          <t>50 km WNW of Happy Valley, Alaska</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7158,38 +7158,38 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>46095.24491516204</v>
+        <v>46096.13122143519</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46095.56136655092</v>
+        <v>46096.13240575232</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>tx2026fcpyki</t>
+          <t>nc75327557</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-100.557</v>
+        <v>-122.757667541504</v>
       </c>
       <c r="C169" t="n">
-        <v>32.791</v>
+        <v>38.7836685180664</v>
       </c>
       <c r="D169" t="n">
-        <v>4.5654</v>
+        <v>2.04999995231628</v>
       </c>
       <c r="E169" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>M 2.9 - 10 km SW of Rotan, Texas</t>
+          <t>M 1.2 - 1 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>10 km SW of Rotan, Texas</t>
+          <t>1 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7198,38 +7198,38 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>46095.24420026621</v>
+        <v>46096.12735844908</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46095.25962405092</v>
+        <v>46096.17521668981</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>nn00912597</t>
+          <t>nc75327552</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-117.1175</v>
+        <v>-120.159332275391</v>
       </c>
       <c r="C170" t="n">
-        <v>37.2164</v>
+        <v>36.105167388916</v>
       </c>
       <c r="D170" t="n">
-        <v>0.0444</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="E170" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>M 1.2 - 46 km NW of Beatty, Nevada</t>
+          <t>M 1.4 - 12 km NNW of Avenal, CA</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>46 km NW of Beatty, Nevada</t>
+          <t>12 km NNW of Avenal, CA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7238,38 +7238,38 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>46095.23686648148</v>
+        <v>46096.12601481481</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46095.23832854167</v>
+        <v>46096.15440421296</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>nn00912595</t>
+          <t>hv74917472</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-117.118</v>
+        <v>-155.253005981445</v>
       </c>
       <c r="C171" t="n">
-        <v>37.2216</v>
+        <v>19.2596664428711</v>
       </c>
       <c r="D171" t="n">
-        <v>0.0643</v>
+        <v>24.2299995422363</v>
       </c>
       <c r="E171" t="n">
-        <v>1.23</v>
+        <v>2.36</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>M 1.2 - 47 km NW of Beatty, Nevada</t>
+          <t>M 2.4 - 20 km S of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>20 km S of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7278,38 +7278,38 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>46095.23179822916</v>
+        <v>46096.11974375</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46095.23326519676</v>
+        <v>46096.1222449074</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>us6000sg8i</t>
+          <t>hv74917477</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>176.4435</v>
+        <v>-155.235000610352</v>
       </c>
       <c r="C172" t="n">
-        <v>52.0909</v>
+        <v>19.2304992675781</v>
       </c>
       <c r="D172" t="n">
-        <v>10</v>
+        <v>27.8999996185303</v>
       </c>
       <c r="E172" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>M 4.4 - 236 km ESE of Attu Station, Alaska</t>
+          <t>M 2.6 - 23 km S of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>236 km ESE of Attu Station, Alaska</t>
+          <t>23 km S of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7318,38 +7318,38 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>46095.22228541667</v>
+        <v>46096.11969131944</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46095.39254373842</v>
+        <v>46096.12205555556</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>nc75327172</t>
+          <t>us6000sgdx</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-121.30883026123</v>
+        <v>152.8602</v>
       </c>
       <c r="C173" t="n">
-        <v>36.6568336486816</v>
+        <v>47.1076</v>
       </c>
       <c r="D173" t="n">
-        <v>4.17000007629395</v>
+        <v>85.952</v>
       </c>
       <c r="E173" t="n">
-        <v>1.81</v>
+        <v>4.3</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>M 1.8 - 15 km S of Tres Pinos, CA</t>
+          <t>M 4.3 - Kuril Islands</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>15 km S of Tres Pinos, CA</t>
+          <t>Kuril Islands</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7358,38 +7358,38 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>46095.21819664352</v>
+        <v>46096.11952268519</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>46095.26552178241</v>
+        <v>46096.14409768519</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tx2026fcontc</t>
+          <t>nc75327547</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>-104.403</v>
+        <v>-122.466499328613</v>
       </c>
       <c r="C174" t="n">
-        <v>31.657</v>
+        <v>37.5961685180664</v>
       </c>
       <c r="D174" t="n">
-        <v>5.177</v>
+        <v>9.72999954223633</v>
       </c>
       <c r="E174" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>M 2.1 - 57 km S of Whites City, New Mexico</t>
+          <t>M 1.5 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>57 km S of Whites City, New Mexico</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7398,38 +7398,38 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>46095.21465760416</v>
+        <v>46096.10495636574</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>46095.92457752315</v>
+        <v>46096.13706527778</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>aka2026fcolgu</t>
+          <t>nn00912672</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-153.226</v>
+        <v>-116.7812</v>
       </c>
       <c r="C175" t="n">
-        <v>59.591</v>
+        <v>38.3201</v>
       </c>
       <c r="D175" t="n">
-        <v>109.6</v>
+        <v>3.2364</v>
       </c>
       <c r="E175" t="n">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>M 1.3 - 54 km ESE of Pedro Bay, Alaska</t>
+          <t>M 1.9 - 48 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>54 km ESE of Pedro Bay, Alaska</t>
+          <t>48 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7438,38 +7438,38 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>46095.21267469908</v>
+        <v>46096.09975644676</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>46095.21408049769</v>
+        <v>46096.1015644213</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>us6000sg8b</t>
+          <t>us6000sgdm</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-90.6785</v>
+        <v>-111.8909</v>
       </c>
       <c r="C176" t="n">
-        <v>13.7887</v>
+        <v>32.5527</v>
       </c>
       <c r="D176" t="n">
-        <v>77.887</v>
+        <v>10</v>
       </c>
       <c r="E176" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>M 4.6 - 16 km S of Iztapa, Guatemala</t>
+          <t>M 2.5 - 5 km S of Tat Momoli, Arizona</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>16 km S of Iztapa, Guatemala</t>
+          <t>5 km S of Tat Momoli, Arizona</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7478,38 +7478,38 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>46095.21222631945</v>
+        <v>46096.09697278935</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>46095.26483412037</v>
+        <v>46096.61202137732</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ci41204015</t>
+          <t>ci41204383</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-117.714</v>
+        <v>-117.512</v>
       </c>
       <c r="C177" t="n">
-        <v>35.8901666666667</v>
+        <v>35.7071666666667</v>
       </c>
       <c r="D177" t="n">
-        <v>6.02</v>
+        <v>6.97</v>
       </c>
       <c r="E177" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>M 1.2 - 18 km ESE of Little Lake, CA</t>
+          <t>M 1.1 - 12 km SW of Searles Valley, CA</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>18 km ESE of Little Lake, CA</t>
+          <t>12 km SW of Searles Valley, CA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -7518,450 +7518,10 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>46095.20766203704</v>
+        <v>46096.09368009259</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>46095.21004755787</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>ci41204007</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>-116.802666666667</v>
-      </c>
-      <c r="C178" t="n">
-        <v>33.2805</v>
-      </c>
-      <c r="D178" t="n">
-        <v>12.26</v>
-      </c>
-      <c r="E178" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>M 1.1 - 6 km NW of Lake Henshaw, CA</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>6 km NW of Lake Henshaw, CA</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="n">
-        <v>46095.20175289352</v>
-      </c>
-      <c r="J178" s="2" t="n">
-        <v>46095.20411341435</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>nn00912593</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>-117.1141</v>
-      </c>
-      <c r="C179" t="n">
-        <v>37.2225</v>
-      </c>
-      <c r="D179" t="n">
-        <v>0.0456</v>
-      </c>
-      <c r="E179" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>47 km NW of Beatty, Nevada</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="n">
-        <v>46095.20134099537</v>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>46095.20256013889</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>nc75327167</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>-122.810997009277</v>
-      </c>
-      <c r="C180" t="n">
-        <v>38.8401679992676</v>
-      </c>
-      <c r="D180" t="n">
-        <v>1.67999994754791</v>
-      </c>
-      <c r="E180" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>8 km WNW of Cobb, CA</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="n">
-        <v>46095.19798460648</v>
-      </c>
-      <c r="J180" s="2" t="n">
-        <v>46095.23077265047</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>aka2026fcnmeg</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>-149.251</v>
-      </c>
-      <c r="C181" t="n">
-        <v>63.818</v>
-      </c>
-      <c r="D181" t="n">
-        <v>5</v>
-      </c>
-      <c r="E181" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>M 1.5 - 14 km WSW of Healy, Alaska</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>14 km WSW of Healy, Alaska</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="n">
-        <v>46095.19244901621</v>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>46095.19378540509</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>nc75327162</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>-122.818496704102</v>
-      </c>
-      <c r="C182" t="n">
-        <v>38.8294982910156</v>
-      </c>
-      <c r="D182" t="n">
-        <v>1.77999997138977</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>M 1.0 - 8 km NW of The Geysers, CA</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>8 km NW of The Geysers, CA</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I182" s="2" t="n">
-        <v>46095.18678217592</v>
-      </c>
-      <c r="J182" s="2" t="n">
-        <v>46095.20303782407</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>pr71509833</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>-63.9228333333333</v>
-      </c>
-      <c r="C183" t="n">
-        <v>18.5633333333333</v>
-      </c>
-      <c r="D183" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E183" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>M 3.4 - 95 km ENE of Cruz Bay, U.S. Virgin Islands</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>95 km ENE of Cruz Bay, U.S. Virgin Islands</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="n">
-        <v>46095.18653703704</v>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>46095.90381990741</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>nc75327157</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>-122.810333251953</v>
-      </c>
-      <c r="C184" t="n">
-        <v>38.8406677246094</v>
-      </c>
-      <c r="D184" t="n">
-        <v>1.82000005245209</v>
-      </c>
-      <c r="E184" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>M 1.5 - 8 km WNW of Cobb, CA</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>8 km WNW of Cobb, CA</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="n">
-        <v>46095.18409155092</v>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>46095.21343270833</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>aka2026fcnayu</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>-155.647</v>
-      </c>
-      <c r="C185" t="n">
-        <v>57.365</v>
-      </c>
-      <c r="D185" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="E185" t="n">
-        <v>2</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>M 2.0 - 75 km WSW of Karluk, Alaska</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>75 km WSW of Karluk, Alaska</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I185" s="2" t="n">
-        <v>46095.18333099537</v>
-      </c>
-      <c r="J185" s="2" t="n">
-        <v>46095.18473165509</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>ci41203999</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>-117.811166666667</v>
-      </c>
-      <c r="C186" t="n">
-        <v>35.3465</v>
-      </c>
-      <c r="D186" t="n">
-        <v>8.34</v>
-      </c>
-      <c r="E186" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>M 1.4 - 16 km W of Johannesburg, CA</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>16 km W of Johannesburg, CA</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="n">
-        <v>46095.18292777778</v>
-      </c>
-      <c r="J186" s="2" t="n">
-        <v>46095.18525748843</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>pr2026073001</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>-67.8205</v>
-      </c>
-      <c r="C187" t="n">
-        <v>18.2136</v>
-      </c>
-      <c r="D187" t="n">
-        <v>127</v>
-      </c>
-      <c r="E187" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>M 3.5 - 61 km WSW of Stella, Puerto Rico</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>61 km WSW of Stella, Puerto Rico</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="n">
-        <v>46095.18075243056</v>
-      </c>
-      <c r="J187" s="2" t="n">
-        <v>46095.22414583333</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>pr2026073000</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>-68.9123</v>
-      </c>
-      <c r="C188" t="n">
-        <v>18.4235</v>
-      </c>
-      <c r="D188" t="n">
-        <v>107</v>
-      </c>
-      <c r="E188" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>M 3.8 - 6 km E of La Romana, Dominican Republic</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>6 km E of La Romana, Dominican Republic</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="n">
-        <v>46095.17578113426</v>
-      </c>
-      <c r="J188" s="2" t="n">
-        <v>46095.21100451389</v>
+        <v>46096.09604913194</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/USGS.xlsx
+++ b/data/raw/USGS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:J176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,29 +487,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tx2026ffzaya</t>
+          <t>aka2026fgejkl</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-104.188</v>
+        <v>-150.208</v>
       </c>
       <c r="C2" t="n">
-        <v>31.703</v>
+        <v>62.214</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4731</v>
+        <v>4.4</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
+          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55 km SSE of Whites City, New Mexico</t>
+          <t>11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,38 +518,38 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46097.06930607639</v>
+        <v>46097.18073642361</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46097.08380681713</v>
+        <v>46097.1817900926</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hv74917612</t>
+          <t>nn00912748</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-155.139495849609</v>
+        <v>-116.7944</v>
       </c>
       <c r="C3" t="n">
-        <v>19.3330001831055</v>
+        <v>38.3084</v>
       </c>
       <c r="D3" t="n">
-        <v>3.76999998092651</v>
+        <v>2.8689</v>
       </c>
       <c r="E3" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,38 +558,38 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46097.06757199074</v>
+        <v>46097.18032635417</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46097.07008101852</v>
+        <v>46097.18299189815</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ci41204799</t>
+          <t>nn00912744</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-117.4825</v>
+        <v>-116.5751</v>
       </c>
       <c r="C4" t="n">
-        <v>35.601</v>
+        <v>38.2761</v>
       </c>
       <c r="D4" t="n">
-        <v>7.7</v>
+        <v>6.7167</v>
       </c>
       <c r="E4" t="n">
-        <v>0.95</v>
+        <v>2.18</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
+          <t>M 2.2 - 61 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18 km E of Ridgecrest, CA</t>
+          <t>61 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -598,38 +598,38 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46097.0600244213</v>
+        <v>46097.17459033565</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46097.06239535879</v>
+        <v>46097.17637523148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tx2026ffyeyx</t>
+          <t>ci41204855</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-104.176</v>
+        <v>-119.120666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>31.711</v>
+        <v>34.9321666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>7.4969</v>
+        <v>0.87</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M 1.9 - 54 km W of Mentone, Texas</t>
+          <t>M 2.3 - 10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>54 km W of Mentone, Texas</t>
+          <t>10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,38 +638,38 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46097.05150728009</v>
+        <v>46097.17414733797</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46097.06865469908</v>
+        <v>46097.18496361111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aka2026ffxzpn</t>
+          <t>nn00912743</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-150.668</v>
+        <v>-116.0158</v>
       </c>
       <c r="C6" t="n">
-        <v>63.582</v>
+        <v>37.795</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>2.4807</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
+          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>52 km E of Denali National Park, Alaska</t>
+          <t>29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -678,38 +678,38 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46097.0471140162</v>
+        <v>46097.17013881944</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46097.04869516204</v>
+        <v>46097.1716130787</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nn00912731</t>
+          <t>nc75328052</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-114.5508</v>
+        <v>-122.765167236328</v>
       </c>
       <c r="C7" t="n">
-        <v>37.2919</v>
+        <v>38.7836685180664</v>
       </c>
       <c r="D7" t="n">
-        <v>15.9298</v>
+        <v>4.19000005722046</v>
       </c>
       <c r="E7" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
+          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>36 km S of Caliente, Nevada</t>
+          <t>1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -718,38 +718,38 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46097.04372652778</v>
+        <v>46097.16834872685</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46097.04546596065</v>
+        <v>46097.18215899306</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ci41204783</t>
+          <t>nn00912742</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-116.366833333333</v>
+        <v>-117.5849</v>
       </c>
       <c r="C8" t="n">
-        <v>33.193</v>
+        <v>37.3479</v>
       </c>
       <c r="D8" t="n">
-        <v>7.35</v>
+        <v>3.7908</v>
       </c>
       <c r="E8" t="n">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
+          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7 km S of Borrego Springs, CA</t>
+          <t>45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -758,38 +758,38 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46097.04078981481</v>
+        <v>46097.15891554398</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46097.04323087963</v>
+        <v>46097.16036833333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nc75327962</t>
+          <t>nn00912740</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-120.523834228516</v>
+        <v>-116.3558</v>
       </c>
       <c r="C9" t="n">
-        <v>35.9671669006348</v>
+        <v>37.5573</v>
       </c>
       <c r="D9" t="n">
-        <v>6.94999980926514</v>
+        <v>8.4693</v>
       </c>
       <c r="E9" t="n">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
+          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11 km NW of Parkfield, CA</t>
+          <t>54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -798,38 +798,38 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46097.03950659722</v>
+        <v>46097.1542737963</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46097.05378733797</v>
+        <v>46097.15577996528</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aka2026ffxmpi</t>
+          <t>nc75328042</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-149.174</v>
+        <v>-122.843170166016</v>
       </c>
       <c r="C10" t="n">
-        <v>63.002</v>
+        <v>38.8208351135254</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2</v>
+        <v>1.67999994754791</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
+          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>44 km SSW of Cantwell, Alaska</t>
+          <t>9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -838,38 +838,38 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46097.03663675926</v>
+        <v>46097.15140474537</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46097.03896524305</v>
+        <v>46097.15253628472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nc75327947</t>
+          <t>nc75328037</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-124.239669799805</v>
+        <v>-122.839668273926</v>
       </c>
       <c r="C11" t="n">
-        <v>40.4664993286133</v>
+        <v>38.8219985961914</v>
       </c>
       <c r="D11" t="n">
-        <v>26.0400009155273</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
+          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12 km WSW of Rio Dell, CA</t>
+          <t>9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -878,38 +878,38 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46097.03397256944</v>
+        <v>46097.15081805555</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46097.08151043981</v>
+        <v>46097.17177512732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nn00912729</t>
+          <t>ci41204839</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-116.2867</v>
+        <v>-117.701833333333</v>
       </c>
       <c r="C12" t="n">
-        <v>37.418</v>
+        <v>35.8715</v>
       </c>
       <c r="D12" t="n">
-        <v>8.758599999999999</v>
+        <v>4.72</v>
       </c>
       <c r="E12" t="n">
-        <v>1.38</v>
+        <v>0.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -918,38 +918,38 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46097.03219180556</v>
+        <v>46097.14808055555</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46097.03392417824</v>
+        <v>46097.15049766203</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hv74917602</t>
+          <t>aka2026fgcope</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-155.143005371094</v>
+        <v>-149.454</v>
       </c>
       <c r="C13" t="n">
-        <v>19.3344993591309</v>
+        <v>62.553</v>
       </c>
       <c r="D13" t="n">
-        <v>4.25</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>2.06</v>
+        <v>1.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -958,38 +958,38 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46097.02269363426</v>
+        <v>46097.14301053241</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46097.02506747685</v>
+        <v>46097.14408171296</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nn00912728</t>
+          <t>nn00912738</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-116.8948</v>
+        <v>-116.4786</v>
       </c>
       <c r="C14" t="n">
-        <v>38.2511</v>
+        <v>38.4752</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7942</v>
+        <v>7.3424</v>
       </c>
       <c r="E14" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
+          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35 km NE of Tonopah, Nevada</t>
+          <t>79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -998,38 +998,38 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46097.02024291667</v>
+        <v>46097.13946230324</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46097.02206256944</v>
+        <v>46097.14130107639</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nn00912725</t>
+          <t>aka2026fgbzeh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-116.3002</v>
+        <v>-149.584</v>
       </c>
       <c r="C15" t="n">
-        <v>36.4986</v>
+        <v>62.358</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7633</v>
+        <v>56.7</v>
       </c>
       <c r="E15" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
+          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>42 km NW of Pahrump, Nevada</t>
+          <t>25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1038,38 +1038,38 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46097.01676708333</v>
+        <v>46097.13059196759</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46097.01802194444</v>
+        <v>46097.13160341435</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aka2026ffwkac</t>
+          <t>aka2026fgbuau</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-147.104</v>
+        <v>-146.643</v>
       </c>
       <c r="C16" t="n">
-        <v>61.221</v>
+        <v>61.432</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
+          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>41 km WNW of Valdez, Alaska</t>
+          <t>37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1078,38 +1078,38 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46097.01360875</v>
+        <v>46097.12645101852</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46097.01453715278</v>
+        <v>46097.12856479167</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nc75327937</t>
+          <t>nc75327997</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-120.16283416748</v>
+        <v>-122.785667419434</v>
       </c>
       <c r="C17" t="n">
-        <v>36.1510009765625</v>
+        <v>38.8154983520508</v>
       </c>
       <c r="D17" t="n">
-        <v>5.53000020980835</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M 1.8 - 8 km SW of Huron, CA</t>
+          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8 km SW of Huron, CA</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1118,38 +1118,38 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46097.00379861111</v>
+        <v>46097.10226643518</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46097.07108120371</v>
+        <v>46097.10338584491</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>aka2026ffvrqe</t>
+          <t>nc75327992</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-150.318</v>
+        <v>-122.786163330078</v>
       </c>
       <c r="C18" t="n">
-        <v>60.621</v>
+        <v>38.8153343200684</v>
       </c>
       <c r="D18" t="n">
-        <v>37.9</v>
+        <v>1.44000005722046</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8</v>
+        <v>1.49</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
+          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26 km ENE of Sterling, Alaska</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1158,38 +1158,38 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46096.99880960648</v>
+        <v>46097.09843321759</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46097.06023194444</v>
+        <v>46097.13356498843</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hv74917597</t>
+          <t>aka2026ffzydk</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-154.981170654297</v>
+        <v>-151.439</v>
       </c>
       <c r="C19" t="n">
-        <v>19.3976669311523</v>
+        <v>59.675</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.560000002384186</v>
+        <v>40.3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
+          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10 km SW of Leilani Estates, Hawaii</t>
+          <t>0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1198,38 +1198,38 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46096.99111076389</v>
+        <v>46097.08785851852</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46096.993578125</v>
+        <v>46097.0893715625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ci41204759</t>
+          <t>nn00912733</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-117.6875</v>
+        <v>-116.2619</v>
       </c>
       <c r="C20" t="n">
-        <v>35.0311666666667</v>
+        <v>38.6278</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.84</v>
+        <v>4.7494</v>
       </c>
       <c r="E20" t="n">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km NW of Boron, CA</t>
+          <t>M 2.7 - 95 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5 km NW of Boron, CA</t>
+          <t>95 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,38 +1238,38 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46096.98700925926</v>
+        <v>46097.08629175926</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46096.98945039352</v>
+        <v>46097.09325277778</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aka2026ffvcuk</t>
+          <t>ci41204823</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-147.706</v>
+        <v>-117.844666666667</v>
       </c>
       <c r="C21" t="n">
-        <v>63.18</v>
+        <v>36.4091666666667</v>
       </c>
       <c r="D21" t="n">
-        <v>4.3</v>
+        <v>3.71</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
+          <t>M 1.2 - 20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>66 km ESE of Cantwell, Alaska</t>
+          <t>20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46096.98682952546</v>
+        <v>46097.08612511574</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46097.05321805555</v>
+        <v>46097.08854572917</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>aka2026ffuxwl</t>
+          <t>tx2026ffzaya</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-149.464</v>
+        <v>-104.188</v>
       </c>
       <c r="C22" t="n">
-        <v>65.532</v>
+        <v>31.703</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>4.4731</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
+          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>32 km E of Rampart, Alaska</t>
+          <t>55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1318,38 +1318,38 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46096.98287351852</v>
+        <v>46097.06930607639</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46096.98871584491</v>
+        <v>46097.08380681713</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nc75327927</t>
+          <t>hv74917612</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-122.759002685547</v>
+        <v>-155.139495849609</v>
       </c>
       <c r="C23" t="n">
-        <v>38.779167175293</v>
+        <v>19.3330001831055</v>
       </c>
       <c r="D23" t="n">
-        <v>1.16999995708466</v>
+        <v>3.76999998092651</v>
       </c>
       <c r="E23" t="n">
-        <v>1.06</v>
+        <v>2.04</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
+          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0 km NW of The Geysers, CA</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1358,38 +1358,38 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46096.98031608796</v>
+        <v>46097.06757199074</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46096.9814612037</v>
+        <v>46097.07008101852</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nc75327922</t>
+          <t>ci41204799</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-120.615669250488</v>
+        <v>-117.4825</v>
       </c>
       <c r="C24" t="n">
-        <v>36.0485000610352</v>
+        <v>35.601</v>
       </c>
       <c r="D24" t="n">
-        <v>2.03999996185303</v>
+        <v>7.7</v>
       </c>
       <c r="E24" t="n">
-        <v>1.65</v>
+        <v>0.95</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
+          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>24 km NW of Parkfield, CA</t>
+          <t>18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1398,38 +1398,38 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46096.97481886574</v>
+        <v>46097.0600244213</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46097.03291697917</v>
+        <v>46097.06239535879</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aka2026fftzga</t>
+          <t>tx2026ffyeyx</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-147.469</v>
+        <v>-104.176</v>
       </c>
       <c r="C25" t="n">
-        <v>64.946</v>
+        <v>31.711</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>7.4969</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M 1.2 - 7 km E of Fox, Alaska</t>
+          <t>M 1.9 - 54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7 km E of Fox, Alaska</t>
+          <t>54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1438,38 +1438,38 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46096.96303546296</v>
+        <v>46097.05150728009</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46096.96398349537</v>
+        <v>46097.06865469908</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nc75327902</t>
+          <t>aka2026ffxzpn</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-124.639663696289</v>
+        <v>-150.668</v>
       </c>
       <c r="C26" t="n">
-        <v>40.34716796875</v>
+        <v>63.582</v>
       </c>
       <c r="D26" t="n">
-        <v>19.4500007629395</v>
+        <v>0.1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.76</v>
+        <v>1.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M 2.8 - 30 km W of Petrolia, CA</t>
+          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>30 km W of Petrolia, CA</t>
+          <t>52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1478,38 +1478,38 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46096.95174398148</v>
+        <v>46097.0471140162</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46097.04291712963</v>
+        <v>46097.04869516204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>us6000sgib</t>
+          <t>nn00912731</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>176.3522</v>
+        <v>-114.5508</v>
       </c>
       <c r="C27" t="n">
-        <v>52.1304</v>
+        <v>37.2919</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15.9298</v>
       </c>
       <c r="E27" t="n">
-        <v>4.6</v>
+        <v>1.58</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
+          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>229 km ESE of Attu Station, Alaska</t>
+          <t>36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1518,38 +1518,38 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46096.94854002315</v>
+        <v>46097.04372652778</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46097.03752361111</v>
+        <v>46097.04546596065</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nn00912719</t>
+          <t>ci41204783</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-119.7167</v>
+        <v>-116.366833333333</v>
       </c>
       <c r="C28" t="n">
-        <v>40.512</v>
+        <v>33.193</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7442</v>
+        <v>7.35</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
+          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>32 km WSW of Empire, Nevada</t>
+          <t>7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1558,38 +1558,38 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46096.94697967593</v>
+        <v>46097.04078981481</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46096.94864458333</v>
+        <v>46097.04323087963</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>aka2026fftern</t>
+          <t>nc75327962</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-145.732</v>
+        <v>-120.523834228516</v>
       </c>
       <c r="C29" t="n">
-        <v>62.165</v>
+        <v>35.9671669006348</v>
       </c>
       <c r="D29" t="n">
-        <v>4.6</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
+          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11 km WNW of Glennallen, Alaska</t>
+          <t>11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1598,38 +1598,38 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46096.94644289352</v>
+        <v>46097.03950659722</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46096.94759246528</v>
+        <v>46097.09886200231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>aka2026ffsxtw</t>
+          <t>aka2026ffxmpi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-150.289</v>
+        <v>-149.174</v>
       </c>
       <c r="C30" t="n">
-        <v>60.111</v>
+        <v>63.002</v>
       </c>
       <c r="D30" t="n">
-        <v>46.9</v>
+        <v>0.2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
+          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>46 km NE of Fox River, Alaska</t>
+          <t>44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46096.94087768519</v>
+        <v>46097.03663675926</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46096.94183203704</v>
+        <v>46097.03896524305</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>aka2026ffsvcz</t>
+          <t>nc75327947</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-141.243</v>
+        <v>-124.239669799805</v>
       </c>
       <c r="C31" t="n">
-        <v>61.573</v>
+        <v>40.4664993286133</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>26.0400009155273</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
+          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>90 km E of McCarthy, Alaska</t>
+          <t>12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1678,38 +1678,38 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46096.93874224537</v>
+        <v>46097.03397256944</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46096.93996863426</v>
+        <v>46097.08151043981</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hv74917587</t>
+          <t>nn00912729</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-155.404998779297</v>
+        <v>-116.2867</v>
       </c>
       <c r="C32" t="n">
-        <v>19.2546672821045</v>
+        <v>37.418</v>
       </c>
       <c r="D32" t="n">
-        <v>30.7900009155273</v>
+        <v>8.758599999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
+          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>9 km NE of Pāhala, Hawaii</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1718,38 +1718,38 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46096.93382974537</v>
+        <v>46097.03219180556</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46096.93618622685</v>
+        <v>46097.03392417824</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nc75327892</t>
+          <t>hv74917602</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-120.513832092285</v>
+        <v>-155.143005371094</v>
       </c>
       <c r="C33" t="n">
-        <v>35.9599990844727</v>
+        <v>19.3344993591309</v>
       </c>
       <c r="D33" t="n">
-        <v>10.1700000762939</v>
+        <v>4.25</v>
       </c>
       <c r="E33" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
+          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10 km NW of Parkfield, CA</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1758,38 +1758,38 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46096.92984074074</v>
+        <v>46097.02269363426</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46096.98773833334</v>
+        <v>46097.02506747685</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tx2026ffruyn</t>
+          <t>nn00912728</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-103.575</v>
+        <v>-116.8948</v>
       </c>
       <c r="C34" t="n">
-        <v>30.876</v>
+        <v>38.2511</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>4.7942</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
+          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20 km SE of Balmorhea, Texas</t>
+          <t>35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1798,38 +1798,38 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46096.91764664352</v>
+        <v>46097.02024291667</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46096.92133662037</v>
+        <v>46097.02206256944</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tx2026ffrhgd</t>
+          <t>nn00912725</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-101.817</v>
+        <v>-116.3002</v>
       </c>
       <c r="C35" t="n">
-        <v>32.349</v>
+        <v>36.4986</v>
       </c>
       <c r="D35" t="n">
-        <v>11.8727</v>
+        <v>1.7633</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
+          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21 km SSW of Ackerly, Texas</t>
+          <t>42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1838,38 +1838,38 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46096.90660459491</v>
+        <v>46097.01676708333</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46096.91322768519</v>
+        <v>46097.01802194444</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nc75327882</t>
+          <t>aka2026ffwkac</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-122.730499267578</v>
+        <v>-147.104</v>
       </c>
       <c r="C36" t="n">
-        <v>38.7738342285156</v>
+        <v>61.221</v>
       </c>
       <c r="D36" t="n">
-        <v>2.02999997138977</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km E of The Geysers, CA</t>
+          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2 km E of The Geysers, CA</t>
+          <t>41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1878,38 +1878,38 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46096.90556168981</v>
+        <v>46097.01360875</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46096.92179327546</v>
+        <v>46097.01453715278</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>aka2026ffqxwe</t>
+          <t>nc75327937</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-145.627</v>
+        <v>-120.16283416748</v>
       </c>
       <c r="C37" t="n">
-        <v>62.093</v>
+        <v>36.1510009765625</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E37" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
+          <t>M 1.8 - 8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4 km WSW of Glennallen, Alaska</t>
+          <t>8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1918,38 +1918,38 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46096.89903701389</v>
+        <v>46097.00379861111</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46096.90023371528</v>
+        <v>46097.07108120371</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nn00912718</t>
+          <t>aka2026ffvrqe</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-117.1162</v>
+        <v>-150.318</v>
       </c>
       <c r="C38" t="n">
-        <v>37.2236</v>
+        <v>60.621</v>
       </c>
       <c r="D38" t="n">
-        <v>0.039</v>
+        <v>37.9</v>
       </c>
       <c r="E38" t="n">
-        <v>1.08</v>
+        <v>2.8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
+          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1958,38 +1958,38 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46096.8946965625</v>
+        <v>46096.99880960648</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46096.89624318287</v>
+        <v>46097.06023194444</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nc75327877</t>
+          <t>hv74917597</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-121.053001403809</v>
+        <v>-154.981170654297</v>
       </c>
       <c r="C39" t="n">
-        <v>36.4648323059082</v>
+        <v>19.3976669311523</v>
       </c>
       <c r="D39" t="n">
-        <v>0.209999993443489</v>
+        <v>-0.560000002384186</v>
       </c>
       <c r="E39" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
+          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11 km SE of Pinnacles, CA</t>
+          <t>10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1998,38 +1998,38 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46096.89354375</v>
+        <v>46096.99111076389</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46096.95303508102</v>
+        <v>46096.993578125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>us6000sghx</t>
+          <t>ci41204759</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-68.8159</v>
+        <v>-117.6875</v>
       </c>
       <c r="C40" t="n">
-        <v>-21.1625</v>
+        <v>35.0311666666667</v>
       </c>
       <c r="D40" t="n">
-        <v>120.691</v>
+        <v>-0.84</v>
       </c>
       <c r="E40" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
+          <t>M 1.3 - 5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>58 km W of Ollagüe, Chile</t>
+          <t>5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2038,38 +2038,38 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46096.89260434028</v>
+        <v>46096.98700925926</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46097.01954907407</v>
+        <v>46096.98945039352</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aka2026ffqnha</t>
+          <t>aka2026ffvcuk</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-146.565</v>
+        <v>-147.706</v>
       </c>
       <c r="C41" t="n">
-        <v>61.519</v>
+        <v>63.18</v>
       </c>
       <c r="D41" t="n">
-        <v>38.2</v>
+        <v>4.3</v>
       </c>
       <c r="E41" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
+          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>44 km NNW of Valdez, Alaska</t>
+          <t>66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2078,38 +2078,38 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46096.89050962963</v>
+        <v>46096.98682952546</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46096.89142732639</v>
+        <v>46097.05321805555</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tx2026ffqmcg</t>
+          <t>aka2026ffuxwl</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-101.512</v>
+        <v>-149.464</v>
       </c>
       <c r="C42" t="n">
-        <v>31.874</v>
+        <v>65.532</v>
       </c>
       <c r="D42" t="n">
-        <v>3.2716</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
+          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3 km WNW of Garden City, Texas</t>
+          <t>32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2118,38 +2118,38 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46096.88956126157</v>
+        <v>46096.98287351852</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46096.9711172801</v>
+        <v>46096.98871584491</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nn00912716</t>
+          <t>nc75327927</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-116.5976</v>
+        <v>-122.759002685547</v>
       </c>
       <c r="C43" t="n">
-        <v>38.2879</v>
+        <v>38.779167175293</v>
       </c>
       <c r="D43" t="n">
-        <v>4.9318</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E43" t="n">
-        <v>2.04</v>
+        <v>1.06</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
+          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>60 km ENE of Tonopah, Nevada</t>
+          <t>0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2158,38 +2158,38 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46096.88044799768</v>
+        <v>46096.98031608796</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46096.88234515046</v>
+        <v>46096.9814612037</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aka2026ffpwxx</t>
+          <t>nc75327922</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-150.536</v>
+        <v>-120.615669250488</v>
       </c>
       <c r="C44" t="n">
-        <v>60.816</v>
+        <v>36.0485000610352</v>
       </c>
       <c r="D44" t="n">
-        <v>14.2</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="E44" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
+          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 km SE of Point Possession, Alaska</t>
+          <t>24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2198,38 +2198,38 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46096.87733195602</v>
+        <v>46096.97481886574</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46096.87884059027</v>
+        <v>46097.03291697917</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tx2026ffpmmk</t>
+          <t>aka2026fftzga</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-102.596</v>
+        <v>-147.469</v>
       </c>
       <c r="C45" t="n">
-        <v>32.426</v>
+        <v>64.946</v>
       </c>
       <c r="D45" t="n">
-        <v>7.1182</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
+          <t>M 1.2 - 7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>12 km NNW of Andrews, Texas</t>
+          <t>7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2238,38 +2238,38 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46096.86891956018</v>
+        <v>46096.96303546296</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46096.87235497685</v>
+        <v>46096.96398349537</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aka2026ffpbrz</t>
+          <t>nc75327902</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-151.569</v>
+        <v>-124.639663696289</v>
       </c>
       <c r="C46" t="n">
-        <v>61.397</v>
+        <v>40.34716796875</v>
       </c>
       <c r="D46" t="n">
-        <v>76.90000000000001</v>
+        <v>19.4500007629395</v>
       </c>
       <c r="E46" t="n">
-        <v>1.4</v>
+        <v>2.76</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
+          <t>M 2.8 - 30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>38 km NW of Beluga, Alaska</t>
+          <t>30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2278,38 +2278,38 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46096.86023665509</v>
+        <v>46096.95174398148</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46096.86153666666</v>
+        <v>46097.04291712963</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aka2026ffoxwo</t>
+          <t>us6000sgib</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-153.073</v>
+        <v>176.3522</v>
       </c>
       <c r="C47" t="n">
-        <v>60.494</v>
+        <v>52.1304</v>
       </c>
       <c r="D47" t="n">
-        <v>146.3</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
+          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>75 km ENE of Port Alsworth, Alaska</t>
+          <t>229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2318,38 +2318,38 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46096.85716821759</v>
+        <v>46096.94854002315</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46096.85982177083</v>
+        <v>46097.14299561342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tx2026ffolko</t>
+          <t>nn00912719</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-104.401</v>
+        <v>-119.7167</v>
       </c>
       <c r="C48" t="n">
-        <v>31.692</v>
+        <v>40.512</v>
       </c>
       <c r="D48" t="n">
-        <v>4.8181</v>
+        <v>0.7442</v>
       </c>
       <c r="E48" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
+          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>53 km S of Whites City, New Mexico</t>
+          <t>32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2358,38 +2358,38 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46096.84736503472</v>
+        <v>46096.94697967593</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46096.93883732639</v>
+        <v>46096.94864458333</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nc75327852</t>
+          <t>aka2026fftern</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-122.464164733887</v>
+        <v>-145.732</v>
       </c>
       <c r="C49" t="n">
-        <v>37.5973320007324</v>
+        <v>62.165</v>
       </c>
       <c r="D49" t="n">
-        <v>9.090000152587891</v>
+        <v>4.6</v>
       </c>
       <c r="E49" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
+          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2398,38 +2398,38 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46096.84368958334</v>
+        <v>46096.94644289352</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46096.84483373843</v>
+        <v>46096.94759246528</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>aka2026ffogkg</t>
+          <t>aka2026ffsxtw</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-150.241</v>
+        <v>-150.289</v>
       </c>
       <c r="C50" t="n">
-        <v>61.578</v>
+        <v>60.111</v>
       </c>
       <c r="D50" t="n">
-        <v>30.7</v>
+        <v>46.9</v>
       </c>
       <c r="E50" t="n">
         <v>1.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
+          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14 km ENE of Susitna, Alaska</t>
+          <t>46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2438,38 +2438,38 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46096.84307547453</v>
+        <v>46096.94087768519</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46096.84451351852</v>
+        <v>46096.94183203704</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nc75327847</t>
+          <t>aka2026ffsvcz</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-122.757667541504</v>
+        <v>-141.243</v>
       </c>
       <c r="C51" t="n">
-        <v>38.7918319702148</v>
+        <v>61.573</v>
       </c>
       <c r="D51" t="n">
-        <v>0.689999997615814</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km N of The Geysers, CA</t>
+          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2 km N of The Geysers, CA</t>
+          <t>90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2478,38 +2478,38 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46096.84258912037</v>
+        <v>46096.93874224537</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46096.84373324074</v>
+        <v>46096.93996863426</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ci41204687</t>
+          <t>hv74917587</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-117.249</v>
+        <v>-155.404998779297</v>
       </c>
       <c r="C52" t="n">
-        <v>33.9988333333333</v>
+        <v>19.2546672821045</v>
       </c>
       <c r="D52" t="n">
-        <v>10.86</v>
+        <v>30.7900009155273</v>
       </c>
       <c r="E52" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
+          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>6 km SSE of Loma Linda, CA</t>
+          <t>9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2518,38 +2518,38 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46096.83063032408</v>
+        <v>46096.93382974537</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46096.83300278935</v>
+        <v>46096.93618622685</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>nn00912714</t>
+          <t>nc75327892</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-116.7227</v>
+        <v>-120.513832092285</v>
       </c>
       <c r="C53" t="n">
-        <v>38.3427</v>
+        <v>35.9599990844727</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1382</v>
+        <v>10.1700000762939</v>
       </c>
       <c r="E53" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
+          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>53 km NE of Tonopah, Nevada</t>
+          <t>10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2558,38 +2558,38 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46096.82208777778</v>
+        <v>46096.92984074074</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46096.82386192129</v>
+        <v>46096.98773833334</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>aka2026ffmxvv</t>
+          <t>tx2026ffruyn</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-151.974</v>
+        <v>-103.575</v>
       </c>
       <c r="C54" t="n">
-        <v>60.349</v>
+        <v>30.876</v>
       </c>
       <c r="D54" t="n">
-        <v>77.2</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
+          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>34 km WNW of Clam Gulch, Alaska</t>
+          <t>20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2598,38 +2598,38 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46096.81522726852</v>
+        <v>46096.91764664352</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46096.81638251158</v>
+        <v>46096.92133662037</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nc75327827</t>
+          <t>tx2026ffrhgd</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-121.9375</v>
+        <v>-101.817</v>
       </c>
       <c r="C55" t="n">
-        <v>37.7731666666667</v>
+        <v>32.349</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>11.8727</v>
       </c>
       <c r="E55" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
+          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4 km ESE of San Ramon, CA</t>
+          <t>21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2638,38 +2638,38 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46096.81305393518</v>
+        <v>46096.90660459491</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46097.01551917824</v>
+        <v>46096.91322768519</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>nc75327822</t>
+          <t>nc75327882</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-122.787170410156</v>
+        <v>-122.730499267578</v>
       </c>
       <c r="C56" t="n">
-        <v>38.7934989929199</v>
+        <v>38.7738342285156</v>
       </c>
       <c r="D56" t="n">
-        <v>2.92000007629395</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="E56" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
+          <t>M 1.0 - 2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2678,38 +2678,38 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46096.81298229167</v>
+        <v>46096.90556168981</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46096.86627753473</v>
+        <v>46096.92179327546</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>us6000sghq</t>
+          <t>aka2026ffqxwe</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>49.7256</v>
+        <v>-145.627</v>
       </c>
       <c r="C57" t="n">
-        <v>32.4853</v>
+        <v>62.093</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
+          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>62 km SW of Fereydūnshahr, Iran</t>
+          <t>4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2718,38 +2718,38 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46096.8103829051</v>
+        <v>46096.89903701389</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46096.86111157407</v>
+        <v>46096.90023371528</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>aka2026ffmjyx</t>
+          <t>nn00912718</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-149.647</v>
+        <v>-117.1162</v>
       </c>
       <c r="C58" t="n">
-        <v>63.036</v>
+        <v>37.2236</v>
       </c>
       <c r="D58" t="n">
-        <v>76.40000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="E58" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
+          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>52 km SW of Cantwell, Alaska</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2758,38 +2758,38 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46096.80405828704</v>
+        <v>46096.8946965625</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46096.80508491898</v>
+        <v>46096.89624318287</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>us6000sghd</t>
+          <t>nc75327877</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>142.6105</v>
+        <v>-121.053001403809</v>
       </c>
       <c r="C59" t="n">
-        <v>41.4045</v>
+        <v>36.4648323059082</v>
       </c>
       <c r="D59" t="n">
-        <v>42.986</v>
+        <v>0.209999993443489</v>
       </c>
       <c r="E59" t="n">
-        <v>4.9</v>
+        <v>1.65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
+          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>84 km SSW of Honchō, Japan</t>
+          <t>11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2798,38 +2798,38 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46096.78951814815</v>
+        <v>46096.89354375</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46096.84466623842</v>
+        <v>46096.95303508102</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>aka2026fflqih</t>
+          <t>us6000sghx</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-150.765</v>
+        <v>-68.8159</v>
       </c>
       <c r="C60" t="n">
-        <v>63.04</v>
+        <v>-21.1625</v>
       </c>
       <c r="D60" t="n">
-        <v>117.3</v>
+        <v>120.691</v>
       </c>
       <c r="E60" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
+          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>60 km N of Petersville, Alaska</t>
+          <t>58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2838,38 +2838,38 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46096.78820800926</v>
+        <v>46096.89260434028</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46096.79154229166</v>
+        <v>46097.01954907407</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>us6000sghb</t>
+          <t>aka2026ffqnha</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>131.6063</v>
+        <v>-146.565</v>
       </c>
       <c r="C61" t="n">
-        <v>31.4194</v>
+        <v>61.519</v>
       </c>
       <c r="D61" t="n">
-        <v>32.903</v>
+        <v>38.2</v>
       </c>
       <c r="E61" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
+          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>30 km SE of Nichinan, Japan</t>
+          <t>44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2878,38 +2878,38 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46096.77722483796</v>
+        <v>46096.89050962963</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46096.91079450231</v>
+        <v>46096.89142732639</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>us6000sgh9</t>
+          <t>tx2026ffqmcg</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-77.5782</v>
+        <v>-101.512</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.3215</v>
+        <v>31.874</v>
       </c>
       <c r="D62" t="n">
-        <v>218.126</v>
+        <v>3.2716</v>
       </c>
       <c r="E62" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
+          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>44 km SE of Tena, Ecuador</t>
+          <t>3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2918,38 +2918,38 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46096.77198028936</v>
+        <v>46096.88956126157</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46096.78392407407</v>
+        <v>46096.9711172801</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nc75327792</t>
+          <t>nn00912716</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-122.471336364746</v>
+        <v>-116.5976</v>
       </c>
       <c r="C63" t="n">
-        <v>37.5974998474121</v>
+        <v>38.2879</v>
       </c>
       <c r="D63" t="n">
-        <v>9.72999954223633</v>
+        <v>4.9318</v>
       </c>
       <c r="E63" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
+          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2 km SE of Pacifica, CA</t>
+          <t>60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2958,38 +2958,38 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46096.77132291667</v>
+        <v>46096.88044799768</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46096.81413002315</v>
+        <v>46096.88234515046</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>aka2026ffklqv</t>
+          <t>aka2026ffpwxx</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-155.854</v>
+        <v>-150.536</v>
       </c>
       <c r="C64" t="n">
-        <v>57.153</v>
+        <v>60.816</v>
       </c>
       <c r="D64" t="n">
-        <v>63.2</v>
+        <v>14.2</v>
       </c>
       <c r="E64" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
+          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>96 km WSW of Karluk, Alaska</t>
+          <t>14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2998,38 +2998,38 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46096.76349226852</v>
+        <v>46096.87733195602</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46096.76507798611</v>
+        <v>46096.87884059027</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>nc75327787</t>
+          <t>tx2026ffpmmk</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-123.346832275391</v>
+        <v>-102.596</v>
       </c>
       <c r="C65" t="n">
-        <v>39.476001739502</v>
+        <v>32.426</v>
       </c>
       <c r="D65" t="n">
-        <v>4.19999980926514</v>
+        <v>7.1182</v>
       </c>
       <c r="E65" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
+          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>5 km NE of Brooktrails, CA</t>
+          <t>12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3038,38 +3038,38 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46096.7527207176</v>
+        <v>46096.86891956018</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46096.79673230324</v>
+        <v>46096.87235497685</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>aka2026ffjrwj</t>
+          <t>aka2026ffpbrz</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-149.163</v>
+        <v>-151.569</v>
       </c>
       <c r="C66" t="n">
-        <v>62.869</v>
+        <v>61.397</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
+          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>59 km S of Cantwell, Alaska</t>
+          <t>38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3078,38 +3078,38 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46096.74754356482</v>
+        <v>46096.86023665509</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46096.7486603125</v>
+        <v>46096.86153666666</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>aka2026ffjpxp</t>
+          <t>aka2026ffoxwo</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-152.555</v>
+        <v>-153.073</v>
       </c>
       <c r="C67" t="n">
-        <v>59.7</v>
+        <v>60.494</v>
       </c>
       <c r="D67" t="n">
-        <v>76.90000000000001</v>
+        <v>146.3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
+          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>41 km WSW of Anchor Point, Alaska</t>
+          <t>75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3118,38 +3118,38 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46096.74597070602</v>
+        <v>46096.85716821759</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46096.74724846065</v>
+        <v>46096.85982177083</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>us6000sgh3</t>
+          <t>tx2026ffolko</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>128.5163</v>
+        <v>-104.401</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.3925</v>
+        <v>31.692</v>
       </c>
       <c r="D68" t="n">
-        <v>137.104</v>
+        <v>4.8181</v>
       </c>
       <c r="E68" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
+          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>208 km NE of Lospalos, Timor Leste</t>
+          <t>53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3158,38 +3158,38 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46096.7350890625</v>
+        <v>46096.84736503472</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46096.81851898148</v>
+        <v>46096.93883732639</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ci41204623</t>
+          <t>nc75327852</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-116.638166666667</v>
+        <v>-122.464164733887</v>
       </c>
       <c r="C69" t="n">
-        <v>32.8055</v>
+        <v>37.5973320007324</v>
       </c>
       <c r="D69" t="n">
-        <v>16.68</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="E69" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10 km W of Pine Valley, CA</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3198,38 +3198,38 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46096.72295416667</v>
+        <v>46096.84368958334</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46096.72542263889</v>
+        <v>46096.84483373843</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>aka2026ffhzps</t>
+          <t>aka2026ffogkg</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-146.822</v>
+        <v>-150.241</v>
       </c>
       <c r="C70" t="n">
-        <v>60.719</v>
+        <v>61.578</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>30.7</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
+          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18 km SSW of Tatitlek, Alaska</t>
+          <t>14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46096.71188380787</v>
+        <v>46096.84307547453</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46096.71385545139</v>
+        <v>46096.84451351852</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tx2026ffhpux</t>
+          <t>nc75327847</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-103.799</v>
+        <v>-122.757667541504</v>
       </c>
       <c r="C71" t="n">
-        <v>31.021</v>
+        <v>38.7918319702148</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="E71" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
+          <t>M 1.0 - 2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>6 km NW of Balmorhea, Texas</t>
+          <t>2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3278,38 +3278,38 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46096.70398288195</v>
+        <v>46096.84258912037</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46096.71967913194</v>
+        <v>46096.84373324074</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>aka2026ffhkgu</t>
+          <t>ci41204687</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-154.974</v>
+        <v>-117.249</v>
       </c>
       <c r="C72" t="n">
-        <v>58.28</v>
+        <v>33.9988333333333</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3</v>
+        <v>10.86</v>
       </c>
       <c r="E72" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
+          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>84 km NNW of Karluk, Alaska</t>
+          <t>6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3318,38 +3318,38 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46096.6993729051</v>
+        <v>46096.83063032408</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46096.7007930787</v>
+        <v>46096.83300278935</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nc75327772</t>
+          <t>nn00912714</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-122.78466796875</v>
+        <v>-116.7227</v>
       </c>
       <c r="C73" t="n">
-        <v>38.7933349609375</v>
+        <v>38.3427</v>
       </c>
       <c r="D73" t="n">
-        <v>3.51999998092651</v>
+        <v>0.1382</v>
       </c>
       <c r="E73" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
+          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3358,38 +3358,38 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46096.69837233796</v>
+        <v>46096.82208777778</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46096.72732706019</v>
+        <v>46096.82386192129</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>us6000sggw</t>
+          <t>aka2026ffmxvv</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>143.3074</v>
+        <v>-151.974</v>
       </c>
       <c r="C74" t="n">
-        <v>40.9048</v>
+        <v>60.349</v>
       </c>
       <c r="D74" t="n">
-        <v>37.859</v>
+        <v>77.2</v>
       </c>
       <c r="E74" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
+          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>139 km SSE of Honchō, Japan</t>
+          <t>34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3398,38 +3398,38 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46096.68937086806</v>
+        <v>46096.81522726852</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46096.69961851852</v>
+        <v>46096.81638251158</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nc75327767</t>
+          <t>nc75327827</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-120.05883026123</v>
+        <v>-121.9375</v>
       </c>
       <c r="C75" t="n">
-        <v>35.7056655883789</v>
+        <v>37.7731666666667</v>
       </c>
       <c r="D75" t="n">
-        <v>7.76999998092651</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>2.22</v>
+        <v>1.57</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>M 2.2 - 22 km E of Cholame, CA</t>
+          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>22 km E of Cholame, CA</t>
+          <t>4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3438,38 +3438,38 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46096.68914074074</v>
+        <v>46096.81305393518</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46096.71344819444</v>
+        <v>46097.01551917824</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>aka2026ffgrhi</t>
+          <t>nc75327822</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-151.417</v>
+        <v>-122.787170410156</v>
       </c>
       <c r="C76" t="n">
-        <v>63.08</v>
+        <v>38.7934989929199</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="E76" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
+          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>53 km SSE of Denali National Park, Alaska</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3478,38 +3478,38 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46096.68422761574</v>
+        <v>46096.81298229167</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46096.68548758102</v>
+        <v>46096.86627753473</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nc75327742</t>
+          <t>us6000sghq</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-121.291664123535</v>
+        <v>49.7256</v>
       </c>
       <c r="C77" t="n">
-        <v>36.9063339233398</v>
+        <v>32.4853</v>
       </c>
       <c r="D77" t="n">
-        <v>7.69000005722046</v>
+        <v>10</v>
       </c>
       <c r="E77" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>M 1.2 - 12 km NE of Hollister, CA</t>
+          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>12 km NE of Hollister, CA</t>
+          <t>62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3518,38 +3518,38 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46096.65917303241</v>
+        <v>46096.8103829051</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46096.69960388889</v>
+        <v>46096.86111157407</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nc75327737</t>
+          <t>aka2026ffmjyx</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-122.806663513184</v>
+        <v>-149.647</v>
       </c>
       <c r="C78" t="n">
-        <v>38.8235015869141</v>
+        <v>63.036</v>
       </c>
       <c r="D78" t="n">
-        <v>2.41000008583069</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
+          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7 km NW of The Geysers, CA</t>
+          <t>52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3558,38 +3558,38 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46096.65873715278</v>
+        <v>46096.80405828704</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46096.67873339121</v>
+        <v>46096.80508491898</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>nn00912713</t>
+          <t>us6000sghd</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-116.393</v>
+        <v>142.6105</v>
       </c>
       <c r="C79" t="n">
-        <v>38.5366</v>
+        <v>41.4045</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0315</v>
+        <v>42.986</v>
       </c>
       <c r="E79" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
+          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>89 km NE of Tonopah, Nevada</t>
+          <t>84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3598,38 +3598,38 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46096.64812005787</v>
+        <v>46096.78951814815</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46096.64995700232</v>
+        <v>46096.84466623842</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nc75327727</t>
+          <t>aka2026fflqih</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-122.743835449219</v>
+        <v>-150.765</v>
       </c>
       <c r="C80" t="n">
-        <v>38.7863349914551</v>
+        <v>63.04</v>
       </c>
       <c r="D80" t="n">
-        <v>0.850000023841858</v>
+        <v>117.3</v>
       </c>
       <c r="E80" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
+          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1 km NE of The Geysers, CA</t>
+          <t>60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3638,38 +3638,38 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46096.64470740741</v>
+        <v>46096.78820800926</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46096.68219443287</v>
+        <v>46096.79154229166</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ci41204591</t>
+          <t>us6000sghb</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-115.8325</v>
+        <v>131.6063</v>
       </c>
       <c r="C81" t="n">
-        <v>31.8188333333333</v>
+        <v>31.4194</v>
       </c>
       <c r="D81" t="n">
-        <v>13.69</v>
+        <v>32.903</v>
       </c>
       <c r="E81" t="n">
-        <v>2.04</v>
+        <v>4.7</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
+          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>70 km E of Maneadero, B.C., MX</t>
+          <t>30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3678,38 +3678,38 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46096.62630196759</v>
+        <v>46096.77722483796</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46096.62875739583</v>
+        <v>46096.91079450231</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nc75327717</t>
+          <t>us6000sgh9</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-121.055168151855</v>
+        <v>-77.5782</v>
       </c>
       <c r="C82" t="n">
-        <v>36.451000213623</v>
+        <v>-1.3215</v>
       </c>
       <c r="D82" t="n">
-        <v>0.409999996423721</v>
+        <v>218.126</v>
       </c>
       <c r="E82" t="n">
-        <v>1.91</v>
+        <v>4.4</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
+          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>12 km SE of Pinnacles, CA</t>
+          <t>44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3718,38 +3718,38 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46096.61927071759</v>
+        <v>46096.77198028936</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46096.64398418982</v>
+        <v>46096.78392407407</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tx2026ffdmwb</t>
+          <t>nc75327792</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-104.429</v>
+        <v>-122.471336364746</v>
       </c>
       <c r="C83" t="n">
-        <v>31.64</v>
+        <v>37.5974998474121</v>
       </c>
       <c r="D83" t="n">
-        <v>3.3848</v>
+        <v>9.72999954223633</v>
       </c>
       <c r="E83" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>M 1.5 - 59 km S of Whites City, New Mexico</t>
+          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>59 km S of Whites City, New Mexico</t>
+          <t>2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3758,38 +3758,38 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46096.6177771875</v>
+        <v>46096.77132291667</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46096.62529559027</v>
+        <v>46096.81413002315</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>aka2026ffcpmw</t>
+          <t>aka2026ffklqv</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-152.825</v>
+        <v>-155.854</v>
       </c>
       <c r="C84" t="n">
-        <v>59.058</v>
+        <v>57.153</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>63.2</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
+          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>61 km WSW of Nanwalek, Alaska</t>
+          <t>96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3798,38 +3798,38 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46096.59896729167</v>
+        <v>46096.76349226852</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46096.91903732639</v>
+        <v>46096.76507798611</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>us6000sggm</t>
+          <t>nc75327787</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>130.0249</v>
+        <v>-123.346832275391</v>
       </c>
       <c r="C85" t="n">
-        <v>-5.5263</v>
+        <v>39.476001739502</v>
       </c>
       <c r="D85" t="n">
-        <v>184.533</v>
+        <v>4.19999980926514</v>
       </c>
       <c r="E85" t="n">
-        <v>4.4</v>
+        <v>1.72</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
+          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>271 km SSE of Amahai, Indonesia</t>
+          <t>5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3838,38 +3838,38 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46096.59319422454</v>
+        <v>46096.7527207176</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46096.69633148148</v>
+        <v>46096.79673230324</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>hv74917522</t>
+          <t>aka2026ffjrwj</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-155.374328613281</v>
+        <v>-149.163</v>
       </c>
       <c r="C86" t="n">
-        <v>19.1918334960938</v>
+        <v>62.869</v>
       </c>
       <c r="D86" t="n">
-        <v>31.7099990844727</v>
+        <v>0.3</v>
       </c>
       <c r="E86" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
+          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>11 km E of Pāhala, Hawaii</t>
+          <t>59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3878,38 +3878,38 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46096.59297361111</v>
+        <v>46096.74754356482</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46096.5954587963</v>
+        <v>46096.7486603125</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ci41204575</t>
+          <t>aka2026ffjpxp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-116.426666666667</v>
+        <v>-152.555</v>
       </c>
       <c r="C87" t="n">
-        <v>33.9901666666667</v>
+        <v>59.7</v>
       </c>
       <c r="D87" t="n">
-        <v>2.17</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E87" t="n">
-        <v>2.36</v>
+        <v>1.8</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3918,38 +3918,38 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46096.58429085648</v>
+        <v>46096.74597070602</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46096.69570008102</v>
+        <v>46096.74724846065</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ci41204567</t>
+          <t>us6000sgh3</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-116.426666666667</v>
+        <v>128.5163</v>
       </c>
       <c r="C88" t="n">
-        <v>33.9915</v>
+        <v>-7.3925</v>
       </c>
       <c r="D88" t="n">
-        <v>2.18</v>
+        <v>137.104</v>
       </c>
       <c r="E88" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3958,38 +3958,38 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46096.57788611111</v>
+        <v>46096.7350890625</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46096.58546979167</v>
+        <v>46096.81851898148</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nn00912712</t>
+          <t>ci41204623</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-116.4988</v>
+        <v>-116.638166666667</v>
       </c>
       <c r="C89" t="n">
-        <v>38.4756</v>
+        <v>32.8055</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0689</v>
+        <v>16.68</v>
       </c>
       <c r="E89" t="n">
-        <v>1.79</v>
+        <v>1.07</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>78 km NE of Tonopah, Nevada</t>
+          <t>10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3998,38 +3998,38 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46096.57585082176</v>
+        <v>46096.72295416667</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46096.57864184028</v>
+        <v>46096.72542263889</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ci41204559</t>
+          <t>aka2026ffhzps</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-118.1145</v>
+        <v>-146.822</v>
       </c>
       <c r="C90" t="n">
-        <v>34.0995</v>
+        <v>60.719</v>
       </c>
       <c r="D90" t="n">
-        <v>8.91</v>
+        <v>19</v>
       </c>
       <c r="E90" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
+          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1 km WNW of San Gabriel, CA</t>
+          <t>18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4038,38 +4038,38 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46096.5639962963</v>
+        <v>46096.71188380787</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46096.56638376157</v>
+        <v>46096.71385545139</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>aka2026ffaxsl</t>
+          <t>tx2026ffhpux</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-153.59</v>
+        <v>-103.799</v>
       </c>
       <c r="C91" t="n">
-        <v>59.151</v>
+        <v>31.021</v>
       </c>
       <c r="D91" t="n">
-        <v>102.5</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4078,38 +4078,38 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46096.56368013889</v>
+        <v>46096.70398288195</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46096.564885625</v>
+        <v>46096.71967913194</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>aka2026ffanxh</t>
+          <t>aka2026ffhkgu</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-149.871</v>
+        <v>-154.974</v>
       </c>
       <c r="C92" t="n">
-        <v>61.849</v>
+        <v>58.28</v>
       </c>
       <c r="D92" t="n">
-        <v>28.4</v>
+        <v>0.3</v>
       </c>
       <c r="E92" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
+          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>14 km NE of Willow, Alaska</t>
+          <t>84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4118,38 +4118,38 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46096.55577541667</v>
+        <v>46096.6993729051</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46096.55684119213</v>
+        <v>46096.7007930787</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>tx2026ffanng</t>
+          <t>nc75327772</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-101.924</v>
+        <v>-122.78466796875</v>
       </c>
       <c r="C93" t="n">
-        <v>32.101</v>
+        <v>38.7933349609375</v>
       </c>
       <c r="D93" t="n">
-        <v>3.9912</v>
+        <v>3.51999998092651</v>
       </c>
       <c r="E93" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
+          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4158,38 +4158,38 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46096.55563410879</v>
+        <v>46096.69837233796</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46096.97107067129</v>
+        <v>46096.72732706019</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nn00912708</t>
+          <t>us6000sggw</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-116.4027</v>
+        <v>143.3074</v>
       </c>
       <c r="C94" t="n">
-        <v>37.3392</v>
+        <v>40.9048</v>
       </c>
       <c r="D94" t="n">
-        <v>13.9737</v>
+        <v>37.859</v>
       </c>
       <c r="E94" t="n">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
+          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>57 km NNE of Beatty, Nevada</t>
+          <t>139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4198,38 +4198,38 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46096.55248135416</v>
+        <v>46096.68937086806</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46096.55406869213</v>
+        <v>46096.69961851852</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nn00912710</t>
+          <t>nc75327767</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-117.9202</v>
+        <v>-120.05883026123</v>
       </c>
       <c r="C95" t="n">
-        <v>38.5488</v>
+        <v>35.7056655883789</v>
       </c>
       <c r="D95" t="n">
-        <v>11.6085</v>
+        <v>7.76999998092651</v>
       </c>
       <c r="E95" t="n">
-        <v>1.63</v>
+        <v>2.22</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
+          <t>M 2.2 - 22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>24 km NE of Mina, Nevada</t>
+          <t>22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4238,38 +4238,38 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46096.55246195602</v>
+        <v>46096.68914074074</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46096.55466255787</v>
+        <v>46096.71344819444</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>aka2026ffagux</t>
+          <t>aka2026ffgrhi</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-149.012</v>
+        <v>-151.417</v>
       </c>
       <c r="C96" t="n">
-        <v>62.698</v>
+        <v>63.08</v>
       </c>
       <c r="D96" t="n">
-        <v>62.2</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
         <v>1.6</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
+          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>62 km ENE of Chase, Alaska</t>
+          <t>53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4278,38 +4278,38 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46096.55006834491</v>
+        <v>46096.68422761574</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46096.5511231713</v>
+        <v>46096.68548758102</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>aka2026ffacwz</t>
+          <t>nc75327742</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-154.211</v>
+        <v>-121.291664123535</v>
       </c>
       <c r="C97" t="n">
-        <v>58.934</v>
+        <v>36.9063339233398</v>
       </c>
       <c r="D97" t="n">
-        <v>126.4</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="E97" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
+          <t>M 1.2 - 12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>64 km SSE of Kokhanok, Alaska</t>
+          <t>12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4318,38 +4318,38 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46096.54689578704</v>
+        <v>46096.65917303241</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46096.54852043981</v>
+        <v>46096.69960388889</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>uw62235651</t>
+          <t>nc75327737</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-124.0351666666667</v>
+        <v>-122.806663513184</v>
       </c>
       <c r="C98" t="n">
-        <v>47.33166666666666</v>
+        <v>38.8235015869141</v>
       </c>
       <c r="D98" t="n">
-        <v>23.98</v>
+        <v>2.41000008583069</v>
       </c>
       <c r="E98" t="n">
-        <v>1.73</v>
+        <v>1.06</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
+          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>12 km NNW of Humptulips, Washington</t>
+          <t>7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4358,38 +4358,38 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46096.54669189815</v>
+        <v>46096.65873715278</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46096.58038923611</v>
+        <v>46096.67873339121</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nc75327692</t>
+          <t>nn00912713</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-122.779335021973</v>
+        <v>-116.393</v>
       </c>
       <c r="C99" t="n">
-        <v>38.8115005493164</v>
+        <v>38.5366</v>
       </c>
       <c r="D99" t="n">
-        <v>0.550000011920929</v>
+        <v>0.0315</v>
       </c>
       <c r="E99" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
+          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4 km NNW of The Geysers, CA</t>
+          <t>89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4398,38 +4398,38 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46096.54474907408</v>
+        <v>46096.64812005787</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46096.5710708449</v>
+        <v>46096.64995700232</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>us6000sgg9</t>
+          <t>nc75327727</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-77.3565</v>
+        <v>-122.743835449219</v>
       </c>
       <c r="C100" t="n">
-        <v>-45.6923</v>
+        <v>38.7863349914551</v>
       </c>
       <c r="D100" t="n">
-        <v>10</v>
+        <v>0.850000023841858</v>
       </c>
       <c r="E100" t="n">
-        <v>4.6</v>
+        <v>1.28</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>M 4.6 - Off the coast of Aisen, Chile</t>
+          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4438,38 +4438,38 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46096.53758378472</v>
+        <v>46096.64470740741</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46096.58026666666</v>
+        <v>46096.68219443287</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>us6000sgg8</t>
+          <t>ci41204591</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-77.3313</v>
+        <v>-115.8325</v>
       </c>
       <c r="C101" t="n">
-        <v>-45.741</v>
+        <v>31.8188333333333</v>
       </c>
       <c r="D101" t="n">
-        <v>10</v>
+        <v>13.69</v>
       </c>
       <c r="E101" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4478,38 +4478,38 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46096.53580871528</v>
+        <v>46096.62630196759</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46096.59747731481</v>
+        <v>46096.62875739583</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>aka2026fezlzd</t>
+          <t>nc75327717</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-150.155</v>
+        <v>-121.055168151855</v>
       </c>
       <c r="C102" t="n">
-        <v>61.309</v>
+        <v>36.451000213623</v>
       </c>
       <c r="D102" t="n">
-        <v>35.8</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="E102" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
+          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>11 km WSW of Point MacKenzie, Alaska</t>
+          <t>12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4518,38 +4518,38 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46096.53327611111</v>
+        <v>46096.61927071759</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46096.53437532407</v>
+        <v>46096.64398418982</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>aka2026feywwv</t>
+          <t>tx2026ffdmwb</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-148.811</v>
+        <v>-104.429</v>
       </c>
       <c r="C103" t="n">
-        <v>63.988</v>
+        <v>31.64</v>
       </c>
       <c r="D103" t="n">
-        <v>113.5</v>
+        <v>3.3848</v>
       </c>
       <c r="E103" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
+          <t>M 1.5 - 59 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>15 km ESE of Ferry, Alaska</t>
+          <t>59 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4558,38 +4558,38 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46096.52110533565</v>
+        <v>46096.6177771875</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46096.52266071759</v>
+        <v>46096.62529559027</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>us6000sgg7</t>
+          <t>aka2026ffcpmw</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-72.47499999999999</v>
+        <v>-152.825</v>
       </c>
       <c r="C104" t="n">
-        <v>41.5071</v>
+        <v>59.058</v>
       </c>
       <c r="D104" t="n">
-        <v>6.072</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
+          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2 km WNW of Moodus, Connecticut</t>
+          <t>61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4598,38 +4598,38 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46096.51831680556</v>
+        <v>46096.59896729167</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46097.0635559375</v>
+        <v>46096.91903732639</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>aka2026feypws</t>
+          <t>us6000sggm</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-151.884</v>
+        <v>130.0249</v>
       </c>
       <c r="C105" t="n">
-        <v>61.213</v>
+        <v>-5.5263</v>
       </c>
       <c r="D105" t="n">
-        <v>92</v>
+        <v>184.533</v>
       </c>
       <c r="E105" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
+          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>43 km WNW of Tyonek, Alaska</t>
+          <t>271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4638,38 +4638,38 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46096.51546960648</v>
+        <v>46096.59319422454</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46096.51679775463</v>
+        <v>46096.69633148148</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>hv74917517</t>
+          <t>hv74917522</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-155.388671875</v>
+        <v>-155.374328613281</v>
       </c>
       <c r="C106" t="n">
-        <v>19.2761669158936</v>
+        <v>19.1918334960938</v>
       </c>
       <c r="D106" t="n">
-        <v>29.1200008392334</v>
+        <v>31.7099990844727</v>
       </c>
       <c r="E106" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
+          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>12 km NE of Pāhala, Hawaii</t>
+          <t>11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4678,38 +4678,38 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46096.51510231481</v>
+        <v>46096.59297361111</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46096.51755763889</v>
+        <v>46096.5954587963</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>us6000sgg3</t>
+          <t>ci41204575</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-72.49160000000001</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C107" t="n">
-        <v>41.4904</v>
+        <v>33.9901666666667</v>
       </c>
       <c r="D107" t="n">
-        <v>6.63</v>
+        <v>2.17</v>
       </c>
       <c r="E107" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
+          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>3 km WSW of Moodus, Connecticut</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4718,38 +4718,38 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46096.51474966435</v>
+        <v>46096.58429085648</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46097.05646988426</v>
+        <v>46096.69570008102</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>us6000sgg2</t>
+          <t>ci41204567</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>155.7691</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C108" t="n">
-        <v>50.1375</v>
+        <v>33.9915</v>
       </c>
       <c r="D108" t="n">
-        <v>93.238</v>
+        <v>2.18</v>
       </c>
       <c r="E108" t="n">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4758,38 +4758,38 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46096.50655835648</v>
+        <v>46096.57788611111</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46096.52194490741</v>
+        <v>46096.58546979167</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>aka2026feycns</t>
+          <t>nn00912712</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-148.959</v>
+        <v>-116.4988</v>
       </c>
       <c r="C109" t="n">
-        <v>63.283</v>
+        <v>38.4756</v>
       </c>
       <c r="D109" t="n">
-        <v>0.6</v>
+        <v>0.0689</v>
       </c>
       <c r="E109" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
+          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>12 km S of Cantwell, Alaska</t>
+          <t>78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4798,38 +4798,38 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46096.50470625</v>
+        <v>46096.57585082176</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46096.50576539352</v>
+        <v>46096.57864184028</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ci41204535</t>
+          <t>ci41204559</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-119.474833333333</v>
+        <v>-118.1145</v>
       </c>
       <c r="C110" t="n">
-        <v>34.3685</v>
+        <v>34.0995</v>
       </c>
       <c r="D110" t="n">
-        <v>0.54</v>
+        <v>8.91</v>
       </c>
       <c r="E110" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
+          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>5 km SE of Carpinteria, CA</t>
+          <t>1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4838,38 +4838,38 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46096.49835740741</v>
+        <v>46096.5639962963</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46096.50080350695</v>
+        <v>46096.56638376157</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>aka2026fewzkc</t>
+          <t>aka2026ffaxsl</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-148.795</v>
+        <v>-153.59</v>
       </c>
       <c r="C111" t="n">
-        <v>62.2</v>
+        <v>59.151</v>
       </c>
       <c r="D111" t="n">
-        <v>22.1</v>
+        <v>102.5</v>
       </c>
       <c r="E111" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
+          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>47 km N of Sutton-Alpine, Alaska</t>
+          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4878,38 +4878,38 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46096.48122515046</v>
+        <v>46096.56368013889</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46096.48264917824</v>
+        <v>46096.564885625</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>us6000sgfx</t>
+          <t>aka2026ffanxh</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-80.1019</v>
+        <v>-149.871</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5871</v>
+        <v>61.849</v>
       </c>
       <c r="D112" t="n">
-        <v>36.381</v>
+        <v>28.4</v>
       </c>
       <c r="E112" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
+          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>9 km WSW of Muisne, Ecuador</t>
+          <t>14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4918,38 +4918,38 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46096.47494160879</v>
+        <v>46096.55577541667</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46096.4911</v>
+        <v>46096.55684119213</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>pr71509923</t>
+          <t>tx2026ffanng</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-66.1071666666667</v>
+        <v>-101.924</v>
       </c>
       <c r="C113" t="n">
-        <v>18.1251666666667</v>
+        <v>32.101</v>
       </c>
       <c r="D113" t="n">
-        <v>24.58</v>
+        <v>3.9912</v>
       </c>
       <c r="E113" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4958,38 +4958,38 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46096.47251458334</v>
+        <v>46096.55563410879</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46096.60321875</v>
+        <v>46096.97107067129</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ci41204519</t>
+          <t>nn00912708</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-118.627833333333</v>
+        <v>-116.4027</v>
       </c>
       <c r="C114" t="n">
-        <v>34.6043333333333</v>
+        <v>37.3392</v>
       </c>
       <c r="D114" t="n">
-        <v>10.64</v>
+        <v>13.9737</v>
       </c>
       <c r="E114" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>M 1.1 - 13 km N of Castaic, CA</t>
+          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>13 km N of Castaic, CA</t>
+          <t>57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4998,38 +4998,38 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46096.46653668981</v>
+        <v>46096.55248135416</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46096.46890145833</v>
+        <v>46096.55406869213</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nn00912706</t>
+          <t>nn00912710</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-119.5178</v>
+        <v>-117.9202</v>
       </c>
       <c r="C115" t="n">
-        <v>38.4812</v>
+        <v>38.5488</v>
       </c>
       <c r="D115" t="n">
-        <v>3.3162</v>
+        <v>11.6085</v>
       </c>
       <c r="E115" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km SW of Walker, California</t>
+          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>5 km SW of Walker, California</t>
+          <t>24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5038,38 +5038,38 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46096.46134278935</v>
+        <v>46096.55246195602</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46096.46294350694</v>
+        <v>46096.55466255787</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nc75327672</t>
+          <t>aka2026ffagux</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-122.810333251953</v>
+        <v>-149.012</v>
       </c>
       <c r="C116" t="n">
-        <v>38.8395004272461</v>
+        <v>62.698</v>
       </c>
       <c r="D116" t="n">
-        <v>1.83000004291534</v>
+        <v>62.2</v>
       </c>
       <c r="E116" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
+          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8 km WNW of Cobb, CA</t>
+          <t>62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5078,38 +5078,38 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46096.46108472222</v>
+        <v>46096.55006834491</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46096.49469679398</v>
+        <v>46096.5511231713</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>pr71509913</t>
+          <t>aka2026ffacwz</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-67.0566666666667</v>
+        <v>-154.211</v>
       </c>
       <c r="C117" t="n">
-        <v>18.1476666666667</v>
+        <v>58.934</v>
       </c>
       <c r="D117" t="n">
-        <v>17.11</v>
+        <v>126.4</v>
       </c>
       <c r="E117" t="n">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5118,38 +5118,38 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46096.44030868055</v>
+        <v>46096.54689578704</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46096.59237719907</v>
+        <v>46096.54852043981</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>aka2026feukwz</t>
+          <t>uw62235651</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-147.764</v>
+        <v>-124.0351666666667</v>
       </c>
       <c r="C118" t="n">
-        <v>60.385</v>
+        <v>47.33166666666666</v>
       </c>
       <c r="D118" t="n">
-        <v>14.9</v>
+        <v>23.98</v>
       </c>
       <c r="E118" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
+          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>38 km NNE of Chenega, Alaska</t>
+          <t>12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5158,38 +5158,38 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46096.42763064815</v>
+        <v>46096.54669189815</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46096.4286147338</v>
+        <v>46096.58038923611</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>aka2026fetqyo</t>
+          <t>nc75327692</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-150.43</v>
+        <v>-122.779335021973</v>
       </c>
       <c r="C119" t="n">
-        <v>60.896</v>
+        <v>38.8115005493164</v>
       </c>
       <c r="D119" t="n">
-        <v>45.5</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="E119" t="n">
-        <v>1.9</v>
+        <v>1.08</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
+          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>14 km ESE of Point Possession, Alaska</t>
+          <t>4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5198,38 +5198,38 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46096.41156589121</v>
+        <v>46096.54474907408</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46096.41261650463</v>
+        <v>46096.5710708449</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ci41204503</t>
+          <t>us6000sgg9</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-117.464333333333</v>
+        <v>-77.3565</v>
       </c>
       <c r="C120" t="n">
-        <v>34.157</v>
+        <v>-45.6923</v>
       </c>
       <c r="D120" t="n">
-        <v>6.87</v>
+        <v>10</v>
       </c>
       <c r="E120" t="n">
-        <v>0.98</v>
+        <v>4.6</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>M 1.0 - 7 km N of Fontana, CA</t>
+          <t>M 4.6 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>7 km N of Fontana, CA</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5238,38 +5238,38 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46096.39763148148</v>
+        <v>46096.53758378472</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46096.39998002315</v>
+        <v>46096.58026666666</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>aka2026fessqh</t>
+          <t>us6000sgg8</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-152.317</v>
+        <v>-77.3313</v>
       </c>
       <c r="C121" t="n">
-        <v>60.36</v>
+        <v>-45.741</v>
       </c>
       <c r="D121" t="n">
-        <v>90.3</v>
+        <v>10</v>
       </c>
       <c r="E121" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>49 km NW of Ninilchik, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5278,38 +5278,38 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46096.39196349537</v>
+        <v>46096.53580871528</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46096.39365355324</v>
+        <v>46096.59747731481</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>nc75327657</t>
+          <t>aka2026fezlzd</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-122.805335998535</v>
+        <v>-150.155</v>
       </c>
       <c r="C122" t="n">
-        <v>38.8190002441406</v>
+        <v>61.309</v>
       </c>
       <c r="D122" t="n">
-        <v>2.17000007629395</v>
+        <v>35.8</v>
       </c>
       <c r="E122" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
+          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5318,38 +5318,38 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46096.37721527777</v>
+        <v>46096.53327611111</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46096.42173711806</v>
+        <v>46096.53437532407</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>aka2026fertpz</t>
+          <t>aka2026feywwv</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-157.698</v>
+        <v>-148.811</v>
       </c>
       <c r="C123" t="n">
-        <v>55.194</v>
+        <v>63.988</v>
       </c>
       <c r="D123" t="n">
-        <v>4.2</v>
+        <v>113.5</v>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
+          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>121 km SE of Perryville, Alaska</t>
+          <t>15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5358,38 +5358,38 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46096.37321436343</v>
+        <v>46096.52110533565</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46096.37804444444</v>
+        <v>46096.52266071759</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>uw62235646</t>
+          <t>us6000sgg7</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-121.9746666666667</v>
+        <v>-72.47499999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>47.82666666666667</v>
+        <v>41.5071</v>
       </c>
       <c r="D124" t="n">
-        <v>26.62</v>
+        <v>6.072</v>
       </c>
       <c r="E124" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km S of Monroe, Washington</t>
+          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>3 km S of Monroe, Washington</t>
+          <t>2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5398,38 +5398,38 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46096.36272453704</v>
+        <v>46096.51831680556</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46096.47082604167</v>
+        <v>46097.0635559375</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>us6000sgfk</t>
+          <t>aka2026feypws</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-77.27330000000001</v>
+        <v>-151.884</v>
       </c>
       <c r="C125" t="n">
-        <v>-45.5694</v>
+        <v>61.213</v>
       </c>
       <c r="D125" t="n">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E125" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>M 5.3 - Off the coast of Aisen, Chile</t>
+          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5438,38 +5438,38 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46096.35320680556</v>
+        <v>46096.51546960648</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46096.38260266204</v>
+        <v>46096.51679775463</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>us6000sgfh</t>
+          <t>hv74917517</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>122.0755</v>
+        <v>-155.388671875</v>
       </c>
       <c r="C126" t="n">
-        <v>24.3607</v>
+        <v>19.2761669158936</v>
       </c>
       <c r="D126" t="n">
-        <v>27.716</v>
+        <v>29.1200008392334</v>
       </c>
       <c r="E126" t="n">
-        <v>4.8</v>
+        <v>1.91</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
+          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>54 km SE of Yilan, Taiwan</t>
+          <t>12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5478,38 +5478,38 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46096.34370333333</v>
+        <v>46096.51510231481</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46096.53583686343</v>
+        <v>46096.51755763889</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>nn00912705</t>
+          <t>us6000sgg3</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-116.5611</v>
+        <v>-72.49160000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>38.4412</v>
+        <v>41.4904</v>
       </c>
       <c r="D127" t="n">
-        <v>3.8472</v>
+        <v>6.63</v>
       </c>
       <c r="E127" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
+          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>71 km NE of Tonopah, Nevada</t>
+          <t>3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5518,38 +5518,38 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46096.34194375</v>
+        <v>46096.51474966435</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46096.34380362269</v>
+        <v>46097.05646988426</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ci41204487</t>
+          <t>us6000sgg2</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-116.419666666667</v>
+        <v>155.7691</v>
       </c>
       <c r="C128" t="n">
-        <v>32.9405</v>
+        <v>50.1375</v>
       </c>
       <c r="D128" t="n">
-        <v>4.88</v>
+        <v>93.238</v>
       </c>
       <c r="E128" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
+          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>17 km NE of Pine Valley, CA</t>
+          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5558,38 +5558,38 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46096.32685023148</v>
+        <v>46096.50655835648</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46096.32921789352</v>
+        <v>46096.52194490741</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ci41204479</t>
+          <t>aka2026feycns</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-117.2475</v>
+        <v>-148.959</v>
       </c>
       <c r="C129" t="n">
-        <v>34.0556666666667</v>
+        <v>63.283</v>
       </c>
       <c r="D129" t="n">
-        <v>15.21</v>
+        <v>0.6</v>
       </c>
       <c r="E129" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
+          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2 km ENE of Loma Linda, CA</t>
+          <t>12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5598,38 +5598,38 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46096.32684571759</v>
+        <v>46096.50470625</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46096.32920631945</v>
+        <v>46096.50576539352</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>aka2026fephrq</t>
+          <t>ci41204535</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-150.634</v>
+        <v>-119.474833333333</v>
       </c>
       <c r="C130" t="n">
-        <v>60.036</v>
+        <v>34.3685</v>
       </c>
       <c r="D130" t="n">
-        <v>63.6</v>
+        <v>0.54</v>
       </c>
       <c r="E130" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
+          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>26 km NE of Fox River, Alaska</t>
+          <t>5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5638,38 +5638,38 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46096.32028525463</v>
+        <v>46096.49835740741</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46096.32365</v>
+        <v>46096.50080350695</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>nn00912702</t>
+          <t>aka2026fewzkc</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-116.579</v>
+        <v>-148.795</v>
       </c>
       <c r="C131" t="n">
-        <v>38.4398</v>
+        <v>62.2</v>
       </c>
       <c r="D131" t="n">
-        <v>3.5596</v>
+        <v>22.1</v>
       </c>
       <c r="E131" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5678,38 +5678,38 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46096.30809262732</v>
+        <v>46096.48122515046</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46096.31003199074</v>
+        <v>46096.48264917824</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>nc75327637</t>
+          <t>us6000sgfx</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-121.911003112793</v>
+        <v>-80.1019</v>
       </c>
       <c r="C132" t="n">
-        <v>38.0525016784668</v>
+        <v>0.5871</v>
       </c>
       <c r="D132" t="n">
-        <v>17.0200004577637</v>
+        <v>36.381</v>
       </c>
       <c r="E132" t="n">
-        <v>1.51</v>
+        <v>4.4</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
+          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>4 km NW of Pittsburg, CA</t>
+          <t>9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5718,38 +5718,38 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46096.29875555556</v>
+        <v>46096.47494160879</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46096.34190163195</v>
+        <v>46096.4911</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>us6000sgf9</t>
+          <t>pr71509923</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>72.05249999999999</v>
+        <v>-66.1071666666667</v>
       </c>
       <c r="C133" t="n">
-        <v>37.629</v>
+        <v>18.1251666666667</v>
       </c>
       <c r="D133" t="n">
-        <v>196.241</v>
+        <v>24.58</v>
       </c>
       <c r="E133" t="n">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
+          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>46 km ENE of Khorugh, Tajikistan</t>
+          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5758,38 +5758,38 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46096.29624704861</v>
+        <v>46096.47251458334</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46096.31303287037</v>
+        <v>46096.60321875</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>aka2026fenxtb</t>
+          <t>ci41204519</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-154.253</v>
+        <v>-118.627833333333</v>
       </c>
       <c r="C134" t="n">
-        <v>58.558</v>
+        <v>34.6043333333333</v>
       </c>
       <c r="D134" t="n">
-        <v>5</v>
+        <v>10.64</v>
       </c>
       <c r="E134" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
+          <t>M 1.1 - 13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>96 km NW of Aleneva, Alaska</t>
+          <t>13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5798,38 +5798,38 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46096.29131623843</v>
+        <v>46096.46653668981</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46096.29275974537</v>
+        <v>46096.46890145833</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>nc75327632</t>
+          <t>nn00912706</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-121.910331726074</v>
+        <v>-119.5178</v>
       </c>
       <c r="C135" t="n">
-        <v>38.0643348693848</v>
+        <v>38.4812</v>
       </c>
       <c r="D135" t="n">
-        <v>18.6900005340576</v>
+        <v>3.3162</v>
       </c>
       <c r="E135" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
+          <t>M 1.3 - 5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>5 km NNW of Pittsburg, CA</t>
+          <t>5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5838,38 +5838,38 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46096.28527893518</v>
+        <v>46096.46134278935</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46096.32459672454</v>
+        <v>46096.46294350694</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>tx2026fenmna</t>
+          <t>nc75327672</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-104.203</v>
+        <v>-122.810333251953</v>
       </c>
       <c r="C136" t="n">
-        <v>31.669</v>
+        <v>38.8395004272461</v>
       </c>
       <c r="D136" t="n">
-        <v>7.2278</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="E136" t="n">
-        <v>1.9</v>
+        <v>0.97</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
+          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5878,38 +5878,38 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46096.28226224537</v>
+        <v>46096.46108472222</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46096.83936486111</v>
+        <v>46096.49469679398</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tx2026fenktd</t>
+          <t>pr71509913</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-104.202</v>
+        <v>-67.0566666666667</v>
       </c>
       <c r="C137" t="n">
-        <v>31.669</v>
+        <v>18.1476666666667</v>
       </c>
       <c r="D137" t="n">
-        <v>7.5739</v>
+        <v>17.11</v>
       </c>
       <c r="E137" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
+          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5918,38 +5918,38 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46096.28124563657</v>
+        <v>46096.44030868055</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46096.70278489583</v>
+        <v>46096.59237719907</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ci41204455</t>
+          <t>aka2026feukwz</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-116.806333333333</v>
+        <v>-147.764</v>
       </c>
       <c r="C138" t="n">
-        <v>33.2463333333333</v>
+        <v>60.385</v>
       </c>
       <c r="D138" t="n">
-        <v>10.1</v>
+        <v>14.9</v>
       </c>
       <c r="E138" t="n">
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
+          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>4 km W of Lake Henshaw, CA</t>
+          <t>38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5958,38 +5958,38 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46096.27805949074</v>
+        <v>46096.42763064815</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46096.28047209491</v>
+        <v>46096.4286147338</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>nn00912698</t>
+          <t>aka2026fetqyo</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-116.6054</v>
+        <v>-150.43</v>
       </c>
       <c r="C139" t="n">
-        <v>38.2724</v>
+        <v>60.896</v>
       </c>
       <c r="D139" t="n">
-        <v>5.7486</v>
+        <v>45.5</v>
       </c>
       <c r="E139" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
+          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>59 km ENE of Tonopah, Nevada</t>
+          <t>14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5998,38 +5998,38 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46096.26913202546</v>
+        <v>46096.41156589121</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46096.27123583333</v>
+        <v>46096.41261650463</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>nn00912696</t>
+          <t>ci41204503</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-116.3473</v>
+        <v>-117.464333333333</v>
       </c>
       <c r="C140" t="n">
-        <v>37.5427</v>
+        <v>34.157</v>
       </c>
       <c r="D140" t="n">
-        <v>15.7841</v>
+        <v>6.87</v>
       </c>
       <c r="E140" t="n">
-        <v>1.48</v>
+        <v>0.98</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.0 - 7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6038,38 +6038,38 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46096.26722096065</v>
+        <v>46096.39763148148</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46096.26890163194</v>
+        <v>46096.39998002315</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>pr71509903</t>
+          <t>aka2026fessqh</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-66.7433333333333</v>
+        <v>-152.317</v>
       </c>
       <c r="C141" t="n">
-        <v>18.043</v>
+        <v>60.36</v>
       </c>
       <c r="D141" t="n">
-        <v>16.94</v>
+        <v>90.3</v>
       </c>
       <c r="E141" t="n">
-        <v>2.09</v>
+        <v>1.3</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6078,38 +6078,38 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46096.26509143518</v>
+        <v>46096.39196349537</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46096.27459479167</v>
+        <v>46096.39365355324</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>nn00912694</t>
+          <t>nc75327657</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-116.5678</v>
+        <v>-122.805335998535</v>
       </c>
       <c r="C142" t="n">
-        <v>38.4757</v>
+        <v>38.8190002441406</v>
       </c>
       <c r="D142" t="n">
-        <v>5.2112</v>
+        <v>2.17000007629395</v>
       </c>
       <c r="E142" t="n">
-        <v>2.01</v>
+        <v>1.1</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>73 km NE of Tonopah, Nevada</t>
+          <t>6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6118,38 +6118,38 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46096.26149202546</v>
+        <v>46096.37721527777</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46096.26338644676</v>
+        <v>46096.42173711806</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>aka2026femdbx</t>
+          <t>aka2026fertpz</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-154.971</v>
+        <v>-157.698</v>
       </c>
       <c r="C143" t="n">
-        <v>57.961</v>
+        <v>55.194</v>
       </c>
       <c r="D143" t="n">
-        <v>86.59999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="E143" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
+          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>53 km NW of Karluk, Alaska</t>
+          <t>121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6158,38 +6158,38 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46096.25371178241</v>
+        <v>46096.37321436343</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46096.2741787037</v>
+        <v>46096.37804444444</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>nn00912691</t>
+          <t>uw62235646</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-116.5734</v>
+        <v>-121.9746666666667</v>
       </c>
       <c r="C144" t="n">
-        <v>38.4423</v>
+        <v>47.82666666666667</v>
       </c>
       <c r="D144" t="n">
-        <v>1.9073</v>
+        <v>26.62</v>
       </c>
       <c r="E144" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 2.0 - 3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6198,38 +6198,38 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46096.25128945602</v>
+        <v>46096.36272453704</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46096.25308243056</v>
+        <v>46096.47082604167</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ci41204447</t>
+          <t>us6000sgfk</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-116.168333333333</v>
+        <v>-77.27330000000001</v>
       </c>
       <c r="C145" t="n">
-        <v>33.8886666666667</v>
+        <v>-45.5694</v>
       </c>
       <c r="D145" t="n">
-        <v>5.52</v>
+        <v>10</v>
       </c>
       <c r="E145" t="n">
-        <v>1.26</v>
+        <v>5.3</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>M 1.3 - 19 km NNE of Indio, CA</t>
+          <t>M 5.3 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>19 km NNE of Indio, CA</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6238,38 +6238,38 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46096.24517546297</v>
+        <v>46096.35320680556</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46096.25266435185</v>
+        <v>46096.38260266204</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>nc75327597</t>
+          <t>us6000sgfh</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-121.635665893555</v>
+        <v>122.0755</v>
       </c>
       <c r="C146" t="n">
-        <v>36.9845008850098</v>
+        <v>24.3607</v>
       </c>
       <c r="D146" t="n">
-        <v>8.989999771118161</v>
+        <v>27.716</v>
       </c>
       <c r="E146" t="n">
-        <v>1.71</v>
+        <v>4.8</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
+          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>6 km WSW of Gilroy, CA</t>
+          <t>54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6278,38 +6278,38 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46096.24306736111</v>
+        <v>46096.34370333333</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46096.29676952546</v>
+        <v>46096.53583686343</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>aka2026fekujg</t>
+          <t>nn00912705</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-150.947</v>
+        <v>-116.5611</v>
       </c>
       <c r="C147" t="n">
-        <v>60.457</v>
+        <v>38.4412</v>
       </c>
       <c r="D147" t="n">
-        <v>50.6</v>
+        <v>3.8472</v>
       </c>
       <c r="E147" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>M 1.6 - 7 km ESE of Soldotna, Alaska</t>
+          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>7 km ESE of Soldotna, Alaska</t>
+          <t>71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6318,38 +6318,38 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>46096.22573243055</v>
+        <v>46096.34194375</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46096.22721925926</v>
+        <v>46096.34380362269</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>us6000sgel</t>
+          <t>ci41204487</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-77.3734</v>
+        <v>-116.419666666667</v>
       </c>
       <c r="C148" t="n">
-        <v>-45.6673</v>
+        <v>32.9405</v>
       </c>
       <c r="D148" t="n">
-        <v>10</v>
+        <v>4.88</v>
       </c>
       <c r="E148" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6358,38 +6358,38 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>46096.22567266204</v>
+        <v>46096.32685023148</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46096.32872731482</v>
+        <v>46096.32921789352</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>nn00912689</t>
+          <t>ci41204479</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-116.8458</v>
+        <v>-117.2475</v>
       </c>
       <c r="C149" t="n">
-        <v>38.2828</v>
+        <v>34.0556666666667</v>
       </c>
       <c r="D149" t="n">
-        <v>5.3648</v>
+        <v>15.21</v>
       </c>
       <c r="E149" t="n">
-        <v>1.92</v>
+        <v>1.09</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>M 1.9 - 41 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>41 km NE of Tonopah, Nevada</t>
+          <t>2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6398,38 +6398,38 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>46096.2170634838</v>
+        <v>46096.32684571759</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46096.21891450231</v>
+        <v>46096.32920631945</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>us6000sgeb</t>
+          <t>aka2026fephrq</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>139.3214</v>
+        <v>-150.634</v>
       </c>
       <c r="C150" t="n">
-        <v>36.3919</v>
+        <v>60.036</v>
       </c>
       <c r="D150" t="n">
-        <v>94.896</v>
+        <v>63.6</v>
       </c>
       <c r="E150" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>M 4.8 - 1 km SW of Kiryū, Japan</t>
+          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1 km SW of Kiryū, Japan</t>
+          <t>26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6438,38 +6438,38 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>46096.21257785879</v>
+        <v>46096.32028525463</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46096.66760255787</v>
+        <v>46096.32365</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>us6000sgea</t>
+          <t>nn00912702</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-88.2997</v>
+        <v>-116.579</v>
       </c>
       <c r="C151" t="n">
-        <v>12.6324</v>
+        <v>38.4398</v>
       </c>
       <c r="D151" t="n">
-        <v>55.856</v>
+        <v>3.5596</v>
       </c>
       <c r="E151" t="n">
-        <v>5.3</v>
+        <v>2.08</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>M 5.3 - 67 km SSW of Chirilagua, El Salvador</t>
+          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>67 km SSW of Chirilagua, El Salvador</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6478,38 +6478,38 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>46096.20880520833</v>
+        <v>46096.30809262732</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46096.62601605324</v>
+        <v>46096.31003199074</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>nn00912685</t>
+          <t>nc75327637</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-117.1071</v>
+        <v>-121.911003112793</v>
       </c>
       <c r="C152" t="n">
-        <v>37.2044</v>
+        <v>38.0525016784668</v>
       </c>
       <c r="D152" t="n">
-        <v>3.7302</v>
+        <v>17.0200004577637</v>
       </c>
       <c r="E152" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>M 1.4 - 45 km NW of Beatty, Nevada</t>
+          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>45 km NW of Beatty, Nevada</t>
+          <t>4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6518,38 +6518,38 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>46096.20641787037</v>
+        <v>46096.29875555556</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46096.20811390047</v>
+        <v>46096.34190163195</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>nc75327582</t>
+          <t>us6000sgf9</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-124.411834716797</v>
+        <v>72.05249999999999</v>
       </c>
       <c r="C153" t="n">
-        <v>40.2961654663086</v>
+        <v>37.629</v>
       </c>
       <c r="D153" t="n">
-        <v>9.22999954223633</v>
+        <v>196.241</v>
       </c>
       <c r="E153" t="n">
-        <v>1.93</v>
+        <v>4.1</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>M 1.9 - 11 km WSW of Petrolia, CA</t>
+          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>11 km WSW of Petrolia, CA</t>
+          <t>46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6558,38 +6558,38 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>46096.20098622685</v>
+        <v>46096.29624704861</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46096.24126574074</v>
+        <v>46096.31303287037</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>us6000sge9</t>
+          <t>aka2026fenxtb</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>142.5299</v>
+        <v>-154.253</v>
       </c>
       <c r="C154" t="n">
-        <v>37.3728</v>
+        <v>58.558</v>
       </c>
       <c r="D154" t="n">
-        <v>38.742</v>
+        <v>5</v>
       </c>
       <c r="E154" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>M 4.3 - 134 km E of Tomioka, Japan</t>
+          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>134 km E of Tomioka, Japan</t>
+          <t>96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6598,38 +6598,38 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>46096.20051677083</v>
+        <v>46096.29131623843</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46096.2139587963</v>
+        <v>46096.29275974537</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>hv74917492</t>
+          <t>nc75327632</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-155.501159667969</v>
+        <v>-121.910331726074</v>
       </c>
       <c r="C155" t="n">
-        <v>19.1526660919189</v>
+        <v>38.0643348693848</v>
       </c>
       <c r="D155" t="n">
-        <v>27.9200000762939</v>
+        <v>18.6900005340576</v>
       </c>
       <c r="E155" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>M 2.2 - 6 km SSW of Pāhala, Hawaii</t>
+          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>6 km SSW of Pāhala, Hawaii</t>
+          <t>5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6638,38 +6638,38 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>46096.19672719907</v>
+        <v>46096.28527893518</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46096.19926747686</v>
+        <v>46096.32459672454</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ci41204415</t>
+          <t>tx2026fenmna</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-115.949666666667</v>
+        <v>-104.203</v>
       </c>
       <c r="C156" t="n">
-        <v>32.903</v>
+        <v>31.669</v>
       </c>
       <c r="D156" t="n">
-        <v>7.34</v>
+        <v>7.2278</v>
       </c>
       <c r="E156" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>M 1.1 - 19 km NNE of Ocotillo, CA</t>
+          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>19 km NNE of Ocotillo, CA</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6678,38 +6678,38 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>46096.19181168982</v>
+        <v>46096.28226224537</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46096.19425657408</v>
+        <v>46096.83936486111</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>us6000sge4</t>
+          <t>tx2026fenktd</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-98.1546</v>
+        <v>-104.202</v>
       </c>
       <c r="C157" t="n">
-        <v>35.4408</v>
+        <v>31.669</v>
       </c>
       <c r="D157" t="n">
-        <v>10</v>
+        <v>7.5739</v>
       </c>
       <c r="E157" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>M 2.7 - 18 km S of Calumet, Oklahoma</t>
+          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>18 km S of Calumet, Oklahoma</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6718,38 +6718,38 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>46096.17096916667</v>
+        <v>46096.28124563657</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46096.19517141204</v>
+        <v>46096.70278489583</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>nn00912683</t>
+          <t>ci41204455</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-115.2794</v>
+        <v>-116.806333333333</v>
       </c>
       <c r="C158" t="n">
-        <v>37.043</v>
+        <v>33.2463333333333</v>
       </c>
       <c r="D158" t="n">
-        <v>3.4848</v>
+        <v>10.1</v>
       </c>
       <c r="E158" t="n">
-        <v>1.67</v>
+        <v>0.95</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>M 1.7 - 37 km SSW of Alamo, Nevada</t>
+          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>37 km SSW of Alamo, Nevada</t>
+          <t>4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6758,38 +6758,38 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>46096.16868928241</v>
+        <v>46096.27805949074</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46096.17050155093</v>
+        <v>46096.28047209491</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>nn00912681</t>
+          <t>nn00912698</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-116.7898</v>
+        <v>-116.6054</v>
       </c>
       <c r="C159" t="n">
-        <v>38.3409</v>
+        <v>38.2724</v>
       </c>
       <c r="D159" t="n">
-        <v>6.6979</v>
+        <v>5.7486</v>
       </c>
       <c r="E159" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>M 1.8 - 49 km NE of Tonopah, Nevada</t>
+          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>49 km NE of Tonopah, Nevada</t>
+          <t>59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6798,38 +6798,38 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>46096.16567495371</v>
+        <v>46096.26913202546</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46096.16754114583</v>
+        <v>46096.27123583333</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>nc75327567</t>
+          <t>nn00912696</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-120.093002319336</v>
+        <v>-116.3473</v>
       </c>
       <c r="C160" t="n">
-        <v>36.1063346862793</v>
+        <v>37.5427</v>
       </c>
       <c r="D160" t="n">
-        <v>8.239999771118161</v>
+        <v>15.7841</v>
       </c>
       <c r="E160" t="n">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>M 2.1 - 11 km S of Huron, CA</t>
+          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>11 km S of Huron, CA</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6838,38 +6838,38 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>46096.16129594907</v>
+        <v>46096.26722096065</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46096.18564616898</v>
+        <v>46096.26890163194</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>aka2026fehrkj</t>
+          <t>pr71509903</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-149.708</v>
+        <v>-66.7433333333333</v>
       </c>
       <c r="C161" t="n">
-        <v>62.155</v>
+        <v>18.043</v>
       </c>
       <c r="D161" t="n">
-        <v>31.4</v>
+        <v>16.94</v>
       </c>
       <c r="E161" t="n">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>M 1.5 - 7 km E of Susitna North, Alaska</t>
+          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>7 km E of Susitna North, Alaska</t>
+          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6878,38 +6878,38 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>46096.16061565972</v>
+        <v>46096.26509143518</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46096.16211004629</v>
+        <v>46096.27459479167</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>nn00912678</t>
+          <t>nn00912694</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-117.1285</v>
+        <v>-116.5678</v>
       </c>
       <c r="C162" t="n">
-        <v>37.2457</v>
+        <v>38.4757</v>
       </c>
       <c r="D162" t="n">
-        <v>13.004</v>
+        <v>5.2112</v>
       </c>
       <c r="E162" t="n">
-        <v>1.59</v>
+        <v>2.01</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>M 1.6 - 49 km NW of Beatty, Nevada</t>
+          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>49 km NW of Beatty, Nevada</t>
+          <t>73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6918,38 +6918,38 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>46096.16059528935</v>
+        <v>46096.26149202546</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46096.16208465278</v>
+        <v>46096.26338644676</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ok2026fdrh</t>
+          <t>aka2026femdbx</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-98.18229675000001</v>
+        <v>-154.971</v>
       </c>
       <c r="C163" t="n">
-        <v>35.44195557</v>
+        <v>57.961</v>
       </c>
       <c r="D163" t="n">
-        <v>0.324695766</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E163" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>M 2.6 - 16 km ESE of Hinton, Oklahoma</t>
+          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>16 km ESE of Hinton, Oklahoma</t>
+          <t>53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6958,38 +6958,38 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>46096.15941979166</v>
+        <v>46096.25371178241</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46096.19862199074</v>
+        <v>46096.2741787037</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>aka2026fegqal</t>
+          <t>nn00912691</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-152.568</v>
+        <v>-116.5734</v>
       </c>
       <c r="C164" t="n">
-        <v>60.006</v>
+        <v>38.4423</v>
       </c>
       <c r="D164" t="n">
-        <v>104.2</v>
+        <v>1.9073</v>
       </c>
       <c r="E164" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>M 1.3 - 47 km W of Happy Valley, Alaska</t>
+          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>47 km W of Happy Valley, Alaska</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6998,38 +6998,38 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>46096.13842898148</v>
+        <v>46096.25128945602</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46096.139836875</v>
+        <v>46096.25308243056</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tx2026fegnxw</t>
+          <t>ci41204447</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-104.428</v>
+        <v>-116.168333333333</v>
       </c>
       <c r="C165" t="n">
-        <v>31.649</v>
+        <v>33.8886666666667</v>
       </c>
       <c r="D165" t="n">
-        <v>7.1765</v>
+        <v>5.52</v>
       </c>
       <c r="E165" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>M 1.8 - 58 km S of Whites City, New Mexico</t>
+          <t>M 1.3 - 19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7038,38 +7038,38 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>46096.13676635417</v>
+        <v>46096.24517546297</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46096.82320827546</v>
+        <v>46096.25266435185</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>tx2026fegkvq</t>
+          <t>nc75327597</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-104.424</v>
+        <v>-121.635665893555</v>
       </c>
       <c r="C166" t="n">
-        <v>31.653</v>
+        <v>36.9845008850098</v>
       </c>
       <c r="D166" t="n">
-        <v>6.0999</v>
+        <v>8.989999771118161</v>
       </c>
       <c r="E166" t="n">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>M 2.4 - 58 km S of Whites City, New Mexico</t>
+          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7078,38 +7078,38 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>46096.13426206019</v>
+        <v>46096.24306736111</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46097.05598633102</v>
+        <v>46096.29676952546</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>nn00912675</t>
+          <t>aka2026fekujg</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-116.8506</v>
+        <v>-150.947</v>
       </c>
       <c r="C167" t="n">
-        <v>37.1599</v>
+        <v>60.457</v>
       </c>
       <c r="D167" t="n">
-        <v>6.4687</v>
+        <v>50.6</v>
       </c>
       <c r="E167" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>M 1.1 - 29 km NNW of Beatty, Nevada</t>
+          <t>M 1.6 - 7 km ESE of Soldotna, Alaska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>29 km NNW of Beatty, Nevada</t>
+          <t>7 km ESE of Soldotna, Alaska</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7118,38 +7118,38 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>46096.13401565972</v>
+        <v>46096.22573243055</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46096.13532696759</v>
+        <v>46096.22721925926</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>aka2026feghag</t>
+          <t>us6000sgel</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-152.61</v>
+        <v>-77.3734</v>
       </c>
       <c r="C168" t="n">
-        <v>60.069</v>
+        <v>-45.6673</v>
       </c>
       <c r="D168" t="n">
-        <v>99.09999999999999</v>
+        <v>10</v>
       </c>
       <c r="E168" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>M 2.3 - 50 km WNW of Happy Valley, Alaska</t>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>50 km WNW of Happy Valley, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7158,38 +7158,38 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>46096.13122143519</v>
+        <v>46096.22567266204</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46096.13240575232</v>
+        <v>46096.32872731482</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>nc75327557</t>
+          <t>nn00912689</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-122.757667541504</v>
+        <v>-116.8458</v>
       </c>
       <c r="C169" t="n">
-        <v>38.7836685180664</v>
+        <v>38.2828</v>
       </c>
       <c r="D169" t="n">
-        <v>2.04999995231628</v>
+        <v>5.3648</v>
       </c>
       <c r="E169" t="n">
-        <v>1.2</v>
+        <v>1.92</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>M 1.2 - 1 km N of The Geysers, CA</t>
+          <t>M 1.9 - 41 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>1 km N of The Geysers, CA</t>
+          <t>41 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7198,38 +7198,38 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>46096.12735844908</v>
+        <v>46096.2170634838</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46096.17521668981</v>
+        <v>46096.21891450231</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>nc75327552</t>
+          <t>us6000sgeb</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-120.159332275391</v>
+        <v>139.3214</v>
       </c>
       <c r="C170" t="n">
-        <v>36.105167388916</v>
+        <v>36.3919</v>
       </c>
       <c r="D170" t="n">
-        <v>9.159999847412109</v>
+        <v>94.896</v>
       </c>
       <c r="E170" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>M 1.4 - 12 km NNW of Avenal, CA</t>
+          <t>M 4.8 - 1 km SW of Kiryū, Japan</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>12 km NNW of Avenal, CA</t>
+          <t>1 km SW of Kiryū, Japan</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7238,38 +7238,38 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>46096.12601481481</v>
+        <v>46096.21257785879</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46096.15440421296</v>
+        <v>46096.66760255787</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>hv74917472</t>
+          <t>us6000sgea</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-155.253005981445</v>
+        <v>-88.2997</v>
       </c>
       <c r="C171" t="n">
-        <v>19.2596664428711</v>
+        <v>12.6324</v>
       </c>
       <c r="D171" t="n">
-        <v>24.2299995422363</v>
+        <v>55.856</v>
       </c>
       <c r="E171" t="n">
-        <v>2.36</v>
+        <v>5.3</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>M 2.4 - 20 km S of Volcano, Hawaii</t>
+          <t>M 5.3 - 67 km SSW of Chirilagua, El Salvador</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20 km S of Volcano, Hawaii</t>
+          <t>67 km SSW of Chirilagua, El Salvador</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7278,38 +7278,38 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>46096.11974375</v>
+        <v>46096.20880520833</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46096.1222449074</v>
+        <v>46096.62601605324</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>hv74917477</t>
+          <t>nn00912685</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-155.235000610352</v>
+        <v>-117.1071</v>
       </c>
       <c r="C172" t="n">
-        <v>19.2304992675781</v>
+        <v>37.2044</v>
       </c>
       <c r="D172" t="n">
-        <v>27.8999996185303</v>
+        <v>3.7302</v>
       </c>
       <c r="E172" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>M 2.6 - 23 km S of Volcano, Hawaii</t>
+          <t>M 1.4 - 45 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>23 km S of Volcano, Hawaii</t>
+          <t>45 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7318,38 +7318,38 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>46096.11969131944</v>
+        <v>46096.20641787037</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46096.12205555556</v>
+        <v>46096.20811390047</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>us6000sgdx</t>
+          <t>nc75327582</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>152.8602</v>
+        <v>-124.411834716797</v>
       </c>
       <c r="C173" t="n">
-        <v>47.1076</v>
+        <v>40.2961654663086</v>
       </c>
       <c r="D173" t="n">
-        <v>85.952</v>
+        <v>9.22999954223633</v>
       </c>
       <c r="E173" t="n">
-        <v>4.3</v>
+        <v>1.93</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>M 4.3 - Kuril Islands</t>
+          <t>M 1.9 - 11 km WSW of Petrolia, CA</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Kuril Islands</t>
+          <t>11 km WSW of Petrolia, CA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7358,38 +7358,38 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>46096.11952268519</v>
+        <v>46096.20098622685</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>46096.14409768519</v>
+        <v>46096.24126574074</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>nc75327547</t>
+          <t>us6000sge9</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>-122.466499328613</v>
+        <v>142.5299</v>
       </c>
       <c r="C174" t="n">
-        <v>37.5961685180664</v>
+        <v>37.3728</v>
       </c>
       <c r="D174" t="n">
-        <v>9.72999954223633</v>
+        <v>38.742</v>
       </c>
       <c r="E174" t="n">
-        <v>1.48</v>
+        <v>4.3</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>M 1.5 - 3 km SE of Pacifica, CA</t>
+          <t>M 4.3 - 134 km E of Tomioka, Japan</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>134 km E of Tomioka, Japan</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7398,38 +7398,38 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>46096.10495636574</v>
+        <v>46096.20051677083</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>46096.13706527778</v>
+        <v>46096.2139587963</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>nn00912672</t>
+          <t>hv74917492</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-116.7812</v>
+        <v>-155.501159667969</v>
       </c>
       <c r="C175" t="n">
-        <v>38.3201</v>
+        <v>19.1526660919189</v>
       </c>
       <c r="D175" t="n">
-        <v>3.2364</v>
+        <v>27.9200000762939</v>
       </c>
       <c r="E175" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>M 1.9 - 48 km NE of Tonopah, Nevada</t>
+          <t>M 2.2 - 6 km SSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>48 km NE of Tonopah, Nevada</t>
+          <t>6 km SSW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7438,38 +7438,38 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>46096.09975644676</v>
+        <v>46096.19672719907</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>46096.1015644213</v>
+        <v>46096.19926747686</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>us6000sgdm</t>
+          <t>ci41204415</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-111.8909</v>
+        <v>-115.949666666667</v>
       </c>
       <c r="C176" t="n">
-        <v>32.5527</v>
+        <v>32.903</v>
       </c>
       <c r="D176" t="n">
-        <v>10</v>
+        <v>7.34</v>
       </c>
       <c r="E176" t="n">
-        <v>2.5</v>
+        <v>1.09</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>M 2.5 - 5 km S of Tat Momoli, Arizona</t>
+          <t>M 1.1 - 19 km NNE of Ocotillo, CA</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>5 km S of Tat Momoli, Arizona</t>
+          <t>19 km NNE of Ocotillo, CA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7478,50 +7478,10 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>46096.09697278935</v>
+        <v>46096.19181168982</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>46096.61202137732</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>ci41204383</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>-117.512</v>
-      </c>
-      <c r="C177" t="n">
-        <v>35.7071666666667</v>
-      </c>
-      <c r="D177" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="E177" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>M 1.1 - 12 km SW of Searles Valley, CA</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>12 km SW of Searles Valley, CA</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="n">
-        <v>46096.09368009259</v>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>46096.09604913194</v>
+        <v>46096.19425657408</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/USGS.xlsx
+++ b/data/raw/USGS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J176"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,7 +641,7 @@
         <v>46097.17414733797</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46097.18496361111</v>
+        <v>46097.19192569445</v>
       </c>
     </row>
     <row r="6">
@@ -881,7 +881,7 @@
         <v>46097.15081805555</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46097.17177512732</v>
+        <v>46097.18912663194</v>
       </c>
     </row>
     <row r="12">
@@ -7402,86 +7402,6 @@
       </c>
       <c r="J174" s="2" t="n">
         <v>46096.2139587963</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>hv74917492</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>-155.501159667969</v>
-      </c>
-      <c r="C175" t="n">
-        <v>19.1526660919189</v>
-      </c>
-      <c r="D175" t="n">
-        <v>27.9200000762939</v>
-      </c>
-      <c r="E175" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>M 2.2 - 6 km SSW of Pāhala, Hawaii</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>6 km SSW of Pāhala, Hawaii</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
-        <v>46096.19672719907</v>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>46096.19926747686</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>ci41204415</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>-115.949666666667</v>
-      </c>
-      <c r="C176" t="n">
-        <v>32.903</v>
-      </c>
-      <c r="D176" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E176" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>M 1.1 - 19 km NNE of Ocotillo, CA</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>19 km NNE of Ocotillo, CA</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="n">
-        <v>46096.19181168982</v>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>46096.19425657408</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/USGS.xlsx
+++ b/data/raw/USGS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,29 +487,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aka2026fgejkl</t>
+          <t>nc75328067</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-150.208</v>
+        <v>-122.458168029785</v>
       </c>
       <c r="C2" t="n">
-        <v>62.214</v>
+        <v>37.5923347473145</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4</v>
+        <v>7.23999977111816</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8</v>
+        <v>1.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11 km S of Trapper Creek, Alaska</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,38 +518,38 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46097.18073642361</v>
+        <v>46097.20110729166</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46097.1817900926</v>
+        <v>46097.20225373843</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nn00912748</t>
+          <t>nc75328062</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-116.7944</v>
+        <v>-122.700668334961</v>
       </c>
       <c r="C3" t="n">
-        <v>38.3084</v>
+        <v>38.7681655883789</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8689</v>
+        <v>0.730000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 1 km SW of Anderson Springs, CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>46 km NE of Tonopah, Nevada</t>
+          <t>1 km SW of Anderson Springs, CA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,38 +558,38 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46097.18032635417</v>
+        <v>46097.1980800926</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46097.18299189815</v>
+        <v>46097.21344644676</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nn00912744</t>
+          <t>aka2026fgejkl</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-116.5751</v>
+        <v>-150.208</v>
       </c>
       <c r="C4" t="n">
-        <v>38.2761</v>
+        <v>62.214</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7167</v>
+        <v>4.4</v>
       </c>
       <c r="E4" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M 2.2 - 61 km ENE of Tonopah, Nevada</t>
+          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>61 km ENE of Tonopah, Nevada</t>
+          <t>11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -598,38 +598,38 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46097.17459033565</v>
+        <v>46097.18073642361</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46097.17637523148</v>
+        <v>46097.1817900926</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ci41204855</t>
+          <t>nn00912748</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-119.120666666667</v>
+        <v>-116.7944</v>
       </c>
       <c r="C5" t="n">
-        <v>34.9321666666667</v>
+        <v>38.3084</v>
       </c>
       <c r="D5" t="n">
-        <v>0.87</v>
+        <v>2.8689</v>
       </c>
       <c r="E5" t="n">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M 2.3 - 10 km NNE of Pine Mountain Club, CA</t>
+          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10 km NNE of Pine Mountain Club, CA</t>
+          <t>46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,38 +638,38 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46097.17414733797</v>
+        <v>46097.18032635417</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46097.19192569445</v>
+        <v>46097.18299189815</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nn00912743</t>
+          <t>nn00912744</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-116.0158</v>
+        <v>-116.5751</v>
       </c>
       <c r="C6" t="n">
-        <v>37.795</v>
+        <v>38.2761</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4807</v>
+        <v>6.7167</v>
       </c>
       <c r="E6" t="n">
-        <v>1.34</v>
+        <v>2.18</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
+          <t>M 2.2 - 61 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29 km NW of Rachel, Nevada</t>
+          <t>61 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -678,38 +678,38 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46097.17013881944</v>
+        <v>46097.17459033565</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46097.1716130787</v>
+        <v>46097.17637523148</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nc75328052</t>
+          <t>ci41204855</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-122.765167236328</v>
+        <v>-119.120666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>38.7836685180664</v>
+        <v>34.9321666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>4.19000005722046</v>
+        <v>0.87</v>
       </c>
       <c r="E7" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
+          <t>M 2.3 - 10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1 km NW of The Geysers, CA</t>
+          <t>10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -718,38 +718,38 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46097.16834872685</v>
+        <v>46097.17414733797</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46097.18215899306</v>
+        <v>46097.20602984953</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nn00912742</t>
+          <t>nn00912743</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-117.5849</v>
+        <v>-116.0158</v>
       </c>
       <c r="C8" t="n">
-        <v>37.3479</v>
+        <v>37.795</v>
       </c>
       <c r="D8" t="n">
-        <v>3.7908</v>
+        <v>2.4807</v>
       </c>
       <c r="E8" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
+          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>45 km S of Silver Peak, Nevada</t>
+          <t>29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -758,38 +758,38 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46097.15891554398</v>
+        <v>46097.17013881944</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46097.16036833333</v>
+        <v>46097.1716130787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nn00912740</t>
+          <t>nc75328052</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-116.3558</v>
+        <v>-122.765167236328</v>
       </c>
       <c r="C9" t="n">
-        <v>37.5573</v>
+        <v>38.7836685180664</v>
       </c>
       <c r="D9" t="n">
-        <v>8.4693</v>
+        <v>4.19000005722046</v>
       </c>
       <c r="E9" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
+          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>54 km W of Rachel, Nevada</t>
+          <t>1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -798,38 +798,38 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46097.1542737963</v>
+        <v>46097.16834872685</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46097.15577996528</v>
+        <v>46097.20647809028</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nc75328042</t>
+          <t>nn00912742</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-122.843170166016</v>
+        <v>-117.5849</v>
       </c>
       <c r="C10" t="n">
-        <v>38.8208351135254</v>
+        <v>37.3479</v>
       </c>
       <c r="D10" t="n">
-        <v>1.67999994754791</v>
+        <v>3.7908</v>
       </c>
       <c r="E10" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
+          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9 km WNW of The Geysers, CA</t>
+          <t>45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -838,38 +838,38 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46097.15140474537</v>
+        <v>46097.15891554398</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46097.15253628472</v>
+        <v>46097.16036833333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nc75328037</t>
+          <t>nn00912740</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-122.839668273926</v>
+        <v>-116.3558</v>
       </c>
       <c r="C11" t="n">
-        <v>38.8219985961914</v>
+        <v>37.5573</v>
       </c>
       <c r="D11" t="n">
-        <v>1.66999995708466</v>
+        <v>8.4693</v>
       </c>
       <c r="E11" t="n">
-        <v>1.96</v>
+        <v>1.15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
+          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9 km NW of The Geysers, CA</t>
+          <t>54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -878,38 +878,38 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46097.15081805555</v>
+        <v>46097.1542737963</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46097.18912663194</v>
+        <v>46097.15577996528</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ci41204839</t>
+          <t>nc75328042</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-117.701833333333</v>
+        <v>-122.843170166016</v>
       </c>
       <c r="C12" t="n">
-        <v>35.8715</v>
+        <v>38.8208351135254</v>
       </c>
       <c r="D12" t="n">
-        <v>4.72</v>
+        <v>1.67999994754791</v>
       </c>
       <c r="E12" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
+          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20 km ESE of Little Lake, CA</t>
+          <t>9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -918,38 +918,38 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46097.14808055555</v>
+        <v>46097.15140474537</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46097.15049766203</v>
+        <v>46097.15253628472</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aka2026fgcope</t>
+          <t>nc75328037</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-149.454</v>
+        <v>-122.839668273926</v>
       </c>
       <c r="C13" t="n">
-        <v>62.553</v>
+        <v>38.8219985961914</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
+          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>35 km ENE of Chase, Alaska</t>
+          <t>9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -958,38 +958,38 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46097.14301053241</v>
+        <v>46097.15081805555</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46097.14408171296</v>
+        <v>46097.18912663194</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nn00912738</t>
+          <t>ci41204839</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-116.4786</v>
+        <v>-117.701833333333</v>
       </c>
       <c r="C14" t="n">
-        <v>38.4752</v>
+        <v>35.8715</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3424</v>
+        <v>4.72</v>
       </c>
       <c r="E14" t="n">
-        <v>1.74</v>
+        <v>0.99</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
+          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>79 km NE of Tonopah, Nevada</t>
+          <t>20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -998,38 +998,38 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46097.13946230324</v>
+        <v>46097.14808055555</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46097.14130107639</v>
+        <v>46097.15049766203</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>aka2026fgbzeh</t>
+          <t>aka2026fgcope</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-149.584</v>
+        <v>-149.454</v>
       </c>
       <c r="C15" t="n">
-        <v>62.358</v>
+        <v>62.553</v>
       </c>
       <c r="D15" t="n">
-        <v>56.7</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
+          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25 km NNE of Susitna North, Alaska</t>
+          <t>35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1038,38 +1038,38 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46097.13059196759</v>
+        <v>46097.14301053241</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46097.13160341435</v>
+        <v>46097.14408171296</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aka2026fgbuau</t>
+          <t>nn00912738</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-146.643</v>
+        <v>-116.4786</v>
       </c>
       <c r="C16" t="n">
-        <v>61.432</v>
+        <v>38.4752</v>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>7.3424</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
+          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>37 km NNW of Valdez, Alaska</t>
+          <t>79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1078,38 +1078,38 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46097.12645101852</v>
+        <v>46097.13946230324</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46097.12856479167</v>
+        <v>46097.14130107639</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nc75327997</t>
+          <t>aka2026fgbzeh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-122.785667419434</v>
+        <v>-149.584</v>
       </c>
       <c r="C17" t="n">
-        <v>38.8154983520508</v>
+        <v>62.358</v>
       </c>
       <c r="D17" t="n">
-        <v>1.46000003814697</v>
+        <v>56.7</v>
       </c>
       <c r="E17" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
+          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1118,38 +1118,38 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46097.10226643518</v>
+        <v>46097.13059196759</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46097.10338584491</v>
+        <v>46097.13160341435</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nc75327992</t>
+          <t>aka2026fgbuau</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-122.786163330078</v>
+        <v>-146.643</v>
       </c>
       <c r="C18" t="n">
-        <v>38.8153343200684</v>
+        <v>61.432</v>
       </c>
       <c r="D18" t="n">
-        <v>1.44000005722046</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
+          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1158,38 +1158,38 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46097.09843321759</v>
+        <v>46097.12645101852</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46097.13356498843</v>
+        <v>46097.12856479167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>aka2026ffzydk</t>
+          <t>nc75327997</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-151.439</v>
+        <v>-122.785667419434</v>
       </c>
       <c r="C19" t="n">
-        <v>59.675</v>
+        <v>38.8154983520508</v>
       </c>
       <c r="D19" t="n">
-        <v>40.3</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
+          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0 km NW of Kachemak, Alaska</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1198,38 +1198,38 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46097.08785851852</v>
+        <v>46097.10226643518</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46097.0893715625</v>
+        <v>46097.10338584491</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nn00912733</t>
+          <t>nc75327992</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-116.2619</v>
+        <v>-122.786163330078</v>
       </c>
       <c r="C20" t="n">
-        <v>38.6278</v>
+        <v>38.8153343200684</v>
       </c>
       <c r="D20" t="n">
-        <v>4.7494</v>
+        <v>1.44000005722046</v>
       </c>
       <c r="E20" t="n">
-        <v>2.71</v>
+        <v>1.49</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>M 2.7 - 95 km SE of Kingston, Nevada</t>
+          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>95 km SE of Kingston, Nevada</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,38 +1238,38 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46097.08629175926</v>
+        <v>46097.09843321759</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46097.09325277778</v>
+        <v>46097.13356498843</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ci41204823</t>
+          <t>aka2026ffzydk</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-117.844666666667</v>
+        <v>-151.439</v>
       </c>
       <c r="C21" t="n">
-        <v>36.4091666666667</v>
+        <v>59.675</v>
       </c>
       <c r="D21" t="n">
-        <v>3.71</v>
+        <v>40.3</v>
       </c>
       <c r="E21" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M 1.2 - 20 km NE of Olancha, CA</t>
+          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20 km NE of Olancha, CA</t>
+          <t>0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46097.08612511574</v>
+        <v>46097.08785851852</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46097.08854572917</v>
+        <v>46097.0893715625</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tx2026ffzaya</t>
+          <t>nn00912733</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-104.188</v>
+        <v>-116.2619</v>
       </c>
       <c r="C22" t="n">
-        <v>31.703</v>
+        <v>38.6278</v>
       </c>
       <c r="D22" t="n">
-        <v>4.4731</v>
+        <v>4.7494</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7</v>
+        <v>2.71</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
+          <t>M 2.7 - 95 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>55 km SSE of Whites City, New Mexico</t>
+          <t>95 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1318,38 +1318,38 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46097.06930607639</v>
+        <v>46097.08629175926</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46097.08380681713</v>
+        <v>46097.09325277778</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hv74917612</t>
+          <t>ci41204823</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-155.139495849609</v>
+        <v>-117.844666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>19.3330001831055</v>
+        <v>36.4091666666667</v>
       </c>
       <c r="D23" t="n">
-        <v>3.76999998092651</v>
+        <v>3.71</v>
       </c>
       <c r="E23" t="n">
-        <v>2.04</v>
+        <v>1.19</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 1.2 - 20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1358,38 +1358,38 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46097.06757199074</v>
+        <v>46097.08612511574</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46097.07008101852</v>
+        <v>46097.08854572917</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ci41204799</t>
+          <t>tx2026ffzaya</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-117.4825</v>
+        <v>-104.188</v>
       </c>
       <c r="C24" t="n">
-        <v>35.601</v>
+        <v>31.703</v>
       </c>
       <c r="D24" t="n">
-        <v>7.7</v>
+        <v>4.4731</v>
       </c>
       <c r="E24" t="n">
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
+          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18 km E of Ridgecrest, CA</t>
+          <t>55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1398,38 +1398,38 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46097.0600244213</v>
+        <v>46097.06930607639</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46097.06239535879</v>
+        <v>46097.08380681713</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tx2026ffyeyx</t>
+          <t>hv74917612</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-104.176</v>
+        <v>-155.139495849609</v>
       </c>
       <c r="C25" t="n">
-        <v>31.711</v>
+        <v>19.3330001831055</v>
       </c>
       <c r="D25" t="n">
-        <v>7.4969</v>
+        <v>3.76999998092651</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M 1.9 - 54 km W of Mentone, Texas</t>
+          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>54 km W of Mentone, Texas</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1438,38 +1438,38 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46097.05150728009</v>
+        <v>46097.06757199074</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46097.06865469908</v>
+        <v>46097.07008101852</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>aka2026ffxzpn</t>
+          <t>ci41204799</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-150.668</v>
+        <v>-117.4825</v>
       </c>
       <c r="C26" t="n">
-        <v>63.582</v>
+        <v>35.601</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1</v>
+        <v>7.7</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7</v>
+        <v>0.95</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
+          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>52 km E of Denali National Park, Alaska</t>
+          <t>18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1478,38 +1478,38 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46097.0471140162</v>
+        <v>46097.0600244213</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46097.04869516204</v>
+        <v>46097.06239535879</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nn00912731</t>
+          <t>tx2026ffyeyx</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-114.5508</v>
+        <v>-104.176</v>
       </c>
       <c r="C27" t="n">
-        <v>37.2919</v>
+        <v>31.711</v>
       </c>
       <c r="D27" t="n">
-        <v>15.9298</v>
+        <v>7.4969</v>
       </c>
       <c r="E27" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
+          <t>M 1.9 - 54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>36 km S of Caliente, Nevada</t>
+          <t>54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1518,38 +1518,38 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46097.04372652778</v>
+        <v>46097.05150728009</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46097.04546596065</v>
+        <v>46097.06865469908</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ci41204783</t>
+          <t>aka2026ffxzpn</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-116.366833333333</v>
+        <v>-150.668</v>
       </c>
       <c r="C28" t="n">
-        <v>33.193</v>
+        <v>63.582</v>
       </c>
       <c r="D28" t="n">
-        <v>7.35</v>
+        <v>0.1</v>
       </c>
       <c r="E28" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
+          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7 km S of Borrego Springs, CA</t>
+          <t>52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1558,38 +1558,38 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46097.04078981481</v>
+        <v>46097.0471140162</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46097.04323087963</v>
+        <v>46097.04869516204</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nc75327962</t>
+          <t>nn00912731</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-120.523834228516</v>
+        <v>-114.5508</v>
       </c>
       <c r="C29" t="n">
-        <v>35.9671669006348</v>
+        <v>37.2919</v>
       </c>
       <c r="D29" t="n">
-        <v>6.94999980926514</v>
+        <v>15.9298</v>
       </c>
       <c r="E29" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
+          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11 km NW of Parkfield, CA</t>
+          <t>36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1598,38 +1598,38 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46097.03950659722</v>
+        <v>46097.04372652778</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46097.09886200231</v>
+        <v>46097.04546596065</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>aka2026ffxmpi</t>
+          <t>ci41204783</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-149.174</v>
+        <v>-116.366833333333</v>
       </c>
       <c r="C30" t="n">
-        <v>63.002</v>
+        <v>33.193</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2</v>
+        <v>7.35</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
+          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>44 km SSW of Cantwell, Alaska</t>
+          <t>7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46097.03663675926</v>
+        <v>46097.04078981481</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46097.03896524305</v>
+        <v>46097.04323087963</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nc75327947</t>
+          <t>nc75327962</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-124.239669799805</v>
+        <v>-120.523834228516</v>
       </c>
       <c r="C31" t="n">
-        <v>40.4664993286133</v>
+        <v>35.9671669006348</v>
       </c>
       <c r="D31" t="n">
-        <v>26.0400009155273</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="E31" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
+          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12 km WSW of Rio Dell, CA</t>
+          <t>11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1678,38 +1678,38 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46097.03397256944</v>
+        <v>46097.03950659722</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46097.08151043981</v>
+        <v>46097.09886200231</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nn00912729</t>
+          <t>aka2026ffxmpi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-116.2867</v>
+        <v>-149.174</v>
       </c>
       <c r="C32" t="n">
-        <v>37.418</v>
+        <v>63.002</v>
       </c>
       <c r="D32" t="n">
-        <v>8.758599999999999</v>
+        <v>0.2</v>
       </c>
       <c r="E32" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1718,38 +1718,38 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46097.03219180556</v>
+        <v>46097.03663675926</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46097.03392417824</v>
+        <v>46097.03896524305</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hv74917602</t>
+          <t>nc75327947</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-155.143005371094</v>
+        <v>-124.239669799805</v>
       </c>
       <c r="C33" t="n">
-        <v>19.3344993591309</v>
+        <v>40.4664993286133</v>
       </c>
       <c r="D33" t="n">
-        <v>4.25</v>
+        <v>26.0400009155273</v>
       </c>
       <c r="E33" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1758,38 +1758,38 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46097.02269363426</v>
+        <v>46097.03397256944</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46097.02506747685</v>
+        <v>46097.08151043981</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nn00912728</t>
+          <t>nn00912729</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-116.8948</v>
+        <v>-116.2867</v>
       </c>
       <c r="C34" t="n">
-        <v>38.2511</v>
+        <v>37.418</v>
       </c>
       <c r="D34" t="n">
-        <v>4.7942</v>
+        <v>8.758599999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
+          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>35 km NE of Tonopah, Nevada</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1798,38 +1798,38 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46097.02024291667</v>
+        <v>46097.03219180556</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46097.02206256944</v>
+        <v>46097.03392417824</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nn00912725</t>
+          <t>hv74917602</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-116.3002</v>
+        <v>-155.143005371094</v>
       </c>
       <c r="C35" t="n">
-        <v>36.4986</v>
+        <v>19.3344993591309</v>
       </c>
       <c r="D35" t="n">
-        <v>1.7633</v>
+        <v>4.25</v>
       </c>
       <c r="E35" t="n">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
+          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>42 km NW of Pahrump, Nevada</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1838,38 +1838,38 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46097.01676708333</v>
+        <v>46097.02269363426</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46097.01802194444</v>
+        <v>46097.02506747685</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aka2026ffwkac</t>
+          <t>nn00912728</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-147.104</v>
+        <v>-116.8948</v>
       </c>
       <c r="C36" t="n">
-        <v>61.221</v>
+        <v>38.2511</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>4.7942</v>
       </c>
       <c r="E36" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
+          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>41 km WNW of Valdez, Alaska</t>
+          <t>35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1878,38 +1878,38 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46097.01360875</v>
+        <v>46097.02024291667</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46097.01453715278</v>
+        <v>46097.02206256944</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nc75327937</t>
+          <t>nn00912725</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-120.16283416748</v>
+        <v>-116.3002</v>
       </c>
       <c r="C37" t="n">
-        <v>36.1510009765625</v>
+        <v>36.4986</v>
       </c>
       <c r="D37" t="n">
-        <v>5.53000020980835</v>
+        <v>1.7633</v>
       </c>
       <c r="E37" t="n">
-        <v>1.8</v>
+        <v>1.13</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M 1.8 - 8 km SW of Huron, CA</t>
+          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8 km SW of Huron, CA</t>
+          <t>42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1918,38 +1918,38 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46097.00379861111</v>
+        <v>46097.01676708333</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46097.07108120371</v>
+        <v>46097.01802194444</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>aka2026ffvrqe</t>
+          <t>aka2026ffwkac</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-150.318</v>
+        <v>-147.104</v>
       </c>
       <c r="C38" t="n">
-        <v>60.621</v>
+        <v>61.221</v>
       </c>
       <c r="D38" t="n">
-        <v>37.9</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
+          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>26 km ENE of Sterling, Alaska</t>
+          <t>41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1958,38 +1958,38 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46096.99880960648</v>
+        <v>46097.01360875</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46097.06023194444</v>
+        <v>46097.01453715278</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hv74917597</t>
+          <t>nc75327937</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-154.981170654297</v>
+        <v>-120.16283416748</v>
       </c>
       <c r="C39" t="n">
-        <v>19.3976669311523</v>
+        <v>36.1510009765625</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.560000002384186</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E39" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
+          <t>M 1.8 - 8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10 km SW of Leilani Estates, Hawaii</t>
+          <t>8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1998,38 +1998,38 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46096.99111076389</v>
+        <v>46097.00379861111</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46096.993578125</v>
+        <v>46097.07108120371</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ci41204759</t>
+          <t>aka2026ffvrqe</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-117.6875</v>
+        <v>-150.318</v>
       </c>
       <c r="C40" t="n">
-        <v>35.0311666666667</v>
+        <v>60.621</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.84</v>
+        <v>37.9</v>
       </c>
       <c r="E40" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km NW of Boron, CA</t>
+          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5 km NW of Boron, CA</t>
+          <t>26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2038,38 +2038,38 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46096.98700925926</v>
+        <v>46096.99880960648</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46096.98945039352</v>
+        <v>46097.06023194444</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aka2026ffvcuk</t>
+          <t>hv74917597</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-147.706</v>
+        <v>-154.981170654297</v>
       </c>
       <c r="C41" t="n">
-        <v>63.18</v>
+        <v>19.3976669311523</v>
       </c>
       <c r="D41" t="n">
-        <v>4.3</v>
+        <v>-0.560000002384186</v>
       </c>
       <c r="E41" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
+          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>66 km ESE of Cantwell, Alaska</t>
+          <t>10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2078,38 +2078,38 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46096.98682952546</v>
+        <v>46096.99111076389</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46097.05321805555</v>
+        <v>46096.993578125</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aka2026ffuxwl</t>
+          <t>ci41204759</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-149.464</v>
+        <v>-117.6875</v>
       </c>
       <c r="C42" t="n">
-        <v>65.532</v>
+        <v>35.0311666666667</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>-0.84</v>
       </c>
       <c r="E42" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
+          <t>M 1.3 - 5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>32 km E of Rampart, Alaska</t>
+          <t>5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2118,38 +2118,38 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46096.98287351852</v>
+        <v>46096.98700925926</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46096.98871584491</v>
+        <v>46096.98945039352</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nc75327927</t>
+          <t>aka2026ffvcuk</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-122.759002685547</v>
+        <v>-147.706</v>
       </c>
       <c r="C43" t="n">
-        <v>38.779167175293</v>
+        <v>63.18</v>
       </c>
       <c r="D43" t="n">
-        <v>1.16999995708466</v>
+        <v>4.3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.06</v>
+        <v>2.4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
+          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0 km NW of The Geysers, CA</t>
+          <t>66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2158,38 +2158,38 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46096.98031608796</v>
+        <v>46096.98682952546</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46096.9814612037</v>
+        <v>46097.05321805555</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>nc75327922</t>
+          <t>aka2026ffuxwl</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-120.615669250488</v>
+        <v>-149.464</v>
       </c>
       <c r="C44" t="n">
-        <v>36.0485000610352</v>
+        <v>65.532</v>
       </c>
       <c r="D44" t="n">
-        <v>2.03999996185303</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
+          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>24 km NW of Parkfield, CA</t>
+          <t>32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2198,38 +2198,38 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46096.97481886574</v>
+        <v>46096.98287351852</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46097.03291697917</v>
+        <v>46096.98871584491</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aka2026fftzga</t>
+          <t>nc75327927</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-147.469</v>
+        <v>-122.759002685547</v>
       </c>
       <c r="C45" t="n">
-        <v>64.946</v>
+        <v>38.779167175293</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E45" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>M 1.2 - 7 km E of Fox, Alaska</t>
+          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7 km E of Fox, Alaska</t>
+          <t>0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2238,38 +2238,38 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46096.96303546296</v>
+        <v>46096.98031608796</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46096.96398349537</v>
+        <v>46096.9814612037</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>nc75327902</t>
+          <t>nc75327922</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-124.639663696289</v>
+        <v>-120.615669250488</v>
       </c>
       <c r="C46" t="n">
-        <v>40.34716796875</v>
+        <v>36.0485000610352</v>
       </c>
       <c r="D46" t="n">
-        <v>19.4500007629395</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="E46" t="n">
-        <v>2.76</v>
+        <v>1.65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>M 2.8 - 30 km W of Petrolia, CA</t>
+          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>30 km W of Petrolia, CA</t>
+          <t>24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2278,38 +2278,38 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46096.95174398148</v>
+        <v>46096.97481886574</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46097.04291712963</v>
+        <v>46097.03291697917</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>us6000sgib</t>
+          <t>aka2026fftzga</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>176.3522</v>
+        <v>-147.469</v>
       </c>
       <c r="C47" t="n">
-        <v>52.1304</v>
+        <v>64.946</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
+          <t>M 1.2 - 7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>229 km ESE of Attu Station, Alaska</t>
+          <t>7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2318,38 +2318,38 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46096.94854002315</v>
+        <v>46096.96303546296</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46097.14299561342</v>
+        <v>46096.96398349537</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>nn00912719</t>
+          <t>nc75327902</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-119.7167</v>
+        <v>-124.639663696289</v>
       </c>
       <c r="C48" t="n">
-        <v>40.512</v>
+        <v>40.34716796875</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7442</v>
+        <v>19.4500007629395</v>
       </c>
       <c r="E48" t="n">
-        <v>1.9</v>
+        <v>2.76</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
+          <t>M 2.8 - 30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>32 km WSW of Empire, Nevada</t>
+          <t>30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2358,38 +2358,38 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46096.94697967593</v>
+        <v>46096.95174398148</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46096.94864458333</v>
+        <v>46097.04291712963</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>aka2026fftern</t>
+          <t>us6000sgib</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-145.732</v>
+        <v>176.3522</v>
       </c>
       <c r="C49" t="n">
-        <v>62.165</v>
+        <v>52.1304</v>
       </c>
       <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
         <v>4.6</v>
       </c>
-      <c r="E49" t="n">
-        <v>1.6</v>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
+          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>11 km WNW of Glennallen, Alaska</t>
+          <t>229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2398,38 +2398,38 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46096.94644289352</v>
+        <v>46096.94854002315</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46096.94759246528</v>
+        <v>46097.14299561342</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>aka2026ffsxtw</t>
+          <t>nn00912719</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-150.289</v>
+        <v>-119.7167</v>
       </c>
       <c r="C50" t="n">
-        <v>60.111</v>
+        <v>40.512</v>
       </c>
       <c r="D50" t="n">
-        <v>46.9</v>
+        <v>0.7442</v>
       </c>
       <c r="E50" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
+          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>46 km NE of Fox River, Alaska</t>
+          <t>32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2438,38 +2438,38 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46096.94087768519</v>
+        <v>46096.94697967593</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46096.94183203704</v>
+        <v>46096.94864458333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aka2026ffsvcz</t>
+          <t>aka2026fftern</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-141.243</v>
+        <v>-145.732</v>
       </c>
       <c r="C51" t="n">
-        <v>61.573</v>
+        <v>62.165</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
+          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>90 km E of McCarthy, Alaska</t>
+          <t>11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2478,38 +2478,38 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46096.93874224537</v>
+        <v>46096.94644289352</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46096.93996863426</v>
+        <v>46096.94759246528</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hv74917587</t>
+          <t>aka2026ffsxtw</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-155.404998779297</v>
+        <v>-150.289</v>
       </c>
       <c r="C52" t="n">
-        <v>19.2546672821045</v>
+        <v>60.111</v>
       </c>
       <c r="D52" t="n">
-        <v>30.7900009155273</v>
+        <v>46.9</v>
       </c>
       <c r="E52" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
+          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9 km NE of Pāhala, Hawaii</t>
+          <t>46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2518,38 +2518,38 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46096.93382974537</v>
+        <v>46096.94087768519</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46096.93618622685</v>
+        <v>46096.94183203704</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>nc75327892</t>
+          <t>aka2026ffsvcz</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-120.513832092285</v>
+        <v>-141.243</v>
       </c>
       <c r="C53" t="n">
-        <v>35.9599990844727</v>
+        <v>61.573</v>
       </c>
       <c r="D53" t="n">
-        <v>10.1700000762939</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
+          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10 km NW of Parkfield, CA</t>
+          <t>90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2558,38 +2558,38 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46096.92984074074</v>
+        <v>46096.93874224537</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46096.98773833334</v>
+        <v>46096.93996863426</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tx2026ffruyn</t>
+          <t>hv74917587</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-103.575</v>
+        <v>-155.404998779297</v>
       </c>
       <c r="C54" t="n">
-        <v>30.876</v>
+        <v>19.2546672821045</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>30.7900009155273</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
+          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20 km SE of Balmorhea, Texas</t>
+          <t>9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2598,38 +2598,38 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46096.91764664352</v>
+        <v>46096.93382974537</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46096.92133662037</v>
+        <v>46096.93618622685</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tx2026ffrhgd</t>
+          <t>nc75327892</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-101.817</v>
+        <v>-120.513832092285</v>
       </c>
       <c r="C55" t="n">
-        <v>32.349</v>
+        <v>35.9599990844727</v>
       </c>
       <c r="D55" t="n">
-        <v>11.8727</v>
+        <v>10.1700000762939</v>
       </c>
       <c r="E55" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
+          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21 km SSW of Ackerly, Texas</t>
+          <t>10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2638,38 +2638,38 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46096.90660459491</v>
+        <v>46096.92984074074</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46096.91322768519</v>
+        <v>46096.98773833334</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>nc75327882</t>
+          <t>tx2026ffruyn</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-122.730499267578</v>
+        <v>-103.575</v>
       </c>
       <c r="C56" t="n">
-        <v>38.7738342285156</v>
+        <v>30.876</v>
       </c>
       <c r="D56" t="n">
-        <v>2.02999997138977</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km E of The Geysers, CA</t>
+          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2 km E of The Geysers, CA</t>
+          <t>20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2678,38 +2678,38 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46096.90556168981</v>
+        <v>46096.91764664352</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46096.92179327546</v>
+        <v>46096.92133662037</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>aka2026ffqxwe</t>
+          <t>tx2026ffrhgd</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-145.627</v>
+        <v>-101.817</v>
       </c>
       <c r="C57" t="n">
-        <v>62.093</v>
+        <v>32.349</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>11.8727</v>
       </c>
       <c r="E57" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
+          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4 km WSW of Glennallen, Alaska</t>
+          <t>21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2718,38 +2718,38 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46096.89903701389</v>
+        <v>46096.90660459491</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46096.90023371528</v>
+        <v>46096.91322768519</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>nn00912718</t>
+          <t>nc75327882</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-117.1162</v>
+        <v>-122.730499267578</v>
       </c>
       <c r="C58" t="n">
-        <v>37.2236</v>
+        <v>38.7738342285156</v>
       </c>
       <c r="D58" t="n">
-        <v>0.039</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="E58" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
+          <t>M 1.0 - 2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2758,38 +2758,38 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46096.8946965625</v>
+        <v>46096.90556168981</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46096.89624318287</v>
+        <v>46096.92179327546</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>nc75327877</t>
+          <t>aka2026ffqxwe</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-121.053001403809</v>
+        <v>-145.627</v>
       </c>
       <c r="C59" t="n">
-        <v>36.4648323059082</v>
+        <v>62.093</v>
       </c>
       <c r="D59" t="n">
-        <v>0.209999993443489</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
+          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11 km SE of Pinnacles, CA</t>
+          <t>4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2798,38 +2798,38 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46096.89354375</v>
+        <v>46096.89903701389</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46096.95303508102</v>
+        <v>46096.90023371528</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>us6000sghx</t>
+          <t>nn00912718</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-68.8159</v>
+        <v>-117.1162</v>
       </c>
       <c r="C60" t="n">
-        <v>-21.1625</v>
+        <v>37.2236</v>
       </c>
       <c r="D60" t="n">
-        <v>120.691</v>
+        <v>0.039</v>
       </c>
       <c r="E60" t="n">
-        <v>4.1</v>
+        <v>1.08</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
+          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>58 km W of Ollagüe, Chile</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2838,38 +2838,38 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46096.89260434028</v>
+        <v>46096.8946965625</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46097.01954907407</v>
+        <v>46096.89624318287</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aka2026ffqnha</t>
+          <t>nc75327877</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-146.565</v>
+        <v>-121.053001403809</v>
       </c>
       <c r="C61" t="n">
-        <v>61.519</v>
+        <v>36.4648323059082</v>
       </c>
       <c r="D61" t="n">
-        <v>38.2</v>
+        <v>0.209999993443489</v>
       </c>
       <c r="E61" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
+          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>44 km NNW of Valdez, Alaska</t>
+          <t>11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2878,38 +2878,38 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46096.89050962963</v>
+        <v>46096.89354375</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46096.89142732639</v>
+        <v>46096.95303508102</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tx2026ffqmcg</t>
+          <t>us6000sghx</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-101.512</v>
+        <v>-68.8159</v>
       </c>
       <c r="C62" t="n">
-        <v>31.874</v>
+        <v>-21.1625</v>
       </c>
       <c r="D62" t="n">
-        <v>3.2716</v>
+        <v>120.691</v>
       </c>
       <c r="E62" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
+          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3 km WNW of Garden City, Texas</t>
+          <t>58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2918,38 +2918,38 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46096.88956126157</v>
+        <v>46096.89260434028</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46096.9711172801</v>
+        <v>46097.01954907407</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nn00912716</t>
+          <t>aka2026ffqnha</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-116.5976</v>
+        <v>-146.565</v>
       </c>
       <c r="C63" t="n">
-        <v>38.2879</v>
+        <v>61.519</v>
       </c>
       <c r="D63" t="n">
-        <v>4.9318</v>
+        <v>38.2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
+          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>60 km ENE of Tonopah, Nevada</t>
+          <t>44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2958,38 +2958,38 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46096.88044799768</v>
+        <v>46096.89050962963</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46096.88234515046</v>
+        <v>46096.89142732639</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>aka2026ffpwxx</t>
+          <t>tx2026ffqmcg</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-150.536</v>
+        <v>-101.512</v>
       </c>
       <c r="C64" t="n">
-        <v>60.816</v>
+        <v>31.874</v>
       </c>
       <c r="D64" t="n">
-        <v>14.2</v>
+        <v>3.2716</v>
       </c>
       <c r="E64" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
+          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14 km SE of Point Possession, Alaska</t>
+          <t>3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2998,38 +2998,38 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46096.87733195602</v>
+        <v>46096.88956126157</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46096.87884059027</v>
+        <v>46096.9711172801</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tx2026ffpmmk</t>
+          <t>nn00912716</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-102.596</v>
+        <v>-116.5976</v>
       </c>
       <c r="C65" t="n">
-        <v>32.426</v>
+        <v>38.2879</v>
       </c>
       <c r="D65" t="n">
-        <v>7.1182</v>
+        <v>4.9318</v>
       </c>
       <c r="E65" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
+          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>12 km NNW of Andrews, Texas</t>
+          <t>60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3038,38 +3038,38 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46096.86891956018</v>
+        <v>46096.88044799768</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46096.87235497685</v>
+        <v>46096.88234515046</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>aka2026ffpbrz</t>
+          <t>aka2026ffpwxx</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-151.569</v>
+        <v>-150.536</v>
       </c>
       <c r="C66" t="n">
-        <v>61.397</v>
+        <v>60.816</v>
       </c>
       <c r="D66" t="n">
-        <v>76.90000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
+          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>38 km NW of Beluga, Alaska</t>
+          <t>14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3078,38 +3078,38 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46096.86023665509</v>
+        <v>46096.87733195602</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46096.86153666666</v>
+        <v>46096.87884059027</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>aka2026ffoxwo</t>
+          <t>tx2026ffpmmk</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-153.073</v>
+        <v>-102.596</v>
       </c>
       <c r="C67" t="n">
-        <v>60.494</v>
+        <v>32.426</v>
       </c>
       <c r="D67" t="n">
-        <v>146.3</v>
+        <v>7.1182</v>
       </c>
       <c r="E67" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
+          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>75 km ENE of Port Alsworth, Alaska</t>
+          <t>12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3118,38 +3118,38 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46096.85716821759</v>
+        <v>46096.86891956018</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46096.85982177083</v>
+        <v>46096.87235497685</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tx2026ffolko</t>
+          <t>aka2026ffpbrz</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-104.401</v>
+        <v>-151.569</v>
       </c>
       <c r="C68" t="n">
-        <v>31.692</v>
+        <v>61.397</v>
       </c>
       <c r="D68" t="n">
-        <v>4.8181</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
+          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>53 km S of Whites City, New Mexico</t>
+          <t>38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3158,38 +3158,38 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46096.84736503472</v>
+        <v>46096.86023665509</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46096.93883732639</v>
+        <v>46096.86153666666</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>nc75327852</t>
+          <t>aka2026ffoxwo</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-122.464164733887</v>
+        <v>-153.073</v>
       </c>
       <c r="C69" t="n">
-        <v>37.5973320007324</v>
+        <v>60.494</v>
       </c>
       <c r="D69" t="n">
-        <v>9.090000152587891</v>
+        <v>146.3</v>
       </c>
       <c r="E69" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
+          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3198,38 +3198,38 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46096.84368958334</v>
+        <v>46096.85716821759</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46096.84483373843</v>
+        <v>46096.85982177083</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>aka2026ffogkg</t>
+          <t>tx2026ffolko</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-150.241</v>
+        <v>-104.401</v>
       </c>
       <c r="C70" t="n">
-        <v>61.578</v>
+        <v>31.692</v>
       </c>
       <c r="D70" t="n">
-        <v>30.7</v>
+        <v>4.8181</v>
       </c>
       <c r="E70" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
+          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14 km ENE of Susitna, Alaska</t>
+          <t>53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46096.84307547453</v>
+        <v>46096.84736503472</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46096.84451351852</v>
+        <v>46096.93883732639</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nc75327847</t>
+          <t>nc75327852</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-122.757667541504</v>
+        <v>-122.464164733887</v>
       </c>
       <c r="C71" t="n">
-        <v>38.7918319702148</v>
+        <v>37.5973320007324</v>
       </c>
       <c r="D71" t="n">
-        <v>0.689999997615814</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="E71" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km N of The Geysers, CA</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2 km N of The Geysers, CA</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3278,38 +3278,38 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46096.84258912037</v>
+        <v>46096.84368958334</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46096.84373324074</v>
+        <v>46096.84483373843</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ci41204687</t>
+          <t>aka2026ffogkg</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-117.249</v>
+        <v>-150.241</v>
       </c>
       <c r="C72" t="n">
-        <v>33.9988333333333</v>
+        <v>61.578</v>
       </c>
       <c r="D72" t="n">
-        <v>10.86</v>
+        <v>30.7</v>
       </c>
       <c r="E72" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
+          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>6 km SSE of Loma Linda, CA</t>
+          <t>14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3318,38 +3318,38 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46096.83063032408</v>
+        <v>46096.84307547453</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46096.83300278935</v>
+        <v>46096.84451351852</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nn00912714</t>
+          <t>nc75327847</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-116.7227</v>
+        <v>-122.757667541504</v>
       </c>
       <c r="C73" t="n">
-        <v>38.3427</v>
+        <v>38.7918319702148</v>
       </c>
       <c r="D73" t="n">
-        <v>0.1382</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="E73" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
+          <t>M 1.0 - 2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>53 km NE of Tonopah, Nevada</t>
+          <t>2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3358,38 +3358,38 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46096.82208777778</v>
+        <v>46096.84258912037</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46096.82386192129</v>
+        <v>46096.84373324074</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>aka2026ffmxvv</t>
+          <t>ci41204687</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-151.974</v>
+        <v>-117.249</v>
       </c>
       <c r="C74" t="n">
-        <v>60.349</v>
+        <v>33.9988333333333</v>
       </c>
       <c r="D74" t="n">
-        <v>77.2</v>
+        <v>10.86</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
+          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>34 km WNW of Clam Gulch, Alaska</t>
+          <t>6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3398,38 +3398,38 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46096.81522726852</v>
+        <v>46096.83063032408</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46096.81638251158</v>
+        <v>46096.83300278935</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nc75327827</t>
+          <t>nn00912714</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-121.9375</v>
+        <v>-116.7227</v>
       </c>
       <c r="C75" t="n">
-        <v>37.7731666666667</v>
+        <v>38.3427</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>0.1382</v>
       </c>
       <c r="E75" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
+          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>4 km ESE of San Ramon, CA</t>
+          <t>53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3438,38 +3438,38 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46096.81305393518</v>
+        <v>46096.82208777778</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46097.01551917824</v>
+        <v>46096.82386192129</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>nc75327822</t>
+          <t>aka2026ffmxvv</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-122.787170410156</v>
+        <v>-151.974</v>
       </c>
       <c r="C76" t="n">
-        <v>38.7934989929199</v>
+        <v>60.349</v>
       </c>
       <c r="D76" t="n">
-        <v>2.92000007629395</v>
+        <v>77.2</v>
       </c>
       <c r="E76" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
+          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3478,38 +3478,38 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46096.81298229167</v>
+        <v>46096.81522726852</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46096.86627753473</v>
+        <v>46096.81638251158</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>us6000sghq</t>
+          <t>nc75327827</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>49.7256</v>
+        <v>-121.9375</v>
       </c>
       <c r="C77" t="n">
-        <v>32.4853</v>
+        <v>37.7731666666667</v>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E77" t="n">
-        <v>4.4</v>
+        <v>1.57</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
+          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>62 km SW of Fereydūnshahr, Iran</t>
+          <t>4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3518,38 +3518,38 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46096.8103829051</v>
+        <v>46096.81305393518</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46096.86111157407</v>
+        <v>46097.01551917824</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>aka2026ffmjyx</t>
+          <t>nc75327822</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-149.647</v>
+        <v>-122.787170410156</v>
       </c>
       <c r="C78" t="n">
-        <v>63.036</v>
+        <v>38.7934989929199</v>
       </c>
       <c r="D78" t="n">
-        <v>76.40000000000001</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="E78" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
+          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>52 km SW of Cantwell, Alaska</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3558,38 +3558,38 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46096.80405828704</v>
+        <v>46096.81298229167</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46096.80508491898</v>
+        <v>46096.86627753473</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>us6000sghd</t>
+          <t>us6000sghq</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>142.6105</v>
+        <v>49.7256</v>
       </c>
       <c r="C79" t="n">
-        <v>41.4045</v>
+        <v>32.4853</v>
       </c>
       <c r="D79" t="n">
-        <v>42.986</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
+          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>84 km SSW of Honchō, Japan</t>
+          <t>62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3598,38 +3598,38 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46096.78951814815</v>
+        <v>46096.8103829051</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46096.84466623842</v>
+        <v>46096.86111157407</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>aka2026fflqih</t>
+          <t>aka2026ffmjyx</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-150.765</v>
+        <v>-149.647</v>
       </c>
       <c r="C80" t="n">
-        <v>63.04</v>
+        <v>63.036</v>
       </c>
       <c r="D80" t="n">
-        <v>117.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
+          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>60 km N of Petersville, Alaska</t>
+          <t>52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3638,38 +3638,38 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46096.78820800926</v>
+        <v>46096.80405828704</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46096.79154229166</v>
+        <v>46096.80508491898</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>us6000sghb</t>
+          <t>us6000sghd</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>131.6063</v>
+        <v>142.6105</v>
       </c>
       <c r="C81" t="n">
-        <v>31.4194</v>
+        <v>41.4045</v>
       </c>
       <c r="D81" t="n">
-        <v>32.903</v>
+        <v>42.986</v>
       </c>
       <c r="E81" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
+          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>30 km SE of Nichinan, Japan</t>
+          <t>84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3678,38 +3678,38 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46096.77722483796</v>
+        <v>46096.78951814815</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46096.91079450231</v>
+        <v>46096.84466623842</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>us6000sgh9</t>
+          <t>aka2026fflqih</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-77.5782</v>
+        <v>-150.765</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.3215</v>
+        <v>63.04</v>
       </c>
       <c r="D82" t="n">
-        <v>218.126</v>
+        <v>117.3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
+          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>44 km SE of Tena, Ecuador</t>
+          <t>60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3718,38 +3718,38 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46096.77198028936</v>
+        <v>46096.78820800926</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46096.78392407407</v>
+        <v>46096.79154229166</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nc75327792</t>
+          <t>us6000sghb</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-122.471336364746</v>
+        <v>131.6063</v>
       </c>
       <c r="C83" t="n">
-        <v>37.5974998474121</v>
+        <v>31.4194</v>
       </c>
       <c r="D83" t="n">
-        <v>9.72999954223633</v>
+        <v>32.903</v>
       </c>
       <c r="E83" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
+          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2 km SE of Pacifica, CA</t>
+          <t>30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3758,38 +3758,38 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46096.77132291667</v>
+        <v>46096.77722483796</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46096.81413002315</v>
+        <v>46096.91079450231</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>aka2026ffklqv</t>
+          <t>us6000sgh9</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-155.854</v>
+        <v>-77.5782</v>
       </c>
       <c r="C84" t="n">
-        <v>57.153</v>
+        <v>-1.3215</v>
       </c>
       <c r="D84" t="n">
-        <v>63.2</v>
+        <v>218.126</v>
       </c>
       <c r="E84" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
+          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>96 km WSW of Karluk, Alaska</t>
+          <t>44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3798,38 +3798,38 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46096.76349226852</v>
+        <v>46096.77198028936</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46096.76507798611</v>
+        <v>46096.78392407407</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nc75327787</t>
+          <t>nc75327792</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-123.346832275391</v>
+        <v>-122.471336364746</v>
       </c>
       <c r="C85" t="n">
-        <v>39.476001739502</v>
+        <v>37.5974998474121</v>
       </c>
       <c r="D85" t="n">
-        <v>4.19999980926514</v>
+        <v>9.72999954223633</v>
       </c>
       <c r="E85" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
+          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>5 km NE of Brooktrails, CA</t>
+          <t>2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3838,38 +3838,38 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46096.7527207176</v>
+        <v>46096.77132291667</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46096.79673230324</v>
+        <v>46096.81413002315</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>aka2026ffjrwj</t>
+          <t>aka2026ffklqv</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-149.163</v>
+        <v>-155.854</v>
       </c>
       <c r="C86" t="n">
-        <v>62.869</v>
+        <v>57.153</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3</v>
+        <v>63.2</v>
       </c>
       <c r="E86" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
+          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>59 km S of Cantwell, Alaska</t>
+          <t>96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3878,38 +3878,38 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46096.74754356482</v>
+        <v>46096.76349226852</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46096.7486603125</v>
+        <v>46096.76507798611</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>aka2026ffjpxp</t>
+          <t>nc75327787</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-152.555</v>
+        <v>-123.346832275391</v>
       </c>
       <c r="C87" t="n">
-        <v>59.7</v>
+        <v>39.476001739502</v>
       </c>
       <c r="D87" t="n">
-        <v>76.90000000000001</v>
+        <v>4.19999980926514</v>
       </c>
       <c r="E87" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
+          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>41 km WSW of Anchor Point, Alaska</t>
+          <t>5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3918,38 +3918,38 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46096.74597070602</v>
+        <v>46096.7527207176</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46096.74724846065</v>
+        <v>46096.79673230324</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>us6000sgh3</t>
+          <t>aka2026ffjrwj</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>128.5163</v>
+        <v>-149.163</v>
       </c>
       <c r="C88" t="n">
-        <v>-7.3925</v>
+        <v>62.869</v>
       </c>
       <c r="D88" t="n">
-        <v>137.104</v>
+        <v>0.3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
+          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>208 km NE of Lospalos, Timor Leste</t>
+          <t>59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3958,38 +3958,38 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46096.7350890625</v>
+        <v>46096.74754356482</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46096.81851898148</v>
+        <v>46096.7486603125</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ci41204623</t>
+          <t>aka2026ffjpxp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-116.638166666667</v>
+        <v>-152.555</v>
       </c>
       <c r="C89" t="n">
-        <v>32.8055</v>
+        <v>59.7</v>
       </c>
       <c r="D89" t="n">
-        <v>16.68</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
+          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>10 km W of Pine Valley, CA</t>
+          <t>41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3998,38 +3998,38 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46096.72295416667</v>
+        <v>46096.74597070602</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46096.72542263889</v>
+        <v>46096.74724846065</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>aka2026ffhzps</t>
+          <t>us6000sgh3</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-146.822</v>
+        <v>128.5163</v>
       </c>
       <c r="C90" t="n">
-        <v>60.719</v>
+        <v>-7.3925</v>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>137.104</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
+          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18 km SSW of Tatitlek, Alaska</t>
+          <t>208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4038,38 +4038,38 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46096.71188380787</v>
+        <v>46096.7350890625</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46096.71385545139</v>
+        <v>46096.81851898148</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>tx2026ffhpux</t>
+          <t>ci41204623</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-103.799</v>
+        <v>-116.638166666667</v>
       </c>
       <c r="C91" t="n">
-        <v>31.021</v>
+        <v>32.8055</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>16.68</v>
       </c>
       <c r="E91" t="n">
-        <v>1.9</v>
+        <v>1.07</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
+          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>6 km NW of Balmorhea, Texas</t>
+          <t>10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4078,38 +4078,38 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46096.70398288195</v>
+        <v>46096.72295416667</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46096.71967913194</v>
+        <v>46096.72542263889</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>aka2026ffhkgu</t>
+          <t>aka2026ffhzps</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-154.974</v>
+        <v>-146.822</v>
       </c>
       <c r="C92" t="n">
-        <v>58.28</v>
+        <v>60.719</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3</v>
+        <v>19</v>
       </c>
       <c r="E92" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
+          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>84 km NNW of Karluk, Alaska</t>
+          <t>18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4118,38 +4118,38 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46096.6993729051</v>
+        <v>46096.71188380787</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46096.7007930787</v>
+        <v>46096.71385545139</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nc75327772</t>
+          <t>tx2026ffhpux</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-122.78466796875</v>
+        <v>-103.799</v>
       </c>
       <c r="C93" t="n">
-        <v>38.7933349609375</v>
+        <v>31.021</v>
       </c>
       <c r="D93" t="n">
-        <v>3.51999998092651</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
+          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4158,38 +4158,38 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46096.69837233796</v>
+        <v>46096.70398288195</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46096.72732706019</v>
+        <v>46096.71967913194</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>us6000sggw</t>
+          <t>aka2026ffhkgu</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>143.3074</v>
+        <v>-154.974</v>
       </c>
       <c r="C94" t="n">
-        <v>40.9048</v>
+        <v>58.28</v>
       </c>
       <c r="D94" t="n">
-        <v>37.859</v>
+        <v>0.3</v>
       </c>
       <c r="E94" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
+          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>139 km SSE of Honchō, Japan</t>
+          <t>84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4198,38 +4198,38 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46096.68937086806</v>
+        <v>46096.6993729051</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46096.69961851852</v>
+        <v>46096.7007930787</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nc75327767</t>
+          <t>nc75327772</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-120.05883026123</v>
+        <v>-122.78466796875</v>
       </c>
       <c r="C95" t="n">
-        <v>35.7056655883789</v>
+        <v>38.7933349609375</v>
       </c>
       <c r="D95" t="n">
-        <v>7.76999998092651</v>
+        <v>3.51999998092651</v>
       </c>
       <c r="E95" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>M 2.2 - 22 km E of Cholame, CA</t>
+          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>22 km E of Cholame, CA</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4238,38 +4238,38 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46096.68914074074</v>
+        <v>46096.69837233796</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46096.71344819444</v>
+        <v>46096.72732706019</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>aka2026ffgrhi</t>
+          <t>us6000sggw</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-151.417</v>
+        <v>143.3074</v>
       </c>
       <c r="C96" t="n">
-        <v>63.08</v>
+        <v>40.9048</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>37.859</v>
       </c>
       <c r="E96" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
+          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>53 km SSE of Denali National Park, Alaska</t>
+          <t>139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4278,38 +4278,38 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46096.68422761574</v>
+        <v>46096.68937086806</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46096.68548758102</v>
+        <v>46096.69961851852</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>nc75327742</t>
+          <t>nc75327767</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-121.291664123535</v>
+        <v>-120.05883026123</v>
       </c>
       <c r="C97" t="n">
-        <v>36.9063339233398</v>
+        <v>35.7056655883789</v>
       </c>
       <c r="D97" t="n">
-        <v>7.69000005722046</v>
+        <v>7.76999998092651</v>
       </c>
       <c r="E97" t="n">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>M 1.2 - 12 km NE of Hollister, CA</t>
+          <t>M 2.2 - 22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>12 km NE of Hollister, CA</t>
+          <t>22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4318,38 +4318,38 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46096.65917303241</v>
+        <v>46096.68914074074</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46096.69960388889</v>
+        <v>46096.71344819444</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>nc75327737</t>
+          <t>aka2026ffgrhi</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-122.806663513184</v>
+        <v>-151.417</v>
       </c>
       <c r="C98" t="n">
-        <v>38.8235015869141</v>
+        <v>63.08</v>
       </c>
       <c r="D98" t="n">
-        <v>2.41000008583069</v>
+        <v>5</v>
       </c>
       <c r="E98" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
+          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>7 km NW of The Geysers, CA</t>
+          <t>53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4358,38 +4358,38 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46096.65873715278</v>
+        <v>46096.68422761574</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46096.67873339121</v>
+        <v>46096.68548758102</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nn00912713</t>
+          <t>nc75327742</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-116.393</v>
+        <v>-121.291664123535</v>
       </c>
       <c r="C99" t="n">
-        <v>38.5366</v>
+        <v>36.9063339233398</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0315</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="E99" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
+          <t>M 1.2 - 12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>89 km NE of Tonopah, Nevada</t>
+          <t>12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4398,38 +4398,38 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46096.64812005787</v>
+        <v>46096.65917303241</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46096.64995700232</v>
+        <v>46096.69960388889</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>nc75327727</t>
+          <t>nc75327737</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-122.743835449219</v>
+        <v>-122.806663513184</v>
       </c>
       <c r="C100" t="n">
-        <v>38.7863349914551</v>
+        <v>38.8235015869141</v>
       </c>
       <c r="D100" t="n">
-        <v>0.850000023841858</v>
+        <v>2.41000008583069</v>
       </c>
       <c r="E100" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
+          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1 km NE of The Geysers, CA</t>
+          <t>7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4438,38 +4438,38 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46096.64470740741</v>
+        <v>46096.65873715278</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46096.68219443287</v>
+        <v>46096.67873339121</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ci41204591</t>
+          <t>nn00912713</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-115.8325</v>
+        <v>-116.393</v>
       </c>
       <c r="C101" t="n">
-        <v>31.8188333333333</v>
+        <v>38.5366</v>
       </c>
       <c r="D101" t="n">
-        <v>13.69</v>
+        <v>0.0315</v>
       </c>
       <c r="E101" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
+          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>70 km E of Maneadero, B.C., MX</t>
+          <t>89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4478,38 +4478,38 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46096.62630196759</v>
+        <v>46096.64812005787</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46096.62875739583</v>
+        <v>46096.64995700232</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>nc75327717</t>
+          <t>nc75327727</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-121.055168151855</v>
+        <v>-122.743835449219</v>
       </c>
       <c r="C102" t="n">
-        <v>36.451000213623</v>
+        <v>38.7863349914551</v>
       </c>
       <c r="D102" t="n">
-        <v>0.409999996423721</v>
+        <v>0.850000023841858</v>
       </c>
       <c r="E102" t="n">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
+          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>12 km SE of Pinnacles, CA</t>
+          <t>1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4518,38 +4518,38 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46096.61927071759</v>
+        <v>46096.64470740741</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46096.64398418982</v>
+        <v>46096.68219443287</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>tx2026ffdmwb</t>
+          <t>ci41204591</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-104.429</v>
+        <v>-115.8325</v>
       </c>
       <c r="C103" t="n">
-        <v>31.64</v>
+        <v>31.8188333333333</v>
       </c>
       <c r="D103" t="n">
-        <v>3.3848</v>
+        <v>13.69</v>
       </c>
       <c r="E103" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>M 1.5 - 59 km S of Whites City, New Mexico</t>
+          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>59 km S of Whites City, New Mexico</t>
+          <t>70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4558,38 +4558,38 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46096.6177771875</v>
+        <v>46096.62630196759</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46096.62529559027</v>
+        <v>46096.62875739583</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>aka2026ffcpmw</t>
+          <t>nc75327717</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-152.825</v>
+        <v>-121.055168151855</v>
       </c>
       <c r="C104" t="n">
-        <v>59.058</v>
+        <v>36.451000213623</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
+          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>61 km WSW of Nanwalek, Alaska</t>
+          <t>12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4598,38 +4598,38 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46096.59896729167</v>
+        <v>46096.61927071759</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46096.91903732639</v>
+        <v>46096.64398418982</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>us6000sggm</t>
+          <t>tx2026ffdmwb</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>130.0249</v>
+        <v>-104.413</v>
       </c>
       <c r="C105" t="n">
-        <v>-5.5263</v>
+        <v>31.649</v>
       </c>
       <c r="D105" t="n">
-        <v>184.533</v>
+        <v>5.946</v>
       </c>
       <c r="E105" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
+          <t>M 1.6 - 58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>271 km SSE of Amahai, Indonesia</t>
+          <t>58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4638,38 +4638,38 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46096.59319422454</v>
+        <v>46096.61776914352</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46096.69633148148</v>
+        <v>46097.20572792824</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>hv74917522</t>
+          <t>aka2026ffcpmw</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-155.374328613281</v>
+        <v>-152.825</v>
       </c>
       <c r="C106" t="n">
-        <v>19.1918334960938</v>
+        <v>59.058</v>
       </c>
       <c r="D106" t="n">
-        <v>31.7099990844727</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
+          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>11 km E of Pāhala, Hawaii</t>
+          <t>61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4678,38 +4678,38 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46096.59297361111</v>
+        <v>46096.59896729167</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46096.5954587963</v>
+        <v>46096.91903732639</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ci41204575</t>
+          <t>us6000sggm</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-116.426666666667</v>
+        <v>130.0249</v>
       </c>
       <c r="C107" t="n">
-        <v>33.9901666666667</v>
+        <v>-5.5263</v>
       </c>
       <c r="D107" t="n">
-        <v>2.17</v>
+        <v>184.533</v>
       </c>
       <c r="E107" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4718,38 +4718,38 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46096.58429085648</v>
+        <v>46096.59319422454</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46096.69570008102</v>
+        <v>46096.69633148148</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ci41204567</t>
+          <t>hv74917522</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-116.426666666667</v>
+        <v>-155.374328613281</v>
       </c>
       <c r="C108" t="n">
-        <v>33.9915</v>
+        <v>19.1918334960938</v>
       </c>
       <c r="D108" t="n">
-        <v>2.18</v>
+        <v>31.7099990844727</v>
       </c>
       <c r="E108" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4758,38 +4758,38 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46096.57788611111</v>
+        <v>46096.59297361111</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46096.58546979167</v>
+        <v>46096.5954587963</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nn00912712</t>
+          <t>ci41204575</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-116.4988</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C109" t="n">
-        <v>38.4756</v>
+        <v>33.9901666666667</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0689</v>
+        <v>2.17</v>
       </c>
       <c r="E109" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
+          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>78 km NE of Tonopah, Nevada</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4798,38 +4798,38 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46096.57585082176</v>
+        <v>46096.58429085648</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46096.57864184028</v>
+        <v>46096.69570008102</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ci41204559</t>
+          <t>ci41204567</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-118.1145</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C110" t="n">
-        <v>34.0995</v>
+        <v>33.9915</v>
       </c>
       <c r="D110" t="n">
-        <v>8.91</v>
+        <v>2.18</v>
       </c>
       <c r="E110" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
+          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1 km WNW of San Gabriel, CA</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4838,38 +4838,38 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46096.5639962963</v>
+        <v>46096.57788611111</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46096.56638376157</v>
+        <v>46096.58546979167</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>aka2026ffaxsl</t>
+          <t>nn00912712</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-153.59</v>
+        <v>-116.4988</v>
       </c>
       <c r="C111" t="n">
-        <v>59.151</v>
+        <v>38.4756</v>
       </c>
       <c r="D111" t="n">
-        <v>102.5</v>
+        <v>0.0689</v>
       </c>
       <c r="E111" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4878,38 +4878,38 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46096.56368013889</v>
+        <v>46096.57585082176</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46096.564885625</v>
+        <v>46096.57864184028</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>aka2026ffanxh</t>
+          <t>ci41204559</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-149.871</v>
+        <v>-118.1145</v>
       </c>
       <c r="C112" t="n">
-        <v>61.849</v>
+        <v>34.0995</v>
       </c>
       <c r="D112" t="n">
-        <v>28.4</v>
+        <v>8.91</v>
       </c>
       <c r="E112" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
+          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>14 km NE of Willow, Alaska</t>
+          <t>1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4918,38 +4918,38 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46096.55577541667</v>
+        <v>46096.5639962963</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46096.55684119213</v>
+        <v>46096.56638376157</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>tx2026ffanng</t>
+          <t>aka2026ffaxsl</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-101.924</v>
+        <v>-153.59</v>
       </c>
       <c r="C113" t="n">
-        <v>32.101</v>
+        <v>59.151</v>
       </c>
       <c r="D113" t="n">
-        <v>3.9912</v>
+        <v>102.5</v>
       </c>
       <c r="E113" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
+          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4958,38 +4958,38 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46096.55563410879</v>
+        <v>46096.56368013889</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46096.97107067129</v>
+        <v>46096.564885625</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nn00912708</t>
+          <t>aka2026ffanxh</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-116.4027</v>
+        <v>-149.871</v>
       </c>
       <c r="C114" t="n">
-        <v>37.3392</v>
+        <v>61.849</v>
       </c>
       <c r="D114" t="n">
-        <v>13.9737</v>
+        <v>28.4</v>
       </c>
       <c r="E114" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
+          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>57 km NNE of Beatty, Nevada</t>
+          <t>14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4998,38 +4998,38 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46096.55248135416</v>
+        <v>46096.55577541667</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46096.55406869213</v>
+        <v>46096.55684119213</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nn00912710</t>
+          <t>tx2026ffanng</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-117.9202</v>
+        <v>-101.924</v>
       </c>
       <c r="C115" t="n">
-        <v>38.5488</v>
+        <v>32.101</v>
       </c>
       <c r="D115" t="n">
-        <v>11.6085</v>
+        <v>3.9912</v>
       </c>
       <c r="E115" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
+          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>24 km NE of Mina, Nevada</t>
+          <t>13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5038,38 +5038,38 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46096.55246195602</v>
+        <v>46096.55563410879</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46096.55466255787</v>
+        <v>46096.97107067129</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>aka2026ffagux</t>
+          <t>nn00912708</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-149.012</v>
+        <v>-116.4027</v>
       </c>
       <c r="C116" t="n">
-        <v>62.698</v>
+        <v>37.3392</v>
       </c>
       <c r="D116" t="n">
-        <v>62.2</v>
+        <v>13.9737</v>
       </c>
       <c r="E116" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
+          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>62 km ENE of Chase, Alaska</t>
+          <t>57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5078,38 +5078,38 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46096.55006834491</v>
+        <v>46096.55248135416</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46096.5511231713</v>
+        <v>46096.55406869213</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>aka2026ffacwz</t>
+          <t>nn00912710</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-154.211</v>
+        <v>-117.9202</v>
       </c>
       <c r="C117" t="n">
-        <v>58.934</v>
+        <v>38.5488</v>
       </c>
       <c r="D117" t="n">
-        <v>126.4</v>
+        <v>11.6085</v>
       </c>
       <c r="E117" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
+          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>64 km SSE of Kokhanok, Alaska</t>
+          <t>24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5118,38 +5118,38 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46096.54689578704</v>
+        <v>46096.55246195602</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46096.54852043981</v>
+        <v>46096.55466255787</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>uw62235651</t>
+          <t>aka2026ffagux</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-124.0351666666667</v>
+        <v>-149.012</v>
       </c>
       <c r="C118" t="n">
-        <v>47.33166666666666</v>
+        <v>62.698</v>
       </c>
       <c r="D118" t="n">
-        <v>23.98</v>
+        <v>62.2</v>
       </c>
       <c r="E118" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
+          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>12 km NNW of Humptulips, Washington</t>
+          <t>62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5158,38 +5158,38 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46096.54669189815</v>
+        <v>46096.55006834491</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46096.58038923611</v>
+        <v>46096.5511231713</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>nc75327692</t>
+          <t>aka2026ffacwz</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-122.779335021973</v>
+        <v>-154.211</v>
       </c>
       <c r="C119" t="n">
-        <v>38.8115005493164</v>
+        <v>58.934</v>
       </c>
       <c r="D119" t="n">
-        <v>0.550000011920929</v>
+        <v>126.4</v>
       </c>
       <c r="E119" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
+          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>4 km NNW of The Geysers, CA</t>
+          <t>64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5198,38 +5198,38 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46096.54474907408</v>
+        <v>46096.54689578704</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46096.5710708449</v>
+        <v>46096.54852043981</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>us6000sgg9</t>
+          <t>uw62235651</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-77.3565</v>
+        <v>-124.0351666666667</v>
       </c>
       <c r="C120" t="n">
-        <v>-45.6923</v>
+        <v>47.33166666666666</v>
       </c>
       <c r="D120" t="n">
-        <v>10</v>
+        <v>23.98</v>
       </c>
       <c r="E120" t="n">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>M 4.6 - Off the coast of Aisen, Chile</t>
+          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5238,38 +5238,38 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46096.53758378472</v>
+        <v>46096.54669189815</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46096.58026666666</v>
+        <v>46096.58038923611</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>us6000sgg8</t>
+          <t>nc75327692</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-77.3313</v>
+        <v>-122.779335021973</v>
       </c>
       <c r="C121" t="n">
-        <v>-45.741</v>
+        <v>38.8115005493164</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="E121" t="n">
-        <v>4.4</v>
+        <v>1.08</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5278,38 +5278,38 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46096.53580871528</v>
+        <v>46096.54474907408</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46096.59747731481</v>
+        <v>46096.5710708449</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>aka2026fezlzd</t>
+          <t>us6000sgg9</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-150.155</v>
+        <v>-77.3565</v>
       </c>
       <c r="C122" t="n">
-        <v>61.309</v>
+        <v>-45.6923</v>
       </c>
       <c r="D122" t="n">
-        <v>35.8</v>
+        <v>10</v>
       </c>
       <c r="E122" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
+          <t>M 4.6 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>11 km WSW of Point MacKenzie, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5318,38 +5318,38 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46096.53327611111</v>
+        <v>46096.53758378472</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46096.53437532407</v>
+        <v>46096.58026666666</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>aka2026feywwv</t>
+          <t>us6000sgg8</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-148.811</v>
+        <v>-77.3313</v>
       </c>
       <c r="C123" t="n">
-        <v>63.988</v>
+        <v>-45.741</v>
       </c>
       <c r="D123" t="n">
-        <v>113.5</v>
+        <v>10</v>
       </c>
       <c r="E123" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>15 km ESE of Ferry, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5358,38 +5358,38 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46096.52110533565</v>
+        <v>46096.53580871528</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46096.52266071759</v>
+        <v>46096.59747731481</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>us6000sgg7</t>
+          <t>aka2026fezlzd</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-72.47499999999999</v>
+        <v>-150.155</v>
       </c>
       <c r="C124" t="n">
-        <v>41.5071</v>
+        <v>61.309</v>
       </c>
       <c r="D124" t="n">
-        <v>6.072</v>
+        <v>35.8</v>
       </c>
       <c r="E124" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
+          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2 km WNW of Moodus, Connecticut</t>
+          <t>11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5398,38 +5398,38 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46096.51831680556</v>
+        <v>46096.53327611111</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46097.0635559375</v>
+        <v>46096.53437532407</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>aka2026feypws</t>
+          <t>aka2026feywwv</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-151.884</v>
+        <v>-148.811</v>
       </c>
       <c r="C125" t="n">
-        <v>61.213</v>
+        <v>63.988</v>
       </c>
       <c r="D125" t="n">
-        <v>92</v>
+        <v>113.5</v>
       </c>
       <c r="E125" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
+          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>43 km WNW of Tyonek, Alaska</t>
+          <t>15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5438,38 +5438,38 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46096.51546960648</v>
+        <v>46096.52110533565</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46096.51679775463</v>
+        <v>46096.52266071759</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>hv74917517</t>
+          <t>us6000sgg7</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-155.388671875</v>
+        <v>-72.47499999999999</v>
       </c>
       <c r="C126" t="n">
-        <v>19.2761669158936</v>
+        <v>41.5071</v>
       </c>
       <c r="D126" t="n">
-        <v>29.1200008392334</v>
+        <v>6.072</v>
       </c>
       <c r="E126" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
+          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>12 km NE of Pāhala, Hawaii</t>
+          <t>2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5478,38 +5478,38 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46096.51510231481</v>
+        <v>46096.51831680556</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46096.51755763889</v>
+        <v>46097.0635559375</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>us6000sgg3</t>
+          <t>aka2026feypws</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-72.49160000000001</v>
+        <v>-151.884</v>
       </c>
       <c r="C127" t="n">
-        <v>41.4904</v>
+        <v>61.213</v>
       </c>
       <c r="D127" t="n">
-        <v>6.63</v>
+        <v>92</v>
       </c>
       <c r="E127" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
+          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>3 km WSW of Moodus, Connecticut</t>
+          <t>43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5518,38 +5518,38 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46096.51474966435</v>
+        <v>46096.51546960648</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46097.05646988426</v>
+        <v>46096.51679775463</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>us6000sgg2</t>
+          <t>hv74917517</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>155.7691</v>
+        <v>-155.388671875</v>
       </c>
       <c r="C128" t="n">
-        <v>50.1375</v>
+        <v>19.2761669158936</v>
       </c>
       <c r="D128" t="n">
-        <v>93.238</v>
+        <v>29.1200008392334</v>
       </c>
       <c r="E128" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5558,38 +5558,38 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46096.50655835648</v>
+        <v>46096.51510231481</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46096.52194490741</v>
+        <v>46096.51755763889</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>aka2026feycns</t>
+          <t>us6000sgg3</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-148.959</v>
+        <v>-72.49160000000001</v>
       </c>
       <c r="C129" t="n">
-        <v>63.283</v>
+        <v>41.4904</v>
       </c>
       <c r="D129" t="n">
-        <v>0.6</v>
+        <v>6.63</v>
       </c>
       <c r="E129" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
+          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>12 km S of Cantwell, Alaska</t>
+          <t>3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5598,38 +5598,38 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46096.50470625</v>
+        <v>46096.51474966435</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46096.50576539352</v>
+        <v>46097.21278487269</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ci41204535</t>
+          <t>us6000sgg2</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-119.474833333333</v>
+        <v>155.7691</v>
       </c>
       <c r="C130" t="n">
-        <v>34.3685</v>
+        <v>50.1375</v>
       </c>
       <c r="D130" t="n">
-        <v>0.54</v>
+        <v>93.238</v>
       </c>
       <c r="E130" t="n">
-        <v>1.49</v>
+        <v>4.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
+          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>5 km SE of Carpinteria, CA</t>
+          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5638,38 +5638,38 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46096.49835740741</v>
+        <v>46096.50655835648</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46096.50080350695</v>
+        <v>46096.52194490741</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>aka2026fewzkc</t>
+          <t>aka2026feycns</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-148.795</v>
+        <v>-148.959</v>
       </c>
       <c r="C131" t="n">
-        <v>62.2</v>
+        <v>63.283</v>
       </c>
       <c r="D131" t="n">
-        <v>22.1</v>
+        <v>0.6</v>
       </c>
       <c r="E131" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
+          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>47 km N of Sutton-Alpine, Alaska</t>
+          <t>12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5678,38 +5678,38 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46096.48122515046</v>
+        <v>46096.50470625</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46096.48264917824</v>
+        <v>46096.50576539352</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>us6000sgfx</t>
+          <t>ci41204535</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-80.1019</v>
+        <v>-119.474833333333</v>
       </c>
       <c r="C132" t="n">
-        <v>0.5871</v>
+        <v>34.3685</v>
       </c>
       <c r="D132" t="n">
-        <v>36.381</v>
+        <v>0.54</v>
       </c>
       <c r="E132" t="n">
-        <v>4.4</v>
+        <v>1.49</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
+          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>9 km WSW of Muisne, Ecuador</t>
+          <t>5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5718,38 +5718,38 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46096.47494160879</v>
+        <v>46096.49835740741</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46096.4911</v>
+        <v>46096.50080350695</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>pr71509923</t>
+          <t>aka2026fewzkc</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-66.1071666666667</v>
+        <v>-148.795</v>
       </c>
       <c r="C133" t="n">
-        <v>18.1251666666667</v>
+        <v>62.2</v>
       </c>
       <c r="D133" t="n">
-        <v>24.58</v>
+        <v>22.1</v>
       </c>
       <c r="E133" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5758,38 +5758,38 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46096.47251458334</v>
+        <v>46096.48122515046</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46096.60321875</v>
+        <v>46096.48264917824</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ci41204519</t>
+          <t>us6000sgfx</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-118.627833333333</v>
+        <v>-80.1019</v>
       </c>
       <c r="C134" t="n">
-        <v>34.6043333333333</v>
+        <v>0.5871</v>
       </c>
       <c r="D134" t="n">
-        <v>10.64</v>
+        <v>36.381</v>
       </c>
       <c r="E134" t="n">
-        <v>1.13</v>
+        <v>4.4</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>M 1.1 - 13 km N of Castaic, CA</t>
+          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>13 km N of Castaic, CA</t>
+          <t>9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5798,38 +5798,38 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46096.46653668981</v>
+        <v>46096.47494160879</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46096.46890145833</v>
+        <v>46096.4911</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>nn00912706</t>
+          <t>pr71509923</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-119.5178</v>
+        <v>-66.1071666666667</v>
       </c>
       <c r="C135" t="n">
-        <v>38.4812</v>
+        <v>18.1251666666667</v>
       </c>
       <c r="D135" t="n">
-        <v>3.3162</v>
+        <v>24.58</v>
       </c>
       <c r="E135" t="n">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km SW of Walker, California</t>
+          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>5 km SW of Walker, California</t>
+          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5838,38 +5838,38 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46096.46134278935</v>
+        <v>46096.47251458334</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46096.46294350694</v>
+        <v>46096.60321875</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>nc75327672</t>
+          <t>ci41204519</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-122.810333251953</v>
+        <v>-118.627833333333</v>
       </c>
       <c r="C136" t="n">
-        <v>38.8395004272461</v>
+        <v>34.6043333333333</v>
       </c>
       <c r="D136" t="n">
-        <v>1.83000004291534</v>
+        <v>10.64</v>
       </c>
       <c r="E136" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
+          <t>M 1.1 - 13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8 km WNW of Cobb, CA</t>
+          <t>13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5878,38 +5878,38 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46096.46108472222</v>
+        <v>46096.46653668981</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46096.49469679398</v>
+        <v>46096.46890145833</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>pr71509913</t>
+          <t>nn00912706</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-67.0566666666667</v>
+        <v>-119.5178</v>
       </c>
       <c r="C137" t="n">
-        <v>18.1476666666667</v>
+        <v>38.4812</v>
       </c>
       <c r="D137" t="n">
-        <v>17.11</v>
+        <v>3.3162</v>
       </c>
       <c r="E137" t="n">
-        <v>2.37</v>
+        <v>1.26</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>M 1.3 - 5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5918,38 +5918,38 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46096.44030868055</v>
+        <v>46096.46134278935</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46096.59237719907</v>
+        <v>46096.46294350694</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>aka2026feukwz</t>
+          <t>nc75327672</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-147.764</v>
+        <v>-122.810333251953</v>
       </c>
       <c r="C138" t="n">
-        <v>60.385</v>
+        <v>38.8395004272461</v>
       </c>
       <c r="D138" t="n">
-        <v>14.9</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="E138" t="n">
-        <v>1.7</v>
+        <v>0.97</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
+          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>38 km NNE of Chenega, Alaska</t>
+          <t>8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5958,38 +5958,38 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46096.42763064815</v>
+        <v>46096.46108472222</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46096.4286147338</v>
+        <v>46096.49469679398</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>aka2026fetqyo</t>
+          <t>pr71509913</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-150.43</v>
+        <v>-67.0566666666667</v>
       </c>
       <c r="C139" t="n">
-        <v>60.896</v>
+        <v>18.1476666666667</v>
       </c>
       <c r="D139" t="n">
-        <v>45.5</v>
+        <v>17.11</v>
       </c>
       <c r="E139" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
+          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>14 km ESE of Point Possession, Alaska</t>
+          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5998,38 +5998,38 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46096.41156589121</v>
+        <v>46096.44030868055</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46096.41261650463</v>
+        <v>46096.59237719907</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ci41204503</t>
+          <t>aka2026feukwz</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-117.464333333333</v>
+        <v>-147.764</v>
       </c>
       <c r="C140" t="n">
-        <v>34.157</v>
+        <v>60.385</v>
       </c>
       <c r="D140" t="n">
-        <v>6.87</v>
+        <v>14.9</v>
       </c>
       <c r="E140" t="n">
-        <v>0.98</v>
+        <v>1.7</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>M 1.0 - 7 km N of Fontana, CA</t>
+          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>7 km N of Fontana, CA</t>
+          <t>38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6038,38 +6038,38 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46096.39763148148</v>
+        <v>46096.42763064815</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46096.39998002315</v>
+        <v>46096.4286147338</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>aka2026fessqh</t>
+          <t>aka2026fetqyo</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-152.317</v>
+        <v>-150.43</v>
       </c>
       <c r="C141" t="n">
-        <v>60.36</v>
+        <v>60.896</v>
       </c>
       <c r="D141" t="n">
-        <v>90.3</v>
+        <v>45.5</v>
       </c>
       <c r="E141" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
+          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>49 km NW of Ninilchik, Alaska</t>
+          <t>14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6078,38 +6078,38 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46096.39196349537</v>
+        <v>46096.41156589121</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46096.39365355324</v>
+        <v>46096.41261650463</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>nc75327657</t>
+          <t>ci41204503</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-122.805335998535</v>
+        <v>-117.464333333333</v>
       </c>
       <c r="C142" t="n">
-        <v>38.8190002441406</v>
+        <v>34.157</v>
       </c>
       <c r="D142" t="n">
-        <v>2.17000007629395</v>
+        <v>6.87</v>
       </c>
       <c r="E142" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
+          <t>M 1.0 - 7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6118,38 +6118,38 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46096.37721527777</v>
+        <v>46096.39763148148</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46096.42173711806</v>
+        <v>46096.39998002315</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>aka2026fertpz</t>
+          <t>aka2026fessqh</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-157.698</v>
+        <v>-152.317</v>
       </c>
       <c r="C143" t="n">
-        <v>55.194</v>
+        <v>60.36</v>
       </c>
       <c r="D143" t="n">
-        <v>4.2</v>
+        <v>90.3</v>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
+          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>121 km SE of Perryville, Alaska</t>
+          <t>49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6158,38 +6158,38 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46096.37321436343</v>
+        <v>46096.39196349537</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46096.37804444444</v>
+        <v>46096.39365355324</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>uw62235646</t>
+          <t>nc75327657</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-121.9746666666667</v>
+        <v>-122.805335998535</v>
       </c>
       <c r="C144" t="n">
-        <v>47.82666666666667</v>
+        <v>38.8190002441406</v>
       </c>
       <c r="D144" t="n">
-        <v>26.62</v>
+        <v>2.17000007629395</v>
       </c>
       <c r="E144" t="n">
-        <v>1.96</v>
+        <v>1.1</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km S of Monroe, Washington</t>
+          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>3 km S of Monroe, Washington</t>
+          <t>6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6198,38 +6198,38 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46096.36272453704</v>
+        <v>46096.37721527777</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46096.47082604167</v>
+        <v>46096.42173711806</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>us6000sgfk</t>
+          <t>aka2026fertpz</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-77.27330000000001</v>
+        <v>-157.698</v>
       </c>
       <c r="C145" t="n">
-        <v>-45.5694</v>
+        <v>55.194</v>
       </c>
       <c r="D145" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="E145" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>M 5.3 - Off the coast of Aisen, Chile</t>
+          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6238,38 +6238,38 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46096.35320680556</v>
+        <v>46096.37321436343</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46096.38260266204</v>
+        <v>46096.37804444444</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>us6000sgfh</t>
+          <t>uw62235646</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>122.0755</v>
+        <v>-121.9746666666667</v>
       </c>
       <c r="C146" t="n">
-        <v>24.3607</v>
+        <v>47.82666666666667</v>
       </c>
       <c r="D146" t="n">
-        <v>27.716</v>
+        <v>26.62</v>
       </c>
       <c r="E146" t="n">
-        <v>4.8</v>
+        <v>1.96</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
+          <t>M 2.0 - 3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>54 km SE of Yilan, Taiwan</t>
+          <t>3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6278,38 +6278,38 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46096.34370333333</v>
+        <v>46096.36272453704</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46096.53583686343</v>
+        <v>46096.47082604167</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>nn00912705</t>
+          <t>us6000sgfk</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-116.5611</v>
+        <v>-77.27330000000001</v>
       </c>
       <c r="C147" t="n">
-        <v>38.4412</v>
+        <v>-45.5694</v>
       </c>
       <c r="D147" t="n">
-        <v>3.8472</v>
+        <v>10</v>
       </c>
       <c r="E147" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
+          <t>M 5.3 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>71 km NE of Tonopah, Nevada</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6318,38 +6318,38 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>46096.34194375</v>
+        <v>46096.35320680556</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46096.34380362269</v>
+        <v>46096.38260266204</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ci41204487</t>
+          <t>us6000sgfh</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-116.419666666667</v>
+        <v>122.0755</v>
       </c>
       <c r="C148" t="n">
-        <v>32.9405</v>
+        <v>24.3607</v>
       </c>
       <c r="D148" t="n">
-        <v>4.88</v>
+        <v>27.716</v>
       </c>
       <c r="E148" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
+          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>17 km NE of Pine Valley, CA</t>
+          <t>54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6358,38 +6358,38 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>46096.32685023148</v>
+        <v>46096.34370333333</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46096.32921789352</v>
+        <v>46096.53583686343</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ci41204479</t>
+          <t>nn00912705</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-117.2475</v>
+        <v>-116.5611</v>
       </c>
       <c r="C149" t="n">
-        <v>34.0556666666667</v>
+        <v>38.4412</v>
       </c>
       <c r="D149" t="n">
-        <v>15.21</v>
+        <v>3.8472</v>
       </c>
       <c r="E149" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
+          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2 km ENE of Loma Linda, CA</t>
+          <t>71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6398,38 +6398,38 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>46096.32684571759</v>
+        <v>46096.34194375</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46096.32920631945</v>
+        <v>46096.34380362269</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>aka2026fephrq</t>
+          <t>ci41204487</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-150.634</v>
+        <v>-116.419666666667</v>
       </c>
       <c r="C150" t="n">
-        <v>60.036</v>
+        <v>32.9405</v>
       </c>
       <c r="D150" t="n">
-        <v>63.6</v>
+        <v>4.88</v>
       </c>
       <c r="E150" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
+          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>26 km NE of Fox River, Alaska</t>
+          <t>17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6438,38 +6438,38 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>46096.32028525463</v>
+        <v>46096.32685023148</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46096.32365</v>
+        <v>46096.32921789352</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>nn00912702</t>
+          <t>ci41204479</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-116.579</v>
+        <v>-117.2475</v>
       </c>
       <c r="C151" t="n">
-        <v>38.4398</v>
+        <v>34.0556666666667</v>
       </c>
       <c r="D151" t="n">
-        <v>3.5596</v>
+        <v>15.21</v>
       </c>
       <c r="E151" t="n">
-        <v>2.08</v>
+        <v>1.09</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6478,38 +6478,38 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>46096.30809262732</v>
+        <v>46096.32684571759</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46096.31003199074</v>
+        <v>46096.32920631945</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>nc75327637</t>
+          <t>aka2026fephrq</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-121.911003112793</v>
+        <v>-150.634</v>
       </c>
       <c r="C152" t="n">
-        <v>38.0525016784668</v>
+        <v>60.036</v>
       </c>
       <c r="D152" t="n">
-        <v>17.0200004577637</v>
+        <v>63.6</v>
       </c>
       <c r="E152" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
+          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>4 km NW of Pittsburg, CA</t>
+          <t>26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6518,38 +6518,38 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>46096.29875555556</v>
+        <v>46096.32028525463</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46096.34190163195</v>
+        <v>46096.32365</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>us6000sgf9</t>
+          <t>nn00912702</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>72.05249999999999</v>
+        <v>-116.579</v>
       </c>
       <c r="C153" t="n">
-        <v>37.629</v>
+        <v>38.4398</v>
       </c>
       <c r="D153" t="n">
-        <v>196.241</v>
+        <v>3.5596</v>
       </c>
       <c r="E153" t="n">
-        <v>4.1</v>
+        <v>2.08</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
+          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>46 km ENE of Khorugh, Tajikistan</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6558,38 +6558,38 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>46096.29624704861</v>
+        <v>46096.30809262732</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46096.31303287037</v>
+        <v>46096.31003199074</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>aka2026fenxtb</t>
+          <t>nc75327637</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-154.253</v>
+        <v>-121.911003112793</v>
       </c>
       <c r="C154" t="n">
-        <v>58.558</v>
+        <v>38.0525016784668</v>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>17.0200004577637</v>
       </c>
       <c r="E154" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
+          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>96 km NW of Aleneva, Alaska</t>
+          <t>4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6598,38 +6598,38 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>46096.29131623843</v>
+        <v>46096.29875555556</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46096.29275974537</v>
+        <v>46096.34190163195</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>nc75327632</t>
+          <t>us6000sgf9</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-121.910331726074</v>
+        <v>72.05249999999999</v>
       </c>
       <c r="C155" t="n">
-        <v>38.0643348693848</v>
+        <v>37.629</v>
       </c>
       <c r="D155" t="n">
-        <v>18.6900005340576</v>
+        <v>196.241</v>
       </c>
       <c r="E155" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
+          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>5 km NNW of Pittsburg, CA</t>
+          <t>46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6638,38 +6638,38 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>46096.28527893518</v>
+        <v>46096.29624704861</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46096.32459672454</v>
+        <v>46096.31303287037</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tx2026fenmna</t>
+          <t>aka2026fenxtb</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-104.203</v>
+        <v>-154.253</v>
       </c>
       <c r="C156" t="n">
-        <v>31.669</v>
+        <v>58.558</v>
       </c>
       <c r="D156" t="n">
-        <v>7.2278</v>
+        <v>5</v>
       </c>
       <c r="E156" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
+          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6678,38 +6678,38 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>46096.28226224537</v>
+        <v>46096.29131623843</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46096.83936486111</v>
+        <v>46096.29275974537</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tx2026fenktd</t>
+          <t>nc75327632</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-104.202</v>
+        <v>-121.910331726074</v>
       </c>
       <c r="C157" t="n">
-        <v>31.669</v>
+        <v>38.0643348693848</v>
       </c>
       <c r="D157" t="n">
-        <v>7.5739</v>
+        <v>18.6900005340576</v>
       </c>
       <c r="E157" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
+          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6718,38 +6718,38 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>46096.28124563657</v>
+        <v>46096.28527893518</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46096.70278489583</v>
+        <v>46096.32459672454</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ci41204455</t>
+          <t>tx2026fenmna</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-116.806333333333</v>
+        <v>-104.203</v>
       </c>
       <c r="C158" t="n">
-        <v>33.2463333333333</v>
+        <v>31.669</v>
       </c>
       <c r="D158" t="n">
-        <v>10.1</v>
+        <v>7.2278</v>
       </c>
       <c r="E158" t="n">
-        <v>0.95</v>
+        <v>1.9</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
+          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4 km W of Lake Henshaw, CA</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6758,38 +6758,38 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>46096.27805949074</v>
+        <v>46096.28226224537</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46096.28047209491</v>
+        <v>46096.83936486111</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>nn00912698</t>
+          <t>tx2026fenktd</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-116.6054</v>
+        <v>-104.202</v>
       </c>
       <c r="C159" t="n">
-        <v>38.2724</v>
+        <v>31.669</v>
       </c>
       <c r="D159" t="n">
-        <v>5.7486</v>
+        <v>7.5739</v>
       </c>
       <c r="E159" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
+          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>59 km ENE of Tonopah, Nevada</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6798,38 +6798,38 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>46096.26913202546</v>
+        <v>46096.28124563657</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46096.27123583333</v>
+        <v>46096.70278489583</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>nn00912696</t>
+          <t>ci41204455</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-116.3473</v>
+        <v>-116.806333333333</v>
       </c>
       <c r="C160" t="n">
-        <v>37.5427</v>
+        <v>33.2463333333333</v>
       </c>
       <c r="D160" t="n">
-        <v>15.7841</v>
+        <v>10.1</v>
       </c>
       <c r="E160" t="n">
-        <v>1.48</v>
+        <v>0.95</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6838,38 +6838,38 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>46096.26722096065</v>
+        <v>46096.27805949074</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46096.26890163194</v>
+        <v>46096.28047209491</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>pr71509903</t>
+          <t>nn00912698</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-66.7433333333333</v>
+        <v>-116.6054</v>
       </c>
       <c r="C161" t="n">
-        <v>18.043</v>
+        <v>38.2724</v>
       </c>
       <c r="D161" t="n">
-        <v>16.94</v>
+        <v>5.7486</v>
       </c>
       <c r="E161" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6878,38 +6878,38 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>46096.26509143518</v>
+        <v>46096.26913202546</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46096.27459479167</v>
+        <v>46096.27123583333</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>nn00912694</t>
+          <t>nn00912696</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-116.5678</v>
+        <v>-116.3473</v>
       </c>
       <c r="C162" t="n">
-        <v>38.4757</v>
+        <v>37.5427</v>
       </c>
       <c r="D162" t="n">
-        <v>5.2112</v>
+        <v>15.7841</v>
       </c>
       <c r="E162" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
+          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>73 km NE of Tonopah, Nevada</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6918,38 +6918,38 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>46096.26149202546</v>
+        <v>46096.26722096065</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46096.26338644676</v>
+        <v>46096.26890163194</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>aka2026femdbx</t>
+          <t>pr71509903</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-154.971</v>
+        <v>-66.7433333333333</v>
       </c>
       <c r="C163" t="n">
-        <v>57.961</v>
+        <v>18.043</v>
       </c>
       <c r="D163" t="n">
-        <v>86.59999999999999</v>
+        <v>16.94</v>
       </c>
       <c r="E163" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
+          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>53 km NW of Karluk, Alaska</t>
+          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6958,38 +6958,38 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>46096.25371178241</v>
+        <v>46096.26509143518</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46096.2741787037</v>
+        <v>46096.27459479167</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nn00912691</t>
+          <t>nn00912694</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-116.5734</v>
+        <v>-116.5678</v>
       </c>
       <c r="C164" t="n">
-        <v>38.4423</v>
+        <v>38.4757</v>
       </c>
       <c r="D164" t="n">
-        <v>1.9073</v>
+        <v>5.2112</v>
       </c>
       <c r="E164" t="n">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6998,38 +6998,38 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>46096.25128945602</v>
+        <v>46096.26149202546</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46096.25308243056</v>
+        <v>46096.26338644676</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ci41204447</t>
+          <t>aka2026femdbx</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-116.168333333333</v>
+        <v>-154.971</v>
       </c>
       <c r="C165" t="n">
-        <v>33.8886666666667</v>
+        <v>57.961</v>
       </c>
       <c r="D165" t="n">
-        <v>5.52</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>M 1.3 - 19 km NNE of Indio, CA</t>
+          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>19 km NNE of Indio, CA</t>
+          <t>53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7038,38 +7038,38 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>46096.24517546297</v>
+        <v>46096.25371178241</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46096.25266435185</v>
+        <v>46096.2741787037</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>nc75327597</t>
+          <t>nn00912691</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-121.635665893555</v>
+        <v>-116.5734</v>
       </c>
       <c r="C166" t="n">
-        <v>36.9845008850098</v>
+        <v>38.4423</v>
       </c>
       <c r="D166" t="n">
-        <v>8.989999771118161</v>
+        <v>1.9073</v>
       </c>
       <c r="E166" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
+          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>6 km WSW of Gilroy, CA</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7078,38 +7078,38 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>46096.24306736111</v>
+        <v>46096.25128945602</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46096.29676952546</v>
+        <v>46096.25308243056</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>aka2026fekujg</t>
+          <t>ci41204447</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-150.947</v>
+        <v>-116.168333333333</v>
       </c>
       <c r="C167" t="n">
-        <v>60.457</v>
+        <v>33.8886666666667</v>
       </c>
       <c r="D167" t="n">
-        <v>50.6</v>
+        <v>5.52</v>
       </c>
       <c r="E167" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>M 1.6 - 7 km ESE of Soldotna, Alaska</t>
+          <t>M 1.3 - 19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>7 km ESE of Soldotna, Alaska</t>
+          <t>19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7118,38 +7118,38 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>46096.22573243055</v>
+        <v>46096.24517546297</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46096.22721925926</v>
+        <v>46096.25266435185</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>us6000sgel</t>
+          <t>nc75327597</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-77.3734</v>
+        <v>-121.635665893555</v>
       </c>
       <c r="C168" t="n">
-        <v>-45.6673</v>
+        <v>36.9845008850098</v>
       </c>
       <c r="D168" t="n">
-        <v>10</v>
+        <v>8.989999771118161</v>
       </c>
       <c r="E168" t="n">
-        <v>4.4</v>
+        <v>1.71</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7158,38 +7158,38 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>46096.22567266204</v>
+        <v>46096.24306736111</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46096.32872731482</v>
+        <v>46096.29676952546</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>nn00912689</t>
+          <t>aka2026fekujg</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-116.8458</v>
+        <v>-150.947</v>
       </c>
       <c r="C169" t="n">
-        <v>38.2828</v>
+        <v>60.457</v>
       </c>
       <c r="D169" t="n">
-        <v>5.3648</v>
+        <v>50.6</v>
       </c>
       <c r="E169" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>M 1.9 - 41 km NE of Tonopah, Nevada</t>
+          <t>M 1.6 - 7 km ESE of Soldotna, Alaska</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>41 km NE of Tonopah, Nevada</t>
+          <t>7 km ESE of Soldotna, Alaska</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7198,38 +7198,38 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>46096.2170634838</v>
+        <v>46096.22573243055</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46096.21891450231</v>
+        <v>46096.22721925926</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>us6000sgeb</t>
+          <t>us6000sgel</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>139.3214</v>
+        <v>-77.3734</v>
       </c>
       <c r="C170" t="n">
-        <v>36.3919</v>
+        <v>-45.6673</v>
       </c>
       <c r="D170" t="n">
-        <v>94.896</v>
+        <v>10</v>
       </c>
       <c r="E170" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>M 4.8 - 1 km SW of Kiryū, Japan</t>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>1 km SW of Kiryū, Japan</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7238,38 +7238,38 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>46096.21257785879</v>
+        <v>46096.22567266204</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46096.66760255787</v>
+        <v>46096.32872731482</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>us6000sgea</t>
+          <t>nn00912689</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-88.2997</v>
+        <v>-116.8458</v>
       </c>
       <c r="C171" t="n">
-        <v>12.6324</v>
+        <v>38.2828</v>
       </c>
       <c r="D171" t="n">
-        <v>55.856</v>
+        <v>5.3648</v>
       </c>
       <c r="E171" t="n">
-        <v>5.3</v>
+        <v>1.92</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>M 5.3 - 67 km SSW of Chirilagua, El Salvador</t>
+          <t>M 1.9 - 41 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>67 km SSW of Chirilagua, El Salvador</t>
+          <t>41 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7278,130 +7278,10 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>46096.20880520833</v>
+        <v>46096.2170634838</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46096.62601605324</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>nn00912685</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>-117.1071</v>
-      </c>
-      <c r="C172" t="n">
-        <v>37.2044</v>
-      </c>
-      <c r="D172" t="n">
-        <v>3.7302</v>
-      </c>
-      <c r="E172" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>M 1.4 - 45 km NW of Beatty, Nevada</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>45 km NW of Beatty, Nevada</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="n">
-        <v>46096.20641787037</v>
-      </c>
-      <c r="J172" s="2" t="n">
-        <v>46096.20811390047</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>nc75327582</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>-124.411834716797</v>
-      </c>
-      <c r="C173" t="n">
-        <v>40.2961654663086</v>
-      </c>
-      <c r="D173" t="n">
-        <v>9.22999954223633</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>M 1.9 - 11 km WSW of Petrolia, CA</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>11 km WSW of Petrolia, CA</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="n">
-        <v>46096.20098622685</v>
-      </c>
-      <c r="J173" s="2" t="n">
-        <v>46096.24126574074</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>us6000sge9</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>142.5299</v>
-      </c>
-      <c r="C174" t="n">
-        <v>37.3728</v>
-      </c>
-      <c r="D174" t="n">
-        <v>38.742</v>
-      </c>
-      <c r="E174" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>M 4.3 - 134 km E of Tomioka, Japan</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>134 km E of Tomioka, Japan</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="n">
-        <v>46096.20051677083</v>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>46096.2139587963</v>
+        <v>46096.21891450231</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/USGS.xlsx
+++ b/data/raw/USGS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,29 +487,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nc75328067</t>
+          <t>nc75328072</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-122.458168029785</v>
+        <v>-121.153663635254</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5923347473145</v>
+        <v>37.1259994506836</v>
       </c>
       <c r="D2" t="n">
-        <v>7.23999977111816</v>
+        <v>9.80000019073486</v>
       </c>
       <c r="E2" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
+          <t>M 2.5 - 20 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>20 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,38 +518,38 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46097.20110729166</v>
+        <v>46097.21683298611</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46097.20225373843</v>
+        <v>46097.21793168982</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nc75328062</t>
+          <t>ci41204887</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-122.700668334961</v>
+        <v>-117.500666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>38.7681655883789</v>
+        <v>34.0881666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.730000019073486</v>
+        <v>10.81</v>
       </c>
       <c r="E3" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M 1.1 - 1 km SW of Anderson Springs, CA</t>
+          <t>M 1.0 - 4 km WSW of Fontana, CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1 km SW of Anderson Springs, CA</t>
+          <t>4 km WSW of Fontana, CA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,38 +558,38 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46097.1980800926</v>
+        <v>46097.21549351852</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46097.21344644676</v>
+        <v>46097.21785097222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aka2026fgejkl</t>
+          <t>nc75328067</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-150.208</v>
+        <v>-122.458168029785</v>
       </c>
       <c r="C4" t="n">
-        <v>62.214</v>
+        <v>37.5923347473145</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4</v>
+        <v>7.23999977111816</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8</v>
+        <v>1.02</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11 km S of Trapper Creek, Alaska</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -598,38 +598,38 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46097.18073642361</v>
+        <v>46097.20110729166</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46097.1817900926</v>
+        <v>46097.2169190162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nn00912748</t>
+          <t>nc75328062</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-116.7944</v>
+        <v>-122.700668334961</v>
       </c>
       <c r="C5" t="n">
-        <v>38.3084</v>
+        <v>38.7681655883789</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8689</v>
+        <v>0.730000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 1 km SW of Anderson Springs, CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>46 km NE of Tonopah, Nevada</t>
+          <t>1 km SW of Anderson Springs, CA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,38 +638,38 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46097.18032635417</v>
+        <v>46097.1980800926</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46097.18299189815</v>
+        <v>46097.21344644676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nn00912744</t>
+          <t>aka2026fgejkl</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-116.5751</v>
+        <v>-150.208</v>
       </c>
       <c r="C6" t="n">
-        <v>38.2761</v>
+        <v>62.214</v>
       </c>
       <c r="D6" t="n">
-        <v>6.7167</v>
+        <v>4.4</v>
       </c>
       <c r="E6" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M 2.2 - 61 km ENE of Tonopah, Nevada</t>
+          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>61 km ENE of Tonopah, Nevada</t>
+          <t>11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -678,38 +678,38 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46097.17459033565</v>
+        <v>46097.18073642361</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46097.17637523148</v>
+        <v>46097.1817900926</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ci41204855</t>
+          <t>nn00912748</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-119.120666666667</v>
+        <v>-116.7944</v>
       </c>
       <c r="C7" t="n">
-        <v>34.9321666666667</v>
+        <v>38.3084</v>
       </c>
       <c r="D7" t="n">
-        <v>0.87</v>
+        <v>2.8689</v>
       </c>
       <c r="E7" t="n">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M 2.3 - 10 km NNE of Pine Mountain Club, CA</t>
+          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10 km NNE of Pine Mountain Club, CA</t>
+          <t>46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -718,38 +718,38 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46097.17414733797</v>
+        <v>46097.18032635417</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46097.20602984953</v>
+        <v>46097.18299189815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nn00912743</t>
+          <t>nn00912744</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-116.0158</v>
+        <v>-116.5751</v>
       </c>
       <c r="C8" t="n">
-        <v>37.795</v>
+        <v>38.2761</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4807</v>
+        <v>6.7167</v>
       </c>
       <c r="E8" t="n">
-        <v>1.34</v>
+        <v>2.18</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
+          <t>M 2.2 - 61 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29 km NW of Rachel, Nevada</t>
+          <t>61 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -758,38 +758,38 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46097.17013881944</v>
+        <v>46097.17459033565</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46097.1716130787</v>
+        <v>46097.17637523148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nc75328052</t>
+          <t>ci41204855</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-122.765167236328</v>
+        <v>-119.120666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>38.7836685180664</v>
+        <v>34.9321666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>4.19000005722046</v>
+        <v>0.87</v>
       </c>
       <c r="E9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
+          <t>M 2.3 - 10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1 km NW of The Geysers, CA</t>
+          <t>10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -798,38 +798,38 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46097.16834872685</v>
+        <v>46097.17414733797</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46097.20647809028</v>
+        <v>46097.20602984953</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nn00912742</t>
+          <t>nn00912743</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-117.5849</v>
+        <v>-116.0158</v>
       </c>
       <c r="C10" t="n">
-        <v>37.3479</v>
+        <v>37.795</v>
       </c>
       <c r="D10" t="n">
-        <v>3.7908</v>
+        <v>2.4807</v>
       </c>
       <c r="E10" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
+          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>45 km S of Silver Peak, Nevada</t>
+          <t>29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -838,38 +838,38 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46097.15891554398</v>
+        <v>46097.17013881944</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46097.16036833333</v>
+        <v>46097.1716130787</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nn00912740</t>
+          <t>nc75328052</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-116.3558</v>
+        <v>-122.765167236328</v>
       </c>
       <c r="C11" t="n">
-        <v>37.5573</v>
+        <v>38.7836685180664</v>
       </c>
       <c r="D11" t="n">
-        <v>8.4693</v>
+        <v>4.19000005722046</v>
       </c>
       <c r="E11" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
+          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>54 km W of Rachel, Nevada</t>
+          <t>1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -878,38 +878,38 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46097.1542737963</v>
+        <v>46097.16834872685</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46097.15577996528</v>
+        <v>46097.20647809028</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nc75328042</t>
+          <t>nn00912742</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-122.843170166016</v>
+        <v>-117.5849</v>
       </c>
       <c r="C12" t="n">
-        <v>38.8208351135254</v>
+        <v>37.3479</v>
       </c>
       <c r="D12" t="n">
-        <v>1.67999994754791</v>
+        <v>3.7908</v>
       </c>
       <c r="E12" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
+          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9 km WNW of The Geysers, CA</t>
+          <t>45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -918,38 +918,38 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46097.15140474537</v>
+        <v>46097.15891554398</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46097.15253628472</v>
+        <v>46097.16036833333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nc75328037</t>
+          <t>nn00912740</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-122.839668273926</v>
+        <v>-116.3558</v>
       </c>
       <c r="C13" t="n">
-        <v>38.8219985961914</v>
+        <v>37.5573</v>
       </c>
       <c r="D13" t="n">
-        <v>1.66999995708466</v>
+        <v>8.4693</v>
       </c>
       <c r="E13" t="n">
-        <v>1.96</v>
+        <v>1.15</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
+          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9 km NW of The Geysers, CA</t>
+          <t>54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -958,38 +958,38 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46097.15081805555</v>
+        <v>46097.1542737963</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46097.18912663194</v>
+        <v>46097.15577996528</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ci41204839</t>
+          <t>nc75328042</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-117.701833333333</v>
+        <v>-122.843170166016</v>
       </c>
       <c r="C14" t="n">
-        <v>35.8715</v>
+        <v>38.8208351135254</v>
       </c>
       <c r="D14" t="n">
-        <v>4.72</v>
+        <v>1.67999994754791</v>
       </c>
       <c r="E14" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
+          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20 km ESE of Little Lake, CA</t>
+          <t>9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -998,38 +998,38 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46097.14808055555</v>
+        <v>46097.15140474537</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46097.15049766203</v>
+        <v>46097.15253628472</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>aka2026fgcope</t>
+          <t>nc75328037</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-149.454</v>
+        <v>-122.839668273926</v>
       </c>
       <c r="C15" t="n">
-        <v>62.553</v>
+        <v>38.8219985961914</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
+          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>35 km ENE of Chase, Alaska</t>
+          <t>9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1038,38 +1038,38 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46097.14301053241</v>
+        <v>46097.15081805555</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46097.14408171296</v>
+        <v>46097.18912663194</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nn00912738</t>
+          <t>ci41204839</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-116.4786</v>
+        <v>-117.701833333333</v>
       </c>
       <c r="C16" t="n">
-        <v>38.4752</v>
+        <v>35.8715</v>
       </c>
       <c r="D16" t="n">
-        <v>7.3424</v>
+        <v>4.72</v>
       </c>
       <c r="E16" t="n">
-        <v>1.74</v>
+        <v>0.99</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
+          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>79 km NE of Tonopah, Nevada</t>
+          <t>20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1078,38 +1078,38 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46097.13946230324</v>
+        <v>46097.14808055555</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46097.14130107639</v>
+        <v>46097.15049766203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>aka2026fgbzeh</t>
+          <t>aka2026fgcope</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-149.584</v>
+        <v>-149.454</v>
       </c>
       <c r="C17" t="n">
-        <v>62.358</v>
+        <v>62.553</v>
       </c>
       <c r="D17" t="n">
-        <v>56.7</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
+          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>25 km NNE of Susitna North, Alaska</t>
+          <t>35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1118,38 +1118,38 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46097.13059196759</v>
+        <v>46097.14301053241</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46097.13160341435</v>
+        <v>46097.14408171296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>aka2026fgbuau</t>
+          <t>nn00912738</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-146.643</v>
+        <v>-116.4786</v>
       </c>
       <c r="C18" t="n">
-        <v>61.432</v>
+        <v>38.4752</v>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>7.3424</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
+          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>37 km NNW of Valdez, Alaska</t>
+          <t>79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1158,38 +1158,38 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46097.12645101852</v>
+        <v>46097.13946230324</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46097.12856479167</v>
+        <v>46097.14130107639</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nc75327997</t>
+          <t>aka2026fgbzeh</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-122.785667419434</v>
+        <v>-149.584</v>
       </c>
       <c r="C19" t="n">
-        <v>38.8154983520508</v>
+        <v>62.358</v>
       </c>
       <c r="D19" t="n">
-        <v>1.46000003814697</v>
+        <v>56.7</v>
       </c>
       <c r="E19" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
+          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1198,38 +1198,38 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46097.10226643518</v>
+        <v>46097.13059196759</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46097.10338584491</v>
+        <v>46097.13160341435</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nc75327992</t>
+          <t>aka2026fgbuau</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-122.786163330078</v>
+        <v>-146.643</v>
       </c>
       <c r="C20" t="n">
-        <v>38.8153343200684</v>
+        <v>61.432</v>
       </c>
       <c r="D20" t="n">
-        <v>1.44000005722046</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
+          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,38 +1238,38 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46097.09843321759</v>
+        <v>46097.12645101852</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46097.13356498843</v>
+        <v>46097.12856479167</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aka2026ffzydk</t>
+          <t>nc75327997</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-151.439</v>
+        <v>-122.785667419434</v>
       </c>
       <c r="C21" t="n">
-        <v>59.675</v>
+        <v>38.8154983520508</v>
       </c>
       <c r="D21" t="n">
-        <v>40.3</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
+          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0 km NW of Kachemak, Alaska</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46097.08785851852</v>
+        <v>46097.10226643518</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46097.0893715625</v>
+        <v>46097.10338584491</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nn00912733</t>
+          <t>nc75327992</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-116.2619</v>
+        <v>-122.786163330078</v>
       </c>
       <c r="C22" t="n">
-        <v>38.6278</v>
+        <v>38.8153343200684</v>
       </c>
       <c r="D22" t="n">
-        <v>4.7494</v>
+        <v>1.44000005722046</v>
       </c>
       <c r="E22" t="n">
-        <v>2.71</v>
+        <v>1.49</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M 2.7 - 95 km SE of Kingston, Nevada</t>
+          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>95 km SE of Kingston, Nevada</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1318,38 +1318,38 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46097.08629175926</v>
+        <v>46097.09843321759</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46097.09325277778</v>
+        <v>46097.13356498843</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ci41204823</t>
+          <t>aka2026ffzydk</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-117.844666666667</v>
+        <v>-151.439</v>
       </c>
       <c r="C23" t="n">
-        <v>36.4091666666667</v>
+        <v>59.675</v>
       </c>
       <c r="D23" t="n">
-        <v>3.71</v>
+        <v>40.3</v>
       </c>
       <c r="E23" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M 1.2 - 20 km NE of Olancha, CA</t>
+          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20 km NE of Olancha, CA</t>
+          <t>0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1358,38 +1358,38 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46097.08612511574</v>
+        <v>46097.08785851852</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46097.08854572917</v>
+        <v>46097.0893715625</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tx2026ffzaya</t>
+          <t>nn00912733</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-104.188</v>
+        <v>-116.2619</v>
       </c>
       <c r="C24" t="n">
-        <v>31.703</v>
+        <v>38.6278</v>
       </c>
       <c r="D24" t="n">
-        <v>4.4731</v>
+        <v>4.7494</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7</v>
+        <v>2.71</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
+          <t>M 2.7 - 95 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>55 km SSE of Whites City, New Mexico</t>
+          <t>95 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1398,38 +1398,38 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46097.06930607639</v>
+        <v>46097.08629175926</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46097.08380681713</v>
+        <v>46097.09325277778</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hv74917612</t>
+          <t>ci41204823</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-155.139495849609</v>
+        <v>-117.844666666667</v>
       </c>
       <c r="C25" t="n">
-        <v>19.3330001831055</v>
+        <v>36.4091666666667</v>
       </c>
       <c r="D25" t="n">
-        <v>3.76999998092651</v>
+        <v>3.71</v>
       </c>
       <c r="E25" t="n">
-        <v>2.04</v>
+        <v>1.19</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 1.2 - 20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1438,38 +1438,38 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46097.06757199074</v>
+        <v>46097.08612511574</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46097.07008101852</v>
+        <v>46097.08854572917</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ci41204799</t>
+          <t>tx2026ffzaya</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-117.4825</v>
+        <v>-104.188</v>
       </c>
       <c r="C26" t="n">
-        <v>35.601</v>
+        <v>31.703</v>
       </c>
       <c r="D26" t="n">
-        <v>7.7</v>
+        <v>4.4731</v>
       </c>
       <c r="E26" t="n">
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
+          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18 km E of Ridgecrest, CA</t>
+          <t>55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1478,38 +1478,38 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46097.0600244213</v>
+        <v>46097.06930607639</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46097.06239535879</v>
+        <v>46097.08380681713</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tx2026ffyeyx</t>
+          <t>hv74917612</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-104.176</v>
+        <v>-155.139495849609</v>
       </c>
       <c r="C27" t="n">
-        <v>31.711</v>
+        <v>19.3330001831055</v>
       </c>
       <c r="D27" t="n">
-        <v>7.4969</v>
+        <v>3.76999998092651</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M 1.9 - 54 km W of Mentone, Texas</t>
+          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>54 km W of Mentone, Texas</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1518,38 +1518,38 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46097.05150728009</v>
+        <v>46097.06757199074</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46097.06865469908</v>
+        <v>46097.07008101852</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>aka2026ffxzpn</t>
+          <t>ci41204799</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-150.668</v>
+        <v>-117.4825</v>
       </c>
       <c r="C28" t="n">
-        <v>63.582</v>
+        <v>35.601</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1</v>
+        <v>7.7</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7</v>
+        <v>0.95</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
+          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>52 km E of Denali National Park, Alaska</t>
+          <t>18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1558,38 +1558,38 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46097.0471140162</v>
+        <v>46097.0600244213</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46097.04869516204</v>
+        <v>46097.06239535879</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nn00912731</t>
+          <t>tx2026ffyeyx</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-114.5508</v>
+        <v>-104.176</v>
       </c>
       <c r="C29" t="n">
-        <v>37.2919</v>
+        <v>31.711</v>
       </c>
       <c r="D29" t="n">
-        <v>15.9298</v>
+        <v>7.4969</v>
       </c>
       <c r="E29" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
+          <t>M 1.9 - 54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>36 km S of Caliente, Nevada</t>
+          <t>54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1598,38 +1598,38 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46097.04372652778</v>
+        <v>46097.05150728009</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46097.04546596065</v>
+        <v>46097.06865469908</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ci41204783</t>
+          <t>aka2026ffxzpn</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-116.366833333333</v>
+        <v>-150.668</v>
       </c>
       <c r="C30" t="n">
-        <v>33.193</v>
+        <v>63.582</v>
       </c>
       <c r="D30" t="n">
-        <v>7.35</v>
+        <v>0.1</v>
       </c>
       <c r="E30" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
+          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7 km S of Borrego Springs, CA</t>
+          <t>52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46097.04078981481</v>
+        <v>46097.0471140162</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46097.04323087963</v>
+        <v>46097.04869516204</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nc75327962</t>
+          <t>nn00912731</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-120.523834228516</v>
+        <v>-114.5508</v>
       </c>
       <c r="C31" t="n">
-        <v>35.9671669006348</v>
+        <v>37.2919</v>
       </c>
       <c r="D31" t="n">
-        <v>6.94999980926514</v>
+        <v>15.9298</v>
       </c>
       <c r="E31" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
+          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11 km NW of Parkfield, CA</t>
+          <t>36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1678,38 +1678,38 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46097.03950659722</v>
+        <v>46097.04372652778</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46097.09886200231</v>
+        <v>46097.04546596065</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aka2026ffxmpi</t>
+          <t>ci41204783</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-149.174</v>
+        <v>-116.366833333333</v>
       </c>
       <c r="C32" t="n">
-        <v>63.002</v>
+        <v>33.193</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>7.35</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
+          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>44 km SSW of Cantwell, Alaska</t>
+          <t>7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1718,38 +1718,38 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46097.03663675926</v>
+        <v>46097.04078981481</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46097.03896524305</v>
+        <v>46097.04323087963</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nc75327947</t>
+          <t>nc75327962</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-124.239669799805</v>
+        <v>-120.523834228516</v>
       </c>
       <c r="C33" t="n">
-        <v>40.4664993286133</v>
+        <v>35.9671669006348</v>
       </c>
       <c r="D33" t="n">
-        <v>26.0400009155273</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="E33" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
+          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12 km WSW of Rio Dell, CA</t>
+          <t>11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1758,38 +1758,38 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46097.03397256944</v>
+        <v>46097.03950659722</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46097.08151043981</v>
+        <v>46097.09886200231</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nn00912729</t>
+          <t>aka2026ffxmpi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-116.2867</v>
+        <v>-149.174</v>
       </c>
       <c r="C34" t="n">
-        <v>37.418</v>
+        <v>63.002</v>
       </c>
       <c r="D34" t="n">
-        <v>8.758599999999999</v>
+        <v>0.2</v>
       </c>
       <c r="E34" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1798,38 +1798,38 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46097.03219180556</v>
+        <v>46097.03663675926</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46097.03392417824</v>
+        <v>46097.03896524305</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hv74917602</t>
+          <t>nc75327947</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-155.143005371094</v>
+        <v>-124.239669799805</v>
       </c>
       <c r="C35" t="n">
-        <v>19.3344993591309</v>
+        <v>40.4664993286133</v>
       </c>
       <c r="D35" t="n">
-        <v>4.25</v>
+        <v>26.0400009155273</v>
       </c>
       <c r="E35" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1838,38 +1838,38 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46097.02269363426</v>
+        <v>46097.03397256944</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46097.02506747685</v>
+        <v>46097.08151043981</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nn00912728</t>
+          <t>nn00912729</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-116.8948</v>
+        <v>-116.2867</v>
       </c>
       <c r="C36" t="n">
-        <v>38.2511</v>
+        <v>37.418</v>
       </c>
       <c r="D36" t="n">
-        <v>4.7942</v>
+        <v>8.758599999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
+          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>35 km NE of Tonopah, Nevada</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1878,38 +1878,38 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46097.02024291667</v>
+        <v>46097.03219180556</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46097.02206256944</v>
+        <v>46097.03392417824</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nn00912725</t>
+          <t>hv74917602</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-116.3002</v>
+        <v>-155.143005371094</v>
       </c>
       <c r="C37" t="n">
-        <v>36.4986</v>
+        <v>19.3344993591309</v>
       </c>
       <c r="D37" t="n">
-        <v>1.7633</v>
+        <v>4.25</v>
       </c>
       <c r="E37" t="n">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
+          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>42 km NW of Pahrump, Nevada</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1918,38 +1918,38 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46097.01676708333</v>
+        <v>46097.02269363426</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46097.01802194444</v>
+        <v>46097.02506747685</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>aka2026ffwkac</t>
+          <t>nn00912728</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-147.104</v>
+        <v>-116.8948</v>
       </c>
       <c r="C38" t="n">
-        <v>61.221</v>
+        <v>38.2511</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>4.7942</v>
       </c>
       <c r="E38" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
+          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>41 km WNW of Valdez, Alaska</t>
+          <t>35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1958,38 +1958,38 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46097.01360875</v>
+        <v>46097.02024291667</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46097.01453715278</v>
+        <v>46097.02206256944</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nc75327937</t>
+          <t>nn00912725</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-120.16283416748</v>
+        <v>-116.3002</v>
       </c>
       <c r="C39" t="n">
-        <v>36.1510009765625</v>
+        <v>36.4986</v>
       </c>
       <c r="D39" t="n">
-        <v>5.53000020980835</v>
+        <v>1.7633</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8</v>
+        <v>1.13</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M 1.8 - 8 km SW of Huron, CA</t>
+          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8 km SW of Huron, CA</t>
+          <t>42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1998,38 +1998,38 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46097.00379861111</v>
+        <v>46097.01676708333</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46097.07108120371</v>
+        <v>46097.01802194444</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>aka2026ffvrqe</t>
+          <t>aka2026ffwkac</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-150.318</v>
+        <v>-147.104</v>
       </c>
       <c r="C40" t="n">
-        <v>60.621</v>
+        <v>61.221</v>
       </c>
       <c r="D40" t="n">
-        <v>37.9</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
+          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>26 km ENE of Sterling, Alaska</t>
+          <t>41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2038,38 +2038,38 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46096.99880960648</v>
+        <v>46097.01360875</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46097.06023194444</v>
+        <v>46097.01453715278</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hv74917597</t>
+          <t>nc75327937</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-154.981170654297</v>
+        <v>-120.16283416748</v>
       </c>
       <c r="C41" t="n">
-        <v>19.3976669311523</v>
+        <v>36.1510009765625</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.560000002384186</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E41" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
+          <t>M 1.8 - 8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10 km SW of Leilani Estates, Hawaii</t>
+          <t>8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2078,38 +2078,38 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46096.99111076389</v>
+        <v>46097.00379861111</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46096.993578125</v>
+        <v>46097.07108120371</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ci41204759</t>
+          <t>aka2026ffvrqe</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-117.6875</v>
+        <v>-150.318</v>
       </c>
       <c r="C42" t="n">
-        <v>35.0311666666667</v>
+        <v>60.621</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.84</v>
+        <v>37.9</v>
       </c>
       <c r="E42" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km NW of Boron, CA</t>
+          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5 km NW of Boron, CA</t>
+          <t>26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2118,38 +2118,38 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46096.98700925926</v>
+        <v>46096.99880960648</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46096.98945039352</v>
+        <v>46097.06023194444</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aka2026ffvcuk</t>
+          <t>hv74917597</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-147.706</v>
+        <v>-154.981170654297</v>
       </c>
       <c r="C43" t="n">
-        <v>63.18</v>
+        <v>19.3976669311523</v>
       </c>
       <c r="D43" t="n">
-        <v>4.3</v>
+        <v>-0.560000002384186</v>
       </c>
       <c r="E43" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
+          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>66 km ESE of Cantwell, Alaska</t>
+          <t>10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2158,38 +2158,38 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46096.98682952546</v>
+        <v>46096.99111076389</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46097.05321805555</v>
+        <v>46096.993578125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aka2026ffuxwl</t>
+          <t>ci41204759</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-149.464</v>
+        <v>-117.6875</v>
       </c>
       <c r="C44" t="n">
-        <v>65.532</v>
+        <v>35.0311666666667</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>-0.84</v>
       </c>
       <c r="E44" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
+          <t>M 1.3 - 5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>32 km E of Rampart, Alaska</t>
+          <t>5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2198,38 +2198,38 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46096.98287351852</v>
+        <v>46096.98700925926</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46096.98871584491</v>
+        <v>46096.98945039352</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>nc75327927</t>
+          <t>aka2026ffvcuk</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-122.759002685547</v>
+        <v>-147.706</v>
       </c>
       <c r="C45" t="n">
-        <v>38.779167175293</v>
+        <v>63.18</v>
       </c>
       <c r="D45" t="n">
-        <v>1.16999995708466</v>
+        <v>4.3</v>
       </c>
       <c r="E45" t="n">
-        <v>1.06</v>
+        <v>2.4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
+          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0 km NW of The Geysers, CA</t>
+          <t>66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2238,38 +2238,38 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46096.98031608796</v>
+        <v>46096.98682952546</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46096.9814612037</v>
+        <v>46097.05321805555</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>nc75327922</t>
+          <t>aka2026ffuxwl</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-120.615669250488</v>
+        <v>-149.464</v>
       </c>
       <c r="C46" t="n">
-        <v>36.0485000610352</v>
+        <v>65.532</v>
       </c>
       <c r="D46" t="n">
-        <v>2.03999996185303</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
+          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>24 km NW of Parkfield, CA</t>
+          <t>32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2278,38 +2278,38 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46096.97481886574</v>
+        <v>46096.98287351852</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46097.03291697917</v>
+        <v>46096.98871584491</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aka2026fftzga</t>
+          <t>nc75327927</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-147.469</v>
+        <v>-122.759002685547</v>
       </c>
       <c r="C47" t="n">
-        <v>64.946</v>
+        <v>38.779167175293</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E47" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M 1.2 - 7 km E of Fox, Alaska</t>
+          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7 km E of Fox, Alaska</t>
+          <t>0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2318,38 +2318,38 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46096.96303546296</v>
+        <v>46096.98031608796</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46096.96398349537</v>
+        <v>46096.9814612037</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>nc75327902</t>
+          <t>nc75327922</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-124.639663696289</v>
+        <v>-120.615669250488</v>
       </c>
       <c r="C48" t="n">
-        <v>40.34716796875</v>
+        <v>36.0485000610352</v>
       </c>
       <c r="D48" t="n">
-        <v>19.4500007629395</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="E48" t="n">
-        <v>2.76</v>
+        <v>1.65</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>M 2.8 - 30 km W of Petrolia, CA</t>
+          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>30 km W of Petrolia, CA</t>
+          <t>24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2358,38 +2358,38 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46096.95174398148</v>
+        <v>46096.97481886574</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46097.04291712963</v>
+        <v>46097.03291697917</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>us6000sgib</t>
+          <t>aka2026fftzga</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>176.3522</v>
+        <v>-147.469</v>
       </c>
       <c r="C49" t="n">
-        <v>52.1304</v>
+        <v>64.946</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
+          <t>M 1.2 - 7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>229 km ESE of Attu Station, Alaska</t>
+          <t>7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2398,38 +2398,38 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46096.94854002315</v>
+        <v>46096.96303546296</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46097.14299561342</v>
+        <v>46096.96398349537</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nn00912719</t>
+          <t>nc75327902</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-119.7167</v>
+        <v>-124.639663696289</v>
       </c>
       <c r="C50" t="n">
-        <v>40.512</v>
+        <v>40.34716796875</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7442</v>
+        <v>19.4500007629395</v>
       </c>
       <c r="E50" t="n">
-        <v>1.9</v>
+        <v>2.76</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
+          <t>M 2.8 - 30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>32 km WSW of Empire, Nevada</t>
+          <t>30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2438,38 +2438,38 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46096.94697967593</v>
+        <v>46096.95174398148</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46096.94864458333</v>
+        <v>46097.04291712963</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aka2026fftern</t>
+          <t>us6000sgib</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-145.732</v>
+        <v>176.3522</v>
       </c>
       <c r="C51" t="n">
-        <v>62.165</v>
+        <v>52.1304</v>
       </c>
       <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="n">
         <v>4.6</v>
       </c>
-      <c r="E51" t="n">
-        <v>1.6</v>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
+          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11 km WNW of Glennallen, Alaska</t>
+          <t>229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2478,38 +2478,38 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46096.94644289352</v>
+        <v>46096.94854002315</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46096.94759246528</v>
+        <v>46097.14299561342</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>aka2026ffsxtw</t>
+          <t>nn00912719</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-150.289</v>
+        <v>-119.7167</v>
       </c>
       <c r="C52" t="n">
-        <v>60.111</v>
+        <v>40.512</v>
       </c>
       <c r="D52" t="n">
-        <v>46.9</v>
+        <v>0.7442</v>
       </c>
       <c r="E52" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
+          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>46 km NE of Fox River, Alaska</t>
+          <t>32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2518,38 +2518,38 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46096.94087768519</v>
+        <v>46096.94697967593</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46096.94183203704</v>
+        <v>46096.94864458333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>aka2026ffsvcz</t>
+          <t>aka2026fftern</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-141.243</v>
+        <v>-145.732</v>
       </c>
       <c r="C53" t="n">
-        <v>61.573</v>
+        <v>62.165</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
+          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>90 km E of McCarthy, Alaska</t>
+          <t>11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2558,38 +2558,38 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46096.93874224537</v>
+        <v>46096.94644289352</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46096.93996863426</v>
+        <v>46096.94759246528</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>hv74917587</t>
+          <t>aka2026ffsxtw</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-155.404998779297</v>
+        <v>-150.289</v>
       </c>
       <c r="C54" t="n">
-        <v>19.2546672821045</v>
+        <v>60.111</v>
       </c>
       <c r="D54" t="n">
-        <v>30.7900009155273</v>
+        <v>46.9</v>
       </c>
       <c r="E54" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
+          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>9 km NE of Pāhala, Hawaii</t>
+          <t>46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2598,38 +2598,38 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46096.93382974537</v>
+        <v>46096.94087768519</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46096.93618622685</v>
+        <v>46096.94183203704</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nc75327892</t>
+          <t>aka2026ffsvcz</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-120.513832092285</v>
+        <v>-141.243</v>
       </c>
       <c r="C55" t="n">
-        <v>35.9599990844727</v>
+        <v>61.573</v>
       </c>
       <c r="D55" t="n">
-        <v>10.1700000762939</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
+          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10 km NW of Parkfield, CA</t>
+          <t>90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2638,38 +2638,38 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46096.92984074074</v>
+        <v>46096.93874224537</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46096.98773833334</v>
+        <v>46096.93996863426</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tx2026ffruyn</t>
+          <t>hv74917587</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-103.575</v>
+        <v>-155.404998779297</v>
       </c>
       <c r="C56" t="n">
-        <v>30.876</v>
+        <v>19.2546672821045</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>30.7900009155273</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
+          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20 km SE of Balmorhea, Texas</t>
+          <t>9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2678,38 +2678,38 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46096.91764664352</v>
+        <v>46096.93382974537</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46096.92133662037</v>
+        <v>46096.93618622685</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tx2026ffrhgd</t>
+          <t>nc75327892</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-101.817</v>
+        <v>-120.513832092285</v>
       </c>
       <c r="C57" t="n">
-        <v>32.349</v>
+        <v>35.9599990844727</v>
       </c>
       <c r="D57" t="n">
-        <v>11.8727</v>
+        <v>10.1700000762939</v>
       </c>
       <c r="E57" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
+          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21 km SSW of Ackerly, Texas</t>
+          <t>10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2718,38 +2718,38 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46096.90660459491</v>
+        <v>46096.92984074074</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46096.91322768519</v>
+        <v>46096.98773833334</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>nc75327882</t>
+          <t>tx2026ffruyn</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-122.730499267578</v>
+        <v>-103.575</v>
       </c>
       <c r="C58" t="n">
-        <v>38.7738342285156</v>
+        <v>30.876</v>
       </c>
       <c r="D58" t="n">
-        <v>2.02999997138977</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km E of The Geysers, CA</t>
+          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2 km E of The Geysers, CA</t>
+          <t>20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2758,38 +2758,38 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46096.90556168981</v>
+        <v>46096.91764664352</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46096.92179327546</v>
+        <v>46096.92133662037</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>aka2026ffqxwe</t>
+          <t>tx2026ffrhgd</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-145.627</v>
+        <v>-101.817</v>
       </c>
       <c r="C59" t="n">
-        <v>62.093</v>
+        <v>32.349</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>11.8727</v>
       </c>
       <c r="E59" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
+          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4 km WSW of Glennallen, Alaska</t>
+          <t>21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2798,38 +2798,38 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46096.89903701389</v>
+        <v>46096.90660459491</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46096.90023371528</v>
+        <v>46096.91322768519</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nn00912718</t>
+          <t>nc75327882</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-117.1162</v>
+        <v>-122.730499267578</v>
       </c>
       <c r="C60" t="n">
-        <v>37.2236</v>
+        <v>38.7738342285156</v>
       </c>
       <c r="D60" t="n">
-        <v>0.039</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="E60" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
+          <t>M 1.0 - 2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2838,38 +2838,38 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46096.8946965625</v>
+        <v>46096.90556168981</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46096.89624318287</v>
+        <v>46096.92179327546</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nc75327877</t>
+          <t>aka2026ffqxwe</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-121.053001403809</v>
+        <v>-145.627</v>
       </c>
       <c r="C61" t="n">
-        <v>36.4648323059082</v>
+        <v>62.093</v>
       </c>
       <c r="D61" t="n">
-        <v>0.209999993443489</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
+          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11 km SE of Pinnacles, CA</t>
+          <t>4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2878,38 +2878,38 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46096.89354375</v>
+        <v>46096.89903701389</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46096.95303508102</v>
+        <v>46096.90023371528</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>us6000sghx</t>
+          <t>nn00912718</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-68.8159</v>
+        <v>-117.1162</v>
       </c>
       <c r="C62" t="n">
-        <v>-21.1625</v>
+        <v>37.2236</v>
       </c>
       <c r="D62" t="n">
-        <v>120.691</v>
+        <v>0.039</v>
       </c>
       <c r="E62" t="n">
-        <v>4.1</v>
+        <v>1.08</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
+          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>58 km W of Ollagüe, Chile</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2918,38 +2918,38 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46096.89260434028</v>
+        <v>46096.8946965625</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46097.01954907407</v>
+        <v>46096.89624318287</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>aka2026ffqnha</t>
+          <t>nc75327877</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-146.565</v>
+        <v>-121.053001403809</v>
       </c>
       <c r="C63" t="n">
-        <v>61.519</v>
+        <v>36.4648323059082</v>
       </c>
       <c r="D63" t="n">
-        <v>38.2</v>
+        <v>0.209999993443489</v>
       </c>
       <c r="E63" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
+          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>44 km NNW of Valdez, Alaska</t>
+          <t>11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2958,38 +2958,38 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46096.89050962963</v>
+        <v>46096.89354375</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46096.89142732639</v>
+        <v>46096.95303508102</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tx2026ffqmcg</t>
+          <t>us6000sghx</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-101.512</v>
+        <v>-68.8159</v>
       </c>
       <c r="C64" t="n">
-        <v>31.874</v>
+        <v>-21.1625</v>
       </c>
       <c r="D64" t="n">
-        <v>3.2716</v>
+        <v>120.691</v>
       </c>
       <c r="E64" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
+          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3 km WNW of Garden City, Texas</t>
+          <t>58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2998,38 +2998,38 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46096.88956126157</v>
+        <v>46096.89260434028</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46096.9711172801</v>
+        <v>46097.01954907407</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>nn00912716</t>
+          <t>aka2026ffqnha</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-116.5976</v>
+        <v>-146.565</v>
       </c>
       <c r="C65" t="n">
-        <v>38.2879</v>
+        <v>61.519</v>
       </c>
       <c r="D65" t="n">
-        <v>4.9318</v>
+        <v>38.2</v>
       </c>
       <c r="E65" t="n">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
+          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>60 km ENE of Tonopah, Nevada</t>
+          <t>44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3038,38 +3038,38 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46096.88044799768</v>
+        <v>46096.89050962963</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46096.88234515046</v>
+        <v>46096.89142732639</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>aka2026ffpwxx</t>
+          <t>tx2026ffqmcg</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-150.536</v>
+        <v>-101.512</v>
       </c>
       <c r="C66" t="n">
-        <v>60.816</v>
+        <v>31.874</v>
       </c>
       <c r="D66" t="n">
-        <v>14.2</v>
+        <v>3.2716</v>
       </c>
       <c r="E66" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
+          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14 km SE of Point Possession, Alaska</t>
+          <t>3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3078,38 +3078,38 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46096.87733195602</v>
+        <v>46096.88956126157</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46096.87884059027</v>
+        <v>46096.9711172801</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tx2026ffpmmk</t>
+          <t>nn00912716</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-102.596</v>
+        <v>-116.5976</v>
       </c>
       <c r="C67" t="n">
-        <v>32.426</v>
+        <v>38.2879</v>
       </c>
       <c r="D67" t="n">
-        <v>7.1182</v>
+        <v>4.9318</v>
       </c>
       <c r="E67" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
+          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>12 km NNW of Andrews, Texas</t>
+          <t>60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3118,38 +3118,38 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46096.86891956018</v>
+        <v>46096.88044799768</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46096.87235497685</v>
+        <v>46096.88234515046</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>aka2026ffpbrz</t>
+          <t>aka2026ffpwxx</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-151.569</v>
+        <v>-150.536</v>
       </c>
       <c r="C68" t="n">
-        <v>61.397</v>
+        <v>60.816</v>
       </c>
       <c r="D68" t="n">
-        <v>76.90000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="E68" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
+          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>38 km NW of Beluga, Alaska</t>
+          <t>14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3158,38 +3158,38 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46096.86023665509</v>
+        <v>46096.87733195602</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46096.86153666666</v>
+        <v>46096.87884059027</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>aka2026ffoxwo</t>
+          <t>tx2026ffpmmk</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-153.073</v>
+        <v>-102.596</v>
       </c>
       <c r="C69" t="n">
-        <v>60.494</v>
+        <v>32.426</v>
       </c>
       <c r="D69" t="n">
-        <v>146.3</v>
+        <v>7.1182</v>
       </c>
       <c r="E69" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
+          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>75 km ENE of Port Alsworth, Alaska</t>
+          <t>12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3198,38 +3198,38 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46096.85716821759</v>
+        <v>46096.86891956018</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46096.85982177083</v>
+        <v>46096.87235497685</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tx2026ffolko</t>
+          <t>aka2026ffpbrz</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-104.401</v>
+        <v>-151.569</v>
       </c>
       <c r="C70" t="n">
-        <v>31.692</v>
+        <v>61.397</v>
       </c>
       <c r="D70" t="n">
-        <v>4.8181</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
+          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>53 km S of Whites City, New Mexico</t>
+          <t>38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46096.84736503472</v>
+        <v>46096.86023665509</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46096.93883732639</v>
+        <v>46096.86153666666</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nc75327852</t>
+          <t>aka2026ffoxwo</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-122.464164733887</v>
+        <v>-153.073</v>
       </c>
       <c r="C71" t="n">
-        <v>37.5973320007324</v>
+        <v>60.494</v>
       </c>
       <c r="D71" t="n">
-        <v>9.090000152587891</v>
+        <v>146.3</v>
       </c>
       <c r="E71" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
+          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3278,38 +3278,38 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46096.84368958334</v>
+        <v>46096.85716821759</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46096.84483373843</v>
+        <v>46096.85982177083</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>aka2026ffogkg</t>
+          <t>tx2026ffolko</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-150.241</v>
+        <v>-104.401</v>
       </c>
       <c r="C72" t="n">
-        <v>61.578</v>
+        <v>31.692</v>
       </c>
       <c r="D72" t="n">
-        <v>30.7</v>
+        <v>4.8181</v>
       </c>
       <c r="E72" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
+          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14 km ENE of Susitna, Alaska</t>
+          <t>53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3318,38 +3318,38 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46096.84307547453</v>
+        <v>46096.84736503472</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46096.84451351852</v>
+        <v>46096.93883732639</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nc75327847</t>
+          <t>nc75327852</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-122.757667541504</v>
+        <v>-122.464164733887</v>
       </c>
       <c r="C73" t="n">
-        <v>38.7918319702148</v>
+        <v>37.5973320007324</v>
       </c>
       <c r="D73" t="n">
-        <v>0.689999997615814</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="E73" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km N of The Geysers, CA</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2 km N of The Geysers, CA</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3358,38 +3358,38 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46096.84258912037</v>
+        <v>46096.84368958334</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46096.84373324074</v>
+        <v>46096.84483373843</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ci41204687</t>
+          <t>aka2026ffogkg</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-117.249</v>
+        <v>-150.241</v>
       </c>
       <c r="C74" t="n">
-        <v>33.9988333333333</v>
+        <v>61.578</v>
       </c>
       <c r="D74" t="n">
-        <v>10.86</v>
+        <v>30.7</v>
       </c>
       <c r="E74" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
+          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>6 km SSE of Loma Linda, CA</t>
+          <t>14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3398,38 +3398,38 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46096.83063032408</v>
+        <v>46096.84307547453</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46096.83300278935</v>
+        <v>46096.84451351852</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nn00912714</t>
+          <t>nc75327847</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-116.7227</v>
+        <v>-122.757667541504</v>
       </c>
       <c r="C75" t="n">
-        <v>38.3427</v>
+        <v>38.7918319702148</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1382</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="E75" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
+          <t>M 1.0 - 2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>53 km NE of Tonopah, Nevada</t>
+          <t>2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3438,38 +3438,38 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46096.82208777778</v>
+        <v>46096.84258912037</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46096.82386192129</v>
+        <v>46096.84373324074</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>aka2026ffmxvv</t>
+          <t>ci41204687</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-151.974</v>
+        <v>-117.249</v>
       </c>
       <c r="C76" t="n">
-        <v>60.349</v>
+        <v>33.9988333333333</v>
       </c>
       <c r="D76" t="n">
-        <v>77.2</v>
+        <v>10.86</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
+          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>34 km WNW of Clam Gulch, Alaska</t>
+          <t>6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3478,38 +3478,38 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46096.81522726852</v>
+        <v>46096.83063032408</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46096.81638251158</v>
+        <v>46096.83300278935</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nc75327827</t>
+          <t>nn00912714</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-121.9375</v>
+        <v>-116.7227</v>
       </c>
       <c r="C77" t="n">
-        <v>37.7731666666667</v>
+        <v>38.3427</v>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>0.1382</v>
       </c>
       <c r="E77" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
+          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4 km ESE of San Ramon, CA</t>
+          <t>53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3518,38 +3518,38 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46096.81305393518</v>
+        <v>46096.82208777778</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46097.01551917824</v>
+        <v>46096.82386192129</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nc75327822</t>
+          <t>aka2026ffmxvv</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-122.787170410156</v>
+        <v>-151.974</v>
       </c>
       <c r="C78" t="n">
-        <v>38.7934989929199</v>
+        <v>60.349</v>
       </c>
       <c r="D78" t="n">
-        <v>2.92000007629395</v>
+        <v>77.2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
+          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3558,38 +3558,38 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46096.81298229167</v>
+        <v>46096.81522726852</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46096.86627753473</v>
+        <v>46096.81638251158</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>us6000sghq</t>
+          <t>nc75327827</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>49.7256</v>
+        <v>-121.9375</v>
       </c>
       <c r="C79" t="n">
-        <v>32.4853</v>
+        <v>37.7731666666667</v>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E79" t="n">
-        <v>4.4</v>
+        <v>1.57</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
+          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>62 km SW of Fereydūnshahr, Iran</t>
+          <t>4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3598,38 +3598,38 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46096.8103829051</v>
+        <v>46096.81305393518</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46096.86111157407</v>
+        <v>46097.01551917824</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>aka2026ffmjyx</t>
+          <t>nc75327822</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-149.647</v>
+        <v>-122.787170410156</v>
       </c>
       <c r="C80" t="n">
-        <v>63.036</v>
+        <v>38.7934989929199</v>
       </c>
       <c r="D80" t="n">
-        <v>76.40000000000001</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="E80" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
+          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>52 km SW of Cantwell, Alaska</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3638,38 +3638,38 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46096.80405828704</v>
+        <v>46096.81298229167</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46096.80508491898</v>
+        <v>46096.86627753473</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>us6000sghd</t>
+          <t>us6000sghq</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>142.6105</v>
+        <v>49.7256</v>
       </c>
       <c r="C81" t="n">
-        <v>41.4045</v>
+        <v>32.4853</v>
       </c>
       <c r="D81" t="n">
-        <v>42.986</v>
+        <v>10</v>
       </c>
       <c r="E81" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
+          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>84 km SSW of Honchō, Japan</t>
+          <t>62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3678,38 +3678,38 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46096.78951814815</v>
+        <v>46096.8103829051</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46096.84466623842</v>
+        <v>46096.86111157407</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>aka2026fflqih</t>
+          <t>aka2026ffmjyx</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-150.765</v>
+        <v>-149.647</v>
       </c>
       <c r="C82" t="n">
-        <v>63.04</v>
+        <v>63.036</v>
       </c>
       <c r="D82" t="n">
-        <v>117.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
+          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>60 km N of Petersville, Alaska</t>
+          <t>52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3718,38 +3718,38 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46096.78820800926</v>
+        <v>46096.80405828704</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46096.79154229166</v>
+        <v>46096.80508491898</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>us6000sghb</t>
+          <t>us6000sghd</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>131.6063</v>
+        <v>142.6105</v>
       </c>
       <c r="C83" t="n">
-        <v>31.4194</v>
+        <v>41.4045</v>
       </c>
       <c r="D83" t="n">
-        <v>32.903</v>
+        <v>42.986</v>
       </c>
       <c r="E83" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
+          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>30 km SE of Nichinan, Japan</t>
+          <t>84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3758,38 +3758,38 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46096.77722483796</v>
+        <v>46096.78951814815</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46096.91079450231</v>
+        <v>46096.84466623842</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>us6000sgh9</t>
+          <t>aka2026fflqih</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-77.5782</v>
+        <v>-150.765</v>
       </c>
       <c r="C84" t="n">
-        <v>-1.3215</v>
+        <v>63.04</v>
       </c>
       <c r="D84" t="n">
-        <v>218.126</v>
+        <v>117.3</v>
       </c>
       <c r="E84" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
+          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>44 km SE of Tena, Ecuador</t>
+          <t>60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3798,38 +3798,38 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46096.77198028936</v>
+        <v>46096.78820800926</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46096.78392407407</v>
+        <v>46096.79154229166</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nc75327792</t>
+          <t>us6000sghb</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-122.471336364746</v>
+        <v>131.6063</v>
       </c>
       <c r="C85" t="n">
-        <v>37.5974998474121</v>
+        <v>31.4194</v>
       </c>
       <c r="D85" t="n">
-        <v>9.72999954223633</v>
+        <v>32.903</v>
       </c>
       <c r="E85" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
+          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2 km SE of Pacifica, CA</t>
+          <t>30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3838,38 +3838,38 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46096.77132291667</v>
+        <v>46096.77722483796</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46096.81413002315</v>
+        <v>46096.91079450231</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>aka2026ffklqv</t>
+          <t>us6000sgh9</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-155.854</v>
+        <v>-77.5782</v>
       </c>
       <c r="C86" t="n">
-        <v>57.153</v>
+        <v>-1.3215</v>
       </c>
       <c r="D86" t="n">
-        <v>63.2</v>
+        <v>218.126</v>
       </c>
       <c r="E86" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
+          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>96 km WSW of Karluk, Alaska</t>
+          <t>44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3878,38 +3878,38 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46096.76349226852</v>
+        <v>46096.77198028936</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46096.76507798611</v>
+        <v>46096.78392407407</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>nc75327787</t>
+          <t>nc75327792</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-123.346832275391</v>
+        <v>-122.471336364746</v>
       </c>
       <c r="C87" t="n">
-        <v>39.476001739502</v>
+        <v>37.5974998474121</v>
       </c>
       <c r="D87" t="n">
-        <v>4.19999980926514</v>
+        <v>9.72999954223633</v>
       </c>
       <c r="E87" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
+          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>5 km NE of Brooktrails, CA</t>
+          <t>2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3918,38 +3918,38 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46096.7527207176</v>
+        <v>46096.77132291667</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46096.79673230324</v>
+        <v>46096.81413002315</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>aka2026ffjrwj</t>
+          <t>aka2026ffklqv</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-149.163</v>
+        <v>-155.854</v>
       </c>
       <c r="C88" t="n">
-        <v>62.869</v>
+        <v>57.153</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3</v>
+        <v>63.2</v>
       </c>
       <c r="E88" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
+          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>59 km S of Cantwell, Alaska</t>
+          <t>96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3958,38 +3958,38 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46096.74754356482</v>
+        <v>46096.76349226852</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46096.7486603125</v>
+        <v>46096.76507798611</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>aka2026ffjpxp</t>
+          <t>nc75327787</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-152.555</v>
+        <v>-123.346832275391</v>
       </c>
       <c r="C89" t="n">
-        <v>59.7</v>
+        <v>39.476001739502</v>
       </c>
       <c r="D89" t="n">
-        <v>76.90000000000001</v>
+        <v>4.19999980926514</v>
       </c>
       <c r="E89" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
+          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>41 km WSW of Anchor Point, Alaska</t>
+          <t>5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3998,38 +3998,38 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46096.74597070602</v>
+        <v>46096.7527207176</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46096.74724846065</v>
+        <v>46096.79673230324</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>us6000sgh3</t>
+          <t>aka2026ffjrwj</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>128.5163</v>
+        <v>-149.163</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.3925</v>
+        <v>62.869</v>
       </c>
       <c r="D90" t="n">
-        <v>137.104</v>
+        <v>0.3</v>
       </c>
       <c r="E90" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
+          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>208 km NE of Lospalos, Timor Leste</t>
+          <t>59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4038,38 +4038,38 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46096.7350890625</v>
+        <v>46096.74754356482</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46096.81851898148</v>
+        <v>46096.7486603125</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ci41204623</t>
+          <t>aka2026ffjpxp</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-116.638166666667</v>
+        <v>-152.555</v>
       </c>
       <c r="C91" t="n">
-        <v>32.8055</v>
+        <v>59.7</v>
       </c>
       <c r="D91" t="n">
-        <v>16.68</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E91" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
+          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>10 km W of Pine Valley, CA</t>
+          <t>41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4078,38 +4078,38 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46096.72295416667</v>
+        <v>46096.74597070602</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46096.72542263889</v>
+        <v>46096.74724846065</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>aka2026ffhzps</t>
+          <t>us6000sgh3</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-146.822</v>
+        <v>128.5163</v>
       </c>
       <c r="C92" t="n">
-        <v>60.719</v>
+        <v>-7.3925</v>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>137.104</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
+          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18 km SSW of Tatitlek, Alaska</t>
+          <t>208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4118,38 +4118,38 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46096.71188380787</v>
+        <v>46096.7350890625</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46096.71385545139</v>
+        <v>46096.81851898148</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>tx2026ffhpux</t>
+          <t>ci41204623</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-103.799</v>
+        <v>-116.638166666667</v>
       </c>
       <c r="C93" t="n">
-        <v>31.021</v>
+        <v>32.8055</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>16.68</v>
       </c>
       <c r="E93" t="n">
-        <v>1.9</v>
+        <v>1.07</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
+          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>6 km NW of Balmorhea, Texas</t>
+          <t>10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4158,38 +4158,38 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46096.70398288195</v>
+        <v>46096.72295416667</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46096.71967913194</v>
+        <v>46096.72542263889</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>aka2026ffhkgu</t>
+          <t>aka2026ffhzps</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-154.974</v>
+        <v>-146.822</v>
       </c>
       <c r="C94" t="n">
-        <v>58.28</v>
+        <v>60.719</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3</v>
+        <v>19</v>
       </c>
       <c r="E94" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
+          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>84 km NNW of Karluk, Alaska</t>
+          <t>18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4198,38 +4198,38 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46096.6993729051</v>
+        <v>46096.71188380787</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46096.7007930787</v>
+        <v>46096.71385545139</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nc75327772</t>
+          <t>tx2026ffhpux</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-122.78466796875</v>
+        <v>-103.799</v>
       </c>
       <c r="C95" t="n">
-        <v>38.7933349609375</v>
+        <v>31.021</v>
       </c>
       <c r="D95" t="n">
-        <v>3.51999998092651</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
+          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4238,38 +4238,38 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46096.69837233796</v>
+        <v>46096.70398288195</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46096.72732706019</v>
+        <v>46096.71967913194</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>us6000sggw</t>
+          <t>aka2026ffhkgu</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>143.3074</v>
+        <v>-154.974</v>
       </c>
       <c r="C96" t="n">
-        <v>40.9048</v>
+        <v>58.28</v>
       </c>
       <c r="D96" t="n">
-        <v>37.859</v>
+        <v>0.3</v>
       </c>
       <c r="E96" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
+          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>139 km SSE of Honchō, Japan</t>
+          <t>84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4278,38 +4278,38 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46096.68937086806</v>
+        <v>46096.6993729051</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46096.69961851852</v>
+        <v>46096.7007930787</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>nc75327767</t>
+          <t>nc75327772</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-120.05883026123</v>
+        <v>-122.78466796875</v>
       </c>
       <c r="C97" t="n">
-        <v>35.7056655883789</v>
+        <v>38.7933349609375</v>
       </c>
       <c r="D97" t="n">
-        <v>7.76999998092651</v>
+        <v>3.51999998092651</v>
       </c>
       <c r="E97" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>M 2.2 - 22 km E of Cholame, CA</t>
+          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>22 km E of Cholame, CA</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4318,38 +4318,38 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46096.68914074074</v>
+        <v>46096.69837233796</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46096.71344819444</v>
+        <v>46096.72732706019</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>aka2026ffgrhi</t>
+          <t>us6000sggw</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-151.417</v>
+        <v>143.3074</v>
       </c>
       <c r="C98" t="n">
-        <v>63.08</v>
+        <v>40.9048</v>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>37.859</v>
       </c>
       <c r="E98" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
+          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>53 km SSE of Denali National Park, Alaska</t>
+          <t>139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4358,38 +4358,38 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46096.68422761574</v>
+        <v>46096.68937086806</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46096.68548758102</v>
+        <v>46096.69961851852</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nc75327742</t>
+          <t>nc75327767</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-121.291664123535</v>
+        <v>-120.05883026123</v>
       </c>
       <c r="C99" t="n">
-        <v>36.9063339233398</v>
+        <v>35.7056655883789</v>
       </c>
       <c r="D99" t="n">
-        <v>7.69000005722046</v>
+        <v>7.76999998092651</v>
       </c>
       <c r="E99" t="n">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>M 1.2 - 12 km NE of Hollister, CA</t>
+          <t>M 2.2 - 22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>12 km NE of Hollister, CA</t>
+          <t>22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4398,38 +4398,38 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46096.65917303241</v>
+        <v>46096.68914074074</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46096.69960388889</v>
+        <v>46096.71344819444</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>nc75327737</t>
+          <t>aka2026ffgrhi</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-122.806663513184</v>
+        <v>-151.417</v>
       </c>
       <c r="C100" t="n">
-        <v>38.8235015869141</v>
+        <v>63.08</v>
       </c>
       <c r="D100" t="n">
-        <v>2.41000008583069</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
+          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>7 km NW of The Geysers, CA</t>
+          <t>53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4438,38 +4438,38 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46096.65873715278</v>
+        <v>46096.68422761574</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46096.67873339121</v>
+        <v>46096.68548758102</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>nn00912713</t>
+          <t>nc75327742</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-116.393</v>
+        <v>-121.291664123535</v>
       </c>
       <c r="C101" t="n">
-        <v>38.5366</v>
+        <v>36.9063339233398</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0315</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="E101" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
+          <t>M 1.2 - 12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>89 km NE of Tonopah, Nevada</t>
+          <t>12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4478,38 +4478,38 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46096.64812005787</v>
+        <v>46096.65917303241</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46096.64995700232</v>
+        <v>46096.69960388889</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>nc75327727</t>
+          <t>nc75327737</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-122.743835449219</v>
+        <v>-122.806663513184</v>
       </c>
       <c r="C102" t="n">
-        <v>38.7863349914551</v>
+        <v>38.8235015869141</v>
       </c>
       <c r="D102" t="n">
-        <v>0.850000023841858</v>
+        <v>2.41000008583069</v>
       </c>
       <c r="E102" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
+          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1 km NE of The Geysers, CA</t>
+          <t>7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4518,38 +4518,38 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46096.64470740741</v>
+        <v>46096.65873715278</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46096.68219443287</v>
+        <v>46096.67873339121</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ci41204591</t>
+          <t>nn00912713</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-115.8325</v>
+        <v>-116.393</v>
       </c>
       <c r="C103" t="n">
-        <v>31.8188333333333</v>
+        <v>38.5366</v>
       </c>
       <c r="D103" t="n">
-        <v>13.69</v>
+        <v>0.0315</v>
       </c>
       <c r="E103" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
+          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>70 km E of Maneadero, B.C., MX</t>
+          <t>89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4558,38 +4558,38 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46096.62630196759</v>
+        <v>46096.64812005787</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46096.62875739583</v>
+        <v>46096.64995700232</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nc75327717</t>
+          <t>nc75327727</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-121.055168151855</v>
+        <v>-122.743835449219</v>
       </c>
       <c r="C104" t="n">
-        <v>36.451000213623</v>
+        <v>38.7863349914551</v>
       </c>
       <c r="D104" t="n">
-        <v>0.409999996423721</v>
+        <v>0.850000023841858</v>
       </c>
       <c r="E104" t="n">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
+          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>12 km SE of Pinnacles, CA</t>
+          <t>1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4598,38 +4598,38 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46096.61927071759</v>
+        <v>46096.64470740741</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46096.64398418982</v>
+        <v>46096.68219443287</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>tx2026ffdmwb</t>
+          <t>ci41204591</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-104.413</v>
+        <v>-115.8325</v>
       </c>
       <c r="C105" t="n">
-        <v>31.649</v>
+        <v>31.8188333333333</v>
       </c>
       <c r="D105" t="n">
-        <v>5.946</v>
+        <v>13.69</v>
       </c>
       <c r="E105" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>M 1.6 - 58 km S of Whites City, New Mexico</t>
+          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4638,38 +4638,38 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46096.61776914352</v>
+        <v>46096.62630196759</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46097.20572792824</v>
+        <v>46096.62875739583</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>aka2026ffcpmw</t>
+          <t>nc75327717</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-152.825</v>
+        <v>-121.055168151855</v>
       </c>
       <c r="C106" t="n">
-        <v>59.058</v>
+        <v>36.451000213623</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
+          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>61 km WSW of Nanwalek, Alaska</t>
+          <t>12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4678,38 +4678,38 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46096.59896729167</v>
+        <v>46096.61927071759</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46096.91903732639</v>
+        <v>46096.64398418982</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>us6000sggm</t>
+          <t>tx2026ffdmwb</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>130.0249</v>
+        <v>-104.413</v>
       </c>
       <c r="C107" t="n">
-        <v>-5.5263</v>
+        <v>31.649</v>
       </c>
       <c r="D107" t="n">
-        <v>184.533</v>
+        <v>5.946</v>
       </c>
       <c r="E107" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
+          <t>M 1.6 - 58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>271 km SSE of Amahai, Indonesia</t>
+          <t>58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4718,38 +4718,38 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46096.59319422454</v>
+        <v>46096.61776914352</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46096.69633148148</v>
+        <v>46097.20572792824</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>hv74917522</t>
+          <t>aka2026ffcpmw</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-155.374328613281</v>
+        <v>-152.825</v>
       </c>
       <c r="C108" t="n">
-        <v>19.1918334960938</v>
+        <v>59.058</v>
       </c>
       <c r="D108" t="n">
-        <v>31.7099990844727</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
+          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>11 km E of Pāhala, Hawaii</t>
+          <t>61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4758,38 +4758,38 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46096.59297361111</v>
+        <v>46096.59896729167</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46096.5954587963</v>
+        <v>46096.91903732639</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ci41204575</t>
+          <t>us6000sggm</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-116.426666666667</v>
+        <v>130.0249</v>
       </c>
       <c r="C109" t="n">
-        <v>33.9901666666667</v>
+        <v>-5.5263</v>
       </c>
       <c r="D109" t="n">
-        <v>2.17</v>
+        <v>184.533</v>
       </c>
       <c r="E109" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4798,38 +4798,38 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46096.58429085648</v>
+        <v>46096.59319422454</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46096.69570008102</v>
+        <v>46096.69633148148</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ci41204567</t>
+          <t>hv74917522</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-116.426666666667</v>
+        <v>-155.374328613281</v>
       </c>
       <c r="C110" t="n">
-        <v>33.9915</v>
+        <v>19.1918334960938</v>
       </c>
       <c r="D110" t="n">
-        <v>2.18</v>
+        <v>31.7099990844727</v>
       </c>
       <c r="E110" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4838,38 +4838,38 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46096.57788611111</v>
+        <v>46096.59297361111</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46096.58546979167</v>
+        <v>46096.5954587963</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nn00912712</t>
+          <t>ci41204575</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-116.4988</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C111" t="n">
-        <v>38.4756</v>
+        <v>33.9901666666667</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0689</v>
+        <v>2.17</v>
       </c>
       <c r="E111" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
+          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>78 km NE of Tonopah, Nevada</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4878,38 +4878,38 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46096.57585082176</v>
+        <v>46096.58429085648</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46096.57864184028</v>
+        <v>46096.69570008102</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ci41204559</t>
+          <t>ci41204567</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-118.1145</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C112" t="n">
-        <v>34.0995</v>
+        <v>33.9915</v>
       </c>
       <c r="D112" t="n">
-        <v>8.91</v>
+        <v>2.18</v>
       </c>
       <c r="E112" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
+          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1 km WNW of San Gabriel, CA</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4918,38 +4918,38 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46096.5639962963</v>
+        <v>46096.57788611111</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46096.56638376157</v>
+        <v>46096.58546979167</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>aka2026ffaxsl</t>
+          <t>nn00912712</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-153.59</v>
+        <v>-116.4988</v>
       </c>
       <c r="C113" t="n">
-        <v>59.151</v>
+        <v>38.4756</v>
       </c>
       <c r="D113" t="n">
-        <v>102.5</v>
+        <v>0.0689</v>
       </c>
       <c r="E113" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4958,38 +4958,38 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46096.56368013889</v>
+        <v>46096.57585082176</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46096.564885625</v>
+        <v>46096.57864184028</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>aka2026ffanxh</t>
+          <t>ci41204559</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-149.871</v>
+        <v>-118.1145</v>
       </c>
       <c r="C114" t="n">
-        <v>61.849</v>
+        <v>34.0995</v>
       </c>
       <c r="D114" t="n">
-        <v>28.4</v>
+        <v>8.91</v>
       </c>
       <c r="E114" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
+          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>14 km NE of Willow, Alaska</t>
+          <t>1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4998,38 +4998,38 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46096.55577541667</v>
+        <v>46096.5639962963</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46096.55684119213</v>
+        <v>46096.56638376157</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>tx2026ffanng</t>
+          <t>aka2026ffaxsl</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-101.924</v>
+        <v>-153.59</v>
       </c>
       <c r="C115" t="n">
-        <v>32.101</v>
+        <v>59.151</v>
       </c>
       <c r="D115" t="n">
-        <v>3.9912</v>
+        <v>102.5</v>
       </c>
       <c r="E115" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
+          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5038,38 +5038,38 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46096.55563410879</v>
+        <v>46096.56368013889</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46096.97107067129</v>
+        <v>46096.564885625</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nn00912708</t>
+          <t>aka2026ffanxh</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-116.4027</v>
+        <v>-149.871</v>
       </c>
       <c r="C116" t="n">
-        <v>37.3392</v>
+        <v>61.849</v>
       </c>
       <c r="D116" t="n">
-        <v>13.9737</v>
+        <v>28.4</v>
       </c>
       <c r="E116" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
+          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>57 km NNE of Beatty, Nevada</t>
+          <t>14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5078,38 +5078,38 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46096.55248135416</v>
+        <v>46096.55577541667</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46096.55406869213</v>
+        <v>46096.55684119213</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>nn00912710</t>
+          <t>tx2026ffanng</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-117.9202</v>
+        <v>-101.924</v>
       </c>
       <c r="C117" t="n">
-        <v>38.5488</v>
+        <v>32.101</v>
       </c>
       <c r="D117" t="n">
-        <v>11.6085</v>
+        <v>3.9912</v>
       </c>
       <c r="E117" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
+          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>24 km NE of Mina, Nevada</t>
+          <t>13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5118,38 +5118,38 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46096.55246195602</v>
+        <v>46096.55563410879</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46096.55466255787</v>
+        <v>46096.97107067129</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>aka2026ffagux</t>
+          <t>nn00912708</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-149.012</v>
+        <v>-116.4027</v>
       </c>
       <c r="C118" t="n">
-        <v>62.698</v>
+        <v>37.3392</v>
       </c>
       <c r="D118" t="n">
-        <v>62.2</v>
+        <v>13.9737</v>
       </c>
       <c r="E118" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
+          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>62 km ENE of Chase, Alaska</t>
+          <t>57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5158,38 +5158,38 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46096.55006834491</v>
+        <v>46096.55248135416</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46096.5511231713</v>
+        <v>46096.55406869213</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>aka2026ffacwz</t>
+          <t>nn00912710</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-154.211</v>
+        <v>-117.9202</v>
       </c>
       <c r="C119" t="n">
-        <v>58.934</v>
+        <v>38.5488</v>
       </c>
       <c r="D119" t="n">
-        <v>126.4</v>
+        <v>11.6085</v>
       </c>
       <c r="E119" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
+          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>64 km SSE of Kokhanok, Alaska</t>
+          <t>24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5198,38 +5198,38 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46096.54689578704</v>
+        <v>46096.55246195602</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46096.54852043981</v>
+        <v>46096.55466255787</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>uw62235651</t>
+          <t>aka2026ffagux</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-124.0351666666667</v>
+        <v>-149.012</v>
       </c>
       <c r="C120" t="n">
-        <v>47.33166666666666</v>
+        <v>62.698</v>
       </c>
       <c r="D120" t="n">
-        <v>23.98</v>
+        <v>62.2</v>
       </c>
       <c r="E120" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
+          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>12 km NNW of Humptulips, Washington</t>
+          <t>62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5238,38 +5238,38 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46096.54669189815</v>
+        <v>46096.55006834491</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46096.58038923611</v>
+        <v>46096.5511231713</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>nc75327692</t>
+          <t>aka2026ffacwz</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-122.779335021973</v>
+        <v>-154.211</v>
       </c>
       <c r="C121" t="n">
-        <v>38.8115005493164</v>
+        <v>58.934</v>
       </c>
       <c r="D121" t="n">
-        <v>0.550000011920929</v>
+        <v>126.4</v>
       </c>
       <c r="E121" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
+          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>4 km NNW of The Geysers, CA</t>
+          <t>64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5278,38 +5278,38 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46096.54474907408</v>
+        <v>46096.54689578704</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46096.5710708449</v>
+        <v>46096.54852043981</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>us6000sgg9</t>
+          <t>uw62235651</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-77.3565</v>
+        <v>-124.0351666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>-45.6923</v>
+        <v>47.33166666666666</v>
       </c>
       <c r="D122" t="n">
-        <v>10</v>
+        <v>23.98</v>
       </c>
       <c r="E122" t="n">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>M 4.6 - Off the coast of Aisen, Chile</t>
+          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5318,38 +5318,38 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46096.53758378472</v>
+        <v>46096.54669189815</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46096.58026666666</v>
+        <v>46096.58038923611</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>us6000sgg8</t>
+          <t>nc75327692</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-77.3313</v>
+        <v>-122.779335021973</v>
       </c>
       <c r="C123" t="n">
-        <v>-45.741</v>
+        <v>38.8115005493164</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="E123" t="n">
-        <v>4.4</v>
+        <v>1.08</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5358,38 +5358,38 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46096.53580871528</v>
+        <v>46096.54474907408</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46096.59747731481</v>
+        <v>46096.5710708449</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>aka2026fezlzd</t>
+          <t>us6000sgg9</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-150.155</v>
+        <v>-77.3565</v>
       </c>
       <c r="C124" t="n">
-        <v>61.309</v>
+        <v>-45.6923</v>
       </c>
       <c r="D124" t="n">
-        <v>35.8</v>
+        <v>10</v>
       </c>
       <c r="E124" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
+          <t>M 4.6 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>11 km WSW of Point MacKenzie, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5398,38 +5398,38 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46096.53327611111</v>
+        <v>46096.53758378472</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46096.53437532407</v>
+        <v>46096.58026666666</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>aka2026feywwv</t>
+          <t>us6000sgg8</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-148.811</v>
+        <v>-77.3313</v>
       </c>
       <c r="C125" t="n">
-        <v>63.988</v>
+        <v>-45.741</v>
       </c>
       <c r="D125" t="n">
-        <v>113.5</v>
+        <v>10</v>
       </c>
       <c r="E125" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>15 km ESE of Ferry, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5438,38 +5438,38 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46096.52110533565</v>
+        <v>46096.53580871528</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46096.52266071759</v>
+        <v>46096.59747731481</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>us6000sgg7</t>
+          <t>aka2026fezlzd</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-72.47499999999999</v>
+        <v>-150.155</v>
       </c>
       <c r="C126" t="n">
-        <v>41.5071</v>
+        <v>61.309</v>
       </c>
       <c r="D126" t="n">
-        <v>6.072</v>
+        <v>35.8</v>
       </c>
       <c r="E126" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
+          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2 km WNW of Moodus, Connecticut</t>
+          <t>11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5478,38 +5478,38 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46096.51831680556</v>
+        <v>46096.53327611111</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46097.0635559375</v>
+        <v>46096.53437532407</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>aka2026feypws</t>
+          <t>aka2026feywwv</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-151.884</v>
+        <v>-148.811</v>
       </c>
       <c r="C127" t="n">
-        <v>61.213</v>
+        <v>63.988</v>
       </c>
       <c r="D127" t="n">
-        <v>92</v>
+        <v>113.5</v>
       </c>
       <c r="E127" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
+          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>43 km WNW of Tyonek, Alaska</t>
+          <t>15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5518,38 +5518,38 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46096.51546960648</v>
+        <v>46096.52110533565</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46096.51679775463</v>
+        <v>46096.52266071759</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>hv74917517</t>
+          <t>us6000sgg7</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-155.388671875</v>
+        <v>-72.47499999999999</v>
       </c>
       <c r="C128" t="n">
-        <v>19.2761669158936</v>
+        <v>41.5071</v>
       </c>
       <c r="D128" t="n">
-        <v>29.1200008392334</v>
+        <v>6.072</v>
       </c>
       <c r="E128" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
+          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>12 km NE of Pāhala, Hawaii</t>
+          <t>2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5558,38 +5558,38 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46096.51510231481</v>
+        <v>46096.51831680556</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46096.51755763889</v>
+        <v>46097.0635559375</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>us6000sgg3</t>
+          <t>aka2026feypws</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-72.49160000000001</v>
+        <v>-151.884</v>
       </c>
       <c r="C129" t="n">
-        <v>41.4904</v>
+        <v>61.213</v>
       </c>
       <c r="D129" t="n">
-        <v>6.63</v>
+        <v>92</v>
       </c>
       <c r="E129" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
+          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>3 km WSW of Moodus, Connecticut</t>
+          <t>43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5598,38 +5598,38 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46096.51474966435</v>
+        <v>46096.51546960648</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46097.21278487269</v>
+        <v>46096.51679775463</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>us6000sgg2</t>
+          <t>hv74917517</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>155.7691</v>
+        <v>-155.388671875</v>
       </c>
       <c r="C130" t="n">
-        <v>50.1375</v>
+        <v>19.2761669158936</v>
       </c>
       <c r="D130" t="n">
-        <v>93.238</v>
+        <v>29.1200008392334</v>
       </c>
       <c r="E130" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5638,38 +5638,38 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46096.50655835648</v>
+        <v>46096.51510231481</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46096.52194490741</v>
+        <v>46096.51755763889</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>aka2026feycns</t>
+          <t>us6000sgg3</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-148.959</v>
+        <v>-72.49160000000001</v>
       </c>
       <c r="C131" t="n">
-        <v>63.283</v>
+        <v>41.4904</v>
       </c>
       <c r="D131" t="n">
-        <v>0.6</v>
+        <v>6.63</v>
       </c>
       <c r="E131" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
+          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>12 km S of Cantwell, Alaska</t>
+          <t>3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5678,38 +5678,38 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46096.50470625</v>
+        <v>46096.51474966435</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46096.50576539352</v>
+        <v>46097.21278487269</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ci41204535</t>
+          <t>us6000sgg2</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-119.474833333333</v>
+        <v>155.7691</v>
       </c>
       <c r="C132" t="n">
-        <v>34.3685</v>
+        <v>50.1375</v>
       </c>
       <c r="D132" t="n">
-        <v>0.54</v>
+        <v>93.238</v>
       </c>
       <c r="E132" t="n">
-        <v>1.49</v>
+        <v>4.5</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
+          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>5 km SE of Carpinteria, CA</t>
+          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5718,38 +5718,38 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46096.49835740741</v>
+        <v>46096.50655835648</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46096.50080350695</v>
+        <v>46096.52194490741</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>aka2026fewzkc</t>
+          <t>aka2026feycns</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-148.795</v>
+        <v>-148.959</v>
       </c>
       <c r="C133" t="n">
-        <v>62.2</v>
+        <v>63.283</v>
       </c>
       <c r="D133" t="n">
-        <v>22.1</v>
+        <v>0.6</v>
       </c>
       <c r="E133" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
+          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>47 km N of Sutton-Alpine, Alaska</t>
+          <t>12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5758,38 +5758,38 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46096.48122515046</v>
+        <v>46096.50470625</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46096.48264917824</v>
+        <v>46096.50576539352</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>us6000sgfx</t>
+          <t>ci41204535</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-80.1019</v>
+        <v>-119.474833333333</v>
       </c>
       <c r="C134" t="n">
-        <v>0.5871</v>
+        <v>34.3685</v>
       </c>
       <c r="D134" t="n">
-        <v>36.381</v>
+        <v>0.54</v>
       </c>
       <c r="E134" t="n">
-        <v>4.4</v>
+        <v>1.49</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
+          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>9 km WSW of Muisne, Ecuador</t>
+          <t>5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5798,38 +5798,38 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46096.47494160879</v>
+        <v>46096.49835740741</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46096.4911</v>
+        <v>46096.50080350695</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>pr71509923</t>
+          <t>aka2026fewzkc</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-66.1071666666667</v>
+        <v>-148.795</v>
       </c>
       <c r="C135" t="n">
-        <v>18.1251666666667</v>
+        <v>62.2</v>
       </c>
       <c r="D135" t="n">
-        <v>24.58</v>
+        <v>22.1</v>
       </c>
       <c r="E135" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5838,38 +5838,38 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46096.47251458334</v>
+        <v>46096.48122515046</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46096.60321875</v>
+        <v>46096.48264917824</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ci41204519</t>
+          <t>us6000sgfx</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-118.627833333333</v>
+        <v>-80.1019</v>
       </c>
       <c r="C136" t="n">
-        <v>34.6043333333333</v>
+        <v>0.5871</v>
       </c>
       <c r="D136" t="n">
-        <v>10.64</v>
+        <v>36.381</v>
       </c>
       <c r="E136" t="n">
-        <v>1.13</v>
+        <v>4.4</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>M 1.1 - 13 km N of Castaic, CA</t>
+          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>13 km N of Castaic, CA</t>
+          <t>9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5878,38 +5878,38 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46096.46653668981</v>
+        <v>46096.47494160879</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46096.46890145833</v>
+        <v>46096.4911</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>nn00912706</t>
+          <t>pr71509923</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-119.5178</v>
+        <v>-66.1071666666667</v>
       </c>
       <c r="C137" t="n">
-        <v>38.4812</v>
+        <v>18.1251666666667</v>
       </c>
       <c r="D137" t="n">
-        <v>3.3162</v>
+        <v>24.58</v>
       </c>
       <c r="E137" t="n">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km SW of Walker, California</t>
+          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>5 km SW of Walker, California</t>
+          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5918,38 +5918,38 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46096.46134278935</v>
+        <v>46096.47251458334</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46096.46294350694</v>
+        <v>46096.60321875</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>nc75327672</t>
+          <t>ci41204519</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-122.810333251953</v>
+        <v>-118.627833333333</v>
       </c>
       <c r="C138" t="n">
-        <v>38.8395004272461</v>
+        <v>34.6043333333333</v>
       </c>
       <c r="D138" t="n">
-        <v>1.83000004291534</v>
+        <v>10.64</v>
       </c>
       <c r="E138" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
+          <t>M 1.1 - 13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8 km WNW of Cobb, CA</t>
+          <t>13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5958,38 +5958,38 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46096.46108472222</v>
+        <v>46096.46653668981</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46096.49469679398</v>
+        <v>46096.46890145833</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>pr71509913</t>
+          <t>nn00912706</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-67.0566666666667</v>
+        <v>-119.5178</v>
       </c>
       <c r="C139" t="n">
-        <v>18.1476666666667</v>
+        <v>38.4812</v>
       </c>
       <c r="D139" t="n">
-        <v>17.11</v>
+        <v>3.3162</v>
       </c>
       <c r="E139" t="n">
-        <v>2.37</v>
+        <v>1.26</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>M 1.3 - 5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5998,38 +5998,38 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46096.44030868055</v>
+        <v>46096.46134278935</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46096.59237719907</v>
+        <v>46096.46294350694</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>aka2026feukwz</t>
+          <t>nc75327672</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-147.764</v>
+        <v>-122.810333251953</v>
       </c>
       <c r="C140" t="n">
-        <v>60.385</v>
+        <v>38.8395004272461</v>
       </c>
       <c r="D140" t="n">
-        <v>14.9</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="E140" t="n">
-        <v>1.7</v>
+        <v>0.97</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
+          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>38 km NNE of Chenega, Alaska</t>
+          <t>8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6038,38 +6038,38 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46096.42763064815</v>
+        <v>46096.46108472222</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46096.4286147338</v>
+        <v>46096.49469679398</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>aka2026fetqyo</t>
+          <t>pr71509913</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-150.43</v>
+        <v>-67.0566666666667</v>
       </c>
       <c r="C141" t="n">
-        <v>60.896</v>
+        <v>18.1476666666667</v>
       </c>
       <c r="D141" t="n">
-        <v>45.5</v>
+        <v>17.11</v>
       </c>
       <c r="E141" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
+          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>14 km ESE of Point Possession, Alaska</t>
+          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6078,38 +6078,38 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46096.41156589121</v>
+        <v>46096.44030868055</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46096.41261650463</v>
+        <v>46096.59237719907</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ci41204503</t>
+          <t>aka2026feukwz</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-117.464333333333</v>
+        <v>-147.764</v>
       </c>
       <c r="C142" t="n">
-        <v>34.157</v>
+        <v>60.385</v>
       </c>
       <c r="D142" t="n">
-        <v>6.87</v>
+        <v>14.9</v>
       </c>
       <c r="E142" t="n">
-        <v>0.98</v>
+        <v>1.7</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>M 1.0 - 7 km N of Fontana, CA</t>
+          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>7 km N of Fontana, CA</t>
+          <t>38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6118,38 +6118,38 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46096.39763148148</v>
+        <v>46096.42763064815</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46096.39998002315</v>
+        <v>46096.4286147338</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>aka2026fessqh</t>
+          <t>aka2026fetqyo</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-152.317</v>
+        <v>-150.43</v>
       </c>
       <c r="C143" t="n">
-        <v>60.36</v>
+        <v>60.896</v>
       </c>
       <c r="D143" t="n">
-        <v>90.3</v>
+        <v>45.5</v>
       </c>
       <c r="E143" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
+          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>49 km NW of Ninilchik, Alaska</t>
+          <t>14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6158,38 +6158,38 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46096.39196349537</v>
+        <v>46096.41156589121</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46096.39365355324</v>
+        <v>46096.41261650463</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>nc75327657</t>
+          <t>ci41204503</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-122.805335998535</v>
+        <v>-117.464333333333</v>
       </c>
       <c r="C144" t="n">
-        <v>38.8190002441406</v>
+        <v>34.157</v>
       </c>
       <c r="D144" t="n">
-        <v>2.17000007629395</v>
+        <v>6.87</v>
       </c>
       <c r="E144" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
+          <t>M 1.0 - 7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6198,38 +6198,38 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46096.37721527777</v>
+        <v>46096.39763148148</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46096.42173711806</v>
+        <v>46096.39998002315</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>aka2026fertpz</t>
+          <t>aka2026fessqh</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-157.698</v>
+        <v>-152.317</v>
       </c>
       <c r="C145" t="n">
-        <v>55.194</v>
+        <v>60.36</v>
       </c>
       <c r="D145" t="n">
-        <v>4.2</v>
+        <v>90.3</v>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
+          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>121 km SE of Perryville, Alaska</t>
+          <t>49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6238,38 +6238,38 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46096.37321436343</v>
+        <v>46096.39196349537</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46096.37804444444</v>
+        <v>46096.39365355324</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>uw62235646</t>
+          <t>nc75327657</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-121.9746666666667</v>
+        <v>-122.805335998535</v>
       </c>
       <c r="C146" t="n">
-        <v>47.82666666666667</v>
+        <v>38.8190002441406</v>
       </c>
       <c r="D146" t="n">
-        <v>26.62</v>
+        <v>2.17000007629395</v>
       </c>
       <c r="E146" t="n">
-        <v>1.96</v>
+        <v>1.1</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km S of Monroe, Washington</t>
+          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>3 km S of Monroe, Washington</t>
+          <t>6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6278,38 +6278,38 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46096.36272453704</v>
+        <v>46096.37721527777</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46096.47082604167</v>
+        <v>46096.42173711806</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>us6000sgfk</t>
+          <t>aka2026fertpz</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-77.27330000000001</v>
+        <v>-157.698</v>
       </c>
       <c r="C147" t="n">
-        <v>-45.5694</v>
+        <v>55.194</v>
       </c>
       <c r="D147" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="E147" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>M 5.3 - Off the coast of Aisen, Chile</t>
+          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6318,38 +6318,38 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>46096.35320680556</v>
+        <v>46096.37321436343</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46096.38260266204</v>
+        <v>46096.37804444444</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>us6000sgfh</t>
+          <t>uw62235646</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>122.0755</v>
+        <v>-121.9746666666667</v>
       </c>
       <c r="C148" t="n">
-        <v>24.3607</v>
+        <v>47.82666666666667</v>
       </c>
       <c r="D148" t="n">
-        <v>27.716</v>
+        <v>26.62</v>
       </c>
       <c r="E148" t="n">
-        <v>4.8</v>
+        <v>1.96</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
+          <t>M 2.0 - 3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>54 km SE of Yilan, Taiwan</t>
+          <t>3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6358,38 +6358,38 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>46096.34370333333</v>
+        <v>46096.36272453704</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46096.53583686343</v>
+        <v>46096.47082604167</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>nn00912705</t>
+          <t>us6000sgfk</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-116.5611</v>
+        <v>-77.27330000000001</v>
       </c>
       <c r="C149" t="n">
-        <v>38.4412</v>
+        <v>-45.5694</v>
       </c>
       <c r="D149" t="n">
-        <v>3.8472</v>
+        <v>10</v>
       </c>
       <c r="E149" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
+          <t>M 5.3 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>71 km NE of Tonopah, Nevada</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6398,38 +6398,38 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>46096.34194375</v>
+        <v>46096.35320680556</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46096.34380362269</v>
+        <v>46096.38260266204</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ci41204487</t>
+          <t>us6000sgfh</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-116.419666666667</v>
+        <v>122.0755</v>
       </c>
       <c r="C150" t="n">
-        <v>32.9405</v>
+        <v>24.3607</v>
       </c>
       <c r="D150" t="n">
-        <v>4.88</v>
+        <v>27.716</v>
       </c>
       <c r="E150" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
+          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>17 km NE of Pine Valley, CA</t>
+          <t>54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6438,38 +6438,38 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>46096.32685023148</v>
+        <v>46096.34370333333</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46096.32921789352</v>
+        <v>46096.53583686343</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ci41204479</t>
+          <t>nn00912705</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-117.2475</v>
+        <v>-116.5611</v>
       </c>
       <c r="C151" t="n">
-        <v>34.0556666666667</v>
+        <v>38.4412</v>
       </c>
       <c r="D151" t="n">
-        <v>15.21</v>
+        <v>3.8472</v>
       </c>
       <c r="E151" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
+          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2 km ENE of Loma Linda, CA</t>
+          <t>71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6478,38 +6478,38 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>46096.32684571759</v>
+        <v>46096.34194375</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46096.32920631945</v>
+        <v>46096.34380362269</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>aka2026fephrq</t>
+          <t>ci41204487</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-150.634</v>
+        <v>-116.419666666667</v>
       </c>
       <c r="C152" t="n">
-        <v>60.036</v>
+        <v>32.9405</v>
       </c>
       <c r="D152" t="n">
-        <v>63.6</v>
+        <v>4.88</v>
       </c>
       <c r="E152" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
+          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>26 km NE of Fox River, Alaska</t>
+          <t>17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6518,38 +6518,38 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>46096.32028525463</v>
+        <v>46096.32685023148</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46096.32365</v>
+        <v>46096.32921789352</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>nn00912702</t>
+          <t>ci41204479</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-116.579</v>
+        <v>-117.2475</v>
       </c>
       <c r="C153" t="n">
-        <v>38.4398</v>
+        <v>34.0556666666667</v>
       </c>
       <c r="D153" t="n">
-        <v>3.5596</v>
+        <v>15.21</v>
       </c>
       <c r="E153" t="n">
-        <v>2.08</v>
+        <v>1.09</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6558,38 +6558,38 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>46096.30809262732</v>
+        <v>46096.32684571759</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46096.31003199074</v>
+        <v>46096.32920631945</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>nc75327637</t>
+          <t>aka2026fephrq</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-121.911003112793</v>
+        <v>-150.634</v>
       </c>
       <c r="C154" t="n">
-        <v>38.0525016784668</v>
+        <v>60.036</v>
       </c>
       <c r="D154" t="n">
-        <v>17.0200004577637</v>
+        <v>63.6</v>
       </c>
       <c r="E154" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
+          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4 km NW of Pittsburg, CA</t>
+          <t>26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6598,38 +6598,38 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>46096.29875555556</v>
+        <v>46096.32028525463</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46096.34190163195</v>
+        <v>46096.32365</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>us6000sgf9</t>
+          <t>nn00912702</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>72.05249999999999</v>
+        <v>-116.579</v>
       </c>
       <c r="C155" t="n">
-        <v>37.629</v>
+        <v>38.4398</v>
       </c>
       <c r="D155" t="n">
-        <v>196.241</v>
+        <v>3.5596</v>
       </c>
       <c r="E155" t="n">
-        <v>4.1</v>
+        <v>2.08</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
+          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>46 km ENE of Khorugh, Tajikistan</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6638,38 +6638,38 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>46096.29624704861</v>
+        <v>46096.30809262732</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46096.31303287037</v>
+        <v>46096.31003199074</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>aka2026fenxtb</t>
+          <t>nc75327637</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-154.253</v>
+        <v>-121.911003112793</v>
       </c>
       <c r="C156" t="n">
-        <v>58.558</v>
+        <v>38.0525016784668</v>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>17.0200004577637</v>
       </c>
       <c r="E156" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
+          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>96 km NW of Aleneva, Alaska</t>
+          <t>4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6678,38 +6678,38 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>46096.29131623843</v>
+        <v>46096.29875555556</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46096.29275974537</v>
+        <v>46096.34190163195</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>nc75327632</t>
+          <t>us6000sgf9</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-121.910331726074</v>
+        <v>72.05249999999999</v>
       </c>
       <c r="C157" t="n">
-        <v>38.0643348693848</v>
+        <v>37.629</v>
       </c>
       <c r="D157" t="n">
-        <v>18.6900005340576</v>
+        <v>196.241</v>
       </c>
       <c r="E157" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
+          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>5 km NNW of Pittsburg, CA</t>
+          <t>46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6718,38 +6718,38 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>46096.28527893518</v>
+        <v>46096.29624704861</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46096.32459672454</v>
+        <v>46096.31303287037</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tx2026fenmna</t>
+          <t>aka2026fenxtb</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-104.203</v>
+        <v>-154.253</v>
       </c>
       <c r="C158" t="n">
-        <v>31.669</v>
+        <v>58.558</v>
       </c>
       <c r="D158" t="n">
-        <v>7.2278</v>
+        <v>5</v>
       </c>
       <c r="E158" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
+          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6758,38 +6758,38 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>46096.28226224537</v>
+        <v>46096.29131623843</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46096.83936486111</v>
+        <v>46096.29275974537</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tx2026fenktd</t>
+          <t>nc75327632</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-104.202</v>
+        <v>-121.910331726074</v>
       </c>
       <c r="C159" t="n">
-        <v>31.669</v>
+        <v>38.0643348693848</v>
       </c>
       <c r="D159" t="n">
-        <v>7.5739</v>
+        <v>18.6900005340576</v>
       </c>
       <c r="E159" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
+          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6798,38 +6798,38 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>46096.28124563657</v>
+        <v>46096.28527893518</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46096.70278489583</v>
+        <v>46096.32459672454</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ci41204455</t>
+          <t>tx2026fenmna</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-116.806333333333</v>
+        <v>-104.203</v>
       </c>
       <c r="C160" t="n">
-        <v>33.2463333333333</v>
+        <v>31.669</v>
       </c>
       <c r="D160" t="n">
-        <v>10.1</v>
+        <v>7.2278</v>
       </c>
       <c r="E160" t="n">
-        <v>0.95</v>
+        <v>1.9</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
+          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>4 km W of Lake Henshaw, CA</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6838,38 +6838,38 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>46096.27805949074</v>
+        <v>46096.28226224537</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46096.28047209491</v>
+        <v>46096.83936486111</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>nn00912698</t>
+          <t>tx2026fenktd</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-116.6054</v>
+        <v>-104.202</v>
       </c>
       <c r="C161" t="n">
-        <v>38.2724</v>
+        <v>31.669</v>
       </c>
       <c r="D161" t="n">
-        <v>5.7486</v>
+        <v>7.5739</v>
       </c>
       <c r="E161" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
+          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>59 km ENE of Tonopah, Nevada</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6878,38 +6878,38 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>46096.26913202546</v>
+        <v>46096.28124563657</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46096.27123583333</v>
+        <v>46096.70278489583</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>nn00912696</t>
+          <t>ci41204455</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-116.3473</v>
+        <v>-116.806333333333</v>
       </c>
       <c r="C162" t="n">
-        <v>37.5427</v>
+        <v>33.2463333333333</v>
       </c>
       <c r="D162" t="n">
-        <v>15.7841</v>
+        <v>10.1</v>
       </c>
       <c r="E162" t="n">
-        <v>1.48</v>
+        <v>0.95</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6918,38 +6918,38 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>46096.26722096065</v>
+        <v>46096.27805949074</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46096.26890163194</v>
+        <v>46096.28047209491</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>pr71509903</t>
+          <t>nn00912698</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-66.7433333333333</v>
+        <v>-116.6054</v>
       </c>
       <c r="C163" t="n">
-        <v>18.043</v>
+        <v>38.2724</v>
       </c>
       <c r="D163" t="n">
-        <v>16.94</v>
+        <v>5.7486</v>
       </c>
       <c r="E163" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6958,38 +6958,38 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>46096.26509143518</v>
+        <v>46096.26913202546</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46096.27459479167</v>
+        <v>46096.27123583333</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nn00912694</t>
+          <t>nn00912696</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-116.5678</v>
+        <v>-116.3473</v>
       </c>
       <c r="C164" t="n">
-        <v>38.4757</v>
+        <v>37.5427</v>
       </c>
       <c r="D164" t="n">
-        <v>5.2112</v>
+        <v>15.7841</v>
       </c>
       <c r="E164" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
+          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>73 km NE of Tonopah, Nevada</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6998,38 +6998,38 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>46096.26149202546</v>
+        <v>46096.26722096065</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46096.26338644676</v>
+        <v>46096.26890163194</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>aka2026femdbx</t>
+          <t>pr71509903</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-154.971</v>
+        <v>-66.7433333333333</v>
       </c>
       <c r="C165" t="n">
-        <v>57.961</v>
+        <v>18.043</v>
       </c>
       <c r="D165" t="n">
-        <v>86.59999999999999</v>
+        <v>16.94</v>
       </c>
       <c r="E165" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
+          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>53 km NW of Karluk, Alaska</t>
+          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7038,38 +7038,38 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>46096.25371178241</v>
+        <v>46096.26509143518</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46096.2741787037</v>
+        <v>46096.27459479167</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>nn00912691</t>
+          <t>nn00912694</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-116.5734</v>
+        <v>-116.5678</v>
       </c>
       <c r="C166" t="n">
-        <v>38.4423</v>
+        <v>38.4757</v>
       </c>
       <c r="D166" t="n">
-        <v>1.9073</v>
+        <v>5.2112</v>
       </c>
       <c r="E166" t="n">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7078,38 +7078,38 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>46096.25128945602</v>
+        <v>46096.26149202546</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46096.25308243056</v>
+        <v>46096.26338644676</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ci41204447</t>
+          <t>aka2026femdbx</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-116.168333333333</v>
+        <v>-154.971</v>
       </c>
       <c r="C167" t="n">
-        <v>33.8886666666667</v>
+        <v>57.961</v>
       </c>
       <c r="D167" t="n">
-        <v>5.52</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E167" t="n">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>M 1.3 - 19 km NNE of Indio, CA</t>
+          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>19 km NNE of Indio, CA</t>
+          <t>53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7118,38 +7118,38 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>46096.24517546297</v>
+        <v>46096.25371178241</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46096.25266435185</v>
+        <v>46096.2741787037</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>nc75327597</t>
+          <t>nn00912691</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-121.635665893555</v>
+        <v>-116.5734</v>
       </c>
       <c r="C168" t="n">
-        <v>36.9845008850098</v>
+        <v>38.4423</v>
       </c>
       <c r="D168" t="n">
-        <v>8.989999771118161</v>
+        <v>1.9073</v>
       </c>
       <c r="E168" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
+          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>6 km WSW of Gilroy, CA</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7158,38 +7158,38 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>46096.24306736111</v>
+        <v>46096.25128945602</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46096.29676952546</v>
+        <v>46096.25308243056</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>aka2026fekujg</t>
+          <t>ci41204447</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-150.947</v>
+        <v>-116.168333333333</v>
       </c>
       <c r="C169" t="n">
-        <v>60.457</v>
+        <v>33.8886666666667</v>
       </c>
       <c r="D169" t="n">
-        <v>50.6</v>
+        <v>5.52</v>
       </c>
       <c r="E169" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>M 1.6 - 7 km ESE of Soldotna, Alaska</t>
+          <t>M 1.3 - 19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>7 km ESE of Soldotna, Alaska</t>
+          <t>19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7198,38 +7198,38 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>46096.22573243055</v>
+        <v>46096.24517546297</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46096.22721925926</v>
+        <v>46096.25266435185</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>us6000sgel</t>
+          <t>nc75327597</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-77.3734</v>
+        <v>-121.635665893555</v>
       </c>
       <c r="C170" t="n">
-        <v>-45.6673</v>
+        <v>36.9845008850098</v>
       </c>
       <c r="D170" t="n">
-        <v>10</v>
+        <v>8.989999771118161</v>
       </c>
       <c r="E170" t="n">
-        <v>4.4</v>
+        <v>1.71</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7238,38 +7238,38 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>46096.22567266204</v>
+        <v>46096.24306736111</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46096.32872731482</v>
+        <v>46096.29676952546</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>nn00912689</t>
+          <t>aka2026fekujg</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-116.8458</v>
+        <v>-150.947</v>
       </c>
       <c r="C171" t="n">
-        <v>38.2828</v>
+        <v>60.457</v>
       </c>
       <c r="D171" t="n">
-        <v>5.3648</v>
+        <v>50.6</v>
       </c>
       <c r="E171" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>M 1.9 - 41 km NE of Tonopah, Nevada</t>
+          <t>M 1.6 - 7 km ESE of Soldotna, Alaska</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>41 km NE of Tonopah, Nevada</t>
+          <t>7 km ESE of Soldotna, Alaska</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7278,10 +7278,50 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>46096.2170634838</v>
+        <v>46096.22573243055</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46096.21891450231</v>
+        <v>46096.22721925926</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>us6000sgel</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>-77.3734</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-45.6673</v>
+      </c>
+      <c r="D172" t="n">
+        <v>10</v>
+      </c>
+      <c r="E172" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Off the coast of Aisen, Chile</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>46096.22567266204</v>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>46096.32872731482</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/USGS.xlsx
+++ b/data/raw/USGS.xlsx
@@ -487,29 +487,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nc75328072</t>
+          <t>nn00912752</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-121.153663635254</v>
+        <v>-116.4741</v>
       </c>
       <c r="C2" t="n">
-        <v>37.1259994506836</v>
+        <v>38.4885</v>
       </c>
       <c r="D2" t="n">
-        <v>9.80000019073486</v>
+        <v>0.0292</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M 2.5 - 20 km SW of Gustine, CA</t>
+          <t>M 1.6 - 81 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20 km SW of Gustine, CA</t>
+          <t>81 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,38 +518,38 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46097.21683298611</v>
+        <v>46097.22186076389</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46097.21793168982</v>
+        <v>46097.22480158565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ci41204887</t>
+          <t>nc75328077</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-117.500666666667</v>
+        <v>-121.173835754395</v>
       </c>
       <c r="C3" t="n">
-        <v>34.0881666666667</v>
+        <v>37.1158332824707</v>
       </c>
       <c r="D3" t="n">
-        <v>10.81</v>
+        <v>8.680000305175779</v>
       </c>
       <c r="E3" t="n">
-        <v>0.99</v>
+        <v>1.49</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km WSW of Fontana, CA</t>
+          <t>M 1.5 - 22 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4 km WSW of Fontana, CA</t>
+          <t>22 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,38 +558,38 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46097.21549351852</v>
+        <v>46097.22094502315</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46097.21785097222</v>
+        <v>46097.22203528935</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nc75328067</t>
+          <t>nc75328072</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-122.458168029785</v>
+        <v>-121.153663635254</v>
       </c>
       <c r="C4" t="n">
-        <v>37.5923347473145</v>
+        <v>37.1259994506836</v>
       </c>
       <c r="D4" t="n">
-        <v>7.23999977111816</v>
+        <v>9.80000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
+          <t>M 2.5 - 20 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>20 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -598,38 +598,38 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46097.20110729166</v>
+        <v>46097.21683298611</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46097.2169190162</v>
+        <v>46097.22382956019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nc75328062</t>
+          <t>ci41204887</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-122.700668334961</v>
+        <v>-117.500666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>38.7681655883789</v>
+        <v>34.0881666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>0.730000019073486</v>
+        <v>10.81</v>
       </c>
       <c r="E5" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M 1.1 - 1 km SW of Anderson Springs, CA</t>
+          <t>M 1.0 - 4 km WSW of Fontana, CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1 km SW of Anderson Springs, CA</t>
+          <t>4 km WSW of Fontana, CA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,38 +638,38 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46097.1980800926</v>
+        <v>46097.21549351852</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46097.21344644676</v>
+        <v>46097.21785097222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aka2026fgejkl</t>
+          <t>nc75328067</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-150.208</v>
+        <v>-122.458168029785</v>
       </c>
       <c r="C6" t="n">
-        <v>62.214</v>
+        <v>37.5923347473145</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4</v>
+        <v>7.23999977111816</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8</v>
+        <v>1.02</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11 km S of Trapper Creek, Alaska</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -678,38 +678,38 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46097.18073642361</v>
+        <v>46097.20110729166</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46097.1817900926</v>
+        <v>46097.2169190162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nn00912748</t>
+          <t>nc75328062</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-116.7944</v>
+        <v>-122.700668334961</v>
       </c>
       <c r="C7" t="n">
-        <v>38.3084</v>
+        <v>38.7681655883789</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8689</v>
+        <v>0.730000019073486</v>
       </c>
       <c r="E7" t="n">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 1 km SW of Anderson Springs, CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>46 km NE of Tonopah, Nevada</t>
+          <t>1 km SW of Anderson Springs, CA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -718,38 +718,38 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46097.18032635417</v>
+        <v>46097.1980800926</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46097.18299189815</v>
+        <v>46097.21344644676</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nn00912744</t>
+          <t>aka2026fgejkl</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-116.5751</v>
+        <v>-150.208</v>
       </c>
       <c r="C8" t="n">
-        <v>38.2761</v>
+        <v>62.214</v>
       </c>
       <c r="D8" t="n">
-        <v>6.7167</v>
+        <v>4.4</v>
       </c>
       <c r="E8" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M 2.2 - 61 km ENE of Tonopah, Nevada</t>
+          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>61 km ENE of Tonopah, Nevada</t>
+          <t>11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -758,38 +758,38 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46097.17459033565</v>
+        <v>46097.18073642361</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46097.17637523148</v>
+        <v>46097.1817900926</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ci41204855</t>
+          <t>nn00912748</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-119.120666666667</v>
+        <v>-116.7944</v>
       </c>
       <c r="C9" t="n">
-        <v>34.9321666666667</v>
+        <v>38.3084</v>
       </c>
       <c r="D9" t="n">
-        <v>0.87</v>
+        <v>2.8689</v>
       </c>
       <c r="E9" t="n">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M 2.3 - 10 km NNE of Pine Mountain Club, CA</t>
+          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10 km NNE of Pine Mountain Club, CA</t>
+          <t>46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -798,38 +798,38 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46097.17414733797</v>
+        <v>46097.18032635417</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46097.20602984953</v>
+        <v>46097.18299189815</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nn00912743</t>
+          <t>nn00912744</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-116.0158</v>
+        <v>-116.5751</v>
       </c>
       <c r="C10" t="n">
-        <v>37.795</v>
+        <v>38.2761</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4807</v>
+        <v>6.7167</v>
       </c>
       <c r="E10" t="n">
-        <v>1.34</v>
+        <v>2.18</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
+          <t>M 2.2 - 61 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29 km NW of Rachel, Nevada</t>
+          <t>61 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -838,38 +838,38 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46097.17013881944</v>
+        <v>46097.17459033565</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46097.1716130787</v>
+        <v>46097.17637523148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nc75328052</t>
+          <t>ci41204855</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-122.765167236328</v>
+        <v>-119.120666666667</v>
       </c>
       <c r="C11" t="n">
-        <v>38.7836685180664</v>
+        <v>34.9321666666667</v>
       </c>
       <c r="D11" t="n">
-        <v>4.19000005722046</v>
+        <v>0.87</v>
       </c>
       <c r="E11" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
+          <t>M 2.3 - 10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1 km NW of The Geysers, CA</t>
+          <t>10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -878,38 +878,38 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46097.16834872685</v>
+        <v>46097.17414733797</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46097.20647809028</v>
+        <v>46097.20602984953</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nn00912742</t>
+          <t>nn00912743</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-117.5849</v>
+        <v>-116.0158</v>
       </c>
       <c r="C12" t="n">
-        <v>37.3479</v>
+        <v>37.795</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7908</v>
+        <v>2.4807</v>
       </c>
       <c r="E12" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
+          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>45 km S of Silver Peak, Nevada</t>
+          <t>29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -918,38 +918,38 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46097.15891554398</v>
+        <v>46097.17013881944</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46097.16036833333</v>
+        <v>46097.1716130787</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nn00912740</t>
+          <t>nc75328052</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-116.3558</v>
+        <v>-122.765167236328</v>
       </c>
       <c r="C13" t="n">
-        <v>37.5573</v>
+        <v>38.7836685180664</v>
       </c>
       <c r="D13" t="n">
-        <v>8.4693</v>
+        <v>4.19000005722046</v>
       </c>
       <c r="E13" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
+          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>54 km W of Rachel, Nevada</t>
+          <t>1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -958,38 +958,38 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46097.1542737963</v>
+        <v>46097.16834872685</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46097.15577996528</v>
+        <v>46097.20647809028</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nc75328042</t>
+          <t>nn00912742</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-122.843170166016</v>
+        <v>-117.5849</v>
       </c>
       <c r="C14" t="n">
-        <v>38.8208351135254</v>
+        <v>37.3479</v>
       </c>
       <c r="D14" t="n">
-        <v>1.67999994754791</v>
+        <v>3.7908</v>
       </c>
       <c r="E14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
+          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9 km WNW of The Geysers, CA</t>
+          <t>45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -998,38 +998,38 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46097.15140474537</v>
+        <v>46097.15891554398</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46097.15253628472</v>
+        <v>46097.16036833333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nc75328037</t>
+          <t>nn00912740</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-122.839668273926</v>
+        <v>-116.3558</v>
       </c>
       <c r="C15" t="n">
-        <v>38.8219985961914</v>
+        <v>37.5573</v>
       </c>
       <c r="D15" t="n">
-        <v>1.66999995708466</v>
+        <v>8.4693</v>
       </c>
       <c r="E15" t="n">
-        <v>1.96</v>
+        <v>1.15</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
+          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9 km NW of The Geysers, CA</t>
+          <t>54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1038,38 +1038,38 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46097.15081805555</v>
+        <v>46097.1542737963</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46097.18912663194</v>
+        <v>46097.15577996528</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ci41204839</t>
+          <t>nc75328042</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-117.701833333333</v>
+        <v>-122.843170166016</v>
       </c>
       <c r="C16" t="n">
-        <v>35.8715</v>
+        <v>38.8208351135254</v>
       </c>
       <c r="D16" t="n">
-        <v>4.72</v>
+        <v>1.67999994754791</v>
       </c>
       <c r="E16" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
+          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20 km ESE of Little Lake, CA</t>
+          <t>9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1078,38 +1078,38 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46097.14808055555</v>
+        <v>46097.15140474537</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46097.15049766203</v>
+        <v>46097.15253628472</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>aka2026fgcope</t>
+          <t>nc75328037</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-149.454</v>
+        <v>-122.839668273926</v>
       </c>
       <c r="C17" t="n">
-        <v>62.553</v>
+        <v>38.8219985961914</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
+          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>35 km ENE of Chase, Alaska</t>
+          <t>9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1118,38 +1118,38 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46097.14301053241</v>
+        <v>46097.15081805555</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46097.14408171296</v>
+        <v>46097.18912663194</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nn00912738</t>
+          <t>ci41204839</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-116.4786</v>
+        <v>-117.701833333333</v>
       </c>
       <c r="C18" t="n">
-        <v>38.4752</v>
+        <v>35.8715</v>
       </c>
       <c r="D18" t="n">
-        <v>7.3424</v>
+        <v>4.72</v>
       </c>
       <c r="E18" t="n">
-        <v>1.74</v>
+        <v>0.99</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
+          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>79 km NE of Tonopah, Nevada</t>
+          <t>20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1158,38 +1158,38 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46097.13946230324</v>
+        <v>46097.14808055555</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46097.14130107639</v>
+        <v>46097.15049766203</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>aka2026fgbzeh</t>
+          <t>aka2026fgcope</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-149.584</v>
+        <v>-149.454</v>
       </c>
       <c r="C19" t="n">
-        <v>62.358</v>
+        <v>62.553</v>
       </c>
       <c r="D19" t="n">
-        <v>56.7</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
+          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25 km NNE of Susitna North, Alaska</t>
+          <t>35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1198,38 +1198,38 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46097.13059196759</v>
+        <v>46097.14301053241</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46097.13160341435</v>
+        <v>46097.14408171296</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>aka2026fgbuau</t>
+          <t>nn00912738</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-146.643</v>
+        <v>-116.4786</v>
       </c>
       <c r="C20" t="n">
-        <v>61.432</v>
+        <v>38.4752</v>
       </c>
       <c r="D20" t="n">
-        <v>17.4</v>
+        <v>7.3424</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
+          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>37 km NNW of Valdez, Alaska</t>
+          <t>79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,38 +1238,38 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46097.12645101852</v>
+        <v>46097.13946230324</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46097.12856479167</v>
+        <v>46097.14130107639</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nc75327997</t>
+          <t>aka2026fgbzeh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-122.785667419434</v>
+        <v>-149.584</v>
       </c>
       <c r="C21" t="n">
-        <v>38.8154983520508</v>
+        <v>62.358</v>
       </c>
       <c r="D21" t="n">
-        <v>1.46000003814697</v>
+        <v>56.7</v>
       </c>
       <c r="E21" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
+          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46097.10226643518</v>
+        <v>46097.13059196759</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46097.10338584491</v>
+        <v>46097.13160341435</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nc75327992</t>
+          <t>aka2026fgbuau</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-122.786163330078</v>
+        <v>-146.643</v>
       </c>
       <c r="C22" t="n">
-        <v>38.8153343200684</v>
+        <v>61.432</v>
       </c>
       <c r="D22" t="n">
-        <v>1.44000005722046</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
+          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1318,38 +1318,38 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46097.09843321759</v>
+        <v>46097.12645101852</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46097.13356498843</v>
+        <v>46097.12856479167</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>aka2026ffzydk</t>
+          <t>nc75327997</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-151.439</v>
+        <v>-122.785667419434</v>
       </c>
       <c r="C23" t="n">
-        <v>59.675</v>
+        <v>38.8154983520508</v>
       </c>
       <c r="D23" t="n">
-        <v>40.3</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
+          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0 km NW of Kachemak, Alaska</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1358,38 +1358,38 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46097.08785851852</v>
+        <v>46097.10226643518</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46097.0893715625</v>
+        <v>46097.10338584491</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nn00912733</t>
+          <t>nc75327992</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-116.2619</v>
+        <v>-122.786163330078</v>
       </c>
       <c r="C24" t="n">
-        <v>38.6278</v>
+        <v>38.8153343200684</v>
       </c>
       <c r="D24" t="n">
-        <v>4.7494</v>
+        <v>1.44000005722046</v>
       </c>
       <c r="E24" t="n">
-        <v>2.71</v>
+        <v>1.49</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M 2.7 - 95 km SE of Kingston, Nevada</t>
+          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>95 km SE of Kingston, Nevada</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1398,38 +1398,38 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46097.08629175926</v>
+        <v>46097.09843321759</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46097.09325277778</v>
+        <v>46097.13356498843</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ci41204823</t>
+          <t>aka2026ffzydk</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-117.844666666667</v>
+        <v>-151.439</v>
       </c>
       <c r="C25" t="n">
-        <v>36.4091666666667</v>
+        <v>59.675</v>
       </c>
       <c r="D25" t="n">
-        <v>3.71</v>
+        <v>40.3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M 1.2 - 20 km NE of Olancha, CA</t>
+          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20 km NE of Olancha, CA</t>
+          <t>0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1438,38 +1438,38 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46097.08612511574</v>
+        <v>46097.08785851852</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46097.08854572917</v>
+        <v>46097.0893715625</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tx2026ffzaya</t>
+          <t>nn00912733</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-104.188</v>
+        <v>-116.2619</v>
       </c>
       <c r="C26" t="n">
-        <v>31.703</v>
+        <v>38.6278</v>
       </c>
       <c r="D26" t="n">
-        <v>4.4731</v>
+        <v>4.7494</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7</v>
+        <v>2.71</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
+          <t>M 2.7 - 95 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>55 km SSE of Whites City, New Mexico</t>
+          <t>95 km SE of Kingston, Nevada</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1478,38 +1478,38 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46097.06930607639</v>
+        <v>46097.08629175926</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46097.08380681713</v>
+        <v>46097.09325277778</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hv74917612</t>
+          <t>ci41204823</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-155.139495849609</v>
+        <v>-117.844666666667</v>
       </c>
       <c r="C27" t="n">
-        <v>19.3330001831055</v>
+        <v>36.4091666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>3.76999998092651</v>
+        <v>3.71</v>
       </c>
       <c r="E27" t="n">
-        <v>2.04</v>
+        <v>1.19</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 1.2 - 20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1518,38 +1518,38 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46097.06757199074</v>
+        <v>46097.08612511574</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46097.07008101852</v>
+        <v>46097.08854572917</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ci41204799</t>
+          <t>tx2026ffzaya</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-117.4825</v>
+        <v>-104.188</v>
       </c>
       <c r="C28" t="n">
-        <v>35.601</v>
+        <v>31.703</v>
       </c>
       <c r="D28" t="n">
-        <v>7.7</v>
+        <v>4.4731</v>
       </c>
       <c r="E28" t="n">
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
+          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18 km E of Ridgecrest, CA</t>
+          <t>55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1558,38 +1558,38 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46097.0600244213</v>
+        <v>46097.06930607639</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46097.06239535879</v>
+        <v>46097.08380681713</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tx2026ffyeyx</t>
+          <t>hv74917612</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-104.176</v>
+        <v>-155.139495849609</v>
       </c>
       <c r="C29" t="n">
-        <v>31.711</v>
+        <v>19.3330001831055</v>
       </c>
       <c r="D29" t="n">
-        <v>7.4969</v>
+        <v>3.76999998092651</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M 1.9 - 54 km W of Mentone, Texas</t>
+          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>54 km W of Mentone, Texas</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1598,38 +1598,38 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46097.05150728009</v>
+        <v>46097.06757199074</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46097.06865469908</v>
+        <v>46097.07008101852</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>aka2026ffxzpn</t>
+          <t>ci41204799</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-150.668</v>
+        <v>-117.4825</v>
       </c>
       <c r="C30" t="n">
-        <v>63.582</v>
+        <v>35.601</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1</v>
+        <v>7.7</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7</v>
+        <v>0.95</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
+          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>52 km E of Denali National Park, Alaska</t>
+          <t>18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46097.0471140162</v>
+        <v>46097.0600244213</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46097.04869516204</v>
+        <v>46097.06239535879</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nn00912731</t>
+          <t>tx2026ffyeyx</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-114.5508</v>
+        <v>-104.176</v>
       </c>
       <c r="C31" t="n">
-        <v>37.2919</v>
+        <v>31.711</v>
       </c>
       <c r="D31" t="n">
-        <v>15.9298</v>
+        <v>7.4969</v>
       </c>
       <c r="E31" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
+          <t>M 1.9 - 54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>36 km S of Caliente, Nevada</t>
+          <t>54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1678,38 +1678,38 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46097.04372652778</v>
+        <v>46097.05150728009</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46097.04546596065</v>
+        <v>46097.06865469908</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ci41204783</t>
+          <t>aka2026ffxzpn</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-116.366833333333</v>
+        <v>-150.668</v>
       </c>
       <c r="C32" t="n">
-        <v>33.193</v>
+        <v>63.582</v>
       </c>
       <c r="D32" t="n">
-        <v>7.35</v>
+        <v>0.1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
+          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7 km S of Borrego Springs, CA</t>
+          <t>52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1718,38 +1718,38 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46097.04078981481</v>
+        <v>46097.0471140162</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46097.04323087963</v>
+        <v>46097.04869516204</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nc75327962</t>
+          <t>nn00912731</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-120.523834228516</v>
+        <v>-114.5508</v>
       </c>
       <c r="C33" t="n">
-        <v>35.9671669006348</v>
+        <v>37.2919</v>
       </c>
       <c r="D33" t="n">
-        <v>6.94999980926514</v>
+        <v>15.9298</v>
       </c>
       <c r="E33" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
+          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11 km NW of Parkfield, CA</t>
+          <t>36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1758,38 +1758,38 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46097.03950659722</v>
+        <v>46097.04372652778</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46097.09886200231</v>
+        <v>46097.04546596065</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>aka2026ffxmpi</t>
+          <t>ci41204783</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-149.174</v>
+        <v>-116.366833333333</v>
       </c>
       <c r="C34" t="n">
-        <v>63.002</v>
+        <v>33.193</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2</v>
+        <v>7.35</v>
       </c>
       <c r="E34" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
+          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>44 km SSW of Cantwell, Alaska</t>
+          <t>7 km S of Borrego Springs, CA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1798,38 +1798,38 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46097.03663675926</v>
+        <v>46097.04078981481</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46097.03896524305</v>
+        <v>46097.04323087963</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nc75327947</t>
+          <t>nc75327962</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-124.239669799805</v>
+        <v>-120.523834228516</v>
       </c>
       <c r="C35" t="n">
-        <v>40.4664993286133</v>
+        <v>35.9671669006348</v>
       </c>
       <c r="D35" t="n">
-        <v>26.0400009155273</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="E35" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
+          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>12 km WSW of Rio Dell, CA</t>
+          <t>11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1838,38 +1838,38 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46097.03397256944</v>
+        <v>46097.03950659722</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46097.08151043981</v>
+        <v>46097.09886200231</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nn00912729</t>
+          <t>aka2026ffxmpi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-116.2867</v>
+        <v>-149.174</v>
       </c>
       <c r="C36" t="n">
-        <v>37.418</v>
+        <v>63.002</v>
       </c>
       <c r="D36" t="n">
-        <v>8.758599999999999</v>
+        <v>0.2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1878,38 +1878,38 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46097.03219180556</v>
+        <v>46097.03663675926</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46097.03392417824</v>
+        <v>46097.03896524305</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hv74917602</t>
+          <t>nc75327947</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-155.143005371094</v>
+        <v>-124.239669799805</v>
       </c>
       <c r="C37" t="n">
-        <v>19.3344993591309</v>
+        <v>40.4664993286133</v>
       </c>
       <c r="D37" t="n">
-        <v>4.25</v>
+        <v>26.0400009155273</v>
       </c>
       <c r="E37" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1918,38 +1918,38 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46097.02269363426</v>
+        <v>46097.03397256944</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46097.02506747685</v>
+        <v>46097.08151043981</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nn00912728</t>
+          <t>nn00912729</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-116.8948</v>
+        <v>-116.2867</v>
       </c>
       <c r="C38" t="n">
-        <v>38.2511</v>
+        <v>37.418</v>
       </c>
       <c r="D38" t="n">
-        <v>4.7942</v>
+        <v>8.758599999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
+          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>35 km NE of Tonopah, Nevada</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1958,38 +1958,38 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46097.02024291667</v>
+        <v>46097.03219180556</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46097.02206256944</v>
+        <v>46097.03392417824</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nn00912725</t>
+          <t>hv74917602</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-116.3002</v>
+        <v>-155.143005371094</v>
       </c>
       <c r="C39" t="n">
-        <v>36.4986</v>
+        <v>19.3344993591309</v>
       </c>
       <c r="D39" t="n">
-        <v>1.7633</v>
+        <v>4.25</v>
       </c>
       <c r="E39" t="n">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
+          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>42 km NW of Pahrump, Nevada</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1998,38 +1998,38 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46097.01676708333</v>
+        <v>46097.02269363426</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46097.01802194444</v>
+        <v>46097.02506747685</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>aka2026ffwkac</t>
+          <t>nn00912728</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-147.104</v>
+        <v>-116.8948</v>
       </c>
       <c r="C40" t="n">
-        <v>61.221</v>
+        <v>38.2511</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>4.7942</v>
       </c>
       <c r="E40" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
+          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>41 km WNW of Valdez, Alaska</t>
+          <t>35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2038,38 +2038,38 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46097.01360875</v>
+        <v>46097.02024291667</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46097.01453715278</v>
+        <v>46097.02206256944</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nc75327937</t>
+          <t>nn00912725</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-120.16283416748</v>
+        <v>-116.3002</v>
       </c>
       <c r="C41" t="n">
-        <v>36.1510009765625</v>
+        <v>36.4986</v>
       </c>
       <c r="D41" t="n">
-        <v>5.53000020980835</v>
+        <v>1.7633</v>
       </c>
       <c r="E41" t="n">
-        <v>1.8</v>
+        <v>1.13</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M 1.8 - 8 km SW of Huron, CA</t>
+          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8 km SW of Huron, CA</t>
+          <t>42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2078,38 +2078,38 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46097.00379861111</v>
+        <v>46097.01676708333</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46097.07108120371</v>
+        <v>46097.01802194444</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aka2026ffvrqe</t>
+          <t>aka2026ffwkac</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-150.318</v>
+        <v>-147.104</v>
       </c>
       <c r="C42" t="n">
-        <v>60.621</v>
+        <v>61.221</v>
       </c>
       <c r="D42" t="n">
-        <v>37.9</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
+          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>26 km ENE of Sterling, Alaska</t>
+          <t>41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2118,38 +2118,38 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46096.99880960648</v>
+        <v>46097.01360875</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46097.06023194444</v>
+        <v>46097.01453715278</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hv74917597</t>
+          <t>nc75327937</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-154.981170654297</v>
+        <v>-120.16283416748</v>
       </c>
       <c r="C43" t="n">
-        <v>19.3976669311523</v>
+        <v>36.1510009765625</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.560000002384186</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E43" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
+          <t>M 1.8 - 8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10 km SW of Leilani Estates, Hawaii</t>
+          <t>8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2158,38 +2158,38 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46096.99111076389</v>
+        <v>46097.00379861111</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46096.993578125</v>
+        <v>46097.07108120371</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ci41204759</t>
+          <t>aka2026ffvrqe</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-117.6875</v>
+        <v>-150.318</v>
       </c>
       <c r="C44" t="n">
-        <v>35.0311666666667</v>
+        <v>60.621</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.84</v>
+        <v>37.9</v>
       </c>
       <c r="E44" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km NW of Boron, CA</t>
+          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5 km NW of Boron, CA</t>
+          <t>26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2198,38 +2198,38 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46096.98700925926</v>
+        <v>46096.99880960648</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46096.98945039352</v>
+        <v>46097.06023194444</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aka2026ffvcuk</t>
+          <t>hv74917597</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-147.706</v>
+        <v>-154.981170654297</v>
       </c>
       <c r="C45" t="n">
-        <v>63.18</v>
+        <v>19.3976669311523</v>
       </c>
       <c r="D45" t="n">
-        <v>4.3</v>
+        <v>-0.560000002384186</v>
       </c>
       <c r="E45" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
+          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>66 km ESE of Cantwell, Alaska</t>
+          <t>10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2238,38 +2238,38 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46096.98682952546</v>
+        <v>46096.99111076389</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46097.05321805555</v>
+        <v>46096.993578125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aka2026ffuxwl</t>
+          <t>ci41204759</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-149.464</v>
+        <v>-117.6875</v>
       </c>
       <c r="C46" t="n">
-        <v>65.532</v>
+        <v>35.0311666666667</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>-0.84</v>
       </c>
       <c r="E46" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
+          <t>M 1.3 - 5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>32 km E of Rampart, Alaska</t>
+          <t>5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2278,38 +2278,38 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46096.98287351852</v>
+        <v>46096.98700925926</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46096.98871584491</v>
+        <v>46096.98945039352</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nc75327927</t>
+          <t>aka2026ffvcuk</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-122.759002685547</v>
+        <v>-147.706</v>
       </c>
       <c r="C47" t="n">
-        <v>38.779167175293</v>
+        <v>63.18</v>
       </c>
       <c r="D47" t="n">
-        <v>1.16999995708466</v>
+        <v>4.3</v>
       </c>
       <c r="E47" t="n">
-        <v>1.06</v>
+        <v>2.4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
+          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0 km NW of The Geysers, CA</t>
+          <t>66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2318,38 +2318,38 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46096.98031608796</v>
+        <v>46096.98682952546</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46096.9814612037</v>
+        <v>46097.05321805555</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>nc75327922</t>
+          <t>aka2026ffuxwl</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-120.615669250488</v>
+        <v>-149.464</v>
       </c>
       <c r="C48" t="n">
-        <v>36.0485000610352</v>
+        <v>65.532</v>
       </c>
       <c r="D48" t="n">
-        <v>2.03999996185303</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
+          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>24 km NW of Parkfield, CA</t>
+          <t>32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2358,38 +2358,38 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46096.97481886574</v>
+        <v>46096.98287351852</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46097.03291697917</v>
+        <v>46096.98871584491</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>aka2026fftzga</t>
+          <t>nc75327927</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-147.469</v>
+        <v>-122.759002685547</v>
       </c>
       <c r="C49" t="n">
-        <v>64.946</v>
+        <v>38.779167175293</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E49" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>M 1.2 - 7 km E of Fox, Alaska</t>
+          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7 km E of Fox, Alaska</t>
+          <t>0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2398,38 +2398,38 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46096.96303546296</v>
+        <v>46096.98031608796</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46096.96398349537</v>
+        <v>46096.9814612037</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nc75327902</t>
+          <t>nc75327922</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-124.639663696289</v>
+        <v>-120.615669250488</v>
       </c>
       <c r="C50" t="n">
-        <v>40.34716796875</v>
+        <v>36.0485000610352</v>
       </c>
       <c r="D50" t="n">
-        <v>19.4500007629395</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="E50" t="n">
-        <v>2.76</v>
+        <v>1.65</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M 2.8 - 30 km W of Petrolia, CA</t>
+          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>30 km W of Petrolia, CA</t>
+          <t>24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2438,38 +2438,38 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46096.95174398148</v>
+        <v>46096.97481886574</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46097.04291712963</v>
+        <v>46097.03291697917</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>us6000sgib</t>
+          <t>aka2026fftzga</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>176.3522</v>
+        <v>-147.469</v>
       </c>
       <c r="C51" t="n">
-        <v>52.1304</v>
+        <v>64.946</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
+          <t>M 1.2 - 7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>229 km ESE of Attu Station, Alaska</t>
+          <t>7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2478,38 +2478,38 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46096.94854002315</v>
+        <v>46096.96303546296</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46097.14299561342</v>
+        <v>46096.96398349537</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nn00912719</t>
+          <t>nc75327902</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-119.7167</v>
+        <v>-124.639663696289</v>
       </c>
       <c r="C52" t="n">
-        <v>40.512</v>
+        <v>40.34716796875</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7442</v>
+        <v>19.4500007629395</v>
       </c>
       <c r="E52" t="n">
-        <v>1.9</v>
+        <v>2.76</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
+          <t>M 2.8 - 30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>32 km WSW of Empire, Nevada</t>
+          <t>30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2518,38 +2518,38 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46096.94697967593</v>
+        <v>46096.95174398148</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46096.94864458333</v>
+        <v>46097.04291712963</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>aka2026fftern</t>
+          <t>us6000sgib</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-145.732</v>
+        <v>176.3522</v>
       </c>
       <c r="C53" t="n">
-        <v>62.165</v>
+        <v>52.1304</v>
       </c>
       <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="n">
         <v>4.6</v>
       </c>
-      <c r="E53" t="n">
-        <v>1.6</v>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
+          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>11 km WNW of Glennallen, Alaska</t>
+          <t>229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2558,38 +2558,38 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46096.94644289352</v>
+        <v>46096.94854002315</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46096.94759246528</v>
+        <v>46097.14299561342</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>aka2026ffsxtw</t>
+          <t>nn00912719</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-150.289</v>
+        <v>-119.7167</v>
       </c>
       <c r="C54" t="n">
-        <v>60.111</v>
+        <v>40.512</v>
       </c>
       <c r="D54" t="n">
-        <v>46.9</v>
+        <v>0.7442</v>
       </c>
       <c r="E54" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
+          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>46 km NE of Fox River, Alaska</t>
+          <t>32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2598,38 +2598,38 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46096.94087768519</v>
+        <v>46096.94697967593</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46096.94183203704</v>
+        <v>46096.94864458333</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>aka2026ffsvcz</t>
+          <t>aka2026fftern</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-141.243</v>
+        <v>-145.732</v>
       </c>
       <c r="C55" t="n">
-        <v>61.573</v>
+        <v>62.165</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
+          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>90 km E of McCarthy, Alaska</t>
+          <t>11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2638,38 +2638,38 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46096.93874224537</v>
+        <v>46096.94644289352</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46096.93996863426</v>
+        <v>46096.94759246528</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hv74917587</t>
+          <t>aka2026ffsxtw</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-155.404998779297</v>
+        <v>-150.289</v>
       </c>
       <c r="C56" t="n">
-        <v>19.2546672821045</v>
+        <v>60.111</v>
       </c>
       <c r="D56" t="n">
-        <v>30.7900009155273</v>
+        <v>46.9</v>
       </c>
       <c r="E56" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
+          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9 km NE of Pāhala, Hawaii</t>
+          <t>46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2678,38 +2678,38 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46096.93382974537</v>
+        <v>46096.94087768519</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46096.93618622685</v>
+        <v>46096.94183203704</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nc75327892</t>
+          <t>aka2026ffsvcz</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-120.513832092285</v>
+        <v>-141.243</v>
       </c>
       <c r="C57" t="n">
-        <v>35.9599990844727</v>
+        <v>61.573</v>
       </c>
       <c r="D57" t="n">
-        <v>10.1700000762939</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
+          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10 km NW of Parkfield, CA</t>
+          <t>90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2718,38 +2718,38 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46096.92984074074</v>
+        <v>46096.93874224537</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46096.98773833334</v>
+        <v>46096.93996863426</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tx2026ffruyn</t>
+          <t>hv74917587</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-103.575</v>
+        <v>-155.404998779297</v>
       </c>
       <c r="C58" t="n">
-        <v>30.876</v>
+        <v>19.2546672821045</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>30.7900009155273</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
+          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20 km SE of Balmorhea, Texas</t>
+          <t>9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2758,38 +2758,38 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46096.91764664352</v>
+        <v>46096.93382974537</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46096.92133662037</v>
+        <v>46096.93618622685</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tx2026ffrhgd</t>
+          <t>nc75327892</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-101.817</v>
+        <v>-120.513832092285</v>
       </c>
       <c r="C59" t="n">
-        <v>32.349</v>
+        <v>35.9599990844727</v>
       </c>
       <c r="D59" t="n">
-        <v>11.8727</v>
+        <v>10.1700000762939</v>
       </c>
       <c r="E59" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
+          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21 km SSW of Ackerly, Texas</t>
+          <t>10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2798,38 +2798,38 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46096.90660459491</v>
+        <v>46096.92984074074</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46096.91322768519</v>
+        <v>46096.98773833334</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nc75327882</t>
+          <t>tx2026ffruyn</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-122.730499267578</v>
+        <v>-103.575</v>
       </c>
       <c r="C60" t="n">
-        <v>38.7738342285156</v>
+        <v>30.876</v>
       </c>
       <c r="D60" t="n">
-        <v>2.02999997138977</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km E of The Geysers, CA</t>
+          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2 km E of The Geysers, CA</t>
+          <t>20 km SE of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2838,38 +2838,38 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46096.90556168981</v>
+        <v>46096.91764664352</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46096.92179327546</v>
+        <v>46096.92133662037</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aka2026ffqxwe</t>
+          <t>tx2026ffrhgd</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-145.627</v>
+        <v>-101.817</v>
       </c>
       <c r="C61" t="n">
-        <v>62.093</v>
+        <v>32.349</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>11.8727</v>
       </c>
       <c r="E61" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
+          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4 km WSW of Glennallen, Alaska</t>
+          <t>21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2878,38 +2878,38 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46096.89903701389</v>
+        <v>46096.90660459491</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46096.90023371528</v>
+        <v>46096.91322768519</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>nn00912718</t>
+          <t>nc75327882</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-117.1162</v>
+        <v>-122.730499267578</v>
       </c>
       <c r="C62" t="n">
-        <v>37.2236</v>
+        <v>38.7738342285156</v>
       </c>
       <c r="D62" t="n">
-        <v>0.039</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="E62" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
+          <t>M 1.0 - 2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2918,38 +2918,38 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46096.8946965625</v>
+        <v>46096.90556168981</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46096.89624318287</v>
+        <v>46096.92179327546</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nc75327877</t>
+          <t>aka2026ffqxwe</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-121.053001403809</v>
+        <v>-145.627</v>
       </c>
       <c r="C63" t="n">
-        <v>36.4648323059082</v>
+        <v>62.093</v>
       </c>
       <c r="D63" t="n">
-        <v>0.209999993443489</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
+          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>11 km SE of Pinnacles, CA</t>
+          <t>4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2958,38 +2958,38 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46096.89354375</v>
+        <v>46096.89903701389</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46096.95303508102</v>
+        <v>46096.90023371528</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>us6000sghx</t>
+          <t>nn00912718</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-68.8159</v>
+        <v>-117.1162</v>
       </c>
       <c r="C64" t="n">
-        <v>-21.1625</v>
+        <v>37.2236</v>
       </c>
       <c r="D64" t="n">
-        <v>120.691</v>
+        <v>0.039</v>
       </c>
       <c r="E64" t="n">
-        <v>4.1</v>
+        <v>1.08</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
+          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>58 km W of Ollagüe, Chile</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2998,38 +2998,38 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46096.89260434028</v>
+        <v>46096.8946965625</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46097.01954907407</v>
+        <v>46096.89624318287</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>aka2026ffqnha</t>
+          <t>nc75327877</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-146.565</v>
+        <v>-121.053001403809</v>
       </c>
       <c r="C65" t="n">
-        <v>61.519</v>
+        <v>36.4648323059082</v>
       </c>
       <c r="D65" t="n">
-        <v>38.2</v>
+        <v>0.209999993443489</v>
       </c>
       <c r="E65" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
+          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>44 km NNW of Valdez, Alaska</t>
+          <t>11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3038,38 +3038,38 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46096.89050962963</v>
+        <v>46096.89354375</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46096.89142732639</v>
+        <v>46096.95303508102</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tx2026ffqmcg</t>
+          <t>us6000sghx</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-101.512</v>
+        <v>-68.8159</v>
       </c>
       <c r="C66" t="n">
-        <v>31.874</v>
+        <v>-21.1625</v>
       </c>
       <c r="D66" t="n">
-        <v>3.2716</v>
+        <v>120.691</v>
       </c>
       <c r="E66" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
+          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3 km WNW of Garden City, Texas</t>
+          <t>58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3078,38 +3078,38 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46096.88956126157</v>
+        <v>46096.89260434028</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46096.9711172801</v>
+        <v>46097.01954907407</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>nn00912716</t>
+          <t>aka2026ffqnha</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-116.5976</v>
+        <v>-146.565</v>
       </c>
       <c r="C67" t="n">
-        <v>38.2879</v>
+        <v>61.519</v>
       </c>
       <c r="D67" t="n">
-        <v>4.9318</v>
+        <v>38.2</v>
       </c>
       <c r="E67" t="n">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
+          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>60 km ENE of Tonopah, Nevada</t>
+          <t>44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3118,38 +3118,38 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46096.88044799768</v>
+        <v>46096.89050962963</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46096.88234515046</v>
+        <v>46096.89142732639</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>aka2026ffpwxx</t>
+          <t>tx2026ffqmcg</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-150.536</v>
+        <v>-101.512</v>
       </c>
       <c r="C68" t="n">
-        <v>60.816</v>
+        <v>31.874</v>
       </c>
       <c r="D68" t="n">
-        <v>14.2</v>
+        <v>3.2716</v>
       </c>
       <c r="E68" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
+          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14 km SE of Point Possession, Alaska</t>
+          <t>3 km WNW of Garden City, Texas</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3158,38 +3158,38 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46096.87733195602</v>
+        <v>46096.88956126157</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46096.87884059027</v>
+        <v>46096.9711172801</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tx2026ffpmmk</t>
+          <t>nn00912716</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-102.596</v>
+        <v>-116.5976</v>
       </c>
       <c r="C69" t="n">
-        <v>32.426</v>
+        <v>38.2879</v>
       </c>
       <c r="D69" t="n">
-        <v>7.1182</v>
+        <v>4.9318</v>
       </c>
       <c r="E69" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
+          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>12 km NNW of Andrews, Texas</t>
+          <t>60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3198,38 +3198,38 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46096.86891956018</v>
+        <v>46096.88044799768</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46096.87235497685</v>
+        <v>46096.88234515046</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>aka2026ffpbrz</t>
+          <t>aka2026ffpwxx</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-151.569</v>
+        <v>-150.536</v>
       </c>
       <c r="C70" t="n">
-        <v>61.397</v>
+        <v>60.816</v>
       </c>
       <c r="D70" t="n">
-        <v>76.90000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="E70" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
+          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>38 km NW of Beluga, Alaska</t>
+          <t>14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46096.86023665509</v>
+        <v>46096.87733195602</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46096.86153666666</v>
+        <v>46096.87884059027</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>aka2026ffoxwo</t>
+          <t>tx2026ffpmmk</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-153.073</v>
+        <v>-102.596</v>
       </c>
       <c r="C71" t="n">
-        <v>60.494</v>
+        <v>32.426</v>
       </c>
       <c r="D71" t="n">
-        <v>146.3</v>
+        <v>7.1182</v>
       </c>
       <c r="E71" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
+          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>75 km ENE of Port Alsworth, Alaska</t>
+          <t>12 km NNW of Andrews, Texas</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3278,38 +3278,38 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46096.85716821759</v>
+        <v>46096.86891956018</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46096.85982177083</v>
+        <v>46096.87235497685</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tx2026ffolko</t>
+          <t>aka2026ffpbrz</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-104.401</v>
+        <v>-151.569</v>
       </c>
       <c r="C72" t="n">
-        <v>31.692</v>
+        <v>61.397</v>
       </c>
       <c r="D72" t="n">
-        <v>4.8181</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
+          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>53 km S of Whites City, New Mexico</t>
+          <t>38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3318,38 +3318,38 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46096.84736503472</v>
+        <v>46096.86023665509</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46096.93883732639</v>
+        <v>46096.86153666666</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nc75327852</t>
+          <t>aka2026ffoxwo</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-122.464164733887</v>
+        <v>-153.073</v>
       </c>
       <c r="C73" t="n">
-        <v>37.5973320007324</v>
+        <v>60.494</v>
       </c>
       <c r="D73" t="n">
-        <v>9.090000152587891</v>
+        <v>146.3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
+          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3358,38 +3358,38 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46096.84368958334</v>
+        <v>46096.85716821759</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46096.84483373843</v>
+        <v>46096.85982177083</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>aka2026ffogkg</t>
+          <t>tx2026ffolko</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-150.241</v>
+        <v>-104.401</v>
       </c>
       <c r="C74" t="n">
-        <v>61.578</v>
+        <v>31.692</v>
       </c>
       <c r="D74" t="n">
-        <v>30.7</v>
+        <v>4.8181</v>
       </c>
       <c r="E74" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
+          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14 km ENE of Susitna, Alaska</t>
+          <t>53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3398,38 +3398,38 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46096.84307547453</v>
+        <v>46096.84736503472</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46096.84451351852</v>
+        <v>46096.93883732639</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nc75327847</t>
+          <t>nc75327852</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-122.757667541504</v>
+        <v>-122.464164733887</v>
       </c>
       <c r="C75" t="n">
-        <v>38.7918319702148</v>
+        <v>37.5973320007324</v>
       </c>
       <c r="D75" t="n">
-        <v>0.689999997615814</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="E75" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km N of The Geysers, CA</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2 km N of The Geysers, CA</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3438,38 +3438,38 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46096.84258912037</v>
+        <v>46096.84368958334</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46096.84373324074</v>
+        <v>46096.84483373843</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ci41204687</t>
+          <t>aka2026ffogkg</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-117.249</v>
+        <v>-150.241</v>
       </c>
       <c r="C76" t="n">
-        <v>33.9988333333333</v>
+        <v>61.578</v>
       </c>
       <c r="D76" t="n">
-        <v>10.86</v>
+        <v>30.7</v>
       </c>
       <c r="E76" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
+          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6 km SSE of Loma Linda, CA</t>
+          <t>14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3478,38 +3478,38 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46096.83063032408</v>
+        <v>46096.84307547453</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46096.83300278935</v>
+        <v>46096.84451351852</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nn00912714</t>
+          <t>nc75327847</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-116.7227</v>
+        <v>-122.757667541504</v>
       </c>
       <c r="C77" t="n">
-        <v>38.3427</v>
+        <v>38.7918319702148</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1382</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="E77" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
+          <t>M 1.0 - 2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>53 km NE of Tonopah, Nevada</t>
+          <t>2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3518,38 +3518,38 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46096.82208777778</v>
+        <v>46096.84258912037</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46096.82386192129</v>
+        <v>46096.84373324074</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>aka2026ffmxvv</t>
+          <t>ci41204687</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-151.974</v>
+        <v>-117.249</v>
       </c>
       <c r="C78" t="n">
-        <v>60.349</v>
+        <v>33.9988333333333</v>
       </c>
       <c r="D78" t="n">
-        <v>77.2</v>
+        <v>10.86</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
+          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>34 km WNW of Clam Gulch, Alaska</t>
+          <t>6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3558,38 +3558,38 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46096.81522726852</v>
+        <v>46096.83063032408</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46096.81638251158</v>
+        <v>46096.83300278935</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>nc75327827</t>
+          <t>nn00912714</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-121.9375</v>
+        <v>-116.7227</v>
       </c>
       <c r="C79" t="n">
-        <v>37.7731666666667</v>
+        <v>38.3427</v>
       </c>
       <c r="D79" t="n">
-        <v>7</v>
+        <v>0.1382</v>
       </c>
       <c r="E79" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
+          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>4 km ESE of San Ramon, CA</t>
+          <t>53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3598,38 +3598,38 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46096.81305393518</v>
+        <v>46096.82208777778</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46097.01551917824</v>
+        <v>46096.82386192129</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nc75327822</t>
+          <t>aka2026ffmxvv</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-122.787170410156</v>
+        <v>-151.974</v>
       </c>
       <c r="C80" t="n">
-        <v>38.7934989929199</v>
+        <v>60.349</v>
       </c>
       <c r="D80" t="n">
-        <v>2.92000007629395</v>
+        <v>77.2</v>
       </c>
       <c r="E80" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
+          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3638,38 +3638,38 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46096.81298229167</v>
+        <v>46096.81522726852</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46096.86627753473</v>
+        <v>46096.81638251158</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>us6000sghq</t>
+          <t>nc75327827</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>49.7256</v>
+        <v>-121.9375</v>
       </c>
       <c r="C81" t="n">
-        <v>32.4853</v>
+        <v>37.7731666666667</v>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E81" t="n">
-        <v>4.4</v>
+        <v>1.57</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
+          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>62 km SW of Fereydūnshahr, Iran</t>
+          <t>4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3678,38 +3678,38 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46096.8103829051</v>
+        <v>46096.81305393518</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46096.86111157407</v>
+        <v>46097.01551917824</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>aka2026ffmjyx</t>
+          <t>nc75327822</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-149.647</v>
+        <v>-122.787170410156</v>
       </c>
       <c r="C82" t="n">
-        <v>63.036</v>
+        <v>38.7934989929199</v>
       </c>
       <c r="D82" t="n">
-        <v>76.40000000000001</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="E82" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
+          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>52 km SW of Cantwell, Alaska</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3718,38 +3718,38 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46096.80405828704</v>
+        <v>46096.81298229167</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46096.80508491898</v>
+        <v>46096.86627753473</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>us6000sghd</t>
+          <t>us6000sghq</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>142.6105</v>
+        <v>49.7256</v>
       </c>
       <c r="C83" t="n">
-        <v>41.4045</v>
+        <v>32.4853</v>
       </c>
       <c r="D83" t="n">
-        <v>42.986</v>
+        <v>10</v>
       </c>
       <c r="E83" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
+          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>84 km SSW of Honchō, Japan</t>
+          <t>62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3758,38 +3758,38 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46096.78951814815</v>
+        <v>46096.8103829051</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46096.84466623842</v>
+        <v>46096.86111157407</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>aka2026fflqih</t>
+          <t>aka2026ffmjyx</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-150.765</v>
+        <v>-149.647</v>
       </c>
       <c r="C84" t="n">
-        <v>63.04</v>
+        <v>63.036</v>
       </c>
       <c r="D84" t="n">
-        <v>117.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E84" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
+          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>60 km N of Petersville, Alaska</t>
+          <t>52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3798,38 +3798,38 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46096.78820800926</v>
+        <v>46096.80405828704</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46096.79154229166</v>
+        <v>46096.80508491898</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>us6000sghb</t>
+          <t>us6000sghd</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>131.6063</v>
+        <v>142.6105</v>
       </c>
       <c r="C85" t="n">
-        <v>31.4194</v>
+        <v>41.4045</v>
       </c>
       <c r="D85" t="n">
-        <v>32.903</v>
+        <v>42.986</v>
       </c>
       <c r="E85" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
+          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>30 km SE of Nichinan, Japan</t>
+          <t>84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3838,38 +3838,38 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46096.77722483796</v>
+        <v>46096.78951814815</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46096.91079450231</v>
+        <v>46096.84466623842</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>us6000sgh9</t>
+          <t>aka2026fflqih</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-77.5782</v>
+        <v>-150.765</v>
       </c>
       <c r="C86" t="n">
-        <v>-1.3215</v>
+        <v>63.04</v>
       </c>
       <c r="D86" t="n">
-        <v>218.126</v>
+        <v>117.3</v>
       </c>
       <c r="E86" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
+          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>44 km SE of Tena, Ecuador</t>
+          <t>60 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3878,38 +3878,38 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46096.77198028936</v>
+        <v>46096.78820800926</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46096.78392407407</v>
+        <v>46096.79154229166</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>nc75327792</t>
+          <t>us6000sghb</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-122.471336364746</v>
+        <v>131.6063</v>
       </c>
       <c r="C87" t="n">
-        <v>37.5974998474121</v>
+        <v>31.4194</v>
       </c>
       <c r="D87" t="n">
-        <v>9.72999954223633</v>
+        <v>32.903</v>
       </c>
       <c r="E87" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
+          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2 km SE of Pacifica, CA</t>
+          <t>30 km SE of Nichinan, Japan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3918,38 +3918,38 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46096.77132291667</v>
+        <v>46096.77722483796</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46096.81413002315</v>
+        <v>46096.91079450231</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>aka2026ffklqv</t>
+          <t>us6000sgh9</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-155.854</v>
+        <v>-77.5782</v>
       </c>
       <c r="C88" t="n">
-        <v>57.153</v>
+        <v>-1.3215</v>
       </c>
       <c r="D88" t="n">
-        <v>63.2</v>
+        <v>218.126</v>
       </c>
       <c r="E88" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
+          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>96 km WSW of Karluk, Alaska</t>
+          <t>44 km SE of Tena, Ecuador</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3958,38 +3958,38 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46096.76349226852</v>
+        <v>46096.77198028936</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46096.76507798611</v>
+        <v>46096.78392407407</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nc75327787</t>
+          <t>nc75327792</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-123.346832275391</v>
+        <v>-122.471336364746</v>
       </c>
       <c r="C89" t="n">
-        <v>39.476001739502</v>
+        <v>37.5974998474121</v>
       </c>
       <c r="D89" t="n">
-        <v>4.19999980926514</v>
+        <v>9.72999954223633</v>
       </c>
       <c r="E89" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
+          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>5 km NE of Brooktrails, CA</t>
+          <t>2 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3998,38 +3998,38 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46096.7527207176</v>
+        <v>46096.77132291667</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46096.79673230324</v>
+        <v>46096.81413002315</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>aka2026ffjrwj</t>
+          <t>aka2026ffklqv</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-149.163</v>
+        <v>-155.854</v>
       </c>
       <c r="C90" t="n">
-        <v>62.869</v>
+        <v>57.153</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3</v>
+        <v>63.2</v>
       </c>
       <c r="E90" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
+          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>59 km S of Cantwell, Alaska</t>
+          <t>96 km WSW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4038,38 +4038,38 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46096.74754356482</v>
+        <v>46096.76349226852</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46096.7486603125</v>
+        <v>46096.76507798611</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>aka2026ffjpxp</t>
+          <t>nc75327787</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-152.555</v>
+        <v>-123.346832275391</v>
       </c>
       <c r="C91" t="n">
-        <v>59.7</v>
+        <v>39.476001739502</v>
       </c>
       <c r="D91" t="n">
-        <v>76.90000000000001</v>
+        <v>4.19999980926514</v>
       </c>
       <c r="E91" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
+          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>41 km WSW of Anchor Point, Alaska</t>
+          <t>5 km NE of Brooktrails, CA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4078,38 +4078,38 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46096.74597070602</v>
+        <v>46096.7527207176</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46096.74724846065</v>
+        <v>46096.79673230324</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>us6000sgh3</t>
+          <t>aka2026ffjrwj</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>128.5163</v>
+        <v>-149.163</v>
       </c>
       <c r="C92" t="n">
-        <v>-7.3925</v>
+        <v>62.869</v>
       </c>
       <c r="D92" t="n">
-        <v>137.104</v>
+        <v>0.3</v>
       </c>
       <c r="E92" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
+          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>208 km NE of Lospalos, Timor Leste</t>
+          <t>59 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4118,38 +4118,38 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46096.7350890625</v>
+        <v>46096.74754356482</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46096.81851898148</v>
+        <v>46096.7486603125</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ci41204623</t>
+          <t>aka2026ffjpxp</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-116.638166666667</v>
+        <v>-152.555</v>
       </c>
       <c r="C93" t="n">
-        <v>32.8055</v>
+        <v>59.7</v>
       </c>
       <c r="D93" t="n">
-        <v>16.68</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E93" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
+          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>10 km W of Pine Valley, CA</t>
+          <t>41 km WSW of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4158,38 +4158,38 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46096.72295416667</v>
+        <v>46096.74597070602</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46096.72542263889</v>
+        <v>46096.74724846065</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>aka2026ffhzps</t>
+          <t>us6000sgh3</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-146.822</v>
+        <v>128.5163</v>
       </c>
       <c r="C94" t="n">
-        <v>60.719</v>
+        <v>-7.3925</v>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
+        <v>137.104</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
+          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18 km SSW of Tatitlek, Alaska</t>
+          <t>208 km NE of Lospalos, Timor Leste</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4198,38 +4198,38 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46096.71188380787</v>
+        <v>46096.7350890625</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46096.71385545139</v>
+        <v>46096.81851898148</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tx2026ffhpux</t>
+          <t>ci41204623</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-103.799</v>
+        <v>-116.638166666667</v>
       </c>
       <c r="C95" t="n">
-        <v>31.021</v>
+        <v>32.8055</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>16.68</v>
       </c>
       <c r="E95" t="n">
-        <v>1.9</v>
+        <v>1.07</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
+          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>6 km NW of Balmorhea, Texas</t>
+          <t>10 km W of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4238,38 +4238,38 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46096.70398288195</v>
+        <v>46096.72295416667</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46096.71967913194</v>
+        <v>46096.72542263889</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>aka2026ffhkgu</t>
+          <t>aka2026ffhzps</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-154.974</v>
+        <v>-146.822</v>
       </c>
       <c r="C96" t="n">
-        <v>58.28</v>
+        <v>60.719</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3</v>
+        <v>19</v>
       </c>
       <c r="E96" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
+          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>84 km NNW of Karluk, Alaska</t>
+          <t>18 km SSW of Tatitlek, Alaska</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4278,38 +4278,38 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46096.6993729051</v>
+        <v>46096.71188380787</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46096.7007930787</v>
+        <v>46096.71385545139</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>nc75327772</t>
+          <t>tx2026ffhpux</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-122.78466796875</v>
+        <v>-103.799</v>
       </c>
       <c r="C97" t="n">
-        <v>38.7933349609375</v>
+        <v>31.021</v>
       </c>
       <c r="D97" t="n">
-        <v>3.51999998092651</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
+          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>6 km NW of Balmorhea, Texas</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4318,38 +4318,38 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46096.69837233796</v>
+        <v>46096.70398288195</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46096.72732706019</v>
+        <v>46096.71967913194</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>us6000sggw</t>
+          <t>aka2026ffhkgu</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>143.3074</v>
+        <v>-154.974</v>
       </c>
       <c r="C98" t="n">
-        <v>40.9048</v>
+        <v>58.28</v>
       </c>
       <c r="D98" t="n">
-        <v>37.859</v>
+        <v>0.3</v>
       </c>
       <c r="E98" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
+          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>139 km SSE of Honchō, Japan</t>
+          <t>84 km NNW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4358,38 +4358,38 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46096.68937086806</v>
+        <v>46096.6993729051</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46096.69961851852</v>
+        <v>46096.7007930787</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nc75327767</t>
+          <t>nc75327772</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-120.05883026123</v>
+        <v>-122.78466796875</v>
       </c>
       <c r="C99" t="n">
-        <v>35.7056655883789</v>
+        <v>38.7933349609375</v>
       </c>
       <c r="D99" t="n">
-        <v>7.76999998092651</v>
+        <v>3.51999998092651</v>
       </c>
       <c r="E99" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>M 2.2 - 22 km E of Cholame, CA</t>
+          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>22 km E of Cholame, CA</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4398,38 +4398,38 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46096.68914074074</v>
+        <v>46096.69837233796</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46096.71344819444</v>
+        <v>46096.72732706019</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>aka2026ffgrhi</t>
+          <t>us6000sggw</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-151.417</v>
+        <v>143.3074</v>
       </c>
       <c r="C100" t="n">
-        <v>63.08</v>
+        <v>40.9048</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>37.859</v>
       </c>
       <c r="E100" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
+          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>53 km SSE of Denali National Park, Alaska</t>
+          <t>139 km SSE of Honchō, Japan</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4438,38 +4438,38 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46096.68422761574</v>
+        <v>46096.68937086806</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46096.68548758102</v>
+        <v>46096.69961851852</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>nc75327742</t>
+          <t>nc75327767</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-121.291664123535</v>
+        <v>-120.05883026123</v>
       </c>
       <c r="C101" t="n">
-        <v>36.9063339233398</v>
+        <v>35.7056655883789</v>
       </c>
       <c r="D101" t="n">
-        <v>7.69000005722046</v>
+        <v>7.76999998092651</v>
       </c>
       <c r="E101" t="n">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>M 1.2 - 12 km NE of Hollister, CA</t>
+          <t>M 2.2 - 22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>12 km NE of Hollister, CA</t>
+          <t>22 km E of Cholame, CA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4478,38 +4478,38 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46096.65917303241</v>
+        <v>46096.68914074074</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46096.69960388889</v>
+        <v>46096.71344819444</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>nc75327737</t>
+          <t>aka2026ffgrhi</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-122.806663513184</v>
+        <v>-151.417</v>
       </c>
       <c r="C102" t="n">
-        <v>38.8235015869141</v>
+        <v>63.08</v>
       </c>
       <c r="D102" t="n">
-        <v>2.41000008583069</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
+          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>7 km NW of The Geysers, CA</t>
+          <t>53 km SSE of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4518,38 +4518,38 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46096.65873715278</v>
+        <v>46096.68422761574</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46096.67873339121</v>
+        <v>46096.68548758102</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>nn00912713</t>
+          <t>nc75327742</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-116.393</v>
+        <v>-121.291664123535</v>
       </c>
       <c r="C103" t="n">
-        <v>38.5366</v>
+        <v>36.9063339233398</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0315</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="E103" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
+          <t>M 1.2 - 12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>89 km NE of Tonopah, Nevada</t>
+          <t>12 km NE of Hollister, CA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4558,38 +4558,38 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46096.64812005787</v>
+        <v>46096.65917303241</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46096.64995700232</v>
+        <v>46096.69960388889</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nc75327727</t>
+          <t>nc75327737</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-122.743835449219</v>
+        <v>-122.806663513184</v>
       </c>
       <c r="C104" t="n">
-        <v>38.7863349914551</v>
+        <v>38.8235015869141</v>
       </c>
       <c r="D104" t="n">
-        <v>0.850000023841858</v>
+        <v>2.41000008583069</v>
       </c>
       <c r="E104" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
+          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1 km NE of The Geysers, CA</t>
+          <t>7 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4598,38 +4598,38 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46096.64470740741</v>
+        <v>46096.65873715278</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46096.68219443287</v>
+        <v>46096.67873339121</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ci41204591</t>
+          <t>nn00912713</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-115.8325</v>
+        <v>-116.393</v>
       </c>
       <c r="C105" t="n">
-        <v>31.8188333333333</v>
+        <v>38.5366</v>
       </c>
       <c r="D105" t="n">
-        <v>13.69</v>
+        <v>0.0315</v>
       </c>
       <c r="E105" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
+          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>70 km E of Maneadero, B.C., MX</t>
+          <t>89 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4638,38 +4638,38 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46096.62630196759</v>
+        <v>46096.64812005787</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46096.62875739583</v>
+        <v>46096.64995700232</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nc75327717</t>
+          <t>nc75327727</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-121.055168151855</v>
+        <v>-122.743835449219</v>
       </c>
       <c r="C106" t="n">
-        <v>36.451000213623</v>
+        <v>38.7863349914551</v>
       </c>
       <c r="D106" t="n">
-        <v>0.409999996423721</v>
+        <v>0.850000023841858</v>
       </c>
       <c r="E106" t="n">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
+          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>12 km SE of Pinnacles, CA</t>
+          <t>1 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4678,38 +4678,38 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46096.61927071759</v>
+        <v>46096.64470740741</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46096.64398418982</v>
+        <v>46096.68219443287</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tx2026ffdmwb</t>
+          <t>ci41204591</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-104.413</v>
+        <v>-115.8325</v>
       </c>
       <c r="C107" t="n">
-        <v>31.649</v>
+        <v>31.8188333333333</v>
       </c>
       <c r="D107" t="n">
-        <v>5.946</v>
+        <v>13.69</v>
       </c>
       <c r="E107" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>M 1.6 - 58 km S of Whites City, New Mexico</t>
+          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>70 km E of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4718,38 +4718,38 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46096.61776914352</v>
+        <v>46096.62630196759</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46097.20572792824</v>
+        <v>46096.62875739583</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>aka2026ffcpmw</t>
+          <t>nc75327717</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-152.825</v>
+        <v>-121.055168151855</v>
       </c>
       <c r="C108" t="n">
-        <v>59.058</v>
+        <v>36.451000213623</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
+          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>61 km WSW of Nanwalek, Alaska</t>
+          <t>12 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4758,38 +4758,38 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46096.59896729167</v>
+        <v>46096.61927071759</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46096.91903732639</v>
+        <v>46096.64398418982</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>us6000sggm</t>
+          <t>tx2026ffdmwb</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>130.0249</v>
+        <v>-104.413</v>
       </c>
       <c r="C109" t="n">
-        <v>-5.5263</v>
+        <v>31.649</v>
       </c>
       <c r="D109" t="n">
-        <v>184.533</v>
+        <v>5.946</v>
       </c>
       <c r="E109" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
+          <t>M 1.6 - 58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>271 km SSE of Amahai, Indonesia</t>
+          <t>58 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4798,38 +4798,38 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46096.59319422454</v>
+        <v>46096.61776914352</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46096.69633148148</v>
+        <v>46097.20572792824</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hv74917522</t>
+          <t>aka2026ffcpmw</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-155.374328613281</v>
+        <v>-152.825</v>
       </c>
       <c r="C110" t="n">
-        <v>19.1918334960938</v>
+        <v>59.058</v>
       </c>
       <c r="D110" t="n">
-        <v>31.7099990844727</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
+          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>11 km E of Pāhala, Hawaii</t>
+          <t>61 km WSW of Nanwalek, Alaska</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4838,38 +4838,38 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46096.59297361111</v>
+        <v>46096.59896729167</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46096.5954587963</v>
+        <v>46096.91903732639</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ci41204575</t>
+          <t>us6000sggm</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-116.426666666667</v>
+        <v>130.0249</v>
       </c>
       <c r="C111" t="n">
-        <v>33.9901666666667</v>
+        <v>-5.5263</v>
       </c>
       <c r="D111" t="n">
-        <v>2.17</v>
+        <v>184.533</v>
       </c>
       <c r="E111" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>271 km SSE of Amahai, Indonesia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4878,38 +4878,38 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46096.58429085648</v>
+        <v>46096.59319422454</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46096.69570008102</v>
+        <v>46096.69633148148</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ci41204567</t>
+          <t>hv74917522</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-116.426666666667</v>
+        <v>-155.374328613281</v>
       </c>
       <c r="C112" t="n">
-        <v>33.9915</v>
+        <v>19.1918334960938</v>
       </c>
       <c r="D112" t="n">
-        <v>2.18</v>
+        <v>31.7099990844727</v>
       </c>
       <c r="E112" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>11 km E of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4918,38 +4918,38 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46096.57788611111</v>
+        <v>46096.59297361111</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46096.58546979167</v>
+        <v>46096.5954587963</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>nn00912712</t>
+          <t>ci41204575</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-116.4988</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C113" t="n">
-        <v>38.4756</v>
+        <v>33.9901666666667</v>
       </c>
       <c r="D113" t="n">
-        <v>0.0689</v>
+        <v>2.17</v>
       </c>
       <c r="E113" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
+          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>78 km NE of Tonopah, Nevada</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4958,38 +4958,38 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46096.57585082176</v>
+        <v>46096.58429085648</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46096.57864184028</v>
+        <v>46096.69570008102</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ci41204559</t>
+          <t>ci41204567</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-118.1145</v>
+        <v>-116.426666666667</v>
       </c>
       <c r="C114" t="n">
-        <v>34.0995</v>
+        <v>33.9915</v>
       </c>
       <c r="D114" t="n">
-        <v>8.91</v>
+        <v>2.18</v>
       </c>
       <c r="E114" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
+          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1 km WNW of San Gabriel, CA</t>
+          <t>8 km ENE of Desert Hot Springs, CA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4998,38 +4998,38 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46096.5639962963</v>
+        <v>46096.57788611111</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46096.56638376157</v>
+        <v>46096.58546979167</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>aka2026ffaxsl</t>
+          <t>nn00912712</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-153.59</v>
+        <v>-116.4988</v>
       </c>
       <c r="C115" t="n">
-        <v>59.151</v>
+        <v>38.4756</v>
       </c>
       <c r="D115" t="n">
-        <v>102.5</v>
+        <v>0.0689</v>
       </c>
       <c r="E115" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>78 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5038,38 +5038,38 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46096.56368013889</v>
+        <v>46096.57585082176</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46096.564885625</v>
+        <v>46096.57864184028</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>aka2026ffanxh</t>
+          <t>ci41204559</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-149.871</v>
+        <v>-118.1145</v>
       </c>
       <c r="C116" t="n">
-        <v>61.849</v>
+        <v>34.0995</v>
       </c>
       <c r="D116" t="n">
-        <v>28.4</v>
+        <v>8.91</v>
       </c>
       <c r="E116" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
+          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>14 km NE of Willow, Alaska</t>
+          <t>1 km WNW of San Gabriel, CA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5078,38 +5078,38 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46096.55577541667</v>
+        <v>46096.5639962963</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46096.55684119213</v>
+        <v>46096.56638376157</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>tx2026ffanng</t>
+          <t>aka2026ffaxsl</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-101.924</v>
+        <v>-153.59</v>
       </c>
       <c r="C117" t="n">
-        <v>32.101</v>
+        <v>59.151</v>
       </c>
       <c r="D117" t="n">
-        <v>3.9912</v>
+        <v>102.5</v>
       </c>
       <c r="E117" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
+          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5118,38 +5118,38 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46096.55563410879</v>
+        <v>46096.56368013889</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46096.97107067129</v>
+        <v>46096.564885625</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>nn00912708</t>
+          <t>aka2026ffanxh</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-116.4027</v>
+        <v>-149.871</v>
       </c>
       <c r="C118" t="n">
-        <v>37.3392</v>
+        <v>61.849</v>
       </c>
       <c r="D118" t="n">
-        <v>13.9737</v>
+        <v>28.4</v>
       </c>
       <c r="E118" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
+          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>57 km NNE of Beatty, Nevada</t>
+          <t>14 km NE of Willow, Alaska</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5158,38 +5158,38 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46096.55248135416</v>
+        <v>46096.55577541667</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46096.55406869213</v>
+        <v>46096.55684119213</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>nn00912710</t>
+          <t>tx2026ffanng</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-117.9202</v>
+        <v>-101.924</v>
       </c>
       <c r="C119" t="n">
-        <v>38.5488</v>
+        <v>32.101</v>
       </c>
       <c r="D119" t="n">
-        <v>11.6085</v>
+        <v>3.9912</v>
       </c>
       <c r="E119" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
+          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>24 km NE of Mina, Nevada</t>
+          <t>13 km WSW of Stanton, Texas</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5198,38 +5198,38 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46096.55246195602</v>
+        <v>46096.55563410879</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46096.55466255787</v>
+        <v>46096.97107067129</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>aka2026ffagux</t>
+          <t>nn00912708</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-149.012</v>
+        <v>-116.4027</v>
       </c>
       <c r="C120" t="n">
-        <v>62.698</v>
+        <v>37.3392</v>
       </c>
       <c r="D120" t="n">
-        <v>62.2</v>
+        <v>13.9737</v>
       </c>
       <c r="E120" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
+          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>62 km ENE of Chase, Alaska</t>
+          <t>57 km NNE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5238,38 +5238,38 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46096.55006834491</v>
+        <v>46096.55248135416</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46096.5511231713</v>
+        <v>46096.55406869213</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>aka2026ffacwz</t>
+          <t>nn00912710</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-154.211</v>
+        <v>-117.9202</v>
       </c>
       <c r="C121" t="n">
-        <v>58.934</v>
+        <v>38.5488</v>
       </c>
       <c r="D121" t="n">
-        <v>126.4</v>
+        <v>11.6085</v>
       </c>
       <c r="E121" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
+          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>64 km SSE of Kokhanok, Alaska</t>
+          <t>24 km NE of Mina, Nevada</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5278,38 +5278,38 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46096.54689578704</v>
+        <v>46096.55246195602</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46096.54852043981</v>
+        <v>46096.55466255787</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>uw62235651</t>
+          <t>aka2026ffagux</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-124.0351666666667</v>
+        <v>-149.012</v>
       </c>
       <c r="C122" t="n">
-        <v>47.33166666666666</v>
+        <v>62.698</v>
       </c>
       <c r="D122" t="n">
-        <v>23.98</v>
+        <v>62.2</v>
       </c>
       <c r="E122" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
+          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>12 km NNW of Humptulips, Washington</t>
+          <t>62 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5318,38 +5318,38 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46096.54669189815</v>
+        <v>46096.55006834491</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46096.58038923611</v>
+        <v>46096.5511231713</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>nc75327692</t>
+          <t>aka2026ffacwz</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-122.779335021973</v>
+        <v>-154.211</v>
       </c>
       <c r="C123" t="n">
-        <v>38.8115005493164</v>
+        <v>58.934</v>
       </c>
       <c r="D123" t="n">
-        <v>0.550000011920929</v>
+        <v>126.4</v>
       </c>
       <c r="E123" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
+          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>4 km NNW of The Geysers, CA</t>
+          <t>64 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5358,38 +5358,38 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46096.54474907408</v>
+        <v>46096.54689578704</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46096.5710708449</v>
+        <v>46096.54852043981</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>us6000sgg9</t>
+          <t>uw62235651</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-77.3565</v>
+        <v>-124.0351666666667</v>
       </c>
       <c r="C124" t="n">
-        <v>-45.6923</v>
+        <v>47.33166666666666</v>
       </c>
       <c r="D124" t="n">
-        <v>10</v>
+        <v>23.98</v>
       </c>
       <c r="E124" t="n">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>M 4.6 - Off the coast of Aisen, Chile</t>
+          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>12 km NNW of Humptulips, Washington</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5398,38 +5398,38 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46096.53758378472</v>
+        <v>46096.54669189815</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46096.58026666666</v>
+        <v>46096.58038923611</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>us6000sgg8</t>
+          <t>nc75327692</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-77.3313</v>
+        <v>-122.779335021973</v>
       </c>
       <c r="C125" t="n">
-        <v>-45.741</v>
+        <v>38.8115005493164</v>
       </c>
       <c r="D125" t="n">
-        <v>10</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="E125" t="n">
-        <v>4.4</v>
+        <v>1.08</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>4 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5438,38 +5438,38 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46096.53580871528</v>
+        <v>46096.54474907408</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46096.59747731481</v>
+        <v>46096.5710708449</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>aka2026fezlzd</t>
+          <t>us6000sgg9</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-150.155</v>
+        <v>-77.3565</v>
       </c>
       <c r="C126" t="n">
-        <v>61.309</v>
+        <v>-45.6923</v>
       </c>
       <c r="D126" t="n">
-        <v>35.8</v>
+        <v>10</v>
       </c>
       <c r="E126" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
+          <t>M 4.6 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>11 km WSW of Point MacKenzie, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5478,38 +5478,38 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46096.53327611111</v>
+        <v>46096.53758378472</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46096.53437532407</v>
+        <v>46096.58026666666</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>aka2026feywwv</t>
+          <t>us6000sgg8</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-148.811</v>
+        <v>-77.3313</v>
       </c>
       <c r="C127" t="n">
-        <v>63.988</v>
+        <v>-45.741</v>
       </c>
       <c r="D127" t="n">
-        <v>113.5</v>
+        <v>10</v>
       </c>
       <c r="E127" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
+          <t>M 4.4 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>15 km ESE of Ferry, Alaska</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5518,38 +5518,38 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46096.52110533565</v>
+        <v>46096.53580871528</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46096.52266071759</v>
+        <v>46096.59747731481</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>us6000sgg7</t>
+          <t>aka2026fezlzd</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-72.47499999999999</v>
+        <v>-150.155</v>
       </c>
       <c r="C128" t="n">
-        <v>41.5071</v>
+        <v>61.309</v>
       </c>
       <c r="D128" t="n">
-        <v>6.072</v>
+        <v>35.8</v>
       </c>
       <c r="E128" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
+          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2 km WNW of Moodus, Connecticut</t>
+          <t>11 km WSW of Point MacKenzie, Alaska</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5558,38 +5558,38 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46096.51831680556</v>
+        <v>46096.53327611111</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46097.0635559375</v>
+        <v>46096.53437532407</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>aka2026feypws</t>
+          <t>aka2026feywwv</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-151.884</v>
+        <v>-148.811</v>
       </c>
       <c r="C129" t="n">
-        <v>61.213</v>
+        <v>63.988</v>
       </c>
       <c r="D129" t="n">
-        <v>92</v>
+        <v>113.5</v>
       </c>
       <c r="E129" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
+          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>43 km WNW of Tyonek, Alaska</t>
+          <t>15 km ESE of Ferry, Alaska</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5598,38 +5598,38 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46096.51546960648</v>
+        <v>46096.52110533565</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46096.51679775463</v>
+        <v>46096.52266071759</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>hv74917517</t>
+          <t>us6000sgg7</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-155.388671875</v>
+        <v>-72.47499999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>19.2761669158936</v>
+        <v>41.5071</v>
       </c>
       <c r="D130" t="n">
-        <v>29.1200008392334</v>
+        <v>6.072</v>
       </c>
       <c r="E130" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
+          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>12 km NE of Pāhala, Hawaii</t>
+          <t>2 km WNW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5638,38 +5638,38 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46096.51510231481</v>
+        <v>46096.51831680556</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46096.51755763889</v>
+        <v>46097.0635559375</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>us6000sgg3</t>
+          <t>aka2026feypws</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-72.49160000000001</v>
+        <v>-151.884</v>
       </c>
       <c r="C131" t="n">
-        <v>41.4904</v>
+        <v>61.213</v>
       </c>
       <c r="D131" t="n">
-        <v>6.63</v>
+        <v>92</v>
       </c>
       <c r="E131" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
+          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>3 km WSW of Moodus, Connecticut</t>
+          <t>43 km WNW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5678,38 +5678,38 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46096.51474966435</v>
+        <v>46096.51546960648</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46097.21278487269</v>
+        <v>46096.51679775463</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>us6000sgg2</t>
+          <t>hv74917517</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>155.7691</v>
+        <v>-155.388671875</v>
       </c>
       <c r="C132" t="n">
-        <v>50.1375</v>
+        <v>19.2761669158936</v>
       </c>
       <c r="D132" t="n">
-        <v>93.238</v>
+        <v>29.1200008392334</v>
       </c>
       <c r="E132" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>12 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5718,38 +5718,38 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46096.50655835648</v>
+        <v>46096.51510231481</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46096.52194490741</v>
+        <v>46096.51755763889</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>aka2026feycns</t>
+          <t>us6000sgg3</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-148.959</v>
+        <v>-72.49160000000001</v>
       </c>
       <c r="C133" t="n">
-        <v>63.283</v>
+        <v>41.4904</v>
       </c>
       <c r="D133" t="n">
-        <v>0.6</v>
+        <v>6.63</v>
       </c>
       <c r="E133" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
+          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>12 km S of Cantwell, Alaska</t>
+          <t>3 km WSW of Moodus, Connecticut</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5758,38 +5758,38 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46096.50470625</v>
+        <v>46096.51474966435</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46096.50576539352</v>
+        <v>46097.21278487269</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ci41204535</t>
+          <t>us6000sgg2</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-119.474833333333</v>
+        <v>155.7691</v>
       </c>
       <c r="C134" t="n">
-        <v>34.3685</v>
+        <v>50.1375</v>
       </c>
       <c r="D134" t="n">
-        <v>0.54</v>
+        <v>93.238</v>
       </c>
       <c r="E134" t="n">
-        <v>1.49</v>
+        <v>4.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
+          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>5 km SE of Carpinteria, CA</t>
+          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5798,38 +5798,38 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46096.49835740741</v>
+        <v>46096.50655835648</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46096.50080350695</v>
+        <v>46096.52194490741</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>aka2026fewzkc</t>
+          <t>aka2026feycns</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-148.795</v>
+        <v>-148.959</v>
       </c>
       <c r="C135" t="n">
-        <v>62.2</v>
+        <v>63.283</v>
       </c>
       <c r="D135" t="n">
-        <v>22.1</v>
+        <v>0.6</v>
       </c>
       <c r="E135" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
+          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>47 km N of Sutton-Alpine, Alaska</t>
+          <t>12 km S of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5838,38 +5838,38 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46096.48122515046</v>
+        <v>46096.50470625</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46096.48264917824</v>
+        <v>46096.50576539352</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>us6000sgfx</t>
+          <t>ci41204535</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-80.1019</v>
+        <v>-119.474833333333</v>
       </c>
       <c r="C136" t="n">
-        <v>0.5871</v>
+        <v>34.3685</v>
       </c>
       <c r="D136" t="n">
-        <v>36.381</v>
+        <v>0.54</v>
       </c>
       <c r="E136" t="n">
-        <v>4.4</v>
+        <v>1.49</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
+          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>9 km WSW of Muisne, Ecuador</t>
+          <t>5 km SE of Carpinteria, CA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5878,38 +5878,38 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46096.47494160879</v>
+        <v>46096.49835740741</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46096.4911</v>
+        <v>46096.50080350695</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>pr71509923</t>
+          <t>aka2026fewzkc</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-66.1071666666667</v>
+        <v>-148.795</v>
       </c>
       <c r="C137" t="n">
-        <v>18.1251666666667</v>
+        <v>62.2</v>
       </c>
       <c r="D137" t="n">
-        <v>24.58</v>
+        <v>22.1</v>
       </c>
       <c r="E137" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>47 km N of Sutton-Alpine, Alaska</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5918,38 +5918,38 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46096.47251458334</v>
+        <v>46096.48122515046</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46096.60321875</v>
+        <v>46096.48264917824</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ci41204519</t>
+          <t>us6000sgfx</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-118.627833333333</v>
+        <v>-80.1019</v>
       </c>
       <c r="C138" t="n">
-        <v>34.6043333333333</v>
+        <v>0.5871</v>
       </c>
       <c r="D138" t="n">
-        <v>10.64</v>
+        <v>36.381</v>
       </c>
       <c r="E138" t="n">
-        <v>1.13</v>
+        <v>4.4</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>M 1.1 - 13 km N of Castaic, CA</t>
+          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>13 km N of Castaic, CA</t>
+          <t>9 km WSW of Muisne, Ecuador</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5958,38 +5958,38 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46096.46653668981</v>
+        <v>46096.47494160879</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46096.46890145833</v>
+        <v>46096.4911</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>nn00912706</t>
+          <t>pr71509923</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-119.5178</v>
+        <v>-66.1071666666667</v>
       </c>
       <c r="C139" t="n">
-        <v>38.4812</v>
+        <v>18.1251666666667</v>
       </c>
       <c r="D139" t="n">
-        <v>3.3162</v>
+        <v>24.58</v>
       </c>
       <c r="E139" t="n">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km SW of Walker, California</t>
+          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>5 km SW of Walker, California</t>
+          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5998,38 +5998,38 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46096.46134278935</v>
+        <v>46096.47251458334</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46096.46294350694</v>
+        <v>46096.60321875</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>nc75327672</t>
+          <t>ci41204519</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-122.810333251953</v>
+        <v>-118.627833333333</v>
       </c>
       <c r="C140" t="n">
-        <v>38.8395004272461</v>
+        <v>34.6043333333333</v>
       </c>
       <c r="D140" t="n">
-        <v>1.83000004291534</v>
+        <v>10.64</v>
       </c>
       <c r="E140" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
+          <t>M 1.1 - 13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8 km WNW of Cobb, CA</t>
+          <t>13 km N of Castaic, CA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6038,38 +6038,38 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46096.46108472222</v>
+        <v>46096.46653668981</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46096.49469679398</v>
+        <v>46096.46890145833</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>pr71509913</t>
+          <t>nn00912706</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-67.0566666666667</v>
+        <v>-119.5178</v>
       </c>
       <c r="C141" t="n">
-        <v>18.1476666666667</v>
+        <v>38.4812</v>
       </c>
       <c r="D141" t="n">
-        <v>17.11</v>
+        <v>3.3162</v>
       </c>
       <c r="E141" t="n">
-        <v>2.37</v>
+        <v>1.26</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>M 1.3 - 5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>5 km SW of Walker, California</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6078,38 +6078,38 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46096.44030868055</v>
+        <v>46096.46134278935</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46096.59237719907</v>
+        <v>46096.46294350694</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>aka2026feukwz</t>
+          <t>nc75327672</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-147.764</v>
+        <v>-122.810333251953</v>
       </c>
       <c r="C142" t="n">
-        <v>60.385</v>
+        <v>38.8395004272461</v>
       </c>
       <c r="D142" t="n">
-        <v>14.9</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="E142" t="n">
-        <v>1.7</v>
+        <v>0.97</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
+          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>38 km NNE of Chenega, Alaska</t>
+          <t>8 km WNW of Cobb, CA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6118,38 +6118,38 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46096.42763064815</v>
+        <v>46096.46108472222</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46096.4286147338</v>
+        <v>46096.49469679398</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>aka2026fetqyo</t>
+          <t>pr71509913</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-150.43</v>
+        <v>-67.0566666666667</v>
       </c>
       <c r="C143" t="n">
-        <v>60.896</v>
+        <v>18.1476666666667</v>
       </c>
       <c r="D143" t="n">
-        <v>45.5</v>
+        <v>17.11</v>
       </c>
       <c r="E143" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
+          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>14 km ESE of Point Possession, Alaska</t>
+          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6158,38 +6158,38 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46096.41156589121</v>
+        <v>46096.44030868055</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46096.41261650463</v>
+        <v>46096.59237719907</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ci41204503</t>
+          <t>aka2026feukwz</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-117.464333333333</v>
+        <v>-147.764</v>
       </c>
       <c r="C144" t="n">
-        <v>34.157</v>
+        <v>60.385</v>
       </c>
       <c r="D144" t="n">
-        <v>6.87</v>
+        <v>14.9</v>
       </c>
       <c r="E144" t="n">
-        <v>0.98</v>
+        <v>1.7</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>M 1.0 - 7 km N of Fontana, CA</t>
+          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>7 km N of Fontana, CA</t>
+          <t>38 km NNE of Chenega, Alaska</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6198,38 +6198,38 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46096.39763148148</v>
+        <v>46096.42763064815</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46096.39998002315</v>
+        <v>46096.4286147338</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>aka2026fessqh</t>
+          <t>aka2026fetqyo</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-152.317</v>
+        <v>-150.43</v>
       </c>
       <c r="C145" t="n">
-        <v>60.36</v>
+        <v>60.896</v>
       </c>
       <c r="D145" t="n">
-        <v>90.3</v>
+        <v>45.5</v>
       </c>
       <c r="E145" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
+          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>49 km NW of Ninilchik, Alaska</t>
+          <t>14 km ESE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6238,38 +6238,38 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46096.39196349537</v>
+        <v>46096.41156589121</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46096.39365355324</v>
+        <v>46096.41261650463</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>nc75327657</t>
+          <t>ci41204503</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-122.805335998535</v>
+        <v>-117.464333333333</v>
       </c>
       <c r="C146" t="n">
-        <v>38.8190002441406</v>
+        <v>34.157</v>
       </c>
       <c r="D146" t="n">
-        <v>2.17000007629395</v>
+        <v>6.87</v>
       </c>
       <c r="E146" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
+          <t>M 1.0 - 7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>7 km N of Fontana, CA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6278,38 +6278,38 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46096.37721527777</v>
+        <v>46096.39763148148</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46096.42173711806</v>
+        <v>46096.39998002315</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>aka2026fertpz</t>
+          <t>aka2026fessqh</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-157.698</v>
+        <v>-152.317</v>
       </c>
       <c r="C147" t="n">
-        <v>55.194</v>
+        <v>60.36</v>
       </c>
       <c r="D147" t="n">
-        <v>4.2</v>
+        <v>90.3</v>
       </c>
       <c r="E147" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
+          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>121 km SE of Perryville, Alaska</t>
+          <t>49 km NW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6318,38 +6318,38 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>46096.37321436343</v>
+        <v>46096.39196349537</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46096.37804444444</v>
+        <v>46096.39365355324</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>uw62235646</t>
+          <t>nc75327657</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-121.9746666666667</v>
+        <v>-122.805335998535</v>
       </c>
       <c r="C148" t="n">
-        <v>47.82666666666667</v>
+        <v>38.8190002441406</v>
       </c>
       <c r="D148" t="n">
-        <v>26.62</v>
+        <v>2.17000007629395</v>
       </c>
       <c r="E148" t="n">
-        <v>1.96</v>
+        <v>1.1</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km S of Monroe, Washington</t>
+          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>3 km S of Monroe, Washington</t>
+          <t>6 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6358,38 +6358,38 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>46096.36272453704</v>
+        <v>46096.37721527777</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46096.47082604167</v>
+        <v>46096.42173711806</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>us6000sgfk</t>
+          <t>aka2026fertpz</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-77.27330000000001</v>
+        <v>-157.698</v>
       </c>
       <c r="C149" t="n">
-        <v>-45.5694</v>
+        <v>55.194</v>
       </c>
       <c r="D149" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="E149" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>M 5.3 - Off the coast of Aisen, Chile</t>
+          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>121 km SE of Perryville, Alaska</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6398,38 +6398,38 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>46096.35320680556</v>
+        <v>46096.37321436343</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46096.38260266204</v>
+        <v>46096.37804444444</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>us6000sgfh</t>
+          <t>uw62235646</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>122.0755</v>
+        <v>-121.9746666666667</v>
       </c>
       <c r="C150" t="n">
-        <v>24.3607</v>
+        <v>47.82666666666667</v>
       </c>
       <c r="D150" t="n">
-        <v>27.716</v>
+        <v>26.62</v>
       </c>
       <c r="E150" t="n">
-        <v>4.8</v>
+        <v>1.96</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
+          <t>M 2.0 - 3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>54 km SE of Yilan, Taiwan</t>
+          <t>3 km S of Monroe, Washington</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6438,38 +6438,38 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>46096.34370333333</v>
+        <v>46096.36272453704</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46096.53583686343</v>
+        <v>46096.47082604167</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>nn00912705</t>
+          <t>us6000sgfk</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-116.5611</v>
+        <v>-77.27330000000001</v>
       </c>
       <c r="C151" t="n">
-        <v>38.4412</v>
+        <v>-45.5694</v>
       </c>
       <c r="D151" t="n">
-        <v>3.8472</v>
+        <v>10</v>
       </c>
       <c r="E151" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
+          <t>M 5.3 - Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>71 km NE of Tonopah, Nevada</t>
+          <t>Off the coast of Aisen, Chile</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6478,38 +6478,38 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>46096.34194375</v>
+        <v>46096.35320680556</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46096.34380362269</v>
+        <v>46096.38260266204</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ci41204487</t>
+          <t>us6000sgfh</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-116.419666666667</v>
+        <v>122.0755</v>
       </c>
       <c r="C152" t="n">
-        <v>32.9405</v>
+        <v>24.3607</v>
       </c>
       <c r="D152" t="n">
-        <v>4.88</v>
+        <v>27.716</v>
       </c>
       <c r="E152" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
+          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>17 km NE of Pine Valley, CA</t>
+          <t>54 km SE of Yilan, Taiwan</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6518,38 +6518,38 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>46096.32685023148</v>
+        <v>46096.34370333333</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46096.32921789352</v>
+        <v>46096.53583686343</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ci41204479</t>
+          <t>nn00912705</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-117.2475</v>
+        <v>-116.5611</v>
       </c>
       <c r="C153" t="n">
-        <v>34.0556666666667</v>
+        <v>38.4412</v>
       </c>
       <c r="D153" t="n">
-        <v>15.21</v>
+        <v>3.8472</v>
       </c>
       <c r="E153" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
+          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2 km ENE of Loma Linda, CA</t>
+          <t>71 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6558,38 +6558,38 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>46096.32684571759</v>
+        <v>46096.34194375</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46096.32920631945</v>
+        <v>46096.34380362269</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>aka2026fephrq</t>
+          <t>ci41204487</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-150.634</v>
+        <v>-116.419666666667</v>
       </c>
       <c r="C154" t="n">
-        <v>60.036</v>
+        <v>32.9405</v>
       </c>
       <c r="D154" t="n">
-        <v>63.6</v>
+        <v>4.88</v>
       </c>
       <c r="E154" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
+          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>26 km NE of Fox River, Alaska</t>
+          <t>17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6598,38 +6598,38 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>46096.32028525463</v>
+        <v>46096.32685023148</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46096.32365</v>
+        <v>46096.32921789352</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>nn00912702</t>
+          <t>ci41204479</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-116.579</v>
+        <v>-117.2475</v>
       </c>
       <c r="C155" t="n">
-        <v>38.4398</v>
+        <v>34.0556666666667</v>
       </c>
       <c r="D155" t="n">
-        <v>3.5596</v>
+        <v>15.21</v>
       </c>
       <c r="E155" t="n">
-        <v>2.08</v>
+        <v>1.09</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>2 km ENE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6638,38 +6638,38 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>46096.30809262732</v>
+        <v>46096.32684571759</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46096.31003199074</v>
+        <v>46096.32920631945</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>nc75327637</t>
+          <t>aka2026fephrq</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-121.911003112793</v>
+        <v>-150.634</v>
       </c>
       <c r="C156" t="n">
-        <v>38.0525016784668</v>
+        <v>60.036</v>
       </c>
       <c r="D156" t="n">
-        <v>17.0200004577637</v>
+        <v>63.6</v>
       </c>
       <c r="E156" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
+          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>4 km NW of Pittsburg, CA</t>
+          <t>26 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6678,38 +6678,38 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>46096.29875555556</v>
+        <v>46096.32028525463</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46096.34190163195</v>
+        <v>46096.32365</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>us6000sgf9</t>
+          <t>nn00912702</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>72.05249999999999</v>
+        <v>-116.579</v>
       </c>
       <c r="C157" t="n">
-        <v>37.629</v>
+        <v>38.4398</v>
       </c>
       <c r="D157" t="n">
-        <v>196.241</v>
+        <v>3.5596</v>
       </c>
       <c r="E157" t="n">
-        <v>4.1</v>
+        <v>2.08</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
+          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>46 km ENE of Khorugh, Tajikistan</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6718,38 +6718,38 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>46096.29624704861</v>
+        <v>46096.30809262732</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46096.31303287037</v>
+        <v>46096.31003199074</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>aka2026fenxtb</t>
+          <t>nc75327637</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-154.253</v>
+        <v>-121.911003112793</v>
       </c>
       <c r="C158" t="n">
-        <v>58.558</v>
+        <v>38.0525016784668</v>
       </c>
       <c r="D158" t="n">
-        <v>5</v>
+        <v>17.0200004577637</v>
       </c>
       <c r="E158" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
+          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>96 km NW of Aleneva, Alaska</t>
+          <t>4 km NW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6758,38 +6758,38 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>46096.29131623843</v>
+        <v>46096.29875555556</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46096.29275974537</v>
+        <v>46096.34190163195</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>nc75327632</t>
+          <t>us6000sgf9</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-121.910331726074</v>
+        <v>72.05249999999999</v>
       </c>
       <c r="C159" t="n">
-        <v>38.0643348693848</v>
+        <v>37.629</v>
       </c>
       <c r="D159" t="n">
-        <v>18.6900005340576</v>
+        <v>196.241</v>
       </c>
       <c r="E159" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
+          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>5 km NNW of Pittsburg, CA</t>
+          <t>46 km ENE of Khorugh, Tajikistan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6798,38 +6798,38 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>46096.28527893518</v>
+        <v>46096.29624704861</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46096.32459672454</v>
+        <v>46096.31303287037</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tx2026fenmna</t>
+          <t>aka2026fenxtb</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-104.203</v>
+        <v>-154.253</v>
       </c>
       <c r="C160" t="n">
-        <v>31.669</v>
+        <v>58.558</v>
       </c>
       <c r="D160" t="n">
-        <v>7.2278</v>
+        <v>5</v>
       </c>
       <c r="E160" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
+          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>96 km NW of Aleneva, Alaska</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6838,38 +6838,38 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>46096.28226224537</v>
+        <v>46096.29131623843</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46096.83936486111</v>
+        <v>46096.29275974537</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tx2026fenktd</t>
+          <t>nc75327632</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-104.202</v>
+        <v>-121.910331726074</v>
       </c>
       <c r="C161" t="n">
-        <v>31.669</v>
+        <v>38.0643348693848</v>
       </c>
       <c r="D161" t="n">
-        <v>7.5739</v>
+        <v>18.6900005340576</v>
       </c>
       <c r="E161" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
+          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>5 km NNW of Pittsburg, CA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6878,38 +6878,38 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>46096.28124563657</v>
+        <v>46096.28527893518</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46096.70278489583</v>
+        <v>46096.32459672454</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ci41204455</t>
+          <t>tx2026fenmna</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-116.806333333333</v>
+        <v>-104.203</v>
       </c>
       <c r="C162" t="n">
-        <v>33.2463333333333</v>
+        <v>31.669</v>
       </c>
       <c r="D162" t="n">
-        <v>10.1</v>
+        <v>7.2278</v>
       </c>
       <c r="E162" t="n">
-        <v>0.95</v>
+        <v>1.9</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
+          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>4 km W of Lake Henshaw, CA</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6918,38 +6918,38 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>46096.27805949074</v>
+        <v>46096.28226224537</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46096.28047209491</v>
+        <v>46096.83936486111</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>nn00912698</t>
+          <t>tx2026fenktd</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-116.6054</v>
+        <v>-104.202</v>
       </c>
       <c r="C163" t="n">
-        <v>38.2724</v>
+        <v>31.669</v>
       </c>
       <c r="D163" t="n">
-        <v>5.7486</v>
+        <v>7.5739</v>
       </c>
       <c r="E163" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
+          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>59 km ENE of Tonopah, Nevada</t>
+          <t>55 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6958,38 +6958,38 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>46096.26913202546</v>
+        <v>46096.28124563657</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46096.27123583333</v>
+        <v>46096.70278489583</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nn00912696</t>
+          <t>ci41204455</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-116.3473</v>
+        <v>-116.806333333333</v>
       </c>
       <c r="C164" t="n">
-        <v>37.5427</v>
+        <v>33.2463333333333</v>
       </c>
       <c r="D164" t="n">
-        <v>15.7841</v>
+        <v>10.1</v>
       </c>
       <c r="E164" t="n">
-        <v>1.48</v>
+        <v>0.95</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>4 km W of Lake Henshaw, CA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6998,38 +6998,38 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>46096.26722096065</v>
+        <v>46096.27805949074</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46096.26890163194</v>
+        <v>46096.28047209491</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>pr71509903</t>
+          <t>nn00912698</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-66.7433333333333</v>
+        <v>-116.6054</v>
       </c>
       <c r="C165" t="n">
-        <v>18.043</v>
+        <v>38.2724</v>
       </c>
       <c r="D165" t="n">
-        <v>16.94</v>
+        <v>5.7486</v>
       </c>
       <c r="E165" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>59 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7038,38 +7038,38 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>46096.26509143518</v>
+        <v>46096.26913202546</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46096.27459479167</v>
+        <v>46096.27123583333</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>nn00912694</t>
+          <t>nn00912696</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-116.5678</v>
+        <v>-116.3473</v>
       </c>
       <c r="C166" t="n">
-        <v>38.4757</v>
+        <v>37.5427</v>
       </c>
       <c r="D166" t="n">
-        <v>5.2112</v>
+        <v>15.7841</v>
       </c>
       <c r="E166" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
+          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>73 km NE of Tonopah, Nevada</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7078,38 +7078,38 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>46096.26149202546</v>
+        <v>46096.26722096065</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46096.26338644676</v>
+        <v>46096.26890163194</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>aka2026femdbx</t>
+          <t>pr71509903</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-154.971</v>
+        <v>-66.7433333333333</v>
       </c>
       <c r="C167" t="n">
-        <v>57.961</v>
+        <v>18.043</v>
       </c>
       <c r="D167" t="n">
-        <v>86.59999999999999</v>
+        <v>16.94</v>
       </c>
       <c r="E167" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
+          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>53 km NW of Karluk, Alaska</t>
+          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7118,38 +7118,38 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>46096.25371178241</v>
+        <v>46096.26509143518</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46096.2741787037</v>
+        <v>46096.27459479167</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>nn00912691</t>
+          <t>nn00912694</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-116.5734</v>
+        <v>-116.5678</v>
       </c>
       <c r="C168" t="n">
-        <v>38.4423</v>
+        <v>38.4757</v>
       </c>
       <c r="D168" t="n">
-        <v>1.9073</v>
+        <v>5.2112</v>
       </c>
       <c r="E168" t="n">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7158,38 +7158,38 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>46096.25128945602</v>
+        <v>46096.26149202546</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46096.25308243056</v>
+        <v>46096.26338644676</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ci41204447</t>
+          <t>aka2026femdbx</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-116.168333333333</v>
+        <v>-154.971</v>
       </c>
       <c r="C169" t="n">
-        <v>33.8886666666667</v>
+        <v>57.961</v>
       </c>
       <c r="D169" t="n">
-        <v>5.52</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E169" t="n">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>M 1.3 - 19 km NNE of Indio, CA</t>
+          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>19 km NNE of Indio, CA</t>
+          <t>53 km NW of Karluk, Alaska</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7198,38 +7198,38 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>46096.24517546297</v>
+        <v>46096.25371178241</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46096.25266435185</v>
+        <v>46096.2741787037</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>nc75327597</t>
+          <t>nn00912691</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-121.635665893555</v>
+        <v>-116.5734</v>
       </c>
       <c r="C170" t="n">
-        <v>36.9845008850098</v>
+        <v>38.4423</v>
       </c>
       <c r="D170" t="n">
-        <v>8.989999771118161</v>
+        <v>1.9073</v>
       </c>
       <c r="E170" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
+          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>6 km WSW of Gilroy, CA</t>
+          <t>70 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7238,38 +7238,38 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>46096.24306736111</v>
+        <v>46096.25128945602</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46096.29676952546</v>
+        <v>46096.25308243056</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>aka2026fekujg</t>
+          <t>ci41204447</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-150.947</v>
+        <v>-116.168333333333</v>
       </c>
       <c r="C171" t="n">
-        <v>60.457</v>
+        <v>33.8886666666667</v>
       </c>
       <c r="D171" t="n">
-        <v>50.6</v>
+        <v>5.52</v>
       </c>
       <c r="E171" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>M 1.6 - 7 km ESE of Soldotna, Alaska</t>
+          <t>M 1.3 - 19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>7 km ESE of Soldotna, Alaska</t>
+          <t>19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7278,38 +7278,38 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>46096.22573243055</v>
+        <v>46096.24517546297</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46096.22721925926</v>
+        <v>46096.25266435185</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>us6000sgel</t>
+          <t>nc75327597</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-77.3734</v>
+        <v>-121.635665893555</v>
       </c>
       <c r="C172" t="n">
-        <v>-45.6673</v>
+        <v>36.9845008850098</v>
       </c>
       <c r="D172" t="n">
-        <v>10</v>
+        <v>8.989999771118161</v>
       </c>
       <c r="E172" t="n">
-        <v>4.4</v>
+        <v>1.71</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>6 km WSW of Gilroy, CA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>46096.22567266204</v>
+        <v>46096.24306736111</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46096.32872731482</v>
+        <v>46096.29676952546</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/USGS.xlsx
+++ b/data/raw/USGS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,29 +487,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nn00912752</t>
+          <t>nc75328332</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-116.4741</v>
+        <v>-118.74683380127</v>
       </c>
       <c r="C2" t="n">
-        <v>38.4885</v>
+        <v>37.4824981689453</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0292</v>
+        <v>3.53999996185303</v>
       </c>
       <c r="E2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M 1.6 - 81 km NE of Tonopah, Nevada</t>
+          <t>M 1.6 - 11 km SW of Toms Place, CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>81 km NE of Tonopah, Nevada</t>
+          <t>11 km SW of Toms Place, CA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,38 +518,38 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46097.22186076389</v>
+        <v>46097.70462268518</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46097.22480158565</v>
+        <v>46097.70571199074</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nc75328077</t>
+          <t>tx2026fhdfid</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-121.173835754395</v>
+        <v>-102.059</v>
       </c>
       <c r="C3" t="n">
-        <v>37.1158332824707</v>
+        <v>32.407</v>
       </c>
       <c r="D3" t="n">
-        <v>8.680000305175779</v>
+        <v>3.7746</v>
       </c>
       <c r="E3" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M 1.5 - 22 km SW of Gustine, CA</t>
+          <t>M 2.0 - 34 km WSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22 km SW of Gustine, CA</t>
+          <t>34 km WSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,38 +558,38 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46097.22094502315</v>
+        <v>46097.70138912037</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46097.22203528935</v>
+        <v>46097.70903872685</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nc75328072</t>
+          <t>aka2026fhdcod</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-121.153663635254</v>
+        <v>-156.175</v>
       </c>
       <c r="C4" t="n">
-        <v>37.1259994506836</v>
+        <v>57.639</v>
       </c>
       <c r="D4" t="n">
-        <v>9.80000019073486</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M 2.5 - 20 km SW of Gustine, CA</t>
+          <t>M 2.4 - 74 km E of Ugashik, Alaska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20 km SW of Gustine, CA</t>
+          <t>74 km E of Ugashik, Alaska</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -598,38 +598,38 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46097.21683298611</v>
+        <v>46097.69902953703</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46097.22382956019</v>
+        <v>46097.70019578704</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ci41204887</t>
+          <t>aka2026fhcyhe</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-117.500666666667</v>
+        <v>-150.514</v>
       </c>
       <c r="C5" t="n">
-        <v>34.0881666666667</v>
+        <v>60.565</v>
       </c>
       <c r="D5" t="n">
-        <v>10.81</v>
+        <v>57</v>
       </c>
       <c r="E5" t="n">
-        <v>0.99</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km WSW of Fontana, CA</t>
+          <t>M 1.9 - 14 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4 km WSW of Fontana, CA</t>
+          <t>14 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,38 +638,38 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46097.21549351852</v>
+        <v>46097.69558802083</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46097.21785097222</v>
+        <v>46097.69695893519</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nc75328067</t>
+          <t>tx2026fhcmkf</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-122.458168029785</v>
+        <v>-104.406</v>
       </c>
       <c r="C6" t="n">
-        <v>37.5923347473145</v>
+        <v>31.686</v>
       </c>
       <c r="D6" t="n">
-        <v>7.23999977111816</v>
+        <v>3.9898</v>
       </c>
       <c r="E6" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
+          <t>M 1.2 - 54 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>54 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -678,38 +678,38 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46097.20110729166</v>
+        <v>46097.68605231481</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46097.2169190162</v>
+        <v>46097.68757355324</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nc75328062</t>
+          <t>tx2026fhckjk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-122.700668334961</v>
+        <v>-101.142</v>
       </c>
       <c r="C7" t="n">
-        <v>38.7681655883789</v>
+        <v>32.279</v>
       </c>
       <c r="D7" t="n">
-        <v>0.730000019073486</v>
+        <v>2.5145</v>
       </c>
       <c r="E7" t="n">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M 1.1 - 1 km SW of Anderson Springs, CA</t>
+          <t>M 1.7 - 14 km SW of Westbrook, Texas</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1 km SW of Anderson Springs, CA</t>
+          <t>14 km SW of Westbrook, Texas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -718,38 +718,38 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46097.1980800926</v>
+        <v>46097.68441585648</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46097.21344644676</v>
+        <v>46097.68718243056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aka2026fgejkl</t>
+          <t>tx2026fhcgdx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-150.208</v>
+        <v>-104.354</v>
       </c>
       <c r="C8" t="n">
-        <v>62.214</v>
+        <v>31.654</v>
       </c>
       <c r="D8" t="n">
-        <v>4.4</v>
+        <v>6.665</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
+          <t>M 1.9 - 57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11 km S of Trapper Creek, Alaska</t>
+          <t>57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -758,38 +758,38 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46097.18073642361</v>
+        <v>46097.682069375</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46097.1817900926</v>
+        <v>46097.68598783565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nn00912748</t>
+          <t>ci41205167</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-116.7944</v>
+        <v>-116.124833333333</v>
       </c>
       <c r="C9" t="n">
-        <v>38.3084</v>
+        <v>32.8211666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8689</v>
+        <v>11.31</v>
       </c>
       <c r="E9" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
+          <t>M 1.5 - 16 km NW of Ocotillo, CA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>46 km NE of Tonopah, Nevada</t>
+          <t>16 km NW of Ocotillo, CA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -798,38 +798,38 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46097.18032635417</v>
+        <v>46097.68161979166</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46097.18299189815</v>
+        <v>46097.68407987268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nn00912744</t>
+          <t>ci41205159</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-116.5751</v>
+        <v>-116.861167907715</v>
       </c>
       <c r="C10" t="n">
-        <v>38.2761</v>
+        <v>33.1121673583984</v>
       </c>
       <c r="D10" t="n">
-        <v>6.7167</v>
+        <v>-0.140000000596046</v>
       </c>
       <c r="E10" t="n">
-        <v>2.18</v>
+        <v>1.38001047851065</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M 2.2 - 61 km ENE of Tonopah, Nevada</t>
+          <t>M 1.4 - 8 km N of Ramona, CA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>61 km ENE of Tonopah, Nevada</t>
+          <t>8 km N of Ramona, CA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -838,38 +838,38 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46097.17459033565</v>
+        <v>46097.68148090278</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46097.17637523148</v>
+        <v>46097.68381611111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ci41204855</t>
+          <t>us6000sgl9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-119.120666666667</v>
+        <v>123.9216</v>
       </c>
       <c r="C11" t="n">
-        <v>34.9321666666667</v>
+        <v>-8.9581</v>
       </c>
       <c r="D11" t="n">
-        <v>0.87</v>
+        <v>80.8</v>
       </c>
       <c r="E11" t="n">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M 2.3 - 10 km NNE of Pine Mountain Club, CA</t>
+          <t>M 4.7 - 57 km WNW of Pante Makasar, Timor Leste</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10 km NNE of Pine Mountain Club, CA</t>
+          <t>57 km WNW of Pante Makasar, Timor Leste</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -878,38 +878,38 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46097.17414733797</v>
+        <v>46097.66752659722</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46097.20602984953</v>
+        <v>46097.70778981481</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nn00912743</t>
+          <t>hv74917762</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-116.0158</v>
+        <v>-155.526336669922</v>
       </c>
       <c r="C12" t="n">
-        <v>37.795</v>
+        <v>19.1658325195312</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4807</v>
+        <v>-0.660000026226044</v>
       </c>
       <c r="E12" t="n">
-        <v>1.34</v>
+        <v>2.35</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
+          <t>M 2.4 - 6 km SW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29 km NW of Rachel, Nevada</t>
+          <t>6 km SW of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -918,38 +918,38 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46097.17013881944</v>
+        <v>46097.66161435185</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46097.1716130787</v>
+        <v>46097.70311388889</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nc75328052</t>
+          <t>nc75328292</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-122.765167236328</v>
+        <v>-122.747833251953</v>
       </c>
       <c r="C13" t="n">
-        <v>38.7836685180664</v>
+        <v>38.798999786377</v>
       </c>
       <c r="D13" t="n">
-        <v>4.19000005722046</v>
+        <v>1.13999998569489</v>
       </c>
       <c r="E13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
+          <t>M 1.0 - 3 km NNE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1 km NW of The Geysers, CA</t>
+          <t>3 km NNE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -958,38 +958,38 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46097.16834872685</v>
+        <v>46097.65723449074</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46097.20647809028</v>
+        <v>46097.68918299769</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nn00912742</t>
+          <t>aka2026fhatbo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-117.5849</v>
+        <v>-150.853</v>
       </c>
       <c r="C14" t="n">
-        <v>37.3479</v>
+        <v>60.881</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7908</v>
+        <v>6.2</v>
       </c>
       <c r="E14" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
+          <t>M 2.1 - 10 km WSW of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>45 km S of Silver Peak, Nevada</t>
+          <t>10 km WSW of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -998,38 +998,38 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46097.15891554398</v>
+        <v>46097.64948021991</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46097.16036833333</v>
+        <v>46097.65093195602</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nn00912740</t>
+          <t>hv74917757</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-116.3558</v>
+        <v>-155.456665039062</v>
       </c>
       <c r="C15" t="n">
-        <v>37.5573</v>
+        <v>19.1399993896484</v>
       </c>
       <c r="D15" t="n">
-        <v>8.4693</v>
+        <v>27.5699996948242</v>
       </c>
       <c r="E15" t="n">
-        <v>1.15</v>
+        <v>2.12</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
+          <t>M 2.1 - 7 km SSE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>54 km W of Rachel, Nevada</t>
+          <t>7 km SSE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1038,38 +1038,38 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46097.1542737963</v>
+        <v>46097.64710127315</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46097.15577996528</v>
+        <v>46097.64962835648</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nc75328042</t>
+          <t>hv74917752</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-122.843170166016</v>
+        <v>-155.373504638672</v>
       </c>
       <c r="C16" t="n">
-        <v>38.8208351135254</v>
+        <v>19.0543327331543</v>
       </c>
       <c r="D16" t="n">
-        <v>1.67999994754791</v>
+        <v>32.9700012207031</v>
       </c>
       <c r="E16" t="n">
-        <v>1.07</v>
+        <v>1.74</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
+          <t>M 1.7 - 19 km SE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9 km WNW of The Geysers, CA</t>
+          <t>19 km SE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1078,38 +1078,38 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46097.15140474537</v>
+        <v>46097.64697847222</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46097.15253628472</v>
+        <v>46097.64955844908</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nc75328037</t>
+          <t>aka2026fhapnw</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-122.839668273926</v>
+        <v>-141.919</v>
       </c>
       <c r="C17" t="n">
-        <v>38.8219985961914</v>
+        <v>61.385</v>
       </c>
       <c r="D17" t="n">
-        <v>1.66999995708466</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="n">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
+          <t>M 1.4 - 53 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9 km NW of The Geysers, CA</t>
+          <t>53 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1118,38 +1118,38 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46097.15081805555</v>
+        <v>46097.64664483797</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46097.18912663194</v>
+        <v>46097.64765140046</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ci41204839</t>
+          <t>nc75328222</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-117.701833333333</v>
+        <v>-122.802665710449</v>
       </c>
       <c r="C18" t="n">
-        <v>35.8715</v>
+        <v>39.3009986877441</v>
       </c>
       <c r="D18" t="n">
-        <v>4.72</v>
+        <v>2.23000001907349</v>
       </c>
       <c r="E18" t="n">
-        <v>0.99</v>
+        <v>1.89</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
+          <t>M 1.9 - 18 km NNE of Upper Lake, CA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20 km ESE of Little Lake, CA</t>
+          <t>18 km NNE of Upper Lake, CA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1158,38 +1158,38 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46097.14808055555</v>
+        <v>46097.57507303241</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46097.15049766203</v>
+        <v>46097.60232115741</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>aka2026fgcope</t>
+          <t>us6000sgl1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-149.454</v>
+        <v>159.5859</v>
       </c>
       <c r="C19" t="n">
-        <v>62.553</v>
+        <v>51.7026</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>43.004</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
+          <t>M 4.8 - 158 km SSE of Vilyuchinsk, Russia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>35 km ENE of Chase, Alaska</t>
+          <t>158 km SSE of Vilyuchinsk, Russia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1198,38 +1198,38 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46097.14301053241</v>
+        <v>46097.5726021875</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46097.14408171296</v>
+        <v>46097.63740787037</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nn00912738</t>
+          <t>ci41205087</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-116.4786</v>
+        <v>-119.608</v>
       </c>
       <c r="C20" t="n">
-        <v>38.4752</v>
+        <v>34.908</v>
       </c>
       <c r="D20" t="n">
-        <v>7.3424</v>
+        <v>7.61</v>
       </c>
       <c r="E20" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
+          <t>M 1.3 - 25 km SW of Maricopa, CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>79 km NE of Tonopah, Nevada</t>
+          <t>25 km SW of Maricopa, CA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,38 +1238,38 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46097.13946230324</v>
+        <v>46097.56340219908</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46097.14130107639</v>
+        <v>46097.5657459838</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aka2026fgbzeh</t>
+          <t>uw62235796</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-149.584</v>
+        <v>-122.1261672973633</v>
       </c>
       <c r="C21" t="n">
-        <v>62.358</v>
+        <v>46.67683410644531</v>
       </c>
       <c r="D21" t="n">
-        <v>56.7</v>
+        <v>21.3199996948242</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
+          <t>M 1.6 - 6 km SE of Mineral, Washington</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>25 km NNE of Susitna North, Alaska</t>
+          <t>6 km SE of Mineral, Washington</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46097.13059196759</v>
+        <v>46097.56116597222</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46097.13160341435</v>
+        <v>46097.56277951389</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>aka2026fgbuau</t>
+          <t>nn00912767</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-146.643</v>
+        <v>-115.8623</v>
       </c>
       <c r="C22" t="n">
-        <v>61.432</v>
+        <v>37.5521</v>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>0.8212</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
+          <t>M 1.3 - 14 km SW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>37 km NNW of Valdez, Alaska</t>
+          <t>14 km SW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1318,38 +1318,38 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46097.12645101852</v>
+        <v>46097.55862295139</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46097.12856479167</v>
+        <v>46097.56035638889</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nc75327997</t>
+          <t>us6000sgkx</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-122.785667419434</v>
+        <v>-178.2166</v>
       </c>
       <c r="C23" t="n">
-        <v>38.8154983520508</v>
+        <v>-17.6505</v>
       </c>
       <c r="D23" t="n">
-        <v>1.46000003814697</v>
+        <v>588.116</v>
       </c>
       <c r="E23" t="n">
-        <v>1.07</v>
+        <v>4.3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
+          <t>M 4.3 - 265 km E of Levuka, Fiji</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>265 km E of Levuka, Fiji</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1358,38 +1358,38 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46097.10226643518</v>
+        <v>46097.54886736111</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46097.10338584491</v>
+        <v>46097.64150509259</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nc75327992</t>
+          <t>aka2026fgvryc</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-122.786163330078</v>
+        <v>-140.824</v>
       </c>
       <c r="C24" t="n">
-        <v>38.8153343200684</v>
+        <v>59.858</v>
       </c>
       <c r="D24" t="n">
-        <v>1.44000005722046</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
+          <t>M 2.0 - 70 km WNW of Yakutat, Alaska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5 km NNW of The Geysers, CA</t>
+          <t>70 km WNW of Yakutat, Alaska</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1398,38 +1398,38 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46097.09843321759</v>
+        <v>46097.54380741898</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46097.13356498843</v>
+        <v>46097.54504167824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aka2026ffzydk</t>
+          <t>us6000sgkw</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-151.439</v>
+        <v>165.3363</v>
       </c>
       <c r="C25" t="n">
-        <v>59.675</v>
+        <v>-62.4511</v>
       </c>
       <c r="D25" t="n">
-        <v>40.3</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
+          <t>M 5.4 - Balleny Islands region</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0 km NW of Kachemak, Alaska</t>
+          <t>Balleny Islands region</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1438,38 +1438,38 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46097.08785851852</v>
+        <v>46097.54284928241</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46097.0893715625</v>
+        <v>46097.64971061343</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nn00912733</t>
+          <t>ci41205063</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-116.2619</v>
+        <v>-116.1705</v>
       </c>
       <c r="C26" t="n">
-        <v>38.6278</v>
+        <v>33.885</v>
       </c>
       <c r="D26" t="n">
-        <v>4.7494</v>
+        <v>5.05</v>
       </c>
       <c r="E26" t="n">
-        <v>2.71</v>
+        <v>1.08</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M 2.7 - 95 km SE of Kingston, Nevada</t>
+          <t>M 1.1 - 19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>95 km SE of Kingston, Nevada</t>
+          <t>19 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1478,38 +1478,38 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46097.08629175926</v>
+        <v>46097.52846921296</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46097.09325277778</v>
+        <v>46097.53084952546</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ci41204823</t>
+          <t>tx2026fguwss</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-117.844666666667</v>
+        <v>-104.378</v>
       </c>
       <c r="C27" t="n">
-        <v>36.4091666666667</v>
+        <v>31.672</v>
       </c>
       <c r="D27" t="n">
-        <v>3.71</v>
+        <v>6.3906</v>
       </c>
       <c r="E27" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M 1.2 - 20 km NE of Olancha, CA</t>
+          <t>M 1.6 - 55 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20 km NE of Olancha, CA</t>
+          <t>55 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1518,38 +1518,38 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46097.08612511574</v>
+        <v>46097.52672488426</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46097.08854572917</v>
+        <v>46097.52869530093</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tx2026ffzaya</t>
+          <t>nn00912765</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-104.188</v>
+        <v>-116.5131</v>
       </c>
       <c r="C28" t="n">
-        <v>31.703</v>
+        <v>38.4624</v>
       </c>
       <c r="D28" t="n">
-        <v>4.4731</v>
+        <v>8.1928</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
+          <t>M 1.9 - 76 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>55 km SSE of Whites City, New Mexico</t>
+          <t>76 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1558,38 +1558,38 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46097.06930607639</v>
+        <v>46097.51777472222</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46097.08380681713</v>
+        <v>46097.51999582176</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hv74917612</t>
+          <t>ci41205047</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-155.139495849609</v>
+        <v>-115.574833333333</v>
       </c>
       <c r="C29" t="n">
-        <v>19.3330001831055</v>
+        <v>33.2123333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>3.76999998092651</v>
+        <v>3.88</v>
       </c>
       <c r="E29" t="n">
-        <v>2.04</v>
+        <v>1.19</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 1.2 - 6 km WSW of Niland, CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>6 km WSW of Niland, CA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1598,38 +1598,38 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46097.06757199074</v>
+        <v>46097.50542395833</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46097.07008101852</v>
+        <v>46097.50780064815</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ci41204799</t>
+          <t>aka2026fgtlnr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-117.4825</v>
+        <v>-150.536</v>
       </c>
       <c r="C30" t="n">
-        <v>35.601</v>
+        <v>63.149</v>
       </c>
       <c r="D30" t="n">
-        <v>7.7</v>
+        <v>123.3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.95</v>
+        <v>2.6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
+          <t>M 2.6 - 73 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18 km E of Ridgecrest, CA</t>
+          <t>73 km N of Petersville, Alaska</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46097.0600244213</v>
+        <v>46097.49674850694</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46097.06239535879</v>
+        <v>46097.52338009259</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tx2026ffyeyx</t>
+          <t>us6000sgku</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-104.176</v>
+        <v>138.9878</v>
       </c>
       <c r="C31" t="n">
-        <v>31.711</v>
+        <v>-2.2256</v>
       </c>
       <c r="D31" t="n">
-        <v>7.4969</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M 1.9 - 54 km W of Mentone, Texas</t>
+          <t>M 4.9 - 187 km WNW of Abepura, Indonesia</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>54 km W of Mentone, Texas</t>
+          <t>187 km WNW of Abepura, Indonesia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1678,38 +1678,38 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46097.05150728009</v>
+        <v>46097.4954309375</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46097.06865469908</v>
+        <v>46097.5176162037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aka2026ffxzpn</t>
+          <t>ci41205039</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-150.668</v>
+        <v>-119.6045</v>
       </c>
       <c r="C32" t="n">
-        <v>63.582</v>
+        <v>34.9143333333333</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1</v>
+        <v>8.66</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
+          <t>M 2.0 - 25 km SW of Maricopa, CA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>52 km E of Denali National Park, Alaska</t>
+          <t>25 km SW of Maricopa, CA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1718,38 +1718,38 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46097.0471140162</v>
+        <v>46097.4932712963</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46097.04869516204</v>
+        <v>46097.63843298611</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nn00912731</t>
+          <t>hv74917727</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-114.5508</v>
+        <v>-155.383163452148</v>
       </c>
       <c r="C33" t="n">
-        <v>37.2919</v>
+        <v>19.0381660461426</v>
       </c>
       <c r="D33" t="n">
-        <v>15.9298</v>
+        <v>28.3400001525879</v>
       </c>
       <c r="E33" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
+          <t>M 1.7 - 20 km SSE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>36 km S of Caliente, Nevada</t>
+          <t>20 km SSE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1758,38 +1758,38 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46097.04372652778</v>
+        <v>46097.48826053241</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46097.04546596065</v>
+        <v>46097.49067152778</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ci41204783</t>
+          <t>us6000sgkr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-116.366833333333</v>
+        <v>118.1226</v>
       </c>
       <c r="C34" t="n">
-        <v>33.193</v>
+        <v>-9.2403</v>
       </c>
       <c r="D34" t="n">
-        <v>7.35</v>
+        <v>79.634</v>
       </c>
       <c r="E34" t="n">
-        <v>1.92</v>
+        <v>4.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>M 1.9 - 7 km S of Borrego Springs, CA</t>
+          <t>M 4.9 - 86 km SSW of Dompu, Indonesia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7 km S of Borrego Springs, CA</t>
+          <t>86 km SSW of Dompu, Indonesia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1798,38 +1798,38 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46097.04078981481</v>
+        <v>46097.48748390046</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46097.04323087963</v>
+        <v>46097.52877170139</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nc75327962</t>
+          <t>us6000sgkn</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-120.523834228516</v>
+        <v>139.4133</v>
       </c>
       <c r="C35" t="n">
-        <v>35.9671669006348</v>
+        <v>34.7732</v>
       </c>
       <c r="D35" t="n">
-        <v>6.94999980926514</v>
+        <v>121.973</v>
       </c>
       <c r="E35" t="n">
-        <v>1.72</v>
+        <v>4.6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
+          <t>M 4.6 - 37 km SE of Itō, Japan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11 km NW of Parkfield, CA</t>
+          <t>37 km SE of Itō, Japan</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1838,38 +1838,38 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46097.03950659722</v>
+        <v>46097.484599375</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46097.09886200231</v>
+        <v>46097.56709004629</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aka2026ffxmpi</t>
+          <t>us6000sgkq</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-149.174</v>
+        <v>139.1303</v>
       </c>
       <c r="C36" t="n">
-        <v>63.002</v>
+        <v>-2.212</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
+          <t>M 4.4 - 172 km WNW of Abepura, Indonesia</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>44 km SSW of Cantwell, Alaska</t>
+          <t>172 km WNW of Abepura, Indonesia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1878,38 +1878,38 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46097.03663675926</v>
+        <v>46097.4812591088</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46097.03896524305</v>
+        <v>46097.53283611111</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nc75327947</t>
+          <t>ci41205031</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-124.239669799805</v>
+        <v>-115.571833333333</v>
       </c>
       <c r="C37" t="n">
-        <v>40.4664993286133</v>
+        <v>33.2126666666667</v>
       </c>
       <c r="D37" t="n">
-        <v>26.0400009155273</v>
+        <v>3.55</v>
       </c>
       <c r="E37" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
+          <t>M 1.2 - 6 km WSW of Niland, CA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12 km WSW of Rio Dell, CA</t>
+          <t>6 km WSW of Niland, CA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1918,38 +1918,38 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46097.03397256944</v>
+        <v>46097.47036724537</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46097.08151043981</v>
+        <v>46097.47276552083</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nn00912729</t>
+          <t>nc75328182</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-116.2867</v>
+        <v>-123.229331970215</v>
       </c>
       <c r="C38" t="n">
-        <v>37.418</v>
+        <v>39.2929992675781</v>
       </c>
       <c r="D38" t="n">
-        <v>8.758599999999999</v>
+        <v>6.25</v>
       </c>
       <c r="E38" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.2 - 4 km NW of Redwood Valley, CA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>4 km NW of Redwood Valley, CA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1958,38 +1958,38 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46097.03219180556</v>
+        <v>46097.46707303241</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46097.03392417824</v>
+        <v>46097.49467026621</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hv74917602</t>
+          <t>ci41205023</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-155.143005371094</v>
+        <v>-119.602166666667</v>
       </c>
       <c r="C39" t="n">
-        <v>19.3344993591309</v>
+        <v>34.9151666666667</v>
       </c>
       <c r="D39" t="n">
-        <v>4.25</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>2.06</v>
+        <v>2.51</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
+          <t>M 2.5 - 24 km SW of Maricopa, CA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14 km S of Fern Forest, Hawaii</t>
+          <t>24 km SW of Maricopa, CA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1998,38 +1998,38 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46097.02269363426</v>
+        <v>46097.45965335648</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46097.02506747685</v>
+        <v>46097.60355482639</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nn00912728</t>
+          <t>aka2026fgrjvu</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-116.8948</v>
+        <v>-151.841</v>
       </c>
       <c r="C40" t="n">
-        <v>38.2511</v>
+        <v>60.703</v>
       </c>
       <c r="D40" t="n">
-        <v>4.7942</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
+          <t>M 1.7 - 30 km WNW of Salamatof, Alaska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>35 km NE of Tonopah, Nevada</t>
+          <t>30 km WNW of Salamatof, Alaska</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2038,38 +2038,38 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46097.02024291667</v>
+        <v>46097.45346623842</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46097.02206256944</v>
+        <v>46097.45477528935</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nn00912725</t>
+          <t>tx2026fgrcsn</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-116.3002</v>
+        <v>-103.434</v>
       </c>
       <c r="C41" t="n">
-        <v>36.4986</v>
+        <v>31.927</v>
       </c>
       <c r="D41" t="n">
-        <v>1.7633</v>
+        <v>5.9076</v>
       </c>
       <c r="E41" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
+          <t>M 1.1 - 29 km NNE of Mentone, Texas</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>42 km NW of Pahrump, Nevada</t>
+          <t>29 km NNE of Mentone, Texas</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2078,38 +2078,38 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46097.01676708333</v>
+        <v>46097.44773530093</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46097.01802194444</v>
+        <v>46097.6427689699</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aka2026ffwkac</t>
+          <t>nc75328167</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-147.104</v>
+        <v>-122.736335754395</v>
       </c>
       <c r="C42" t="n">
-        <v>61.221</v>
+        <v>38.7903327941895</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>2.05999994277954</v>
       </c>
       <c r="E42" t="n">
-        <v>1.5</v>
+        <v>0.95</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
+          <t>M 1.0 - 2 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>41 km WNW of Valdez, Alaska</t>
+          <t>2 km NE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2118,38 +2118,38 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46097.01360875</v>
+        <v>46097.44591331018</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46097.01453715278</v>
+        <v>46097.4634284838</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nc75327937</t>
+          <t>nc75328162</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-120.16283416748</v>
+        <v>-122.735664367676</v>
       </c>
       <c r="C43" t="n">
-        <v>36.1510009765625</v>
+        <v>38.7874984741211</v>
       </c>
       <c r="D43" t="n">
-        <v>5.53000020980835</v>
+        <v>1.62999999523163</v>
       </c>
       <c r="E43" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M 1.8 - 8 km SW of Huron, CA</t>
+          <t>M 2.3 - 2 km ENE of The Geysers, CA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8 km SW of Huron, CA</t>
+          <t>2 km ENE of The Geysers, CA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2158,38 +2158,38 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46097.00379861111</v>
+        <v>46097.44316493056</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46097.07108120371</v>
+        <v>46097.46693584491</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aka2026ffvrqe</t>
+          <t>hv74917722</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-150.318</v>
+        <v>-155.085159301758</v>
       </c>
       <c r="C44" t="n">
-        <v>60.621</v>
+        <v>18.7789993286133</v>
       </c>
       <c r="D44" t="n">
-        <v>37.9</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="E44" t="n">
-        <v>2.8</v>
+        <v>1.88</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
+          <t>M 1.9 - 61 km ESE of Naalehu, Hawaii</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>26 km ENE of Sterling, Alaska</t>
+          <t>61 km ESE of Naalehu, Hawaii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2198,38 +2198,38 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46096.99880960648</v>
+        <v>46097.43856087963</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46097.06023194444</v>
+        <v>46097.44147534722</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hv74917597</t>
+          <t>nn00912762</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-154.981170654297</v>
+        <v>-116.4833</v>
       </c>
       <c r="C45" t="n">
-        <v>19.3976669311523</v>
+        <v>38.504</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.560000002384186</v>
+        <v>8.5548</v>
       </c>
       <c r="E45" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
+          <t>M 1.7 - 81 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>10 km SW of Leilani Estates, Hawaii</t>
+          <t>81 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2238,38 +2238,38 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46096.99111076389</v>
+        <v>46097.43275981482</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46096.993578125</v>
+        <v>46097.43454292824</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ci41204759</t>
+          <t>tx2026fgqarn</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-117.6875</v>
+        <v>-103.325</v>
       </c>
       <c r="C46" t="n">
-        <v>35.0311666666667</v>
+        <v>31.503</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.84</v>
+        <v>2.5191</v>
       </c>
       <c r="E46" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km NW of Boron, CA</t>
+          <t>M 1.5 - 8 km NE of Barstow, Texas</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5 km NW of Boron, CA</t>
+          <t>8 km NE of Barstow, Texas</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2278,38 +2278,38 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46096.98700925926</v>
+        <v>46097.42534109954</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46096.98945039352</v>
+        <v>46097.45914571759</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aka2026ffvcuk</t>
+          <t>tx2026fgpzwz</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-147.706</v>
+        <v>-100.559</v>
       </c>
       <c r="C47" t="n">
-        <v>63.18</v>
+        <v>32.78</v>
       </c>
       <c r="D47" t="n">
-        <v>4.3</v>
+        <v>4.0283</v>
       </c>
       <c r="E47" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
+          <t>M 2.6 - 11 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>66 km ESE of Cantwell, Alaska</t>
+          <t>11 km SW of Rotan, Texas</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2318,38 +2318,38 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46096.98682952546</v>
+        <v>46097.42449480324</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46097.05321805555</v>
+        <v>46097.58341481481</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>aka2026ffuxwl</t>
+          <t>pr71509948</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-149.464</v>
+        <v>-64.374</v>
       </c>
       <c r="C48" t="n">
-        <v>65.532</v>
+        <v>18.9518333333333</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>47.25</v>
       </c>
       <c r="E48" t="n">
-        <v>1.5</v>
+        <v>3.32</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
+          <t>M 3.3 - 81 km NNE of Cruz Bay, U.S. Virgin Islands</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>32 km E of Rampart, Alaska</t>
+          <t>81 km NNE of Cruz Bay, U.S. Virgin Islands</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2358,38 +2358,38 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46096.98287351852</v>
+        <v>46097.41994490741</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46096.98871584491</v>
+        <v>46097.5788662037</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nc75327927</t>
+          <t>ci41204991</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-122.759002685547</v>
+        <v>-116.4185</v>
       </c>
       <c r="C49" t="n">
-        <v>38.779167175293</v>
+        <v>32.9371666666667</v>
       </c>
       <c r="D49" t="n">
-        <v>1.16999995708466</v>
+        <v>5.01</v>
       </c>
       <c r="E49" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
+          <t>M 1.1 - 17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0 km NW of The Geysers, CA</t>
+          <t>17 km NE of Pine Valley, CA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2398,38 +2398,38 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46096.98031608796</v>
+        <v>46097.41846469908</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46096.9814612037</v>
+        <v>46097.42092306713</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nc75327922</t>
+          <t>tx2026fgprzm</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-120.615669250488</v>
+        <v>-104.009</v>
       </c>
       <c r="C50" t="n">
-        <v>36.0485000610352</v>
+        <v>31.522</v>
       </c>
       <c r="D50" t="n">
-        <v>2.03999996185303</v>
+        <v>7.6508</v>
       </c>
       <c r="E50" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
+          <t>M 1.4 - 30 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>24 km NW of Parkfield, CA</t>
+          <t>30 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2438,38 +2438,38 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46096.97481886574</v>
+        <v>46097.41812233796</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46097.03291697917</v>
+        <v>46097.68319959491</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aka2026fftzga</t>
+          <t>aka2026fgphpf</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-147.469</v>
+        <v>-143.542</v>
       </c>
       <c r="C51" t="n">
-        <v>64.946</v>
+        <v>62.072</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>26.4</v>
       </c>
       <c r="E51" t="n">
         <v>1.2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>M 1.2 - 7 km E of Fox, Alaska</t>
+          <t>M 1.2 - 43 km SW of Nabesna, Alaska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>7 km E of Fox, Alaska</t>
+          <t>43 km SW of Nabesna, Alaska</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2478,38 +2478,38 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46096.96303546296</v>
+        <v>46097.40975712963</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46096.96398349537</v>
+        <v>46097.41069762732</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nc75327902</t>
+          <t>ci41204975</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-124.639663696289</v>
+        <v>-116.1085</v>
       </c>
       <c r="C52" t="n">
-        <v>40.34716796875</v>
+        <v>33.1673333333333</v>
       </c>
       <c r="D52" t="n">
-        <v>19.4500007629395</v>
+        <v>9.75</v>
       </c>
       <c r="E52" t="n">
-        <v>2.76</v>
+        <v>2.17</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>M 2.8 - 30 km W of Petrolia, CA</t>
+          <t>M 2.2 - 3 km NE of Ocotillo Wells, CA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>30 km W of Petrolia, CA</t>
+          <t>3 km NE of Ocotillo Wells, CA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2518,38 +2518,38 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46096.95174398148</v>
+        <v>46097.40551909722</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46097.04291712963</v>
+        <v>46097.53346547454</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>us6000sgib</t>
+          <t>aka2026fgpbls</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>176.3522</v>
+        <v>-151.474</v>
       </c>
       <c r="C53" t="n">
-        <v>52.1304</v>
+        <v>60.906</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
+          <t>M 1.9 - 25 km SW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>229 km ESE of Attu Station, Alaska</t>
+          <t>25 km SW of Tyonek, Alaska</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2558,38 +2558,38 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46096.94854002315</v>
+        <v>46097.40482002315</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46097.14299561342</v>
+        <v>46097.40608826389</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>nn00912719</t>
+          <t>hv74917707</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-119.7167</v>
+        <v>-155.365173339844</v>
       </c>
       <c r="C54" t="n">
-        <v>40.512</v>
+        <v>19.058666229248</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7442</v>
+        <v>32.1300010681152</v>
       </c>
       <c r="E54" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
+          <t>M 1.7 - 19 km SE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>32 km WSW of Empire, Nevada</t>
+          <t>19 km SE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2598,38 +2598,38 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46096.94697967593</v>
+        <v>46097.40409050926</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46096.94864458333</v>
+        <v>46097.40652650463</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>aka2026fftern</t>
+          <t>nc75328147</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-145.732</v>
+        <v>-121.950836181641</v>
       </c>
       <c r="C55" t="n">
-        <v>62.165</v>
+        <v>37.7729988098145</v>
       </c>
       <c r="D55" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="E55" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
+          <t>M 1.8 - 3 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11 km WNW of Glennallen, Alaska</t>
+          <t>3 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2638,38 +2638,38 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46096.94644289352</v>
+        <v>46097.40365023148</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46096.94759246528</v>
+        <v>46097.44607680556</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>aka2026ffsxtw</t>
+          <t>nn00912760</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-150.289</v>
+        <v>-117.7028</v>
       </c>
       <c r="C56" t="n">
-        <v>60.111</v>
+        <v>38.0551</v>
       </c>
       <c r="D56" t="n">
-        <v>46.9</v>
+        <v>0.0334</v>
       </c>
       <c r="E56" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
+          <t>M 2.2 - 33 km N of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>46 km NE of Fox River, Alaska</t>
+          <t>33 km N of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2678,38 +2678,38 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46096.94087768519</v>
+        <v>46097.39123678241</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46096.94183203704</v>
+        <v>46097.39342989583</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>aka2026ffsvcz</t>
+          <t>nn00912758</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-141.243</v>
+        <v>-117.0414</v>
       </c>
       <c r="C57" t="n">
-        <v>61.573</v>
+        <v>37.8063</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>15.142</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
+          <t>M 2.0 - 20 km ENE of Goldfield, Nevada</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>90 km E of McCarthy, Alaska</t>
+          <t>20 km ENE of Goldfield, Nevada</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2718,38 +2718,38 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46096.93874224537</v>
+        <v>46097.39113305556</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46096.93996863426</v>
+        <v>46097.71944440973</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hv74917587</t>
+          <t>us6000sgkc</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-155.404998779297</v>
+        <v>-74.9438</v>
       </c>
       <c r="C58" t="n">
-        <v>19.2546672821045</v>
+        <v>-10.3463</v>
       </c>
       <c r="D58" t="n">
-        <v>30.7900009155273</v>
+        <v>25.524</v>
       </c>
       <c r="E58" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
+          <t>M 4.6 - 56 km NE of Villa Rica, Peru</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9 km NE of Pāhala, Hawaii</t>
+          <t>56 km NE of Villa Rica, Peru</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2758,38 +2758,38 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46096.93382974537</v>
+        <v>46097.38833016204</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46096.93618622685</v>
+        <v>46097.43299814815</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>nc75327892</t>
+          <t>hv74917697</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-120.513832092285</v>
+        <v>-155.395660400391</v>
       </c>
       <c r="C59" t="n">
-        <v>35.9599990844727</v>
+        <v>19.2746658325195</v>
       </c>
       <c r="D59" t="n">
-        <v>10.1700000762939</v>
+        <v>31.5400009155273</v>
       </c>
       <c r="E59" t="n">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
+          <t>M 2.1 - 11 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>10 km NW of Parkfield, CA</t>
+          <t>11 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2798,38 +2798,38 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46096.92984074074</v>
+        <v>46097.38741423611</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46096.98773833334</v>
+        <v>46097.38983009259</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tx2026ffruyn</t>
+          <t>ci41204959</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-103.575</v>
+        <v>-116.168666666667</v>
       </c>
       <c r="C60" t="n">
-        <v>30.876</v>
+        <v>33.8505</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>M 2.0 - 20 km SE of Balmorhea, Texas</t>
+          <t>M 1.1 - 15 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20 km SE of Balmorhea, Texas</t>
+          <t>15 km NNE of Indio, CA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2838,38 +2838,38 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46096.91764664352</v>
+        <v>46097.38499432871</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46096.92133662037</v>
+        <v>46097.38741824074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tx2026ffrhgd</t>
+          <t>aka2026fgnuse</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-101.817</v>
+        <v>-152.259</v>
       </c>
       <c r="C61" t="n">
-        <v>32.349</v>
+        <v>61.302</v>
       </c>
       <c r="D61" t="n">
-        <v>11.8727</v>
+        <v>6.6</v>
       </c>
       <c r="E61" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
+          <t>M 1.0 - 65 km WNW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21 km SSW of Ackerly, Texas</t>
+          <t>65 km WNW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2878,38 +2878,38 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46096.90660459491</v>
+        <v>46097.37842760417</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46096.91322768519</v>
+        <v>46097.37946575232</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>nc75327882</t>
+          <t>nn00912756</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-122.730499267578</v>
+        <v>-116.466</v>
       </c>
       <c r="C62" t="n">
-        <v>38.7738342285156</v>
+        <v>38.4942</v>
       </c>
       <c r="D62" t="n">
-        <v>2.02999997138977</v>
+        <v>3.5467</v>
       </c>
       <c r="E62" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km E of The Geysers, CA</t>
+          <t>M 2.0 - 81 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2 km E of The Geysers, CA</t>
+          <t>81 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2918,38 +2918,38 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46096.90556168981</v>
+        <v>46097.37704569445</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46096.92179327546</v>
+        <v>46097.3788640625</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>aka2026ffqxwe</t>
+          <t>aka2026fgmykb</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-145.627</v>
+        <v>-152.933</v>
       </c>
       <c r="C63" t="n">
-        <v>62.093</v>
+        <v>59.744</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>97.3</v>
       </c>
       <c r="E63" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
+          <t>M 2.1 - 62 km W of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4 km WSW of Glennallen, Alaska</t>
+          <t>62 km W of Anchor Point, Alaska</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2958,38 +2958,38 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46096.89903701389</v>
+        <v>46097.36043855324</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46096.90023371528</v>
+        <v>46097.36301819445</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>nn00912718</t>
+          <t>us6000sgk5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-117.1162</v>
+        <v>25.2362</v>
       </c>
       <c r="C64" t="n">
-        <v>37.2236</v>
+        <v>33.8061</v>
       </c>
       <c r="D64" t="n">
-        <v>0.039</v>
+        <v>35</v>
       </c>
       <c r="E64" t="n">
-        <v>1.08</v>
+        <v>4.4</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
+          <t>M 4.4 - 133 km S of Pýrgos, Greece</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>47 km NW of Beatty, Nevada</t>
+          <t>133 km S of Pýrgos, Greece</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2998,38 +2998,38 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46096.8946965625</v>
+        <v>46097.35849653935</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46096.89624318287</v>
+        <v>46097.38657453703</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>nc75327877</t>
+          <t>aka2026fgmmib</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-121.053001403809</v>
+        <v>-154.338</v>
       </c>
       <c r="C65" t="n">
-        <v>36.4648323059082</v>
+        <v>58.651</v>
       </c>
       <c r="D65" t="n">
-        <v>0.209999993443489</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
+          <t>M 3.4 - 91 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11 km SE of Pinnacles, CA</t>
+          <t>91 km SSE of Kokhanok, Alaska</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3038,38 +3038,38 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46096.89354375</v>
+        <v>46097.35069123843</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46096.95303508102</v>
+        <v>46097.35182166666</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>us6000sghx</t>
+          <t>nc75328127</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-68.8159</v>
+        <v>-122.817497253418</v>
       </c>
       <c r="C66" t="n">
-        <v>-21.1625</v>
+        <v>38.8346672058105</v>
       </c>
       <c r="D66" t="n">
-        <v>120.691</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="E66" t="n">
-        <v>4.1</v>
+        <v>1.39</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
+          <t>M 1.4 - 8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>58 km W of Ollagüe, Chile</t>
+          <t>8 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3078,38 +3078,38 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46096.89260434028</v>
+        <v>46097.32765821759</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46097.01954907407</v>
+        <v>46097.34884475695</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>aka2026ffqnha</t>
+          <t>ci41204943</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-146.565</v>
+        <v>-115.647</v>
       </c>
       <c r="C67" t="n">
-        <v>61.519</v>
+        <v>31.5156666666667</v>
       </c>
       <c r="D67" t="n">
-        <v>38.2</v>
+        <v>0.9</v>
       </c>
       <c r="E67" t="n">
-        <v>1.3</v>
+        <v>3.29</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
+          <t>M 3.3 - 90 km ESE of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>44 km NNW of Valdez, Alaska</t>
+          <t>90 km ESE of Maneadero, B.C., MX</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3118,38 +3118,38 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46096.89050962963</v>
+        <v>46097.32341759259</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46096.89142732639</v>
+        <v>46097.70582089121</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tx2026ffqmcg</t>
+          <t>us6000sgk0</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-101.512</v>
+        <v>-127.7751</v>
       </c>
       <c r="C68" t="n">
-        <v>31.874</v>
+        <v>43.7912</v>
       </c>
       <c r="D68" t="n">
-        <v>3.2716</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>M 1.7 - 3 km WNW of Garden City, Texas</t>
+          <t>M 4.3 - 282 km WNW of Bandon, Oregon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3 km WNW of Garden City, Texas</t>
+          <t>282 km WNW of Bandon, Oregon</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3158,38 +3158,38 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46096.88956126157</v>
+        <v>46097.32263005787</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46096.9711172801</v>
+        <v>46097.57968369213</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>nn00912716</t>
+          <t>ok2026ffuf</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-116.5976</v>
+        <v>-98.03633333000001</v>
       </c>
       <c r="C69" t="n">
-        <v>38.2879</v>
+        <v>35.6215</v>
       </c>
       <c r="D69" t="n">
-        <v>4.9318</v>
+        <v>7.03</v>
       </c>
       <c r="E69" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
+          <t>M 1.5 - 7 km ENE of Calumet, Oklahoma</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>60 km ENE of Tonopah, Nevada</t>
+          <t>7 km ENE of Calumet, Oklahoma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3198,38 +3198,38 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46096.88044799768</v>
+        <v>46097.31783077546</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46096.88234515046</v>
+        <v>46097.50869105324</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>aka2026ffpwxx</t>
+          <t>tx2026fgkltm</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-150.536</v>
+        <v>-104.398</v>
       </c>
       <c r="C70" t="n">
-        <v>60.816</v>
+        <v>31.657</v>
       </c>
       <c r="D70" t="n">
-        <v>14.2</v>
+        <v>6.0999</v>
       </c>
       <c r="E70" t="n">
         <v>1.8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
+          <t>M 1.8 - 57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14 km SE of Point Possession, Alaska</t>
+          <t>57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3238,38 +3238,38 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46096.87733195602</v>
+        <v>46097.3095750463</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46096.87884059027</v>
+        <v>46097.53055753472</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tx2026ffpmmk</t>
+          <t>ci41204935</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-102.596</v>
+        <v>-117.684</v>
       </c>
       <c r="C71" t="n">
-        <v>32.426</v>
+        <v>35.9473333333333</v>
       </c>
       <c r="D71" t="n">
-        <v>7.1182</v>
+        <v>3.66</v>
       </c>
       <c r="E71" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Andrews, Texas</t>
+          <t>M 1.3 - 20 km E of Little Lake, CA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>12 km NNW of Andrews, Texas</t>
+          <t>20 km E of Little Lake, CA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3278,38 +3278,38 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46096.86891956018</v>
+        <v>46097.30919537037</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46096.87235497685</v>
+        <v>46097.53374041666</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>aka2026ffpbrz</t>
+          <t>pr71509938</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-151.569</v>
+        <v>-65.91</v>
       </c>
       <c r="C72" t="n">
-        <v>61.397</v>
+        <v>19.4303333333333</v>
       </c>
       <c r="D72" t="n">
-        <v>76.90000000000001</v>
+        <v>59.31</v>
       </c>
       <c r="E72" t="n">
-        <v>1.4</v>
+        <v>3.34</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
+          <t>M 3.3 - 108 km N of San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>38 km NW of Beluga, Alaska</t>
+          <t>108 km N of San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3318,38 +3318,38 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46096.86023665509</v>
+        <v>46097.29709976852</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46096.86153666666</v>
+        <v>46097.31015185185</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>aka2026ffoxwo</t>
+          <t>tx2026fgjvcc</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-153.073</v>
+        <v>-104.4</v>
       </c>
       <c r="C73" t="n">
-        <v>60.494</v>
+        <v>31.654</v>
       </c>
       <c r="D73" t="n">
-        <v>146.3</v>
+        <v>6.0999</v>
       </c>
       <c r="E73" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
+          <t>M 1.8 - 57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>75 km ENE of Port Alsworth, Alaska</t>
+          <t>57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3358,38 +3358,38 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46096.85716821759</v>
+        <v>46097.29519961806</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46096.85982177083</v>
+        <v>46097.54978502315</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tx2026ffolko</t>
+          <t>us6000sgjq</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-104.401</v>
+        <v>-70.9734</v>
       </c>
       <c r="C74" t="n">
-        <v>31.692</v>
+        <v>-35.3432</v>
       </c>
       <c r="D74" t="n">
-        <v>4.8181</v>
+        <v>101.669</v>
       </c>
       <c r="E74" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
+          <t>M 5.0 - 37 km SE of Molina, Chile</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>53 km S of Whites City, New Mexico</t>
+          <t>37 km SE of Molina, Chile</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3398,38 +3398,38 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46096.84736503472</v>
+        <v>46097.291128125</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46096.93883732639</v>
+        <v>46097.61164398148</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nc75327852</t>
+          <t>uu80006493</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-122.464164733887</v>
+        <v>-111.093333333333</v>
       </c>
       <c r="C75" t="n">
-        <v>37.5973320007324</v>
+        <v>38.3338333333333</v>
       </c>
       <c r="D75" t="n">
-        <v>9.090000152587891</v>
+        <v>1.82</v>
       </c>
       <c r="E75" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
+          <t>M 1.4 - 28 km E of Torrey, Utah</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3 km SE of Pacifica, CA</t>
+          <t>28 km E of Torrey, Utah</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3438,38 +3438,38 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46096.84368958334</v>
+        <v>46097.289715625</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46096.84483373843</v>
+        <v>46097.65491296296</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>aka2026ffogkg</t>
+          <t>aka2026fgjncb</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-150.241</v>
+        <v>-152.67</v>
       </c>
       <c r="C76" t="n">
-        <v>61.578</v>
+        <v>60.284</v>
       </c>
       <c r="D76" t="n">
-        <v>30.7</v>
+        <v>41.8</v>
       </c>
       <c r="E76" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
+          <t>M 1.0 - 61 km WNW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14 km ENE of Susitna, Alaska</t>
+          <t>61 km WNW of Ninilchik, Alaska</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3478,38 +3478,38 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46096.84307547453</v>
+        <v>46097.28846599537</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46096.84451351852</v>
+        <v>46097.28942068287</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nc75327847</t>
+          <t>nc75328122</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-122.757667541504</v>
+        <v>-123.295166015625</v>
       </c>
       <c r="C77" t="n">
-        <v>38.7918319702148</v>
+        <v>39.3580017089844</v>
       </c>
       <c r="D77" t="n">
-        <v>0.689999997615814</v>
+        <v>0.379999995231628</v>
       </c>
       <c r="E77" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>M 1.0 - 2 km N of The Geysers, CA</t>
+          <t>M 1.5 - 8 km SE of Willits, CA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2 km N of The Geysers, CA</t>
+          <t>8 km SE of Willits, CA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3518,38 +3518,38 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46096.84258912037</v>
+        <v>46097.28752141204</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46096.84373324074</v>
+        <v>46097.3314922338</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ci41204687</t>
+          <t>tx2026fgjjld</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-117.249</v>
+        <v>-104.405</v>
       </c>
       <c r="C78" t="n">
-        <v>33.9988333333333</v>
+        <v>31.664</v>
       </c>
       <c r="D78" t="n">
-        <v>10.86</v>
+        <v>6.0999</v>
       </c>
       <c r="E78" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
+          <t>M 1.8 - 56 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>6 km SSE of Loma Linda, CA</t>
+          <t>56 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3558,38 +3558,38 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46096.83063032408</v>
+        <v>46097.28551806713</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46096.83300278935</v>
+        <v>46097.5200364699</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>nn00912714</t>
+          <t>us6000sgjm</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-116.7227</v>
+        <v>25.2899</v>
       </c>
       <c r="C79" t="n">
-        <v>38.3427</v>
+        <v>33.8944</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1382</v>
+        <v>35</v>
       </c>
       <c r="E79" t="n">
-        <v>1.89</v>
+        <v>4.9</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
+          <t>M 4.9 - 123 km S of Pýrgos, Greece</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>53 km NE of Tonopah, Nevada</t>
+          <t>123 km S of Pýrgos, Greece</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3598,38 +3598,38 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46096.82208777778</v>
+        <v>46097.28220314815</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46096.82386192129</v>
+        <v>46097.37678287037</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>aka2026ffmxvv</t>
+          <t>tx2026fgjfhc</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-151.974</v>
+        <v>-104.403</v>
       </c>
       <c r="C80" t="n">
-        <v>60.349</v>
+        <v>31.66</v>
       </c>
       <c r="D80" t="n">
-        <v>77.2</v>
+        <v>5.8948</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
+          <t>M 3.0 - 57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>34 km WNW of Clam Gulch, Alaska</t>
+          <t>57 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3638,38 +3638,38 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46096.81522726852</v>
+        <v>46097.28217200231</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46096.81638251158</v>
+        <v>46097.28888540509</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nc75327827</t>
+          <t>tx2026fgjdaz</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-121.9375</v>
+        <v>-104.107</v>
       </c>
       <c r="C81" t="n">
-        <v>37.7731666666667</v>
+        <v>31.566</v>
       </c>
       <c r="D81" t="n">
-        <v>7</v>
+        <v>6.5613</v>
       </c>
       <c r="E81" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
+          <t>M 1.3 - 40 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>4 km ESE of San Ramon, CA</t>
+          <t>40 km NW of Toyah, Texas</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3678,38 +3678,38 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46096.81305393518</v>
+        <v>46097.28059408565</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46097.01551917824</v>
+        <v>46097.67315170139</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nc75327822</t>
+          <t>us6000sgk9</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-122.787170410156</v>
+        <v>-178.4376</v>
       </c>
       <c r="C82" t="n">
-        <v>38.7934989929199</v>
+        <v>-32.6404</v>
       </c>
       <c r="D82" t="n">
-        <v>2.92000007629395</v>
+        <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>1.38</v>
+        <v>4.8</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
+          <t>M 4.8 - south of the Kermadec Islands</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>south of the Kermadec Islands</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3718,38 +3718,38 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46096.81298229167</v>
+        <v>46097.27745630787</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46096.86627753473</v>
+        <v>46097.56848425926</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>us6000sghq</t>
+          <t>nn00912754</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>49.7256</v>
+        <v>-116.2669</v>
       </c>
       <c r="C83" t="n">
-        <v>32.4853</v>
+        <v>36.6499</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>0.0414</v>
       </c>
       <c r="E83" t="n">
-        <v>4.4</v>
+        <v>1.62</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
+          <t>M 1.6 - 52 km ESE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>62 km SW of Fereydūnshahr, Iran</t>
+          <t>52 km ESE of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3758,38 +3758,38 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46096.8103829051</v>
+        <v>46097.27733434028</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46096.86111157407</v>
+        <v>46097.27857869213</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>aka2026ffmjyx</t>
+          <t>hv74917652</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-149.647</v>
+        <v>-155.272659301758</v>
       </c>
       <c r="C84" t="n">
-        <v>63.036</v>
+        <v>19.2988338470459</v>
       </c>
       <c r="D84" t="n">
-        <v>76.40000000000001</v>
+        <v>1.86000001430511</v>
       </c>
       <c r="E84" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
+          <t>M 1.9 - 16 km SSW of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>52 km SW of Cantwell, Alaska</t>
+          <t>16 km SSW of Volcano, Hawaii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3798,38 +3798,38 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46096.80405828704</v>
+        <v>46097.27633101852</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46096.80508491898</v>
+        <v>46097.27904085648</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>us6000sghd</t>
+          <t>uu80006498</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>142.6105</v>
+        <v>-112.886</v>
       </c>
       <c r="C85" t="n">
-        <v>41.4045</v>
+        <v>37.0848333333333</v>
       </c>
       <c r="D85" t="n">
-        <v>42.986</v>
+        <v>17.14</v>
       </c>
       <c r="E85" t="n">
-        <v>4.9</v>
+        <v>1.12</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
+          <t>M 1.1 - 11 km NE of Hildale, Utah</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>84 km SSW of Honchō, Japan</t>
+          <t>11 km NE of Hildale, Utah</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3838,38 +3838,38 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46096.78951814815</v>
+        <v>46097.27323564815</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46096.84466623842</v>
+        <v>46097.65640069445</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>aka2026fflqih</t>
+          <t>hv74917647</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-150.765</v>
+        <v>-155.386169433594</v>
       </c>
       <c r="C86" t="n">
-        <v>63.04</v>
+        <v>19.0621662139893</v>
       </c>
       <c r="D86" t="n">
-        <v>117.3</v>
+        <v>32.9900016784668</v>
       </c>
       <c r="E86" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
+          <t>M 2.7 - 18 km SSE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>60 km N of Petersville, Alaska</t>
+          <t>18 km SSE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3878,38 +3878,38 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46096.78820800926</v>
+        <v>46097.27120636574</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46096.79154229166</v>
+        <v>46097.27399606482</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>us6000sghb</t>
+          <t>nc75328092</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>131.6063</v>
+        <v>-123.060165405273</v>
       </c>
       <c r="C87" t="n">
-        <v>31.4194</v>
+        <v>39.1538314819336</v>
       </c>
       <c r="D87" t="n">
-        <v>32.903</v>
+        <v>6.28000020980835</v>
       </c>
       <c r="E87" t="n">
-        <v>4.7</v>
+        <v>1.67</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
+          <t>M 1.7 - 10 km ENE of Talmage, CA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>30 km SE of Nichinan, Japan</t>
+          <t>10 km ENE of Talmage, CA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3918,38 +3918,38 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46096.77722483796</v>
+        <v>46097.2584287037</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46096.91079450231</v>
+        <v>46097.29680061343</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>us6000sgh9</t>
+          <t>aka2026fghjjd</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-77.5782</v>
+        <v>-149.716</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.3215</v>
+        <v>61.284</v>
       </c>
       <c r="D88" t="n">
-        <v>218.126</v>
+        <v>37.1</v>
       </c>
       <c r="E88" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
+          <t>M 1.4 - 5 km WNW of Elmendorf Air Force Base, Alaska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>44 km SE of Tena, Ecuador</t>
+          <t>5 km WNW of Elmendorf Air Force Base, Alaska</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3958,38 +3958,38 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46096.77198028936</v>
+        <v>46097.24356443287</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46096.78392407407</v>
+        <v>46097.24464640046</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nc75327792</t>
+          <t>hv74917637</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-122.471336364746</v>
+        <v>-155.372665405273</v>
       </c>
       <c r="C89" t="n">
-        <v>37.5974998474121</v>
+        <v>19.054666519165</v>
       </c>
       <c r="D89" t="n">
-        <v>9.72999954223633</v>
+        <v>32.189998626709</v>
       </c>
       <c r="E89" t="n">
-        <v>1.14</v>
+        <v>1.93</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
+          <t>M 1.9 - 19 km SE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2 km SE of Pacifica, CA</t>
+          <t>19 km SE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3998,38 +3998,38 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46096.77132291667</v>
+        <v>46097.24117708334</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46096.81413002315</v>
+        <v>46097.24410208334</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>aka2026ffklqv</t>
+          <t>nn00912752</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-155.854</v>
+        <v>-116.4741</v>
       </c>
       <c r="C90" t="n">
-        <v>57.153</v>
+        <v>38.4885</v>
       </c>
       <c r="D90" t="n">
-        <v>63.2</v>
+        <v>0.0292</v>
       </c>
       <c r="E90" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
+          <t>M 1.6 - 81 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>96 km WSW of Karluk, Alaska</t>
+          <t>81 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4038,38 +4038,38 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46096.76349226852</v>
+        <v>46097.22186076389</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46096.76507798611</v>
+        <v>46097.22480158565</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nc75327787</t>
+          <t>nc75328077</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-123.346832275391</v>
+        <v>-121.173835754395</v>
       </c>
       <c r="C91" t="n">
-        <v>39.476001739502</v>
+        <v>37.1158332824707</v>
       </c>
       <c r="D91" t="n">
-        <v>4.19999980926514</v>
+        <v>8.680000305175779</v>
       </c>
       <c r="E91" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
+          <t>M 1.5 - 22 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>5 km NE of Brooktrails, CA</t>
+          <t>22 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4078,38 +4078,38 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46096.7527207176</v>
+        <v>46097.22094502315</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46096.79673230324</v>
+        <v>46097.26208627315</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>aka2026ffjrwj</t>
+          <t>nc75328072</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-149.163</v>
+        <v>-121.153663635254</v>
       </c>
       <c r="C92" t="n">
-        <v>62.869</v>
+        <v>37.1259994506836</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3</v>
+        <v>9.80000019073486</v>
       </c>
       <c r="E92" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
+          <t>M 2.5 - 20 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>59 km S of Cantwell, Alaska</t>
+          <t>20 km SW of Gustine, CA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4118,38 +4118,38 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46096.74754356482</v>
+        <v>46097.21683298611</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46096.7486603125</v>
+        <v>46097.24468857639</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>aka2026ffjpxp</t>
+          <t>ci41204887</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-152.555</v>
+        <v>-117.500666666667</v>
       </c>
       <c r="C93" t="n">
-        <v>59.7</v>
+        <v>34.0881666666667</v>
       </c>
       <c r="D93" t="n">
-        <v>76.90000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="E93" t="n">
-        <v>1.8</v>
+        <v>0.99</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
+          <t>M 1.0 - 4 km WSW of Fontana, CA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>41 km WSW of Anchor Point, Alaska</t>
+          <t>4 km WSW of Fontana, CA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4158,38 +4158,38 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46096.74597070602</v>
+        <v>46097.21549351852</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46096.74724846065</v>
+        <v>46097.53414554398</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>us6000sgh3</t>
+          <t>nc75328067</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>128.5163</v>
+        <v>-122.458168029785</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.3925</v>
+        <v>37.5923347473145</v>
       </c>
       <c r="D94" t="n">
-        <v>137.104</v>
+        <v>7.23999977111816</v>
       </c>
       <c r="E94" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>208 km NE of Lospalos, Timor Leste</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4198,38 +4198,38 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46096.7350890625</v>
+        <v>46097.20110729166</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46096.81851898148</v>
+        <v>46097.2342590162</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ci41204623</t>
+          <t>nc75328062</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-116.638166666667</v>
+        <v>-122.700668334961</v>
       </c>
       <c r="C95" t="n">
-        <v>32.8055</v>
+        <v>38.7681655883789</v>
       </c>
       <c r="D95" t="n">
-        <v>16.68</v>
+        <v>0.730000019073486</v>
       </c>
       <c r="E95" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
+          <t>M 1.1 - 1 km SW of Anderson Springs, CA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>10 km W of Pine Valley, CA</t>
+          <t>1 km SW of Anderson Springs, CA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4238,38 +4238,38 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46096.72295416667</v>
+        <v>46097.1980800926</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46096.72542263889</v>
+        <v>46097.21344644676</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>aka2026ffhzps</t>
+          <t>aka2026fgejkl</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-146.822</v>
+        <v>-150.208</v>
       </c>
       <c r="C96" t="n">
-        <v>60.719</v>
+        <v>62.214</v>
       </c>
       <c r="D96" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>M 2.0 - 18 km SSW of Tatitlek, Alaska</t>
+          <t>M 1.8 - 11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>18 km SSW of Tatitlek, Alaska</t>
+          <t>11 km S of Trapper Creek, Alaska</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4278,38 +4278,38 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46096.71188380787</v>
+        <v>46097.18073642361</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46096.71385545139</v>
+        <v>46097.1817900926</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tx2026ffhpux</t>
+          <t>nn00912748</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-103.799</v>
+        <v>-116.7944</v>
       </c>
       <c r="C97" t="n">
-        <v>31.021</v>
+        <v>38.3084</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>2.8689</v>
       </c>
       <c r="E97" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>M 1.9 - 6 km NW of Balmorhea, Texas</t>
+          <t>M 1.7 - 46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>6 km NW of Balmorhea, Texas</t>
+          <t>46 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4318,38 +4318,38 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46096.70398288195</v>
+        <v>46097.18032635417</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46096.71967913194</v>
+        <v>46097.18299189815</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>aka2026ffhkgu</t>
+          <t>nn00912744</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-154.974</v>
+        <v>-116.5464</v>
       </c>
       <c r="C98" t="n">
-        <v>58.28</v>
+        <v>38.4504</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3</v>
+        <v>6.6997</v>
       </c>
       <c r="E98" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>M 2.3 - 84 km NNW of Karluk, Alaska</t>
+          <t>M 2.4 - 73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>84 km NNW of Karluk, Alaska</t>
+          <t>73 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4358,38 +4358,38 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46096.6993729051</v>
+        <v>46097.17456006944</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46096.7007930787</v>
+        <v>46097.70677204861</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nc75327772</t>
+          <t>ci41204855</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-122.78466796875</v>
+        <v>-119.120166666667</v>
       </c>
       <c r="C99" t="n">
-        <v>38.7933349609375</v>
+        <v>34.9345</v>
       </c>
       <c r="D99" t="n">
-        <v>3.51999998092651</v>
+        <v>1.51</v>
       </c>
       <c r="E99" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km NW of The Geysers, CA</t>
+          <t>M 2.4 - 10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>3 km NW of The Geysers, CA</t>
+          <t>10 km NNE of Pine Mountain Club, CA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4398,38 +4398,38 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46096.69837233796</v>
+        <v>46097.17414722222</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46096.72732706019</v>
+        <v>46097.62172386574</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>us6000sggw</t>
+          <t>nn00912743</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>143.3074</v>
+        <v>-116.0158</v>
       </c>
       <c r="C100" t="n">
-        <v>40.9048</v>
+        <v>37.795</v>
       </c>
       <c r="D100" t="n">
-        <v>37.859</v>
+        <v>2.4807</v>
       </c>
       <c r="E100" t="n">
-        <v>4.8</v>
+        <v>1.34</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>M 4.8 - 139 km SSE of Honchō, Japan</t>
+          <t>M 1.3 - 29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>139 km SSE of Honchō, Japan</t>
+          <t>29 km NW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4438,38 +4438,38 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46096.68937086806</v>
+        <v>46097.17013881944</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46096.69961851852</v>
+        <v>46097.1716130787</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>nc75327767</t>
+          <t>nc75328052</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-120.05883026123</v>
+        <v>-122.765167236328</v>
       </c>
       <c r="C101" t="n">
-        <v>35.7056655883789</v>
+        <v>38.7836685180664</v>
       </c>
       <c r="D101" t="n">
-        <v>7.76999998092651</v>
+        <v>4.19000005722046</v>
       </c>
       <c r="E101" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>M 2.2 - 22 km E of Cholame, CA</t>
+          <t>M 1.0 - 1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>22 km E of Cholame, CA</t>
+          <t>1 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4478,38 +4478,38 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46096.68914074074</v>
+        <v>46097.16834872685</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46096.71344819444</v>
+        <v>46097.20647809028</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>aka2026ffgrhi</t>
+          <t>nn00912742</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-151.417</v>
+        <v>-117.5849</v>
       </c>
       <c r="C102" t="n">
-        <v>63.08</v>
+        <v>37.3479</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>3.7908</v>
       </c>
       <c r="E102" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>M 1.6 - 53 km SSE of Denali National Park, Alaska</t>
+          <t>M 1.0 - 45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>53 km SSE of Denali National Park, Alaska</t>
+          <t>45 km S of Silver Peak, Nevada</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4518,38 +4518,38 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46096.68422761574</v>
+        <v>46097.15891554398</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46096.68548758102</v>
+        <v>46097.16036833333</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>nc75327742</t>
+          <t>nn00912740</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-121.291664123535</v>
+        <v>-116.3558</v>
       </c>
       <c r="C103" t="n">
-        <v>36.9063339233398</v>
+        <v>37.5573</v>
       </c>
       <c r="D103" t="n">
-        <v>7.69000005722046</v>
+        <v>8.4693</v>
       </c>
       <c r="E103" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>M 1.2 - 12 km NE of Hollister, CA</t>
+          <t>M 1.2 - 54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>12 km NE of Hollister, CA</t>
+          <t>54 km W of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4558,38 +4558,38 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46096.65917303241</v>
+        <v>46097.1542737963</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46096.69960388889</v>
+        <v>46097.15577996528</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nc75327737</t>
+          <t>nc75328042</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-122.806663513184</v>
+        <v>-122.843170166016</v>
       </c>
       <c r="C104" t="n">
-        <v>38.8235015869141</v>
+        <v>38.8208351135254</v>
       </c>
       <c r="D104" t="n">
-        <v>2.41000008583069</v>
+        <v>1.67999994754791</v>
       </c>
       <c r="E104" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>M 1.1 - 7 km NW of The Geysers, CA</t>
+          <t>M 1.1 - 9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>7 km NW of The Geysers, CA</t>
+          <t>9 km WNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4598,38 +4598,38 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46096.65873715278</v>
+        <v>46097.15140474537</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46096.67873339121</v>
+        <v>46097.15253628472</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nn00912713</t>
+          <t>nc75328037</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-116.393</v>
+        <v>-122.839668273926</v>
       </c>
       <c r="C105" t="n">
-        <v>38.5366</v>
+        <v>38.8219985961914</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0315</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="E105" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>M 2.2 - 89 km NE of Tonopah, Nevada</t>
+          <t>M 2.0 - 9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>89 km NE of Tonopah, Nevada</t>
+          <t>9 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4638,38 +4638,38 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46096.64812005787</v>
+        <v>46097.15081805555</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46096.64995700232</v>
+        <v>46097.18912663194</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nc75327727</t>
+          <t>ci41204839</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-122.743835449219</v>
+        <v>-117.701833333333</v>
       </c>
       <c r="C106" t="n">
-        <v>38.7863349914551</v>
+        <v>35.8715</v>
       </c>
       <c r="D106" t="n">
-        <v>0.850000023841858</v>
+        <v>4.72</v>
       </c>
       <c r="E106" t="n">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km NE of The Geysers, CA</t>
+          <t>M 1.0 - 20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1 km NE of The Geysers, CA</t>
+          <t>20 km ESE of Little Lake, CA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4678,38 +4678,38 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46096.64470740741</v>
+        <v>46097.14808055555</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46096.68219443287</v>
+        <v>46097.15049766203</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ci41204591</t>
+          <t>aka2026fgcope</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-115.8325</v>
+        <v>-149.454</v>
       </c>
       <c r="C107" t="n">
-        <v>31.8188333333333</v>
+        <v>62.553</v>
       </c>
       <c r="D107" t="n">
-        <v>13.69</v>
+        <v>13</v>
       </c>
       <c r="E107" t="n">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>M 2.0 - 70 km E of Maneadero, B.C., MX</t>
+          <t>M 1.2 - 35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>70 km E of Maneadero, B.C., MX</t>
+          <t>35 km ENE of Chase, Alaska</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4718,38 +4718,38 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46096.62630196759</v>
+        <v>46097.14301053241</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46096.62875739583</v>
+        <v>46097.14408171296</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nc75327717</t>
+          <t>nn00912738</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-121.055168151855</v>
+        <v>-116.4786</v>
       </c>
       <c r="C108" t="n">
-        <v>36.451000213623</v>
+        <v>38.4752</v>
       </c>
       <c r="D108" t="n">
-        <v>0.409999996423721</v>
+        <v>7.3424</v>
       </c>
       <c r="E108" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km SE of Pinnacles, CA</t>
+          <t>M 1.7 - 79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>12 km SE of Pinnacles, CA</t>
+          <t>79 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4758,38 +4758,38 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46096.61927071759</v>
+        <v>46097.13946230324</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46096.64398418982</v>
+        <v>46097.14130107639</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tx2026ffdmwb</t>
+          <t>aka2026fgbzeh</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-104.413</v>
+        <v>-149.584</v>
       </c>
       <c r="C109" t="n">
-        <v>31.649</v>
+        <v>62.358</v>
       </c>
       <c r="D109" t="n">
-        <v>5.946</v>
+        <v>56.7</v>
       </c>
       <c r="E109" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>M 1.6 - 58 km S of Whites City, New Mexico</t>
+          <t>M 2.0 - 25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>58 km S of Whites City, New Mexico</t>
+          <t>25 km NNE of Susitna North, Alaska</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4798,38 +4798,38 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46096.61776914352</v>
+        <v>46097.13059196759</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46097.20572792824</v>
+        <v>46097.13160341435</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>aka2026ffcpmw</t>
+          <t>aka2026fgbuau</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-152.825</v>
+        <v>-146.643</v>
       </c>
       <c r="C110" t="n">
-        <v>59.058</v>
+        <v>61.432</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>17.4</v>
       </c>
       <c r="E110" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>M 2.0 - 61 km WSW of Nanwalek, Alaska</t>
+          <t>M 2.1 - 37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>61 km WSW of Nanwalek, Alaska</t>
+          <t>37 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4838,38 +4838,38 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46096.59896729167</v>
+        <v>46097.12645101852</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46096.91903732639</v>
+        <v>46097.12856479167</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>us6000sggm</t>
+          <t>nc75327997</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>130.0249</v>
+        <v>-122.785667419434</v>
       </c>
       <c r="C111" t="n">
-        <v>-5.5263</v>
+        <v>38.8154983520508</v>
       </c>
       <c r="D111" t="n">
-        <v>184.533</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="E111" t="n">
-        <v>4.4</v>
+        <v>1.07</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>M 4.4 - 271 km SSE of Amahai, Indonesia</t>
+          <t>M 1.1 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>271 km SSE of Amahai, Indonesia</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4878,38 +4878,38 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46096.59319422454</v>
+        <v>46097.10226643518</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46096.69633148148</v>
+        <v>46097.10338584491</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>hv74917522</t>
+          <t>nc75327992</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-155.374328613281</v>
+        <v>-122.786163330078</v>
       </c>
       <c r="C112" t="n">
-        <v>19.1918334960938</v>
+        <v>38.8153343200684</v>
       </c>
       <c r="D112" t="n">
-        <v>31.7099990844727</v>
+        <v>1.44000005722046</v>
       </c>
       <c r="E112" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>M 2.0 - 11 km E of Pāhala, Hawaii</t>
+          <t>M 1.5 - 5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>11 km E of Pāhala, Hawaii</t>
+          <t>5 km NNW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4918,38 +4918,38 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46096.59297361111</v>
+        <v>46097.09843321759</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46096.5954587963</v>
+        <v>46097.13356498843</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ci41204575</t>
+          <t>aka2026ffzydk</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-116.426666666667</v>
+        <v>-151.439</v>
       </c>
       <c r="C113" t="n">
-        <v>33.9901666666667</v>
+        <v>59.675</v>
       </c>
       <c r="D113" t="n">
-        <v>2.17</v>
+        <v>40.3</v>
       </c>
       <c r="E113" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>M 2.4 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 2.0 - 0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>0 km NW of Kachemak, Alaska</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4958,38 +4958,38 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46096.58429085648</v>
+        <v>46097.08785851852</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46096.69570008102</v>
+        <v>46097.0893715625</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ci41204567</t>
+          <t>nn00912733</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-116.426666666667</v>
+        <v>-116.5191</v>
       </c>
       <c r="C114" t="n">
-        <v>33.9915</v>
+        <v>38.4354</v>
       </c>
       <c r="D114" t="n">
-        <v>2.18</v>
+        <v>10.9772</v>
       </c>
       <c r="E114" t="n">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>M 2.0 - 8 km ENE of Desert Hot Springs, CA</t>
+          <t>M 2.5 - 74 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8 km ENE of Desert Hot Springs, CA</t>
+          <t>74 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4998,38 +4998,38 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46096.57788611111</v>
+        <v>46097.08633068287</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46096.58546979167</v>
+        <v>46097.69176289352</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nn00912712</t>
+          <t>ci41204823</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-116.4988</v>
+        <v>-117.844666666667</v>
       </c>
       <c r="C115" t="n">
-        <v>38.4756</v>
+        <v>36.4091666666667</v>
       </c>
       <c r="D115" t="n">
-        <v>0.0689</v>
+        <v>3.71</v>
       </c>
       <c r="E115" t="n">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>M 1.8 - 78 km NE of Tonopah, Nevada</t>
+          <t>M 1.2 - 20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>78 km NE of Tonopah, Nevada</t>
+          <t>20 km NE of Olancha, CA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5038,38 +5038,38 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46096.57585082176</v>
+        <v>46097.08612511574</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46096.57864184028</v>
+        <v>46097.53472175926</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ci41204559</t>
+          <t>tx2026ffzaya</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-118.1145</v>
+        <v>-104.184</v>
       </c>
       <c r="C116" t="n">
-        <v>34.0995</v>
+        <v>31.705</v>
       </c>
       <c r="D116" t="n">
-        <v>8.91</v>
+        <v>6.3947</v>
       </c>
       <c r="E116" t="n">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>M 1.3 - 1 km WNW of San Gabriel, CA</t>
+          <t>M 1.7 - 55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1 km WNW of San Gabriel, CA</t>
+          <t>55 km SSE of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5078,38 +5078,38 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46096.5639962963</v>
+        <v>46097.06930424769</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46096.56638376157</v>
+        <v>46097.53959163195</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>aka2026ffaxsl</t>
+          <t>hv74917612</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-153.59</v>
+        <v>-155.139495849609</v>
       </c>
       <c r="C117" t="n">
-        <v>59.151</v>
+        <v>19.3330001831055</v>
       </c>
       <c r="D117" t="n">
-        <v>102.5</v>
+        <v>3.76999998092651</v>
       </c>
       <c r="E117" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>M 1.5 - 68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>M 2.0 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>68 km SE of Pope-Vannoy Landing, Alaska</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5118,38 +5118,38 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46096.56368013889</v>
+        <v>46097.06757199074</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46096.564885625</v>
+        <v>46097.07008101852</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>aka2026ffanxh</t>
+          <t>ci41204799</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-149.871</v>
+        <v>-117.4825</v>
       </c>
       <c r="C118" t="n">
-        <v>61.849</v>
+        <v>35.601</v>
       </c>
       <c r="D118" t="n">
-        <v>28.4</v>
+        <v>7.7</v>
       </c>
       <c r="E118" t="n">
-        <v>1.5</v>
+        <v>0.95</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>M 1.5 - 14 km NE of Willow, Alaska</t>
+          <t>M 1.0 - 18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>14 km NE of Willow, Alaska</t>
+          <t>18 km E of Ridgecrest, CA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5158,38 +5158,38 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46096.55577541667</v>
+        <v>46097.0600244213</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46096.55684119213</v>
+        <v>46097.06239535879</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>tx2026ffanng</t>
+          <t>tx2026ffyeyx</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-101.924</v>
+        <v>-104.176</v>
       </c>
       <c r="C119" t="n">
-        <v>32.101</v>
+        <v>31.711</v>
       </c>
       <c r="D119" t="n">
-        <v>3.9912</v>
+        <v>7.4969</v>
       </c>
       <c r="E119" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>M 1.3 - 13 km WSW of Stanton, Texas</t>
+          <t>M 1.9 - 54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>13 km WSW of Stanton, Texas</t>
+          <t>54 km W of Mentone, Texas</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5198,38 +5198,38 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46096.55563410879</v>
+        <v>46097.05150728009</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46096.97107067129</v>
+        <v>46097.06865469908</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>nn00912708</t>
+          <t>aka2026ffxzpn</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-116.4027</v>
+        <v>-150.668</v>
       </c>
       <c r="C120" t="n">
-        <v>37.3392</v>
+        <v>63.582</v>
       </c>
       <c r="D120" t="n">
-        <v>13.9737</v>
+        <v>0.1</v>
       </c>
       <c r="E120" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>M 1.4 - 57 km NNE of Beatty, Nevada</t>
+          <t>M 1.7 - 52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>57 km NNE of Beatty, Nevada</t>
+          <t>52 km E of Denali National Park, Alaska</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5238,38 +5238,38 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46096.55248135416</v>
+        <v>46097.0471140162</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46096.55406869213</v>
+        <v>46097.04869516204</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>nn00912710</t>
+          <t>nn00912731</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-117.9202</v>
+        <v>-114.5508</v>
       </c>
       <c r="C121" t="n">
-        <v>38.5488</v>
+        <v>37.2919</v>
       </c>
       <c r="D121" t="n">
-        <v>11.6085</v>
+        <v>15.9298</v>
       </c>
       <c r="E121" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>M 1.6 - 24 km NE of Mina, Nevada</t>
+          <t>M 1.6 - 36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>24 km NE of Mina, Nevada</t>
+          <t>36 km S of Caliente, Nevada</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5278,38 +5278,38 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46096.55246195602</v>
+        <v>46097.04372652778</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46096.55466255787</v>
+        <v>46097.04546596065</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>aka2026ffagux</t>
+          <t>nc75327962</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-149.012</v>
+        <v>-120.523834228516</v>
       </c>
       <c r="C122" t="n">
-        <v>62.698</v>
+        <v>35.9671669006348</v>
       </c>
       <c r="D122" t="n">
-        <v>62.2</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="E122" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>M 1.6 - 62 km ENE of Chase, Alaska</t>
+          <t>M 1.7 - 11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>62 km ENE of Chase, Alaska</t>
+          <t>11 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5318,38 +5318,38 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46096.55006834491</v>
+        <v>46097.03950659722</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46096.5511231713</v>
+        <v>46097.09886200231</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>aka2026ffacwz</t>
+          <t>aka2026ffxmpi</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-154.211</v>
+        <v>-149.174</v>
       </c>
       <c r="C123" t="n">
-        <v>58.934</v>
+        <v>63.002</v>
       </c>
       <c r="D123" t="n">
-        <v>126.4</v>
+        <v>0.2</v>
       </c>
       <c r="E123" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>M 1.9 - 64 km SSE of Kokhanok, Alaska</t>
+          <t>M 1.8 - 44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>64 km SSE of Kokhanok, Alaska</t>
+          <t>44 km SSW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5358,38 +5358,38 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46096.54689578704</v>
+        <v>46097.03663675926</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46096.54852043981</v>
+        <v>46097.03896524305</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>uw62235651</t>
+          <t>nc75327947</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-124.0351666666667</v>
+        <v>-124.239669799805</v>
       </c>
       <c r="C124" t="n">
-        <v>47.33166666666666</v>
+        <v>40.4664993286133</v>
       </c>
       <c r="D124" t="n">
-        <v>23.98</v>
+        <v>26.0400009155273</v>
       </c>
       <c r="E124" t="n">
-        <v>1.73</v>
+        <v>3.3</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>M 1.7 - 12 km NNW of Humptulips, Washington</t>
+          <t>M 3.3 - 12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>12 km NNW of Humptulips, Washington</t>
+          <t>12 km WSW of Rio Dell, CA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5398,38 +5398,38 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46096.54669189815</v>
+        <v>46097.03397256944</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46096.58038923611</v>
+        <v>46097.2788665162</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>nc75327692</t>
+          <t>nn00912729</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-122.779335021973</v>
+        <v>-116.2867</v>
       </c>
       <c r="C125" t="n">
-        <v>38.8115005493164</v>
+        <v>37.418</v>
       </c>
       <c r="D125" t="n">
-        <v>0.550000011920929</v>
+        <v>8.758599999999999</v>
       </c>
       <c r="E125" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>M 1.1 - 4 km NNW of The Geysers, CA</t>
+          <t>M 1.4 - 54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>4 km NNW of The Geysers, CA</t>
+          <t>54 km WSW of Rachel, Nevada</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5438,38 +5438,38 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46096.54474907408</v>
+        <v>46097.03219180556</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46096.5710708449</v>
+        <v>46097.03392417824</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>us6000sgg9</t>
+          <t>hv74917602</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-77.3565</v>
+        <v>-155.143005371094</v>
       </c>
       <c r="C126" t="n">
-        <v>-45.6923</v>
+        <v>19.3344993591309</v>
       </c>
       <c r="D126" t="n">
-        <v>10</v>
+        <v>4.25</v>
       </c>
       <c r="E126" t="n">
-        <v>4.6</v>
+        <v>2.06</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>M 4.6 - Off the coast of Aisen, Chile</t>
+          <t>M 2.1 - 14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>14 km S of Fern Forest, Hawaii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5478,38 +5478,38 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46096.53758378472</v>
+        <v>46097.02269363426</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46096.58026666666</v>
+        <v>46097.02506747685</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>us6000sgg8</t>
+          <t>nn00912728</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-77.3313</v>
+        <v>-116.8948</v>
       </c>
       <c r="C127" t="n">
-        <v>-45.741</v>
+        <v>38.2511</v>
       </c>
       <c r="D127" t="n">
-        <v>10</v>
+        <v>4.7942</v>
       </c>
       <c r="E127" t="n">
-        <v>4.4</v>
+        <v>1.63</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>M 4.4 - Off the coast of Aisen, Chile</t>
+          <t>M 1.6 - 35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>35 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5518,38 +5518,38 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46096.53580871528</v>
+        <v>46097.02024291667</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46096.59747731481</v>
+        <v>46097.02206256944</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>aka2026fezlzd</t>
+          <t>nn00912725</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-150.155</v>
+        <v>-116.3002</v>
       </c>
       <c r="C128" t="n">
-        <v>61.309</v>
+        <v>36.4986</v>
       </c>
       <c r="D128" t="n">
-        <v>35.8</v>
+        <v>1.7633</v>
       </c>
       <c r="E128" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>M 1.4 - 11 km WSW of Point MacKenzie, Alaska</t>
+          <t>M 1.1 - 42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>11 km WSW of Point MacKenzie, Alaska</t>
+          <t>42 km NW of Pahrump, Nevada</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5558,38 +5558,38 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46096.53327611111</v>
+        <v>46097.01676708333</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46096.53437532407</v>
+        <v>46097.01802194444</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>aka2026feywwv</t>
+          <t>aka2026ffwkac</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-148.811</v>
+        <v>-147.104</v>
       </c>
       <c r="C129" t="n">
-        <v>63.988</v>
+        <v>61.221</v>
       </c>
       <c r="D129" t="n">
-        <v>113.5</v>
+        <v>7</v>
       </c>
       <c r="E129" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>M 1.6 - 15 km ESE of Ferry, Alaska</t>
+          <t>M 1.5 - 41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>15 km ESE of Ferry, Alaska</t>
+          <t>41 km WNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5598,38 +5598,38 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46096.52110533565</v>
+        <v>46097.01360875</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46096.52266071759</v>
+        <v>46097.01453715278</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>us6000sgg7</t>
+          <t>nc75327937</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-72.47499999999999</v>
+        <v>-120.16283416748</v>
       </c>
       <c r="C130" t="n">
-        <v>41.5071</v>
+        <v>36.1510009765625</v>
       </c>
       <c r="D130" t="n">
-        <v>6.072</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E130" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>M 1.9 - 2 km WNW of Moodus, Connecticut</t>
+          <t>M 1.8 - 8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2 km WNW of Moodus, Connecticut</t>
+          <t>8 km SW of Huron, CA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5638,38 +5638,38 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46096.51831680556</v>
+        <v>46097.00379861111</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46097.0635559375</v>
+        <v>46097.07108120371</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>aka2026feypws</t>
+          <t>aka2026ffvrqe</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-151.884</v>
+        <v>-150.318</v>
       </c>
       <c r="C131" t="n">
-        <v>61.213</v>
+        <v>60.621</v>
       </c>
       <c r="D131" t="n">
-        <v>92</v>
+        <v>37.9</v>
       </c>
       <c r="E131" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>M 1.8 - 43 km WNW of Tyonek, Alaska</t>
+          <t>M 2.8 - 26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>43 km WNW of Tyonek, Alaska</t>
+          <t>26 km ENE of Sterling, Alaska</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5678,38 +5678,38 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46096.51546960648</v>
+        <v>46096.99880960648</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46096.51679775463</v>
+        <v>46097.06023194444</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>hv74917517</t>
+          <t>hv74917597</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-155.388671875</v>
+        <v>-154.981170654297</v>
       </c>
       <c r="C132" t="n">
-        <v>19.2761669158936</v>
+        <v>19.3976669311523</v>
       </c>
       <c r="D132" t="n">
-        <v>29.1200008392334</v>
+        <v>-0.560000002384186</v>
       </c>
       <c r="E132" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>M 1.9 - 12 km NE of Pāhala, Hawaii</t>
+          <t>M 1.8 - 10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>12 km NE of Pāhala, Hawaii</t>
+          <t>10 km SW of Leilani Estates, Hawaii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5718,38 +5718,38 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46096.51510231481</v>
+        <v>46096.99111076389</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46096.51755763889</v>
+        <v>46096.993578125</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>us6000sgg3</t>
+          <t>ci41204759</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-72.49160000000001</v>
+        <v>-117.6875</v>
       </c>
       <c r="C133" t="n">
-        <v>41.4904</v>
+        <v>35.0311666666667</v>
       </c>
       <c r="D133" t="n">
-        <v>6.63</v>
+        <v>-0.84</v>
       </c>
       <c r="E133" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>M 2.1 - 3 km WSW of Moodus, Connecticut</t>
+          <t>M 1.3 - 5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3 km WSW of Moodus, Connecticut</t>
+          <t>5 km NW of Boron, CA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5758,38 +5758,38 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46096.51474966435</v>
+        <v>46096.98700925926</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46097.21278487269</v>
+        <v>46096.98945039352</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>us6000sgg2</t>
+          <t>aka2026ffvcuk</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>155.7691</v>
+        <v>-147.706</v>
       </c>
       <c r="C134" t="n">
-        <v>50.1375</v>
+        <v>63.18</v>
       </c>
       <c r="D134" t="n">
-        <v>93.238</v>
+        <v>4.3</v>
       </c>
       <c r="E134" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>M 4.5 - 65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>M 2.4 - 66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>65 km SSW of Severo-Kuril’sk, Russia</t>
+          <t>66 km ESE of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5798,38 +5798,38 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46096.50655835648</v>
+        <v>46096.98682952546</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46096.52194490741</v>
+        <v>46097.05321805555</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>aka2026feycns</t>
+          <t>aka2026ffuxwl</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-148.959</v>
+        <v>-149.464</v>
       </c>
       <c r="C135" t="n">
-        <v>63.283</v>
+        <v>65.532</v>
       </c>
       <c r="D135" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="E135" t="n">
         <v>1.5</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>M 1.5 - 12 km S of Cantwell, Alaska</t>
+          <t>M 1.5 - 32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>12 km S of Cantwell, Alaska</t>
+          <t>32 km E of Rampart, Alaska</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5838,38 +5838,38 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46096.50470625</v>
+        <v>46096.98287351852</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46096.50576539352</v>
+        <v>46096.98871584491</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ci41204535</t>
+          <t>nc75327927</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-119.474833333333</v>
+        <v>-122.759002685547</v>
       </c>
       <c r="C136" t="n">
-        <v>34.3685</v>
+        <v>38.779167175293</v>
       </c>
       <c r="D136" t="n">
-        <v>0.54</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E136" t="n">
-        <v>1.49</v>
+        <v>1.06</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>M 1.5 - 5 km SE of Carpinteria, CA</t>
+          <t>M 1.1 - 0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>5 km SE of Carpinteria, CA</t>
+          <t>0 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5878,38 +5878,38 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46096.49835740741</v>
+        <v>46096.98031608796</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46096.50080350695</v>
+        <v>46096.9814612037</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>aka2026fewzkc</t>
+          <t>nc75327922</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-148.795</v>
+        <v>-120.615669250488</v>
       </c>
       <c r="C137" t="n">
-        <v>62.2</v>
+        <v>36.0485000610352</v>
       </c>
       <c r="D137" t="n">
-        <v>22.1</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="E137" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>M 2.2 - 47 km N of Sutton-Alpine, Alaska</t>
+          <t>M 1.7 - 24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>47 km N of Sutton-Alpine, Alaska</t>
+          <t>24 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5918,38 +5918,38 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46096.48122515046</v>
+        <v>46096.97481886574</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46096.48264917824</v>
+        <v>46097.03291697917</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>us6000sgfx</t>
+          <t>aka2026fftzga</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-80.1019</v>
+        <v>-147.469</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5871</v>
+        <v>64.946</v>
       </c>
       <c r="D138" t="n">
-        <v>36.381</v>
+        <v>5</v>
       </c>
       <c r="E138" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>M 4.4 - 9 km WSW of Muisne, Ecuador</t>
+          <t>M 1.2 - 7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>9 km WSW of Muisne, Ecuador</t>
+          <t>7 km E of Fox, Alaska</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5958,38 +5958,38 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46096.47494160879</v>
+        <v>46096.96303546296</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46096.4911</v>
+        <v>46096.96398349537</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>pr71509923</t>
+          <t>nc75327902</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-66.1071666666667</v>
+        <v>-124.639663696289</v>
       </c>
       <c r="C139" t="n">
-        <v>18.1251666666667</v>
+        <v>40.34716796875</v>
       </c>
       <c r="D139" t="n">
-        <v>24.58</v>
+        <v>19.4500007629395</v>
       </c>
       <c r="E139" t="n">
-        <v>1.85</v>
+        <v>2.76</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>M 1.9 - 0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>M 2.8 - 30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>0 km SW of G. L. Garcia, Puerto Rico</t>
+          <t>30 km W of Petrolia, CA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5998,38 +5998,38 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46096.47251458334</v>
+        <v>46096.95174398148</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46096.60321875</v>
+        <v>46097.04291712963</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ci41204519</t>
+          <t>us6000sgib</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-118.627833333333</v>
+        <v>176.3522</v>
       </c>
       <c r="C140" t="n">
-        <v>34.6043333333333</v>
+        <v>52.1304</v>
       </c>
       <c r="D140" t="n">
-        <v>10.64</v>
+        <v>10</v>
       </c>
       <c r="E140" t="n">
-        <v>1.13</v>
+        <v>4.6</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>M 1.1 - 13 km N of Castaic, CA</t>
+          <t>M 4.6 - 229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>13 km N of Castaic, CA</t>
+          <t>229 km ESE of Attu Station, Alaska</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6038,38 +6038,38 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46096.46653668981</v>
+        <v>46096.94854002315</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46096.46890145833</v>
+        <v>46097.14299561342</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>nn00912706</t>
+          <t>nn00912719</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-119.5178</v>
+        <v>-119.7167</v>
       </c>
       <c r="C141" t="n">
-        <v>38.4812</v>
+        <v>40.512</v>
       </c>
       <c r="D141" t="n">
-        <v>3.3162</v>
+        <v>0.7442</v>
       </c>
       <c r="E141" t="n">
-        <v>1.26</v>
+        <v>1.9</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>M 1.3 - 5 km SW of Walker, California</t>
+          <t>M 1.9 - 32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>5 km SW of Walker, California</t>
+          <t>32 km WSW of Empire, Nevada</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6078,38 +6078,38 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46096.46134278935</v>
+        <v>46096.94697967593</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46096.46294350694</v>
+        <v>46096.94864458333</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>nc75327672</t>
+          <t>aka2026fftern</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-122.810333251953</v>
+        <v>-145.732</v>
       </c>
       <c r="C142" t="n">
-        <v>38.8395004272461</v>
+        <v>62.165</v>
       </c>
       <c r="D142" t="n">
-        <v>1.83000004291534</v>
+        <v>4.6</v>
       </c>
       <c r="E142" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>M 1.0 - 8 km WNW of Cobb, CA</t>
+          <t>M 1.6 - 11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>8 km WNW of Cobb, CA</t>
+          <t>11 km WNW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6118,38 +6118,38 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46096.46108472222</v>
+        <v>46096.94644289352</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46096.49469679398</v>
+        <v>46096.94759246528</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>pr71509913</t>
+          <t>aka2026ffsxtw</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-67.0566666666667</v>
+        <v>-150.289</v>
       </c>
       <c r="C143" t="n">
-        <v>18.1476666666667</v>
+        <v>60.111</v>
       </c>
       <c r="D143" t="n">
-        <v>17.11</v>
+        <v>46.9</v>
       </c>
       <c r="E143" t="n">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>M 2.4 - 7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>M 1.7 - 46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>7 km NNE of Sabana Eneas, Puerto Rico</t>
+          <t>46 km NE of Fox River, Alaska</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6158,38 +6158,38 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46096.44030868055</v>
+        <v>46096.94087768519</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46096.59237719907</v>
+        <v>46096.94183203704</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>aka2026feukwz</t>
+          <t>aka2026ffsvcz</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-147.764</v>
+        <v>-141.243</v>
       </c>
       <c r="C144" t="n">
-        <v>60.385</v>
+        <v>61.573</v>
       </c>
       <c r="D144" t="n">
-        <v>14.9</v>
+        <v>5</v>
       </c>
       <c r="E144" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>M 1.7 - 38 km NNE of Chenega, Alaska</t>
+          <t>M 2.0 - 90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>38 km NNE of Chenega, Alaska</t>
+          <t>90 km E of McCarthy, Alaska</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6198,38 +6198,38 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46096.42763064815</v>
+        <v>46096.93874224537</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46096.4286147338</v>
+        <v>46096.93996863426</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>aka2026fetqyo</t>
+          <t>hv74917587</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-150.43</v>
+        <v>-155.404998779297</v>
       </c>
       <c r="C145" t="n">
-        <v>60.896</v>
+        <v>19.2546672821045</v>
       </c>
       <c r="D145" t="n">
-        <v>45.5</v>
+        <v>30.7900009155273</v>
       </c>
       <c r="E145" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>M 1.9 - 14 km ESE of Point Possession, Alaska</t>
+          <t>M 1.7 - 9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>14 km ESE of Point Possession, Alaska</t>
+          <t>9 km NE of Pāhala, Hawaii</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6238,38 +6238,38 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46096.41156589121</v>
+        <v>46096.93382974537</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46096.41261650463</v>
+        <v>46096.93618622685</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ci41204503</t>
+          <t>nc75327892</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-117.464333333333</v>
+        <v>-120.513832092285</v>
       </c>
       <c r="C146" t="n">
-        <v>34.157</v>
+        <v>35.9599990844727</v>
       </c>
       <c r="D146" t="n">
-        <v>6.87</v>
+        <v>10.1700000762939</v>
       </c>
       <c r="E146" t="n">
-        <v>0.98</v>
+        <v>1.61</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>M 1.0 - 7 km N of Fontana, CA</t>
+          <t>M 1.6 - 10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>7 km N of Fontana, CA</t>
+          <t>10 km NW of Parkfield, CA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6278,38 +6278,38 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46096.39763148148</v>
+        <v>46096.92984074074</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46096.39998002315</v>
+        <v>46096.98773833334</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>aka2026fessqh</t>
+          <t>uu80132196</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-152.317</v>
+        <v>-112.894</v>
       </c>
       <c r="C147" t="n">
-        <v>60.36</v>
+        <v>37.079</v>
       </c>
       <c r="D147" t="n">
-        <v>90.3</v>
+        <v>15.99</v>
       </c>
       <c r="E147" t="n">
-        <v>1.3</v>
+        <v>1.86</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>M 1.3 - 49 km NW of Ninilchik, Alaska</t>
+          <t>M 1.9 - 10 km NE of Hildale, Utah</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>49 km NW of Ninilchik, Alaska</t>
+          <t>10 km NE of Hildale, Utah</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6318,38 +6318,38 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>46096.39196349537</v>
+        <v>46096.9288693287</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46096.39365355324</v>
+        <v>46097.66425104166</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>nc75327657</t>
+          <t>tx2026ffrhgd</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-122.805335998535</v>
+        <v>-101.817</v>
       </c>
       <c r="C148" t="n">
-        <v>38.8190002441406</v>
+        <v>32.349</v>
       </c>
       <c r="D148" t="n">
-        <v>2.17000007629395</v>
+        <v>11.8727</v>
       </c>
       <c r="E148" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>M 1.1 - 6 km NW of The Geysers, CA</t>
+          <t>M 1.2 - 21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>6 km NW of The Geysers, CA</t>
+          <t>21 km SSW of Ackerly, Texas</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6358,38 +6358,38 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>46096.37721527777</v>
+        <v>46096.90660459491</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46096.42173711806</v>
+        <v>46096.91322768519</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>aka2026fertpz</t>
+          <t>nc75327882</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-157.698</v>
+        <v>-122.730499267578</v>
       </c>
       <c r="C149" t="n">
-        <v>55.194</v>
+        <v>38.7738342285156</v>
       </c>
       <c r="D149" t="n">
-        <v>4.2</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="E149" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>M 3.0 - 121 km SE of Perryville, Alaska</t>
+          <t>M 1.0 - 2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>121 km SE of Perryville, Alaska</t>
+          <t>2 km E of The Geysers, CA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6398,38 +6398,38 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>46096.37321436343</v>
+        <v>46096.90556168981</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46096.37804444444</v>
+        <v>46096.92179327546</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>uw62235646</t>
+          <t>aka2026ffqxwe</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-121.9746666666667</v>
+        <v>-145.627</v>
       </c>
       <c r="C150" t="n">
-        <v>47.82666666666667</v>
+        <v>62.093</v>
       </c>
       <c r="D150" t="n">
-        <v>26.62</v>
+        <v>5</v>
       </c>
       <c r="E150" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>M 2.0 - 3 km S of Monroe, Washington</t>
+          <t>M 1.9 - 4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>3 km S of Monroe, Washington</t>
+          <t>4 km WSW of Glennallen, Alaska</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6438,38 +6438,38 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>46096.36272453704</v>
+        <v>46096.89903701389</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46096.47082604167</v>
+        <v>46096.90023371528</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>us6000sgfk</t>
+          <t>nn00912718</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-77.27330000000001</v>
+        <v>-117.1162</v>
       </c>
       <c r="C151" t="n">
-        <v>-45.5694</v>
+        <v>37.2236</v>
       </c>
       <c r="D151" t="n">
-        <v>10</v>
+        <v>0.039</v>
       </c>
       <c r="E151" t="n">
-        <v>5.3</v>
+        <v>1.08</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>M 5.3 - Off the coast of Aisen, Chile</t>
+          <t>M 1.1 - 47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Off the coast of Aisen, Chile</t>
+          <t>47 km NW of Beatty, Nevada</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6478,38 +6478,38 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>46096.35320680556</v>
+        <v>46096.8946965625</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46096.38260266204</v>
+        <v>46096.89624318287</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>us6000sgfh</t>
+          <t>nc75327877</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>122.0755</v>
+        <v>-121.053001403809</v>
       </c>
       <c r="C152" t="n">
-        <v>24.3607</v>
+        <v>36.4648323059082</v>
       </c>
       <c r="D152" t="n">
-        <v>27.716</v>
+        <v>0.209999993443489</v>
       </c>
       <c r="E152" t="n">
-        <v>4.8</v>
+        <v>1.65</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>M 4.8 - 54 km SE of Yilan, Taiwan</t>
+          <t>M 1.7 - 11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>54 km SE of Yilan, Taiwan</t>
+          <t>11 km SE of Pinnacles, CA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6518,38 +6518,38 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>46096.34370333333</v>
+        <v>46096.89354375</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46096.53583686343</v>
+        <v>46096.95303508102</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>nn00912705</t>
+          <t>us6000sghx</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-116.5611</v>
+        <v>-68.8159</v>
       </c>
       <c r="C153" t="n">
-        <v>38.4412</v>
+        <v>-21.1625</v>
       </c>
       <c r="D153" t="n">
-        <v>3.8472</v>
+        <v>120.691</v>
       </c>
       <c r="E153" t="n">
-        <v>2.14</v>
+        <v>4.1</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>M 2.1 - 71 km NE of Tonopah, Nevada</t>
+          <t>M 4.1 - 58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>71 km NE of Tonopah, Nevada</t>
+          <t>58 km W of Ollagüe, Chile</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6558,38 +6558,38 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>46096.34194375</v>
+        <v>46096.89260434028</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46096.34380362269</v>
+        <v>46097.01954907407</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ci41204487</t>
+          <t>aka2026ffqnha</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-116.419666666667</v>
+        <v>-146.565</v>
       </c>
       <c r="C154" t="n">
-        <v>32.9405</v>
+        <v>61.519</v>
       </c>
       <c r="D154" t="n">
-        <v>4.88</v>
+        <v>38.2</v>
       </c>
       <c r="E154" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>M 1.0 - 17 km NE of Pine Valley, CA</t>
+          <t>M 1.3 - 44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>17 km NE of Pine Valley, CA</t>
+          <t>44 km NNW of Valdez, Alaska</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6598,38 +6598,38 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>46096.32685023148</v>
+        <v>46096.89050962963</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46096.32921789352</v>
+        <v>46096.89142732639</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ci41204479</t>
+          <t>tx2026ffqmcg</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-117.2475</v>
+        <v>-101.503</v>
       </c>
       <c r="C155" t="n">
-        <v>34.0556666666667</v>
+        <v>31.879</v>
       </c>
       <c r="D155" t="n">
-        <v>15.21</v>
+        <v>8.6914</v>
       </c>
       <c r="E155" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>M 1.1 - 2 km ENE of Loma Linda, CA</t>
+          <t>M 1.5 - 2 km NW of Garden City, Texas</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2 km ENE of Loma Linda, CA</t>
+          <t>2 km NW of Garden City, Texas</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6638,38 +6638,38 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>46096.32684571759</v>
+        <v>46096.889565</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46096.32920631945</v>
+        <v>46097.51249144676</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>aka2026fephrq</t>
+          <t>nn00912716</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-150.634</v>
+        <v>-116.5976</v>
       </c>
       <c r="C156" t="n">
-        <v>60.036</v>
+        <v>38.2879</v>
       </c>
       <c r="D156" t="n">
-        <v>63.6</v>
+        <v>4.9318</v>
       </c>
       <c r="E156" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>M 2.1 - 26 km NE of Fox River, Alaska</t>
+          <t>M 2.0 - 60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>26 km NE of Fox River, Alaska</t>
+          <t>60 km ENE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6678,38 +6678,38 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>46096.32028525463</v>
+        <v>46096.88044799768</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46096.32365</v>
+        <v>46096.88234515046</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>nn00912702</t>
+          <t>aka2026ffpwxx</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-116.579</v>
+        <v>-150.536</v>
       </c>
       <c r="C157" t="n">
-        <v>38.4398</v>
+        <v>60.816</v>
       </c>
       <c r="D157" t="n">
-        <v>3.5596</v>
+        <v>14.2</v>
       </c>
       <c r="E157" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>M 2.1 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 1.8 - 14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>14 km SE of Point Possession, Alaska</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6718,38 +6718,38 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>46096.30809262732</v>
+        <v>46096.87733195602</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46096.31003199074</v>
+        <v>46096.87884059027</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>nc75327637</t>
+          <t>aka2026ffpbrz</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-121.911003112793</v>
+        <v>-151.569</v>
       </c>
       <c r="C158" t="n">
-        <v>38.0525016784668</v>
+        <v>61.397</v>
       </c>
       <c r="D158" t="n">
-        <v>17.0200004577637</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E158" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>M 1.5 - 4 km NW of Pittsburg, CA</t>
+          <t>M 1.4 - 38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4 km NW of Pittsburg, CA</t>
+          <t>38 km NW of Beluga, Alaska</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6758,38 +6758,38 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>46096.29875555556</v>
+        <v>46096.86023665509</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46096.34190163195</v>
+        <v>46096.86153666666</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>us6000sgf9</t>
+          <t>aka2026ffoxwo</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>72.05249999999999</v>
+        <v>-153.073</v>
       </c>
       <c r="C159" t="n">
-        <v>37.629</v>
+        <v>60.494</v>
       </c>
       <c r="D159" t="n">
-        <v>196.241</v>
+        <v>146.3</v>
       </c>
       <c r="E159" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>M 4.1 - 46 km ENE of Khorugh, Tajikistan</t>
+          <t>M 2.1 - 75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>46 km ENE of Khorugh, Tajikistan</t>
+          <t>75 km ENE of Port Alsworth, Alaska</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6798,38 +6798,38 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>46096.29624704861</v>
+        <v>46096.85716821759</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46096.31303287037</v>
+        <v>46096.85982177083</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>aka2026fenxtb</t>
+          <t>us6000sght</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-154.253</v>
+        <v>132.1964</v>
       </c>
       <c r="C160" t="n">
-        <v>58.558</v>
+        <v>33.6084</v>
       </c>
       <c r="D160" t="n">
-        <v>5</v>
+        <v>66.404</v>
       </c>
       <c r="E160" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>M 1.3 - 96 km NW of Aleneva, Alaska</t>
+          <t>M 4.3 - 27 km NW of Yawatahama, Japan</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>96 km NW of Aleneva, Alaska</t>
+          <t>27 km NW of Yawatahama, Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6838,38 +6838,38 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>46096.29131623843</v>
+        <v>46096.85089461806</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46096.29275974537</v>
+        <v>46097.61717638889</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>nc75327632</t>
+          <t>tx2026ffolko</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-121.910331726074</v>
+        <v>-104.401</v>
       </c>
       <c r="C161" t="n">
-        <v>38.0643348693848</v>
+        <v>31.692</v>
       </c>
       <c r="D161" t="n">
-        <v>18.6900005340576</v>
+        <v>4.8181</v>
       </c>
       <c r="E161" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>M 2.3 - 5 km NNW of Pittsburg, CA</t>
+          <t>M 3.5 - 53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>5 km NNW of Pittsburg, CA</t>
+          <t>53 km S of Whites City, New Mexico</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6878,38 +6878,38 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>46096.28527893518</v>
+        <v>46096.84736503472</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46096.32459672454</v>
+        <v>46096.93883732639</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tx2026fenmna</t>
+          <t>nc75327852</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-104.203</v>
+        <v>-122.464164733887</v>
       </c>
       <c r="C162" t="n">
-        <v>31.669</v>
+        <v>37.5973320007324</v>
       </c>
       <c r="D162" t="n">
-        <v>7.2278</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="E162" t="n">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>M 1.9 - 55 km NW of Toyah, Texas</t>
+          <t>M 1.0 - 3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>3 km SE of Pacifica, CA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6918,38 +6918,38 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>46096.28226224537</v>
+        <v>46096.84368958334</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46096.83936486111</v>
+        <v>46096.84483373843</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tx2026fenktd</t>
+          <t>aka2026ffogkg</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-104.202</v>
+        <v>-150.241</v>
       </c>
       <c r="C163" t="n">
-        <v>31.669</v>
+        <v>61.578</v>
       </c>
       <c r="D163" t="n">
-        <v>7.5739</v>
+        <v>30.7</v>
       </c>
       <c r="E163" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>M 2.5 - 55 km NW of Toyah, Texas</t>
+          <t>M 1.7 - 14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>55 km NW of Toyah, Texas</t>
+          <t>14 km ENE of Susitna, Alaska</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6958,38 +6958,38 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>46096.28124563657</v>
+        <v>46096.84307547453</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46096.70278489583</v>
+        <v>46096.84451351852</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ci41204455</t>
+          <t>nc75327847</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-116.806333333333</v>
+        <v>-122.757667541504</v>
       </c>
       <c r="C164" t="n">
-        <v>33.2463333333333</v>
+        <v>38.7918319702148</v>
       </c>
       <c r="D164" t="n">
-        <v>10.1</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="E164" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>M 1.0 - 4 km W of Lake Henshaw, CA</t>
+          <t>M 1.0 - 2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>4 km W of Lake Henshaw, CA</t>
+          <t>2 km N of The Geysers, CA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6998,38 +6998,38 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>46096.27805949074</v>
+        <v>46096.84258912037</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46096.28047209491</v>
+        <v>46096.84373324074</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>nn00912698</t>
+          <t>ci41204687</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-116.6054</v>
+        <v>-117.249</v>
       </c>
       <c r="C165" t="n">
-        <v>38.2724</v>
+        <v>33.9988333333333</v>
       </c>
       <c r="D165" t="n">
-        <v>5.7486</v>
+        <v>10.86</v>
       </c>
       <c r="E165" t="n">
-        <v>2.11</v>
+        <v>1.03</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>M 2.1 - 59 km ENE of Tonopah, Nevada</t>
+          <t>M 1.0 - 6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>59 km ENE of Tonopah, Nevada</t>
+          <t>6 km SSE of Loma Linda, CA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7038,38 +7038,38 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>46096.26913202546</v>
+        <v>46096.83063032408</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46096.27123583333</v>
+        <v>46096.83300278935</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>nn00912696</t>
+          <t>nn00912714</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-116.3473</v>
+        <v>-116.7227</v>
       </c>
       <c r="C166" t="n">
-        <v>37.5427</v>
+        <v>38.3427</v>
       </c>
       <c r="D166" t="n">
-        <v>15.7841</v>
+        <v>0.1382</v>
       </c>
       <c r="E166" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>M 1.5 - 54 km WSW of Rachel, Nevada</t>
+          <t>M 1.9 - 53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>54 km WSW of Rachel, Nevada</t>
+          <t>53 km NE of Tonopah, Nevada</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7078,38 +7078,38 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>46096.26722096065</v>
+        <v>46096.82208777778</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46096.26890163194</v>
+        <v>46096.82386192129</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>pr71509903</t>
+          <t>aka2026ffmxvv</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-66.7433333333333</v>
+        <v>-151.974</v>
       </c>
       <c r="C167" t="n">
-        <v>18.043</v>
+        <v>60.349</v>
       </c>
       <c r="D167" t="n">
-        <v>16.94</v>
+        <v>77.2</v>
       </c>
       <c r="E167" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>M 2.1 - 2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>M 2.0 - 34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2 km SSE of Santo Domingo, Puerto Rico</t>
+          <t>34 km WNW of Clam Gulch, Alaska</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7118,38 +7118,38 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>46096.26509143518</v>
+        <v>46096.81522726852</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46096.27459479167</v>
+        <v>46096.81638251158</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>nn00912694</t>
+          <t>nc75327827</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-116.5678</v>
+        <v>-121.9375</v>
       </c>
       <c r="C168" t="n">
-        <v>38.4757</v>
+        <v>37.7731666666667</v>
       </c>
       <c r="D168" t="n">
-        <v>5.2112</v>
+        <v>7</v>
       </c>
       <c r="E168" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>M 2.0 - 73 km NE of Tonopah, Nevada</t>
+          <t>M 1.6 - 4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>73 km NE of Tonopah, Nevada</t>
+          <t>4 km ESE of San Ramon, CA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7158,38 +7158,38 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>46096.26149202546</v>
+        <v>46096.81305393518</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46096.26338644676</v>
+        <v>46097.01551917824</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>aka2026femdbx</t>
+          <t>nc75327822</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-154.971</v>
+        <v>-122.787170410156</v>
       </c>
       <c r="C169" t="n">
-        <v>57.961</v>
+        <v>38.7934989929199</v>
       </c>
       <c r="D169" t="n">
-        <v>86.59999999999999</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="E169" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>M 2.8 - 53 km NW of Karluk, Alaska</t>
+          <t>M 1.4 - 3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>53 km NW of Karluk, Alaska</t>
+          <t>3 km NW of The Geysers, CA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7198,38 +7198,38 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>46096.25371178241</v>
+        <v>46096.81298229167</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46096.2741787037</v>
+        <v>46096.86627753473</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>nn00912691</t>
+          <t>us6000sghq</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-116.5734</v>
+        <v>49.7256</v>
       </c>
       <c r="C170" t="n">
-        <v>38.4423</v>
+        <v>32.4853</v>
       </c>
       <c r="D170" t="n">
-        <v>1.9073</v>
+        <v>10</v>
       </c>
       <c r="E170" t="n">
-        <v>1.63</v>
+        <v>4.4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>M 1.6 - 70 km NE of Tonopah, Nevada</t>
+          <t>M 4.4 - 62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>70 km NE of Tonopah, Nevada</t>
+          <t>62 km SW of Fereydūnshahr, Iran</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7238,38 +7238,38 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>46096.25128945602</v>
+        <v>46096.8103829051</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46096.25308243056</v>
+        <v>46097.52903651621</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ci41204447</t>
+          <t>aka2026ffmjyx</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-116.168333333333</v>
+        <v>-149.647</v>
       </c>
       <c r="C171" t="n">
-        <v>33.8886666666667</v>
+        <v>63.036</v>
       </c>
       <c r="D171" t="n">
-        <v>5.52</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E171" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>M 1.3 - 19 km NNE of Indio, CA</t>
+          <t>M 1.4 - 52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>19 km NNE of Indio, CA</t>
+          <t>52 km SW of Cantwell, Alaska</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7278,38 +7278,38 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>46096.24517546297</v>
+        <v>46096.80405828704</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46096.25266435185</v>
+        <v>46096.80508491898</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>nc75327597</t>
+          <t>us6000sghd</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-121.635665893555</v>
+        <v>142.6105</v>
       </c>
       <c r="C172" t="n">
-        <v>36.9845008850098</v>
+        <v>41.4045</v>
       </c>
       <c r="D172" t="n">
-        <v>8.989999771118161</v>
+        <v>42.986</v>
       </c>
       <c r="E172" t="n">
-        <v>1.71</v>
+        <v>4.9</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>M 1.7 - 6 km WSW of Gilroy, CA</t>
+          <t>M 4.9 - 84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>6 km WSW of Gilroy, CA</t>
+          <t>84 km SSW of Honchō, Japan</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7318,10 +7318,410 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>46096.24306736111</v>
+        <v>46096.78951814815</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46096.29676952546</v>
+        <v>46096.84466623842</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>aka2026fflqih</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>-150.765</v>
+      </c>
+      <c r="C173" t="n">
+        <v>63.04</v>
+      </c>
+      <c r="D173" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>M 2.2 - 60 km N of Petersville, Alaska</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>60 km N of Petersville, Alaska</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>46096.78820800926</v>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>46096.79154229166</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>us6000sghb</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>131.6063</v>
+      </c>
+      <c r="C174" t="n">
+        <v>31.4194</v>
+      </c>
+      <c r="D174" t="n">
+        <v>32.903</v>
+      </c>
+      <c r="E174" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>M 4.7 - 30 km SE of Nichinan, Japan</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>30 km SE of Nichinan, Japan</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>46096.77722483796</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>46096.91079450231</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>us6000sgh9</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>-77.5782</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-1.3215</v>
+      </c>
+      <c r="D175" t="n">
+        <v>218.126</v>
+      </c>
+      <c r="E175" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>M 4.4 - 44 km SE of Tena, Ecuador</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>44 km SE of Tena, Ecuador</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>46096.77198028936</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>46096.78392407407</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>nc75327792</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>-122.471336364746</v>
+      </c>
+      <c r="C176" t="n">
+        <v>37.5974998474121</v>
+      </c>
+      <c r="D176" t="n">
+        <v>9.72999954223633</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>M 1.1 - 2 km SE of Pacifica, CA</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2 km SE of Pacifica, CA</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>46096.77132291667</v>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>46096.81413002315</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>aka2026ffklqv</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>-155.854</v>
+      </c>
+      <c r="C177" t="n">
+        <v>57.153</v>
+      </c>
+      <c r="D177" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>M 2.1 - 96 km WSW of Karluk, Alaska</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>96 km WSW of Karluk, Alaska</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>46096.76349226852</v>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>46096.76507798611</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>nc75327787</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>-123.346832275391</v>
+      </c>
+      <c r="C178" t="n">
+        <v>39.476001739502</v>
+      </c>
+      <c r="D178" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>M 1.7 - 5 km NE of Brooktrails, CA</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>5 km NE of Brooktrails, CA</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>46096.7527207176</v>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>46096.79673230324</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>aka2026ffjrwj</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>-149.163</v>
+      </c>
+      <c r="C179" t="n">
+        <v>62.869</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>M 1.6 - 59 km S of Cantwell, Alaska</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>59 km S of Cantwell, Alaska</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>46096.74754356482</v>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>46096.7486603125</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>aka2026ffjpxp</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>-152.555</v>
+      </c>
+      <c r="C180" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D180" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>M 1.8 - 41 km WSW of Anchor Point, Alaska</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>41 km WSW of Anchor Point, Alaska</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>46096.74597070602</v>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>46096.74724846065</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>us6000sgh3</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>128.5163</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-7.3925</v>
+      </c>
+      <c r="D181" t="n">
+        <v>137.104</v>
+      </c>
+      <c r="E181" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>M 4.2 - 208 km NE of Lospalos, Timor Leste</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>208 km NE of Lospalos, Timor Leste</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>46096.7350890625</v>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>46096.81851898148</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ci41204623</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>-116.638166666667</v>
+      </c>
+      <c r="C182" t="n">
+        <v>32.8055</v>
+      </c>
+      <c r="D182" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>M 1.1 - 10 km W of Pine Valley, CA</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>10 km W of Pine Valley, CA</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>46096.72295416667</v>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>46097.53581584491</v>
       </c>
     </row>
   </sheetData>
